--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -4,12 +4,12 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-311_FAI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAR_RESULTS" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATL_PROC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVALIDATION" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="7" state="veryHidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_STATUS_CORE">'_LISTS'!$A$2:$A$7</definedName>
@@ -891,7 +891,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="380">
+  <borders count="386">
     <border>
       <left/>
       <right/>
@@ -5004,11 +5004,79 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="776">
+  <cellXfs count="819">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6945,6 +7013,117 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="342" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="384" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="382" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="383" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="77" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="77" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="77" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -7063,6 +7242,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7093,6 +7275,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7123,6 +7308,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7153,6 +7341,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7528,476 +7719,299 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="662" t="n"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="53" t="n"/>
+      <c r="A1" s="776" t="n"/>
+      <c r="B1" s="268" t="n"/>
+      <c r="C1" s="268" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="268" t="n"/>
+      <c r="I1" s="268" t="n"/>
+      <c r="J1" s="268" t="n"/>
+      <c r="K1" s="268" t="n"/>
+      <c r="L1" s="268" t="n"/>
+      <c r="M1" s="268" t="n"/>
+      <c r="N1" s="268" t="n"/>
+      <c r="O1" s="268" t="n"/>
+      <c r="P1" s="325" t="n"/>
       <c r="Q1" s="663" t="inlineStr">
         <is>
           <t>FAI REPORT</t>
         </is>
       </c>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="2" t="n"/>
-      <c r="AI1" s="2" t="n"/>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="2" t="n"/>
-      <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
-      <c r="AQ1" s="2" t="n"/>
-      <c r="AR1" s="2" t="n"/>
-      <c r="AS1" s="2" t="n"/>
-      <c r="AT1" s="2" t="n"/>
-      <c r="AU1" s="2" t="n"/>
-      <c r="AV1" s="2" t="n"/>
-      <c r="AW1" s="2" t="n"/>
-      <c r="AX1" s="2" t="n"/>
-      <c r="AY1" s="2" t="n"/>
-      <c r="AZ1" s="2" t="n"/>
-      <c r="BA1" s="2" t="n"/>
-      <c r="BB1" s="2" t="n"/>
-      <c r="BC1" s="2" t="n"/>
-      <c r="BD1" s="2" t="n"/>
-      <c r="BE1" s="2" t="n"/>
-      <c r="BF1" s="2" t="n"/>
-      <c r="BG1" s="2" t="n"/>
-      <c r="BH1" s="2" t="n"/>
-      <c r="BI1" s="2" t="n"/>
-      <c r="BJ1" s="2" t="n"/>
-      <c r="BK1" s="664" t="inlineStr">
+      <c r="R1" s="268" t="n"/>
+      <c r="S1" s="268" t="n"/>
+      <c r="T1" s="268" t="n"/>
+      <c r="U1" s="268" t="n"/>
+      <c r="V1" s="268" t="n"/>
+      <c r="W1" s="268" t="n"/>
+      <c r="X1" s="268" t="n"/>
+      <c r="Y1" s="268" t="n"/>
+      <c r="Z1" s="268" t="n"/>
+      <c r="AA1" s="268" t="n"/>
+      <c r="AB1" s="268" t="n"/>
+      <c r="AC1" s="268" t="n"/>
+      <c r="AD1" s="268" t="n"/>
+      <c r="AE1" s="268" t="n"/>
+      <c r="AF1" s="268" t="n"/>
+      <c r="AG1" s="268" t="n"/>
+      <c r="AH1" s="268" t="n"/>
+      <c r="AI1" s="268" t="n"/>
+      <c r="AJ1" s="268" t="n"/>
+      <c r="AK1" s="268" t="n"/>
+      <c r="AL1" s="268" t="n"/>
+      <c r="AM1" s="268" t="n"/>
+      <c r="AN1" s="268" t="n"/>
+      <c r="AO1" s="268" t="n"/>
+      <c r="AP1" s="268" t="n"/>
+      <c r="AQ1" s="268" t="n"/>
+      <c r="AR1" s="268" t="n"/>
+      <c r="AS1" s="268" t="n"/>
+      <c r="AT1" s="268" t="n"/>
+      <c r="AU1" s="268" t="n"/>
+      <c r="AV1" s="268" t="n"/>
+      <c r="AW1" s="268" t="n"/>
+      <c r="AX1" s="268" t="n"/>
+      <c r="AY1" s="268" t="n"/>
+      <c r="AZ1" s="268" t="n"/>
+      <c r="BA1" s="268" t="n"/>
+      <c r="BB1" s="268" t="n"/>
+      <c r="BC1" s="268" t="n"/>
+      <c r="BD1" s="268" t="n"/>
+      <c r="BE1" s="268" t="n"/>
+      <c r="BF1" s="268" t="n"/>
+      <c r="BG1" s="268" t="n"/>
+      <c r="BH1" s="268" t="n"/>
+      <c r="BI1" s="268" t="n"/>
+      <c r="BJ1" s="268" t="n"/>
+      <c r="BK1" s="777" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="BL1" s="2" t="n"/>
-      <c r="BM1" s="2" t="n"/>
-      <c r="BN1" s="2" t="n"/>
-      <c r="BO1" s="2" t="n"/>
-      <c r="BP1" s="2" t="n"/>
-      <c r="BQ1" s="2" t="n"/>
-      <c r="BR1" s="665" t="n"/>
-      <c r="BS1" s="666" t="inlineStr">
+      <c r="BL1" s="268" t="n"/>
+      <c r="BM1" s="268" t="n"/>
+      <c r="BN1" s="268" t="n"/>
+      <c r="BO1" s="268" t="n"/>
+      <c r="BP1" s="268" t="n"/>
+      <c r="BQ1" s="268" t="n"/>
+      <c r="BR1" s="778" t="n"/>
+      <c r="BS1" s="719" t="inlineStr">
         <is>
           <t>FRM-311</t>
         </is>
       </c>
-      <c r="BT1" s="2" t="n"/>
-      <c r="BU1" s="2" t="n"/>
-      <c r="BV1" s="2" t="n"/>
-      <c r="BW1" s="2" t="n"/>
-      <c r="BX1" s="2" t="n"/>
-      <c r="BY1" s="2" t="n"/>
-      <c r="BZ1" s="2" t="n"/>
-      <c r="CA1" s="2" t="n"/>
-      <c r="CB1" s="2" t="n"/>
-      <c r="CC1" s="2" t="n"/>
-      <c r="CD1" s="53" t="n"/>
+      <c r="BT1" s="268" t="n"/>
+      <c r="BU1" s="268" t="n"/>
+      <c r="BV1" s="268" t="n"/>
+      <c r="BW1" s="268" t="n"/>
+      <c r="BX1" s="268" t="n"/>
+      <c r="BY1" s="268" t="n"/>
+      <c r="BZ1" s="268" t="n"/>
+      <c r="CA1" s="268" t="n"/>
+      <c r="CB1" s="268" t="n"/>
+      <c r="CC1" s="268" t="n"/>
+      <c r="CD1" s="325" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="54" t="n"/>
-      <c r="Q2" s="9" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="10" t="n"/>
-      <c r="AE2" s="10" t="n"/>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="10" t="n"/>
-      <c r="AI2" s="10" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="10" t="n"/>
-      <c r="AO2" s="10" t="n"/>
-      <c r="AP2" s="10" t="n"/>
-      <c r="AQ2" s="10" t="n"/>
-      <c r="AR2" s="10" t="n"/>
-      <c r="AS2" s="10" t="n"/>
-      <c r="AT2" s="10" t="n"/>
-      <c r="AU2" s="10" t="n"/>
-      <c r="AV2" s="10" t="n"/>
-      <c r="AW2" s="10" t="n"/>
-      <c r="AX2" s="10" t="n"/>
-      <c r="AY2" s="10" t="n"/>
-      <c r="AZ2" s="10" t="n"/>
-      <c r="BA2" s="10" t="n"/>
-      <c r="BB2" s="10" t="n"/>
-      <c r="BC2" s="10" t="n"/>
-      <c r="BD2" s="10" t="n"/>
-      <c r="BE2" s="10" t="n"/>
-      <c r="BF2" s="10" t="n"/>
-      <c r="BG2" s="10" t="n"/>
-      <c r="BH2" s="10" t="n"/>
-      <c r="BI2" s="10" t="n"/>
-      <c r="BJ2" s="10" t="n"/>
-      <c r="BK2" s="667" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="P2" s="326" t="n"/>
+      <c r="Q2" s="275" t="n"/>
+      <c r="BK2" s="779" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="BL2" s="668" t="n"/>
-      <c r="BM2" s="668" t="n"/>
-      <c r="BN2" s="668" t="n"/>
-      <c r="BO2" s="668" t="n"/>
-      <c r="BP2" s="668" t="n"/>
-      <c r="BQ2" s="668" t="n"/>
-      <c r="BR2" s="669" t="n"/>
-      <c r="BS2" s="670" t="inlineStr">
+      <c r="BL2" s="780" t="n"/>
+      <c r="BM2" s="780" t="n"/>
+      <c r="BN2" s="780" t="n"/>
+      <c r="BO2" s="780" t="n"/>
+      <c r="BP2" s="780" t="n"/>
+      <c r="BQ2" s="780" t="n"/>
+      <c r="BR2" s="781" t="n"/>
+      <c r="BS2" s="723" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="BT2" s="668" t="n"/>
-      <c r="BU2" s="668" t="n"/>
-      <c r="BV2" s="668" t="n"/>
-      <c r="BW2" s="668" t="n"/>
-      <c r="BX2" s="668" t="n"/>
-      <c r="BY2" s="668" t="n"/>
-      <c r="BZ2" s="668" t="n"/>
-      <c r="CA2" s="668" t="n"/>
-      <c r="CB2" s="668" t="n"/>
-      <c r="CC2" s="668" t="n"/>
-      <c r="CD2" s="671" t="n"/>
+      <c r="BT2" s="780" t="n"/>
+      <c r="BU2" s="780" t="n"/>
+      <c r="BV2" s="780" t="n"/>
+      <c r="BW2" s="780" t="n"/>
+      <c r="BX2" s="780" t="n"/>
+      <c r="BY2" s="780" t="n"/>
+      <c r="BZ2" s="780" t="n"/>
+      <c r="CA2" s="780" t="n"/>
+      <c r="CB2" s="780" t="n"/>
+      <c r="CC2" s="780" t="n"/>
+      <c r="CD2" s="782" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="54" t="n"/>
-      <c r="Q3" s="9" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="10" t="n"/>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="10" t="n"/>
-      <c r="AI3" s="10" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="10" t="n"/>
-      <c r="AO3" s="10" t="n"/>
-      <c r="AP3" s="10" t="n"/>
-      <c r="AQ3" s="10" t="n"/>
-      <c r="AR3" s="10" t="n"/>
-      <c r="AS3" s="10" t="n"/>
-      <c r="AT3" s="10" t="n"/>
-      <c r="AU3" s="10" t="n"/>
-      <c r="AV3" s="10" t="n"/>
-      <c r="AW3" s="10" t="n"/>
-      <c r="AX3" s="10" t="n"/>
-      <c r="AY3" s="10" t="n"/>
-      <c r="AZ3" s="10" t="n"/>
-      <c r="BA3" s="10" t="n"/>
-      <c r="BB3" s="10" t="n"/>
-      <c r="BC3" s="10" t="n"/>
-      <c r="BD3" s="10" t="n"/>
-      <c r="BE3" s="10" t="n"/>
-      <c r="BF3" s="10" t="n"/>
-      <c r="BG3" s="10" t="n"/>
-      <c r="BH3" s="10" t="n"/>
-      <c r="BI3" s="10" t="n"/>
-      <c r="BJ3" s="10" t="n"/>
-      <c r="BK3" s="667" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="P3" s="326" t="n"/>
+      <c r="Q3" s="275" t="n"/>
+      <c r="BK3" s="779" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="BL3" s="668" t="n"/>
-      <c r="BM3" s="668" t="n"/>
-      <c r="BN3" s="668" t="n"/>
-      <c r="BO3" s="668" t="n"/>
-      <c r="BP3" s="668" t="n"/>
-      <c r="BQ3" s="668" t="n"/>
-      <c r="BR3" s="669" t="n"/>
-      <c r="BS3" s="670" t="inlineStr">
+      <c r="BL3" s="780" t="n"/>
+      <c r="BM3" s="780" t="n"/>
+      <c r="BN3" s="780" t="n"/>
+      <c r="BO3" s="780" t="n"/>
+      <c r="BP3" s="780" t="n"/>
+      <c r="BQ3" s="780" t="n"/>
+      <c r="BR3" s="781" t="n"/>
+      <c r="BS3" s="723" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="BT3" s="668" t="n"/>
-      <c r="BU3" s="668" t="n"/>
-      <c r="BV3" s="668" t="n"/>
-      <c r="BW3" s="668" t="n"/>
-      <c r="BX3" s="668" t="n"/>
-      <c r="BY3" s="668" t="n"/>
-      <c r="BZ3" s="668" t="n"/>
-      <c r="CA3" s="668" t="n"/>
-      <c r="CB3" s="668" t="n"/>
-      <c r="CC3" s="668" t="n"/>
-      <c r="CD3" s="671" t="n"/>
+      <c r="BT3" s="780" t="n"/>
+      <c r="BU3" s="780" t="n"/>
+      <c r="BV3" s="780" t="n"/>
+      <c r="BW3" s="780" t="n"/>
+      <c r="BX3" s="780" t="n"/>
+      <c r="BY3" s="780" t="n"/>
+      <c r="BZ3" s="780" t="n"/>
+      <c r="CA3" s="780" t="n"/>
+      <c r="CB3" s="780" t="n"/>
+      <c r="CC3" s="780" t="n"/>
+      <c r="CD3" s="782" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="P4" s="326" t="n"/>
       <c r="Q4" s="672" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="10" t="n"/>
-      <c r="AE4" s="10" t="n"/>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="10" t="n"/>
-      <c r="AI4" s="10" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="10" t="n"/>
-      <c r="AO4" s="10" t="n"/>
-      <c r="AP4" s="10" t="n"/>
-      <c r="AQ4" s="10" t="n"/>
-      <c r="AR4" s="10" t="n"/>
-      <c r="AS4" s="10" t="n"/>
-      <c r="AT4" s="10" t="n"/>
-      <c r="AU4" s="10" t="n"/>
-      <c r="AV4" s="10" t="n"/>
-      <c r="AW4" s="10" t="n"/>
-      <c r="AX4" s="10" t="n"/>
-      <c r="AY4" s="10" t="n"/>
-      <c r="AZ4" s="10" t="n"/>
-      <c r="BA4" s="10" t="n"/>
-      <c r="BB4" s="10" t="n"/>
-      <c r="BC4" s="10" t="n"/>
-      <c r="BD4" s="10" t="n"/>
-      <c r="BE4" s="10" t="n"/>
-      <c r="BF4" s="10" t="n"/>
-      <c r="BG4" s="10" t="n"/>
-      <c r="BH4" s="10" t="n"/>
-      <c r="BI4" s="10" t="n"/>
-      <c r="BJ4" s="10" t="n"/>
-      <c r="BK4" s="667" t="inlineStr">
+      <c r="BK4" s="779" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="BL4" s="668" t="n"/>
-      <c r="BM4" s="668" t="n"/>
-      <c r="BN4" s="668" t="n"/>
-      <c r="BO4" s="668" t="n"/>
-      <c r="BP4" s="668" t="n"/>
-      <c r="BQ4" s="668" t="n"/>
-      <c r="BR4" s="669" t="n"/>
-      <c r="BS4" s="670" t="inlineStr">
+      <c r="BL4" s="780" t="n"/>
+      <c r="BM4" s="780" t="n"/>
+      <c r="BN4" s="780" t="n"/>
+      <c r="BO4" s="780" t="n"/>
+      <c r="BP4" s="780" t="n"/>
+      <c r="BQ4" s="780" t="n"/>
+      <c r="BR4" s="781" t="n"/>
+      <c r="BS4" s="723" t="inlineStr">
         <is>
           <t>QA / Engineering</t>
         </is>
       </c>
-      <c r="BT4" s="668" t="n"/>
-      <c r="BU4" s="668" t="n"/>
-      <c r="BV4" s="668" t="n"/>
-      <c r="BW4" s="668" t="n"/>
-      <c r="BX4" s="668" t="n"/>
-      <c r="BY4" s="668" t="n"/>
-      <c r="BZ4" s="668" t="n"/>
-      <c r="CA4" s="668" t="n"/>
-      <c r="CB4" s="668" t="n"/>
-      <c r="CC4" s="668" t="n"/>
-      <c r="CD4" s="671" t="n"/>
+      <c r="BT4" s="780" t="n"/>
+      <c r="BU4" s="780" t="n"/>
+      <c r="BV4" s="780" t="n"/>
+      <c r="BW4" s="780" t="n"/>
+      <c r="BX4" s="780" t="n"/>
+      <c r="BY4" s="780" t="n"/>
+      <c r="BZ4" s="780" t="n"/>
+      <c r="CA4" s="780" t="n"/>
+      <c r="CB4" s="780" t="n"/>
+      <c r="CC4" s="780" t="n"/>
+      <c r="CD4" s="782" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
-      <c r="I5" s="19" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="19" t="n"/>
-      <c r="L5" s="19" t="n"/>
-      <c r="M5" s="19" t="n"/>
-      <c r="N5" s="19" t="n"/>
-      <c r="O5" s="19" t="n"/>
-      <c r="P5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="283" t="n"/>
+      <c r="C5" s="283" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
+      <c r="H5" s="283" t="n"/>
+      <c r="I5" s="283" t="n"/>
+      <c r="J5" s="283" t="n"/>
+      <c r="K5" s="283" t="n"/>
+      <c r="L5" s="283" t="n"/>
+      <c r="M5" s="283" t="n"/>
+      <c r="N5" s="283" t="n"/>
+      <c r="O5" s="283" t="n"/>
+      <c r="P5" s="287" t="n"/>
       <c r="Q5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="R5" s="19" t="n"/>
-      <c r="S5" s="19" t="n"/>
-      <c r="T5" s="19" t="n"/>
-      <c r="U5" s="19" t="n"/>
-      <c r="V5" s="19" t="n"/>
-      <c r="W5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
-      <c r="Y5" s="19" t="n"/>
-      <c r="Z5" s="19" t="n"/>
-      <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="19" t="n"/>
-      <c r="AC5" s="19" t="n"/>
-      <c r="AD5" s="19" t="n"/>
-      <c r="AE5" s="19" t="n"/>
-      <c r="AF5" s="19" t="n"/>
-      <c r="AG5" s="19" t="n"/>
-      <c r="AH5" s="19" t="n"/>
-      <c r="AI5" s="19" t="n"/>
-      <c r="AJ5" s="19" t="n"/>
-      <c r="AK5" s="19" t="n"/>
-      <c r="AL5" s="19" t="n"/>
-      <c r="AM5" s="19" t="n"/>
-      <c r="AN5" s="19" t="n"/>
-      <c r="AO5" s="19" t="n"/>
-      <c r="AP5" s="19" t="n"/>
-      <c r="AQ5" s="19" t="n"/>
-      <c r="AR5" s="19" t="n"/>
-      <c r="AS5" s="19" t="n"/>
-      <c r="AT5" s="19" t="n"/>
-      <c r="AU5" s="19" t="n"/>
-      <c r="AV5" s="19" t="n"/>
-      <c r="AW5" s="19" t="n"/>
-      <c r="AX5" s="19" t="n"/>
-      <c r="AY5" s="19" t="n"/>
-      <c r="AZ5" s="19" t="n"/>
-      <c r="BA5" s="19" t="n"/>
-      <c r="BB5" s="19" t="n"/>
-      <c r="BC5" s="19" t="n"/>
-      <c r="BD5" s="19" t="n"/>
-      <c r="BE5" s="19" t="n"/>
-      <c r="BF5" s="19" t="n"/>
-      <c r="BG5" s="19" t="n"/>
-      <c r="BH5" s="19" t="n"/>
-      <c r="BI5" s="19" t="n"/>
-      <c r="BJ5" s="19" t="n"/>
-      <c r="BK5" s="673" t="inlineStr">
+      <c r="R5" s="283" t="n"/>
+      <c r="S5" s="283" t="n"/>
+      <c r="T5" s="283" t="n"/>
+      <c r="U5" s="283" t="n"/>
+      <c r="V5" s="283" t="n"/>
+      <c r="W5" s="283" t="n"/>
+      <c r="X5" s="283" t="n"/>
+      <c r="Y5" s="283" t="n"/>
+      <c r="Z5" s="283" t="n"/>
+      <c r="AA5" s="283" t="n"/>
+      <c r="AB5" s="283" t="n"/>
+      <c r="AC5" s="283" t="n"/>
+      <c r="AD5" s="283" t="n"/>
+      <c r="AE5" s="283" t="n"/>
+      <c r="AF5" s="283" t="n"/>
+      <c r="AG5" s="283" t="n"/>
+      <c r="AH5" s="283" t="n"/>
+      <c r="AI5" s="283" t="n"/>
+      <c r="AJ5" s="283" t="n"/>
+      <c r="AK5" s="283" t="n"/>
+      <c r="AL5" s="283" t="n"/>
+      <c r="AM5" s="283" t="n"/>
+      <c r="AN5" s="283" t="n"/>
+      <c r="AO5" s="283" t="n"/>
+      <c r="AP5" s="283" t="n"/>
+      <c r="AQ5" s="283" t="n"/>
+      <c r="AR5" s="283" t="n"/>
+      <c r="AS5" s="283" t="n"/>
+      <c r="AT5" s="283" t="n"/>
+      <c r="AU5" s="283" t="n"/>
+      <c r="AV5" s="283" t="n"/>
+      <c r="AW5" s="283" t="n"/>
+      <c r="AX5" s="283" t="n"/>
+      <c r="AY5" s="283" t="n"/>
+      <c r="AZ5" s="283" t="n"/>
+      <c r="BA5" s="283" t="n"/>
+      <c r="BB5" s="283" t="n"/>
+      <c r="BC5" s="283" t="n"/>
+      <c r="BD5" s="283" t="n"/>
+      <c r="BE5" s="283" t="n"/>
+      <c r="BF5" s="283" t="n"/>
+      <c r="BG5" s="283" t="n"/>
+      <c r="BH5" s="283" t="n"/>
+      <c r="BI5" s="283" t="n"/>
+      <c r="BJ5" s="283" t="n"/>
+      <c r="BK5" s="783" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="BL5" s="674" t="n"/>
-      <c r="BM5" s="674" t="n"/>
-      <c r="BN5" s="674" t="n"/>
-      <c r="BO5" s="674" t="n"/>
-      <c r="BP5" s="674" t="n"/>
-      <c r="BQ5" s="674" t="n"/>
-      <c r="BR5" s="675" t="n"/>
-      <c r="BS5" s="676" t="inlineStr">
+      <c r="BL5" s="784" t="n"/>
+      <c r="BM5" s="784" t="n"/>
+      <c r="BN5" s="784" t="n"/>
+      <c r="BO5" s="784" t="n"/>
+      <c r="BP5" s="784" t="n"/>
+      <c r="BQ5" s="784" t="n"/>
+      <c r="BR5" s="785" t="n"/>
+      <c r="BS5" s="731" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="BT5" s="674" t="n"/>
-      <c r="BU5" s="674" t="n"/>
-      <c r="BV5" s="674" t="n"/>
-      <c r="BW5" s="674" t="n"/>
-      <c r="BX5" s="674" t="n"/>
-      <c r="BY5" s="674" t="n"/>
-      <c r="BZ5" s="674" t="n"/>
-      <c r="CA5" s="674" t="n"/>
-      <c r="CB5" s="674" t="n"/>
-      <c r="CC5" s="674" t="n"/>
-      <c r="CD5" s="677" t="n"/>
+      <c r="BT5" s="784" t="n"/>
+      <c r="BU5" s="784" t="n"/>
+      <c r="BV5" s="784" t="n"/>
+      <c r="BW5" s="784" t="n"/>
+      <c r="BX5" s="784" t="n"/>
+      <c r="BY5" s="784" t="n"/>
+      <c r="BZ5" s="784" t="n"/>
+      <c r="CA5" s="784" t="n"/>
+      <c r="CB5" s="784" t="n"/>
+      <c r="CC5" s="784" t="n"/>
+      <c r="CD5" s="786" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="678" t="n"/>
@@ -8084,552 +8098,552 @@
       <c r="CD6" s="678" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="679" t="inlineStr">
+      <c r="A7" s="787" t="inlineStr">
         <is>
           <t>1.  FAI HEADER</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n"/>
-      <c r="T7" s="27" t="n"/>
-      <c r="U7" s="27" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="27" t="n"/>
-      <c r="X7" s="27" t="n"/>
-      <c r="Y7" s="27" t="n"/>
-      <c r="Z7" s="27" t="n"/>
-      <c r="AA7" s="27" t="n"/>
-      <c r="AB7" s="27" t="n"/>
-      <c r="AC7" s="27" t="n"/>
-      <c r="AD7" s="27" t="n"/>
-      <c r="AE7" s="27" t="n"/>
-      <c r="AF7" s="27" t="n"/>
-      <c r="AG7" s="27" t="n"/>
-      <c r="AH7" s="27" t="n"/>
-      <c r="AI7" s="27" t="n"/>
-      <c r="AJ7" s="27" t="n"/>
-      <c r="AK7" s="27" t="n"/>
-      <c r="AL7" s="27" t="n"/>
-      <c r="AM7" s="27" t="n"/>
-      <c r="AN7" s="27" t="n"/>
-      <c r="AO7" s="27" t="n"/>
-      <c r="AP7" s="27" t="n"/>
-      <c r="AQ7" s="27" t="n"/>
-      <c r="AR7" s="27" t="n"/>
-      <c r="AS7" s="27" t="n"/>
-      <c r="AT7" s="27" t="n"/>
-      <c r="AU7" s="27" t="n"/>
-      <c r="AV7" s="27" t="n"/>
-      <c r="AW7" s="27" t="n"/>
-      <c r="AX7" s="27" t="n"/>
-      <c r="AY7" s="27" t="n"/>
-      <c r="AZ7" s="27" t="n"/>
-      <c r="BA7" s="27" t="n"/>
-      <c r="BB7" s="27" t="n"/>
-      <c r="BC7" s="27" t="n"/>
-      <c r="BD7" s="27" t="n"/>
-      <c r="BE7" s="27" t="n"/>
-      <c r="BF7" s="27" t="n"/>
-      <c r="BG7" s="27" t="n"/>
-      <c r="BH7" s="27" t="n"/>
-      <c r="BI7" s="27" t="n"/>
-      <c r="BJ7" s="27" t="n"/>
-      <c r="BK7" s="27" t="n"/>
-      <c r="BL7" s="27" t="n"/>
-      <c r="BM7" s="27" t="n"/>
-      <c r="BN7" s="27" t="n"/>
-      <c r="BO7" s="27" t="n"/>
-      <c r="BP7" s="27" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
-      <c r="BR7" s="27" t="n"/>
-      <c r="BS7" s="27" t="n"/>
-      <c r="BT7" s="27" t="n"/>
-      <c r="BU7" s="27" t="n"/>
-      <c r="BV7" s="27" t="n"/>
-      <c r="BW7" s="27" t="n"/>
-      <c r="BX7" s="27" t="n"/>
-      <c r="BY7" s="27" t="n"/>
-      <c r="BZ7" s="27" t="n"/>
-      <c r="CA7" s="27" t="n"/>
-      <c r="CB7" s="27" t="n"/>
-      <c r="CC7" s="27" t="n"/>
-      <c r="CD7" s="28" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="289" t="n"/>
+      <c r="J7" s="289" t="n"/>
+      <c r="K7" s="289" t="n"/>
+      <c r="L7" s="289" t="n"/>
+      <c r="M7" s="289" t="n"/>
+      <c r="N7" s="289" t="n"/>
+      <c r="O7" s="289" t="n"/>
+      <c r="P7" s="289" t="n"/>
+      <c r="Q7" s="289" t="n"/>
+      <c r="R7" s="289" t="n"/>
+      <c r="S7" s="289" t="n"/>
+      <c r="T7" s="289" t="n"/>
+      <c r="U7" s="289" t="n"/>
+      <c r="V7" s="289" t="n"/>
+      <c r="W7" s="289" t="n"/>
+      <c r="X7" s="289" t="n"/>
+      <c r="Y7" s="289" t="n"/>
+      <c r="Z7" s="289" t="n"/>
+      <c r="AA7" s="289" t="n"/>
+      <c r="AB7" s="289" t="n"/>
+      <c r="AC7" s="289" t="n"/>
+      <c r="AD7" s="289" t="n"/>
+      <c r="AE7" s="289" t="n"/>
+      <c r="AF7" s="289" t="n"/>
+      <c r="AG7" s="289" t="n"/>
+      <c r="AH7" s="289" t="n"/>
+      <c r="AI7" s="289" t="n"/>
+      <c r="AJ7" s="289" t="n"/>
+      <c r="AK7" s="289" t="n"/>
+      <c r="AL7" s="289" t="n"/>
+      <c r="AM7" s="289" t="n"/>
+      <c r="AN7" s="289" t="n"/>
+      <c r="AO7" s="289" t="n"/>
+      <c r="AP7" s="289" t="n"/>
+      <c r="AQ7" s="289" t="n"/>
+      <c r="AR7" s="289" t="n"/>
+      <c r="AS7" s="289" t="n"/>
+      <c r="AT7" s="289" t="n"/>
+      <c r="AU7" s="289" t="n"/>
+      <c r="AV7" s="289" t="n"/>
+      <c r="AW7" s="289" t="n"/>
+      <c r="AX7" s="289" t="n"/>
+      <c r="AY7" s="289" t="n"/>
+      <c r="AZ7" s="289" t="n"/>
+      <c r="BA7" s="289" t="n"/>
+      <c r="BB7" s="289" t="n"/>
+      <c r="BC7" s="289" t="n"/>
+      <c r="BD7" s="289" t="n"/>
+      <c r="BE7" s="289" t="n"/>
+      <c r="BF7" s="289" t="n"/>
+      <c r="BG7" s="289" t="n"/>
+      <c r="BH7" s="289" t="n"/>
+      <c r="BI7" s="289" t="n"/>
+      <c r="BJ7" s="289" t="n"/>
+      <c r="BK7" s="289" t="n"/>
+      <c r="BL7" s="289" t="n"/>
+      <c r="BM7" s="289" t="n"/>
+      <c r="BN7" s="289" t="n"/>
+      <c r="BO7" s="289" t="n"/>
+      <c r="BP7" s="289" t="n"/>
+      <c r="BQ7" s="289" t="n"/>
+      <c r="BR7" s="289" t="n"/>
+      <c r="BS7" s="289" t="n"/>
+      <c r="BT7" s="289" t="n"/>
+      <c r="BU7" s="289" t="n"/>
+      <c r="BV7" s="289" t="n"/>
+      <c r="BW7" s="289" t="n"/>
+      <c r="BX7" s="289" t="n"/>
+      <c r="BY7" s="289" t="n"/>
+      <c r="BZ7" s="289" t="n"/>
+      <c r="CA7" s="289" t="n"/>
+      <c r="CB7" s="289" t="n"/>
+      <c r="CC7" s="289" t="n"/>
+      <c r="CD7" s="290" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="680" t="inlineStr">
+      <c r="A8" s="788" t="inlineStr">
         <is>
           <t>Job / WO</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="30" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="5" t="n"/>
-      <c r="AA8" s="5" t="n"/>
-      <c r="AB8" s="5" t="n"/>
-      <c r="AC8" s="5" t="n"/>
-      <c r="AD8" s="5" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="5" t="n"/>
-      <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="5" t="n"/>
-      <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="5" t="n"/>
-      <c r="AN8" s="5" t="n"/>
-      <c r="AO8" s="6" t="n"/>
-      <c r="AP8" s="681" t="inlineStr">
+      <c r="B8" s="271" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="271" t="n"/>
+      <c r="F8" s="271" t="n"/>
+      <c r="G8" s="271" t="n"/>
+      <c r="H8" s="271" t="n"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="271" t="n"/>
+      <c r="K8" s="271" t="n"/>
+      <c r="L8" s="271" t="n"/>
+      <c r="M8" s="271" t="n"/>
+      <c r="N8" s="272" t="n"/>
+      <c r="O8" s="292" t="n"/>
+      <c r="P8" s="271" t="n"/>
+      <c r="Q8" s="271" t="n"/>
+      <c r="R8" s="271" t="n"/>
+      <c r="S8" s="271" t="n"/>
+      <c r="T8" s="271" t="n"/>
+      <c r="U8" s="271" t="n"/>
+      <c r="V8" s="271" t="n"/>
+      <c r="W8" s="271" t="n"/>
+      <c r="X8" s="271" t="n"/>
+      <c r="Y8" s="271" t="n"/>
+      <c r="Z8" s="271" t="n"/>
+      <c r="AA8" s="271" t="n"/>
+      <c r="AB8" s="271" t="n"/>
+      <c r="AC8" s="271" t="n"/>
+      <c r="AD8" s="271" t="n"/>
+      <c r="AE8" s="271" t="n"/>
+      <c r="AF8" s="271" t="n"/>
+      <c r="AG8" s="271" t="n"/>
+      <c r="AH8" s="271" t="n"/>
+      <c r="AI8" s="271" t="n"/>
+      <c r="AJ8" s="271" t="n"/>
+      <c r="AK8" s="271" t="n"/>
+      <c r="AL8" s="271" t="n"/>
+      <c r="AM8" s="271" t="n"/>
+      <c r="AN8" s="271" t="n"/>
+      <c r="AO8" s="272" t="n"/>
+      <c r="AP8" s="789" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="AQ8" s="5" t="n"/>
-      <c r="AR8" s="5" t="n"/>
-      <c r="AS8" s="5" t="n"/>
-      <c r="AT8" s="5" t="n"/>
-      <c r="AU8" s="5" t="n"/>
-      <c r="AV8" s="5" t="n"/>
-      <c r="AW8" s="5" t="n"/>
-      <c r="AX8" s="5" t="n"/>
-      <c r="AY8" s="5" t="n"/>
-      <c r="AZ8" s="5" t="n"/>
-      <c r="BA8" s="5" t="n"/>
-      <c r="BB8" s="5" t="n"/>
-      <c r="BC8" s="6" t="n"/>
-      <c r="BD8" s="30" t="n"/>
-      <c r="BE8" s="5" t="n"/>
-      <c r="BF8" s="5" t="n"/>
-      <c r="BG8" s="5" t="n"/>
-      <c r="BH8" s="5" t="n"/>
-      <c r="BI8" s="5" t="n"/>
-      <c r="BJ8" s="5" t="n"/>
-      <c r="BK8" s="5" t="n"/>
-      <c r="BL8" s="5" t="n"/>
-      <c r="BM8" s="5" t="n"/>
-      <c r="BN8" s="5" t="n"/>
-      <c r="BO8" s="5" t="n"/>
-      <c r="BP8" s="5" t="n"/>
-      <c r="BQ8" s="5" t="n"/>
-      <c r="BR8" s="5" t="n"/>
-      <c r="BS8" s="5" t="n"/>
-      <c r="BT8" s="5" t="n"/>
-      <c r="BU8" s="5" t="n"/>
-      <c r="BV8" s="5" t="n"/>
-      <c r="BW8" s="5" t="n"/>
-      <c r="BX8" s="5" t="n"/>
-      <c r="BY8" s="5" t="n"/>
-      <c r="BZ8" s="5" t="n"/>
-      <c r="CA8" s="5" t="n"/>
-      <c r="CB8" s="5" t="n"/>
-      <c r="CC8" s="5" t="n"/>
-      <c r="CD8" s="8" t="n"/>
+      <c r="AQ8" s="271" t="n"/>
+      <c r="AR8" s="271" t="n"/>
+      <c r="AS8" s="271" t="n"/>
+      <c r="AT8" s="271" t="n"/>
+      <c r="AU8" s="271" t="n"/>
+      <c r="AV8" s="271" t="n"/>
+      <c r="AW8" s="271" t="n"/>
+      <c r="AX8" s="271" t="n"/>
+      <c r="AY8" s="271" t="n"/>
+      <c r="AZ8" s="271" t="n"/>
+      <c r="BA8" s="271" t="n"/>
+      <c r="BB8" s="271" t="n"/>
+      <c r="BC8" s="272" t="n"/>
+      <c r="BD8" s="294" t="n"/>
+      <c r="BE8" s="271" t="n"/>
+      <c r="BF8" s="271" t="n"/>
+      <c r="BG8" s="271" t="n"/>
+      <c r="BH8" s="271" t="n"/>
+      <c r="BI8" s="271" t="n"/>
+      <c r="BJ8" s="271" t="n"/>
+      <c r="BK8" s="271" t="n"/>
+      <c r="BL8" s="271" t="n"/>
+      <c r="BM8" s="271" t="n"/>
+      <c r="BN8" s="271" t="n"/>
+      <c r="BO8" s="271" t="n"/>
+      <c r="BP8" s="271" t="n"/>
+      <c r="BQ8" s="271" t="n"/>
+      <c r="BR8" s="271" t="n"/>
+      <c r="BS8" s="271" t="n"/>
+      <c r="BT8" s="271" t="n"/>
+      <c r="BU8" s="271" t="n"/>
+      <c r="BV8" s="271" t="n"/>
+      <c r="BW8" s="271" t="n"/>
+      <c r="BX8" s="271" t="n"/>
+      <c r="BY8" s="271" t="n"/>
+      <c r="BZ8" s="271" t="n"/>
+      <c r="CA8" s="271" t="n"/>
+      <c r="CB8" s="271" t="n"/>
+      <c r="CC8" s="271" t="n"/>
+      <c r="CD8" s="274" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="682" t="inlineStr">
+      <c r="A9" s="790" t="inlineStr">
         <is>
           <t>Machine / Cell</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
-      <c r="S9" s="12" t="n"/>
-      <c r="T9" s="12" t="n"/>
-      <c r="U9" s="12" t="n"/>
-      <c r="V9" s="12" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="12" t="n"/>
-      <c r="Y9" s="12" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="12" t="n"/>
-      <c r="AB9" s="12" t="n"/>
-      <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="12" t="n"/>
-      <c r="AH9" s="12" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="12" t="n"/>
-      <c r="AK9" s="12" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="12" t="n"/>
-      <c r="AN9" s="12" t="n"/>
-      <c r="AO9" s="13" t="n"/>
-      <c r="AP9" s="683" t="inlineStr">
+      <c r="B9" s="277" t="n"/>
+      <c r="C9" s="277" t="n"/>
+      <c r="D9" s="277" t="n"/>
+      <c r="E9" s="277" t="n"/>
+      <c r="F9" s="277" t="n"/>
+      <c r="G9" s="277" t="n"/>
+      <c r="H9" s="277" t="n"/>
+      <c r="I9" s="277" t="n"/>
+      <c r="J9" s="277" t="n"/>
+      <c r="K9" s="277" t="n"/>
+      <c r="L9" s="277" t="n"/>
+      <c r="M9" s="277" t="n"/>
+      <c r="N9" s="278" t="n"/>
+      <c r="O9" s="296" t="n"/>
+      <c r="P9" s="277" t="n"/>
+      <c r="Q9" s="277" t="n"/>
+      <c r="R9" s="277" t="n"/>
+      <c r="S9" s="277" t="n"/>
+      <c r="T9" s="277" t="n"/>
+      <c r="U9" s="277" t="n"/>
+      <c r="V9" s="277" t="n"/>
+      <c r="W9" s="277" t="n"/>
+      <c r="X9" s="277" t="n"/>
+      <c r="Y9" s="277" t="n"/>
+      <c r="Z9" s="277" t="n"/>
+      <c r="AA9" s="277" t="n"/>
+      <c r="AB9" s="277" t="n"/>
+      <c r="AC9" s="277" t="n"/>
+      <c r="AD9" s="277" t="n"/>
+      <c r="AE9" s="277" t="n"/>
+      <c r="AF9" s="277" t="n"/>
+      <c r="AG9" s="277" t="n"/>
+      <c r="AH9" s="277" t="n"/>
+      <c r="AI9" s="277" t="n"/>
+      <c r="AJ9" s="277" t="n"/>
+      <c r="AK9" s="277" t="n"/>
+      <c r="AL9" s="277" t="n"/>
+      <c r="AM9" s="277" t="n"/>
+      <c r="AN9" s="277" t="n"/>
+      <c r="AO9" s="278" t="n"/>
+      <c r="AP9" s="791" t="inlineStr">
         <is>
           <t>FAI Owner</t>
         </is>
       </c>
-      <c r="AQ9" s="12" t="n"/>
-      <c r="AR9" s="12" t="n"/>
-      <c r="AS9" s="12" t="n"/>
-      <c r="AT9" s="12" t="n"/>
-      <c r="AU9" s="12" t="n"/>
-      <c r="AV9" s="12" t="n"/>
-      <c r="AW9" s="12" t="n"/>
-      <c r="AX9" s="12" t="n"/>
-      <c r="AY9" s="12" t="n"/>
-      <c r="AZ9" s="12" t="n"/>
-      <c r="BA9" s="12" t="n"/>
-      <c r="BB9" s="12" t="n"/>
-      <c r="BC9" s="13" t="n"/>
-      <c r="BD9" s="14" t="n"/>
-      <c r="BE9" s="12" t="n"/>
-      <c r="BF9" s="12" t="n"/>
-      <c r="BG9" s="12" t="n"/>
-      <c r="BH9" s="12" t="n"/>
-      <c r="BI9" s="12" t="n"/>
-      <c r="BJ9" s="12" t="n"/>
-      <c r="BK9" s="12" t="n"/>
-      <c r="BL9" s="12" t="n"/>
-      <c r="BM9" s="12" t="n"/>
-      <c r="BN9" s="12" t="n"/>
-      <c r="BO9" s="12" t="n"/>
-      <c r="BP9" s="12" t="n"/>
-      <c r="BQ9" s="12" t="n"/>
-      <c r="BR9" s="12" t="n"/>
-      <c r="BS9" s="12" t="n"/>
-      <c r="BT9" s="12" t="n"/>
-      <c r="BU9" s="12" t="n"/>
-      <c r="BV9" s="12" t="n"/>
-      <c r="BW9" s="12" t="n"/>
-      <c r="BX9" s="12" t="n"/>
-      <c r="BY9" s="12" t="n"/>
-      <c r="BZ9" s="12" t="n"/>
-      <c r="CA9" s="12" t="n"/>
-      <c r="CB9" s="12" t="n"/>
-      <c r="CC9" s="12" t="n"/>
-      <c r="CD9" s="15" t="n"/>
+      <c r="AQ9" s="277" t="n"/>
+      <c r="AR9" s="277" t="n"/>
+      <c r="AS9" s="277" t="n"/>
+      <c r="AT9" s="277" t="n"/>
+      <c r="AU9" s="277" t="n"/>
+      <c r="AV9" s="277" t="n"/>
+      <c r="AW9" s="277" t="n"/>
+      <c r="AX9" s="277" t="n"/>
+      <c r="AY9" s="277" t="n"/>
+      <c r="AZ9" s="277" t="n"/>
+      <c r="BA9" s="277" t="n"/>
+      <c r="BB9" s="277" t="n"/>
+      <c r="BC9" s="278" t="n"/>
+      <c r="BD9" s="279" t="n"/>
+      <c r="BE9" s="277" t="n"/>
+      <c r="BF9" s="277" t="n"/>
+      <c r="BG9" s="277" t="n"/>
+      <c r="BH9" s="277" t="n"/>
+      <c r="BI9" s="277" t="n"/>
+      <c r="BJ9" s="277" t="n"/>
+      <c r="BK9" s="277" t="n"/>
+      <c r="BL9" s="277" t="n"/>
+      <c r="BM9" s="277" t="n"/>
+      <c r="BN9" s="277" t="n"/>
+      <c r="BO9" s="277" t="n"/>
+      <c r="BP9" s="277" t="n"/>
+      <c r="BQ9" s="277" t="n"/>
+      <c r="BR9" s="277" t="n"/>
+      <c r="BS9" s="277" t="n"/>
+      <c r="BT9" s="277" t="n"/>
+      <c r="BU9" s="277" t="n"/>
+      <c r="BV9" s="277" t="n"/>
+      <c r="BW9" s="277" t="n"/>
+      <c r="BX9" s="277" t="n"/>
+      <c r="BY9" s="277" t="n"/>
+      <c r="BZ9" s="277" t="n"/>
+      <c r="CA9" s="277" t="n"/>
+      <c r="CB9" s="277" t="n"/>
+      <c r="CC9" s="277" t="n"/>
+      <c r="CD9" s="280" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="682" t="inlineStr">
+      <c r="A10" s="790" t="inlineStr">
         <is>
           <t>Gage / Program Ref.</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n"/>
-      <c r="T10" s="12" t="n"/>
-      <c r="U10" s="12" t="n"/>
-      <c r="V10" s="12" t="n"/>
-      <c r="W10" s="12" t="n"/>
-      <c r="X10" s="12" t="n"/>
-      <c r="Y10" s="12" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="12" t="n"/>
-      <c r="AB10" s="12" t="n"/>
-      <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="12" t="n"/>
-      <c r="AE10" s="12" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="12" t="n"/>
-      <c r="AH10" s="12" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="12" t="n"/>
-      <c r="AK10" s="12" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="12" t="n"/>
-      <c r="AN10" s="12" t="n"/>
-      <c r="AO10" s="13" t="n"/>
-      <c r="AP10" s="683" t="inlineStr">
+      <c r="B10" s="277" t="n"/>
+      <c r="C10" s="277" t="n"/>
+      <c r="D10" s="277" t="n"/>
+      <c r="E10" s="277" t="n"/>
+      <c r="F10" s="277" t="n"/>
+      <c r="G10" s="277" t="n"/>
+      <c r="H10" s="277" t="n"/>
+      <c r="I10" s="277" t="n"/>
+      <c r="J10" s="277" t="n"/>
+      <c r="K10" s="277" t="n"/>
+      <c r="L10" s="277" t="n"/>
+      <c r="M10" s="277" t="n"/>
+      <c r="N10" s="278" t="n"/>
+      <c r="O10" s="296" t="n"/>
+      <c r="P10" s="277" t="n"/>
+      <c r="Q10" s="277" t="n"/>
+      <c r="R10" s="277" t="n"/>
+      <c r="S10" s="277" t="n"/>
+      <c r="T10" s="277" t="n"/>
+      <c r="U10" s="277" t="n"/>
+      <c r="V10" s="277" t="n"/>
+      <c r="W10" s="277" t="n"/>
+      <c r="X10" s="277" t="n"/>
+      <c r="Y10" s="277" t="n"/>
+      <c r="Z10" s="277" t="n"/>
+      <c r="AA10" s="277" t="n"/>
+      <c r="AB10" s="277" t="n"/>
+      <c r="AC10" s="277" t="n"/>
+      <c r="AD10" s="277" t="n"/>
+      <c r="AE10" s="277" t="n"/>
+      <c r="AF10" s="277" t="n"/>
+      <c r="AG10" s="277" t="n"/>
+      <c r="AH10" s="277" t="n"/>
+      <c r="AI10" s="277" t="n"/>
+      <c r="AJ10" s="277" t="n"/>
+      <c r="AK10" s="277" t="n"/>
+      <c r="AL10" s="277" t="n"/>
+      <c r="AM10" s="277" t="n"/>
+      <c r="AN10" s="277" t="n"/>
+      <c r="AO10" s="278" t="n"/>
+      <c r="AP10" s="791" t="inlineStr">
         <is>
           <t>Balloon / Method Rev.</t>
         </is>
       </c>
-      <c r="AQ10" s="12" t="n"/>
-      <c r="AR10" s="12" t="n"/>
-      <c r="AS10" s="12" t="n"/>
-      <c r="AT10" s="12" t="n"/>
-      <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="12" t="n"/>
-      <c r="AW10" s="12" t="n"/>
-      <c r="AX10" s="12" t="n"/>
-      <c r="AY10" s="12" t="n"/>
-      <c r="AZ10" s="12" t="n"/>
-      <c r="BA10" s="12" t="n"/>
-      <c r="BB10" s="12" t="n"/>
-      <c r="BC10" s="13" t="n"/>
-      <c r="BD10" s="14" t="n"/>
-      <c r="BE10" s="12" t="n"/>
-      <c r="BF10" s="12" t="n"/>
-      <c r="BG10" s="12" t="n"/>
-      <c r="BH10" s="12" t="n"/>
-      <c r="BI10" s="12" t="n"/>
-      <c r="BJ10" s="12" t="n"/>
-      <c r="BK10" s="12" t="n"/>
-      <c r="BL10" s="12" t="n"/>
-      <c r="BM10" s="12" t="n"/>
-      <c r="BN10" s="12" t="n"/>
-      <c r="BO10" s="12" t="n"/>
-      <c r="BP10" s="12" t="n"/>
-      <c r="BQ10" s="12" t="n"/>
-      <c r="BR10" s="12" t="n"/>
-      <c r="BS10" s="12" t="n"/>
-      <c r="BT10" s="12" t="n"/>
-      <c r="BU10" s="12" t="n"/>
-      <c r="BV10" s="12" t="n"/>
-      <c r="BW10" s="12" t="n"/>
-      <c r="BX10" s="12" t="n"/>
-      <c r="BY10" s="12" t="n"/>
-      <c r="BZ10" s="12" t="n"/>
-      <c r="CA10" s="12" t="n"/>
-      <c r="CB10" s="12" t="n"/>
-      <c r="CC10" s="12" t="n"/>
-      <c r="CD10" s="15" t="n"/>
+      <c r="AQ10" s="277" t="n"/>
+      <c r="AR10" s="277" t="n"/>
+      <c r="AS10" s="277" t="n"/>
+      <c r="AT10" s="277" t="n"/>
+      <c r="AU10" s="277" t="n"/>
+      <c r="AV10" s="277" t="n"/>
+      <c r="AW10" s="277" t="n"/>
+      <c r="AX10" s="277" t="n"/>
+      <c r="AY10" s="277" t="n"/>
+      <c r="AZ10" s="277" t="n"/>
+      <c r="BA10" s="277" t="n"/>
+      <c r="BB10" s="277" t="n"/>
+      <c r="BC10" s="278" t="n"/>
+      <c r="BD10" s="279" t="n"/>
+      <c r="BE10" s="277" t="n"/>
+      <c r="BF10" s="277" t="n"/>
+      <c r="BG10" s="277" t="n"/>
+      <c r="BH10" s="277" t="n"/>
+      <c r="BI10" s="277" t="n"/>
+      <c r="BJ10" s="277" t="n"/>
+      <c r="BK10" s="277" t="n"/>
+      <c r="BL10" s="277" t="n"/>
+      <c r="BM10" s="277" t="n"/>
+      <c r="BN10" s="277" t="n"/>
+      <c r="BO10" s="277" t="n"/>
+      <c r="BP10" s="277" t="n"/>
+      <c r="BQ10" s="277" t="n"/>
+      <c r="BR10" s="277" t="n"/>
+      <c r="BS10" s="277" t="n"/>
+      <c r="BT10" s="277" t="n"/>
+      <c r="BU10" s="277" t="n"/>
+      <c r="BV10" s="277" t="n"/>
+      <c r="BW10" s="277" t="n"/>
+      <c r="BX10" s="277" t="n"/>
+      <c r="BY10" s="277" t="n"/>
+      <c r="BZ10" s="277" t="n"/>
+      <c r="CA10" s="277" t="n"/>
+      <c r="CB10" s="277" t="n"/>
+      <c r="CC10" s="277" t="n"/>
+      <c r="CD10" s="280" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="682" t="inlineStr">
+      <c r="A11" s="790" t="inlineStr">
         <is>
           <t>Evidence Folder</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="12" t="n"/>
-      <c r="S11" s="12" t="n"/>
-      <c r="T11" s="12" t="n"/>
-      <c r="U11" s="12" t="n"/>
-      <c r="V11" s="12" t="n"/>
-      <c r="W11" s="12" t="n"/>
-      <c r="X11" s="12" t="n"/>
-      <c r="Y11" s="12" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="12" t="n"/>
-      <c r="AB11" s="12" t="n"/>
-      <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="12" t="n"/>
-      <c r="AE11" s="12" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="12" t="n"/>
-      <c r="AH11" s="12" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="12" t="n"/>
-      <c r="AK11" s="12" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="12" t="n"/>
-      <c r="AN11" s="12" t="n"/>
-      <c r="AO11" s="13" t="n"/>
-      <c r="AP11" s="683" t="inlineStr">
+      <c r="B11" s="277" t="n"/>
+      <c r="C11" s="277" t="n"/>
+      <c r="D11" s="277" t="n"/>
+      <c r="E11" s="277" t="n"/>
+      <c r="F11" s="277" t="n"/>
+      <c r="G11" s="277" t="n"/>
+      <c r="H11" s="277" t="n"/>
+      <c r="I11" s="277" t="n"/>
+      <c r="J11" s="277" t="n"/>
+      <c r="K11" s="277" t="n"/>
+      <c r="L11" s="277" t="n"/>
+      <c r="M11" s="277" t="n"/>
+      <c r="N11" s="278" t="n"/>
+      <c r="O11" s="296" t="n"/>
+      <c r="P11" s="277" t="n"/>
+      <c r="Q11" s="277" t="n"/>
+      <c r="R11" s="277" t="n"/>
+      <c r="S11" s="277" t="n"/>
+      <c r="T11" s="277" t="n"/>
+      <c r="U11" s="277" t="n"/>
+      <c r="V11" s="277" t="n"/>
+      <c r="W11" s="277" t="n"/>
+      <c r="X11" s="277" t="n"/>
+      <c r="Y11" s="277" t="n"/>
+      <c r="Z11" s="277" t="n"/>
+      <c r="AA11" s="277" t="n"/>
+      <c r="AB11" s="277" t="n"/>
+      <c r="AC11" s="277" t="n"/>
+      <c r="AD11" s="277" t="n"/>
+      <c r="AE11" s="277" t="n"/>
+      <c r="AF11" s="277" t="n"/>
+      <c r="AG11" s="277" t="n"/>
+      <c r="AH11" s="277" t="n"/>
+      <c r="AI11" s="277" t="n"/>
+      <c r="AJ11" s="277" t="n"/>
+      <c r="AK11" s="277" t="n"/>
+      <c r="AL11" s="277" t="n"/>
+      <c r="AM11" s="277" t="n"/>
+      <c r="AN11" s="277" t="n"/>
+      <c r="AO11" s="278" t="n"/>
+      <c r="AP11" s="791" t="inlineStr">
         <is>
           <t>FAI Type / Scope</t>
         </is>
       </c>
-      <c r="AQ11" s="12" t="n"/>
-      <c r="AR11" s="12" t="n"/>
-      <c r="AS11" s="12" t="n"/>
-      <c r="AT11" s="12" t="n"/>
-      <c r="AU11" s="12" t="n"/>
-      <c r="AV11" s="12" t="n"/>
-      <c r="AW11" s="12" t="n"/>
-      <c r="AX11" s="12" t="n"/>
-      <c r="AY11" s="12" t="n"/>
-      <c r="AZ11" s="12" t="n"/>
-      <c r="BA11" s="12" t="n"/>
-      <c r="BB11" s="12" t="n"/>
-      <c r="BC11" s="13" t="n"/>
-      <c r="BD11" s="14" t="n"/>
-      <c r="BE11" s="12" t="n"/>
-      <c r="BF11" s="12" t="n"/>
-      <c r="BG11" s="12" t="n"/>
-      <c r="BH11" s="12" t="n"/>
-      <c r="BI11" s="12" t="n"/>
-      <c r="BJ11" s="12" t="n"/>
-      <c r="BK11" s="12" t="n"/>
-      <c r="BL11" s="12" t="n"/>
-      <c r="BM11" s="12" t="n"/>
-      <c r="BN11" s="12" t="n"/>
-      <c r="BO11" s="12" t="n"/>
-      <c r="BP11" s="12" t="n"/>
-      <c r="BQ11" s="12" t="n"/>
-      <c r="BR11" s="12" t="n"/>
-      <c r="BS11" s="12" t="n"/>
-      <c r="BT11" s="12" t="n"/>
-      <c r="BU11" s="12" t="n"/>
-      <c r="BV11" s="12" t="n"/>
-      <c r="BW11" s="12" t="n"/>
-      <c r="BX11" s="12" t="n"/>
-      <c r="BY11" s="12" t="n"/>
-      <c r="BZ11" s="12" t="n"/>
-      <c r="CA11" s="12" t="n"/>
-      <c r="CB11" s="12" t="n"/>
-      <c r="CC11" s="12" t="n"/>
-      <c r="CD11" s="15" t="n"/>
+      <c r="AQ11" s="277" t="n"/>
+      <c r="AR11" s="277" t="n"/>
+      <c r="AS11" s="277" t="n"/>
+      <c r="AT11" s="277" t="n"/>
+      <c r="AU11" s="277" t="n"/>
+      <c r="AV11" s="277" t="n"/>
+      <c r="AW11" s="277" t="n"/>
+      <c r="AX11" s="277" t="n"/>
+      <c r="AY11" s="277" t="n"/>
+      <c r="AZ11" s="277" t="n"/>
+      <c r="BA11" s="277" t="n"/>
+      <c r="BB11" s="277" t="n"/>
+      <c r="BC11" s="278" t="n"/>
+      <c r="BD11" s="279" t="n"/>
+      <c r="BE11" s="277" t="n"/>
+      <c r="BF11" s="277" t="n"/>
+      <c r="BG11" s="277" t="n"/>
+      <c r="BH11" s="277" t="n"/>
+      <c r="BI11" s="277" t="n"/>
+      <c r="BJ11" s="277" t="n"/>
+      <c r="BK11" s="277" t="n"/>
+      <c r="BL11" s="277" t="n"/>
+      <c r="BM11" s="277" t="n"/>
+      <c r="BN11" s="277" t="n"/>
+      <c r="BO11" s="277" t="n"/>
+      <c r="BP11" s="277" t="n"/>
+      <c r="BQ11" s="277" t="n"/>
+      <c r="BR11" s="277" t="n"/>
+      <c r="BS11" s="277" t="n"/>
+      <c r="BT11" s="277" t="n"/>
+      <c r="BU11" s="277" t="n"/>
+      <c r="BV11" s="277" t="n"/>
+      <c r="BW11" s="277" t="n"/>
+      <c r="BX11" s="277" t="n"/>
+      <c r="BY11" s="277" t="n"/>
+      <c r="BZ11" s="277" t="n"/>
+      <c r="CA11" s="277" t="n"/>
+      <c r="CB11" s="277" t="n"/>
+      <c r="CC11" s="277" t="n"/>
+      <c r="CD11" s="280" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="684" t="inlineStr">
+      <c r="A12" s="792" t="inlineStr">
         <is>
           <t>Sample / First Article ID</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="22" t="n"/>
-      <c r="O12" s="23" t="n"/>
-      <c r="P12" s="19" t="n"/>
-      <c r="Q12" s="19" t="n"/>
-      <c r="R12" s="19" t="n"/>
-      <c r="S12" s="19" t="n"/>
-      <c r="T12" s="19" t="n"/>
-      <c r="U12" s="19" t="n"/>
-      <c r="V12" s="19" t="n"/>
-      <c r="W12" s="19" t="n"/>
-      <c r="X12" s="19" t="n"/>
-      <c r="Y12" s="19" t="n"/>
-      <c r="Z12" s="19" t="n"/>
-      <c r="AA12" s="19" t="n"/>
-      <c r="AB12" s="19" t="n"/>
-      <c r="AC12" s="19" t="n"/>
-      <c r="AD12" s="19" t="n"/>
-      <c r="AE12" s="19" t="n"/>
-      <c r="AF12" s="19" t="n"/>
-      <c r="AG12" s="19" t="n"/>
-      <c r="AH12" s="19" t="n"/>
-      <c r="AI12" s="19" t="n"/>
-      <c r="AJ12" s="19" t="n"/>
-      <c r="AK12" s="19" t="n"/>
-      <c r="AL12" s="19" t="n"/>
-      <c r="AM12" s="19" t="n"/>
-      <c r="AN12" s="19" t="n"/>
-      <c r="AO12" s="22" t="n"/>
-      <c r="AP12" s="685" t="inlineStr">
+      <c r="B12" s="283" t="n"/>
+      <c r="C12" s="283" t="n"/>
+      <c r="D12" s="283" t="n"/>
+      <c r="E12" s="283" t="n"/>
+      <c r="F12" s="283" t="n"/>
+      <c r="G12" s="283" t="n"/>
+      <c r="H12" s="283" t="n"/>
+      <c r="I12" s="283" t="n"/>
+      <c r="J12" s="283" t="n"/>
+      <c r="K12" s="283" t="n"/>
+      <c r="L12" s="283" t="n"/>
+      <c r="M12" s="283" t="n"/>
+      <c r="N12" s="285" t="n"/>
+      <c r="O12" s="299" t="n"/>
+      <c r="P12" s="283" t="n"/>
+      <c r="Q12" s="283" t="n"/>
+      <c r="R12" s="283" t="n"/>
+      <c r="S12" s="283" t="n"/>
+      <c r="T12" s="283" t="n"/>
+      <c r="U12" s="283" t="n"/>
+      <c r="V12" s="283" t="n"/>
+      <c r="W12" s="283" t="n"/>
+      <c r="X12" s="283" t="n"/>
+      <c r="Y12" s="283" t="n"/>
+      <c r="Z12" s="283" t="n"/>
+      <c r="AA12" s="283" t="n"/>
+      <c r="AB12" s="283" t="n"/>
+      <c r="AC12" s="283" t="n"/>
+      <c r="AD12" s="283" t="n"/>
+      <c r="AE12" s="283" t="n"/>
+      <c r="AF12" s="283" t="n"/>
+      <c r="AG12" s="283" t="n"/>
+      <c r="AH12" s="283" t="n"/>
+      <c r="AI12" s="283" t="n"/>
+      <c r="AJ12" s="283" t="n"/>
+      <c r="AK12" s="283" t="n"/>
+      <c r="AL12" s="283" t="n"/>
+      <c r="AM12" s="283" t="n"/>
+      <c r="AN12" s="283" t="n"/>
+      <c r="AO12" s="285" t="n"/>
+      <c r="AP12" s="793" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AQ12" s="19" t="n"/>
-      <c r="AR12" s="19" t="n"/>
-      <c r="AS12" s="19" t="n"/>
-      <c r="AT12" s="19" t="n"/>
-      <c r="AU12" s="19" t="n"/>
-      <c r="AV12" s="19" t="n"/>
-      <c r="AW12" s="19" t="n"/>
-      <c r="AX12" s="19" t="n"/>
-      <c r="AY12" s="19" t="n"/>
-      <c r="AZ12" s="19" t="n"/>
-      <c r="BA12" s="19" t="n"/>
-      <c r="BB12" s="19" t="n"/>
-      <c r="BC12" s="22" t="n"/>
-      <c r="BD12" s="23" t="n"/>
-      <c r="BE12" s="19" t="n"/>
-      <c r="BF12" s="19" t="n"/>
-      <c r="BG12" s="19" t="n"/>
-      <c r="BH12" s="19" t="n"/>
-      <c r="BI12" s="19" t="n"/>
-      <c r="BJ12" s="19" t="n"/>
-      <c r="BK12" s="19" t="n"/>
-      <c r="BL12" s="19" t="n"/>
-      <c r="BM12" s="19" t="n"/>
-      <c r="BN12" s="19" t="n"/>
-      <c r="BO12" s="19" t="n"/>
-      <c r="BP12" s="19" t="n"/>
-      <c r="BQ12" s="19" t="n"/>
-      <c r="BR12" s="19" t="n"/>
-      <c r="BS12" s="19" t="n"/>
-      <c r="BT12" s="19" t="n"/>
-      <c r="BU12" s="19" t="n"/>
-      <c r="BV12" s="19" t="n"/>
-      <c r="BW12" s="19" t="n"/>
-      <c r="BX12" s="19" t="n"/>
-      <c r="BY12" s="19" t="n"/>
-      <c r="BZ12" s="19" t="n"/>
-      <c r="CA12" s="19" t="n"/>
-      <c r="CB12" s="19" t="n"/>
-      <c r="CC12" s="19" t="n"/>
-      <c r="CD12" s="24" t="n"/>
+      <c r="AQ12" s="283" t="n"/>
+      <c r="AR12" s="283" t="n"/>
+      <c r="AS12" s="283" t="n"/>
+      <c r="AT12" s="283" t="n"/>
+      <c r="AU12" s="283" t="n"/>
+      <c r="AV12" s="283" t="n"/>
+      <c r="AW12" s="283" t="n"/>
+      <c r="AX12" s="283" t="n"/>
+      <c r="AY12" s="283" t="n"/>
+      <c r="AZ12" s="283" t="n"/>
+      <c r="BA12" s="283" t="n"/>
+      <c r="BB12" s="283" t="n"/>
+      <c r="BC12" s="285" t="n"/>
+      <c r="BD12" s="286" t="n"/>
+      <c r="BE12" s="283" t="n"/>
+      <c r="BF12" s="283" t="n"/>
+      <c r="BG12" s="283" t="n"/>
+      <c r="BH12" s="283" t="n"/>
+      <c r="BI12" s="283" t="n"/>
+      <c r="BJ12" s="283" t="n"/>
+      <c r="BK12" s="283" t="n"/>
+      <c r="BL12" s="283" t="n"/>
+      <c r="BM12" s="283" t="n"/>
+      <c r="BN12" s="283" t="n"/>
+      <c r="BO12" s="283" t="n"/>
+      <c r="BP12" s="283" t="n"/>
+      <c r="BQ12" s="283" t="n"/>
+      <c r="BR12" s="283" t="n"/>
+      <c r="BS12" s="283" t="n"/>
+      <c r="BT12" s="283" t="n"/>
+      <c r="BU12" s="283" t="n"/>
+      <c r="BV12" s="283" t="n"/>
+      <c r="BW12" s="283" t="n"/>
+      <c r="BX12" s="283" t="n"/>
+      <c r="BY12" s="283" t="n"/>
+      <c r="BZ12" s="283" t="n"/>
+      <c r="CA12" s="283" t="n"/>
+      <c r="CB12" s="283" t="n"/>
+      <c r="CC12" s="283" t="n"/>
+      <c r="CD12" s="287" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="686" t="n"/>
@@ -8716,460 +8730,460 @@
       <c r="CD13" s="10" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="679" t="inlineStr">
+      <c r="A14" s="787" t="inlineStr">
         <is>
           <t>2.  CHARACTERISTIC RESULTS SECTION</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="27" t="n"/>
-      <c r="R14" s="27" t="n"/>
-      <c r="S14" s="27" t="n"/>
-      <c r="T14" s="27" t="n"/>
-      <c r="U14" s="27" t="n"/>
-      <c r="V14" s="27" t="n"/>
-      <c r="W14" s="27" t="n"/>
-      <c r="X14" s="27" t="n"/>
-      <c r="Y14" s="27" t="n"/>
-      <c r="Z14" s="27" t="n"/>
-      <c r="AA14" s="27" t="n"/>
-      <c r="AB14" s="27" t="n"/>
-      <c r="AC14" s="27" t="n"/>
-      <c r="AD14" s="27" t="n"/>
-      <c r="AE14" s="27" t="n"/>
-      <c r="AF14" s="27" t="n"/>
-      <c r="AG14" s="27" t="n"/>
-      <c r="AH14" s="27" t="n"/>
-      <c r="AI14" s="27" t="n"/>
-      <c r="AJ14" s="27" t="n"/>
-      <c r="AK14" s="27" t="n"/>
-      <c r="AL14" s="27" t="n"/>
-      <c r="AM14" s="27" t="n"/>
-      <c r="AN14" s="27" t="n"/>
-      <c r="AO14" s="27" t="n"/>
-      <c r="AP14" s="27" t="n"/>
-      <c r="AQ14" s="27" t="n"/>
-      <c r="AR14" s="27" t="n"/>
-      <c r="AS14" s="27" t="n"/>
-      <c r="AT14" s="27" t="n"/>
-      <c r="AU14" s="27" t="n"/>
-      <c r="AV14" s="27" t="n"/>
-      <c r="AW14" s="27" t="n"/>
-      <c r="AX14" s="27" t="n"/>
-      <c r="AY14" s="27" t="n"/>
-      <c r="AZ14" s="27" t="n"/>
-      <c r="BA14" s="27" t="n"/>
-      <c r="BB14" s="27" t="n"/>
-      <c r="BC14" s="27" t="n"/>
-      <c r="BD14" s="27" t="n"/>
-      <c r="BE14" s="27" t="n"/>
-      <c r="BF14" s="27" t="n"/>
-      <c r="BG14" s="27" t="n"/>
-      <c r="BH14" s="27" t="n"/>
-      <c r="BI14" s="27" t="n"/>
-      <c r="BJ14" s="27" t="n"/>
-      <c r="BK14" s="27" t="n"/>
-      <c r="BL14" s="27" t="n"/>
-      <c r="BM14" s="27" t="n"/>
-      <c r="BN14" s="27" t="n"/>
-      <c r="BO14" s="27" t="n"/>
-      <c r="BP14" s="27" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
-      <c r="BR14" s="27" t="n"/>
-      <c r="BS14" s="27" t="n"/>
-      <c r="BT14" s="27" t="n"/>
-      <c r="BU14" s="27" t="n"/>
-      <c r="BV14" s="27" t="n"/>
-      <c r="BW14" s="27" t="n"/>
-      <c r="BX14" s="27" t="n"/>
-      <c r="BY14" s="27" t="n"/>
-      <c r="BZ14" s="27" t="n"/>
-      <c r="CA14" s="27" t="n"/>
-      <c r="CB14" s="27" t="n"/>
-      <c r="CC14" s="27" t="n"/>
-      <c r="CD14" s="28" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
+      <c r="I14" s="289" t="n"/>
+      <c r="J14" s="289" t="n"/>
+      <c r="K14" s="289" t="n"/>
+      <c r="L14" s="289" t="n"/>
+      <c r="M14" s="289" t="n"/>
+      <c r="N14" s="289" t="n"/>
+      <c r="O14" s="289" t="n"/>
+      <c r="P14" s="289" t="n"/>
+      <c r="Q14" s="289" t="n"/>
+      <c r="R14" s="289" t="n"/>
+      <c r="S14" s="289" t="n"/>
+      <c r="T14" s="289" t="n"/>
+      <c r="U14" s="289" t="n"/>
+      <c r="V14" s="289" t="n"/>
+      <c r="W14" s="289" t="n"/>
+      <c r="X14" s="289" t="n"/>
+      <c r="Y14" s="289" t="n"/>
+      <c r="Z14" s="289" t="n"/>
+      <c r="AA14" s="289" t="n"/>
+      <c r="AB14" s="289" t="n"/>
+      <c r="AC14" s="289" t="n"/>
+      <c r="AD14" s="289" t="n"/>
+      <c r="AE14" s="289" t="n"/>
+      <c r="AF14" s="289" t="n"/>
+      <c r="AG14" s="289" t="n"/>
+      <c r="AH14" s="289" t="n"/>
+      <c r="AI14" s="289" t="n"/>
+      <c r="AJ14" s="289" t="n"/>
+      <c r="AK14" s="289" t="n"/>
+      <c r="AL14" s="289" t="n"/>
+      <c r="AM14" s="289" t="n"/>
+      <c r="AN14" s="289" t="n"/>
+      <c r="AO14" s="289" t="n"/>
+      <c r="AP14" s="289" t="n"/>
+      <c r="AQ14" s="289" t="n"/>
+      <c r="AR14" s="289" t="n"/>
+      <c r="AS14" s="289" t="n"/>
+      <c r="AT14" s="289" t="n"/>
+      <c r="AU14" s="289" t="n"/>
+      <c r="AV14" s="289" t="n"/>
+      <c r="AW14" s="289" t="n"/>
+      <c r="AX14" s="289" t="n"/>
+      <c r="AY14" s="289" t="n"/>
+      <c r="AZ14" s="289" t="n"/>
+      <c r="BA14" s="289" t="n"/>
+      <c r="BB14" s="289" t="n"/>
+      <c r="BC14" s="289" t="n"/>
+      <c r="BD14" s="289" t="n"/>
+      <c r="BE14" s="289" t="n"/>
+      <c r="BF14" s="289" t="n"/>
+      <c r="BG14" s="289" t="n"/>
+      <c r="BH14" s="289" t="n"/>
+      <c r="BI14" s="289" t="n"/>
+      <c r="BJ14" s="289" t="n"/>
+      <c r="BK14" s="289" t="n"/>
+      <c r="BL14" s="289" t="n"/>
+      <c r="BM14" s="289" t="n"/>
+      <c r="BN14" s="289" t="n"/>
+      <c r="BO14" s="289" t="n"/>
+      <c r="BP14" s="289" t="n"/>
+      <c r="BQ14" s="289" t="n"/>
+      <c r="BR14" s="289" t="n"/>
+      <c r="BS14" s="289" t="n"/>
+      <c r="BT14" s="289" t="n"/>
+      <c r="BU14" s="289" t="n"/>
+      <c r="BV14" s="289" t="n"/>
+      <c r="BW14" s="289" t="n"/>
+      <c r="BX14" s="289" t="n"/>
+      <c r="BY14" s="289" t="n"/>
+      <c r="BZ14" s="289" t="n"/>
+      <c r="CA14" s="289" t="n"/>
+      <c r="CB14" s="289" t="n"/>
+      <c r="CC14" s="289" t="n"/>
+      <c r="CD14" s="290" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="680" t="inlineStr">
+      <c r="A15" s="788" t="inlineStr">
         <is>
           <t>FAI Trigger / Scope</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="30" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-      <c r="Y15" s="5" t="n"/>
-      <c r="Z15" s="5" t="n"/>
-      <c r="AA15" s="5" t="n"/>
-      <c r="AB15" s="5" t="n"/>
-      <c r="AC15" s="5" t="n"/>
-      <c r="AD15" s="5" t="n"/>
-      <c r="AE15" s="5" t="n"/>
-      <c r="AF15" s="5" t="n"/>
-      <c r="AG15" s="5" t="n"/>
-      <c r="AH15" s="5" t="n"/>
-      <c r="AI15" s="5" t="n"/>
-      <c r="AJ15" s="5" t="n"/>
-      <c r="AK15" s="5" t="n"/>
-      <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="5" t="n"/>
-      <c r="AN15" s="5" t="n"/>
-      <c r="AO15" s="6" t="n"/>
-      <c r="AP15" s="681" t="inlineStr">
+      <c r="B15" s="271" t="n"/>
+      <c r="C15" s="271" t="n"/>
+      <c r="D15" s="271" t="n"/>
+      <c r="E15" s="271" t="n"/>
+      <c r="F15" s="271" t="n"/>
+      <c r="G15" s="271" t="n"/>
+      <c r="H15" s="271" t="n"/>
+      <c r="I15" s="271" t="n"/>
+      <c r="J15" s="271" t="n"/>
+      <c r="K15" s="271" t="n"/>
+      <c r="L15" s="271" t="n"/>
+      <c r="M15" s="271" t="n"/>
+      <c r="N15" s="272" t="n"/>
+      <c r="O15" s="292" t="n"/>
+      <c r="P15" s="271" t="n"/>
+      <c r="Q15" s="271" t="n"/>
+      <c r="R15" s="271" t="n"/>
+      <c r="S15" s="271" t="n"/>
+      <c r="T15" s="271" t="n"/>
+      <c r="U15" s="271" t="n"/>
+      <c r="V15" s="271" t="n"/>
+      <c r="W15" s="271" t="n"/>
+      <c r="X15" s="271" t="n"/>
+      <c r="Y15" s="271" t="n"/>
+      <c r="Z15" s="271" t="n"/>
+      <c r="AA15" s="271" t="n"/>
+      <c r="AB15" s="271" t="n"/>
+      <c r="AC15" s="271" t="n"/>
+      <c r="AD15" s="271" t="n"/>
+      <c r="AE15" s="271" t="n"/>
+      <c r="AF15" s="271" t="n"/>
+      <c r="AG15" s="271" t="n"/>
+      <c r="AH15" s="271" t="n"/>
+      <c r="AI15" s="271" t="n"/>
+      <c r="AJ15" s="271" t="n"/>
+      <c r="AK15" s="271" t="n"/>
+      <c r="AL15" s="271" t="n"/>
+      <c r="AM15" s="271" t="n"/>
+      <c r="AN15" s="271" t="n"/>
+      <c r="AO15" s="272" t="n"/>
+      <c r="AP15" s="789" t="inlineStr">
         <is>
           <t>Disposition</t>
         </is>
       </c>
-      <c r="AQ15" s="5" t="n"/>
-      <c r="AR15" s="5" t="n"/>
-      <c r="AS15" s="5" t="n"/>
-      <c r="AT15" s="5" t="n"/>
-      <c r="AU15" s="5" t="n"/>
-      <c r="AV15" s="5" t="n"/>
-      <c r="AW15" s="5" t="n"/>
-      <c r="AX15" s="5" t="n"/>
-      <c r="AY15" s="5" t="n"/>
-      <c r="AZ15" s="5" t="n"/>
-      <c r="BA15" s="5" t="n"/>
-      <c r="BB15" s="5" t="n"/>
-      <c r="BC15" s="6" t="n"/>
-      <c r="BD15" s="30" t="n"/>
-      <c r="BE15" s="5" t="n"/>
-      <c r="BF15" s="5" t="n"/>
-      <c r="BG15" s="5" t="n"/>
-      <c r="BH15" s="5" t="n"/>
-      <c r="BI15" s="5" t="n"/>
-      <c r="BJ15" s="5" t="n"/>
-      <c r="BK15" s="5" t="n"/>
-      <c r="BL15" s="5" t="n"/>
-      <c r="BM15" s="5" t="n"/>
-      <c r="BN15" s="5" t="n"/>
-      <c r="BO15" s="5" t="n"/>
-      <c r="BP15" s="5" t="n"/>
-      <c r="BQ15" s="5" t="n"/>
-      <c r="BR15" s="5" t="n"/>
-      <c r="BS15" s="5" t="n"/>
-      <c r="BT15" s="5" t="n"/>
-      <c r="BU15" s="5" t="n"/>
-      <c r="BV15" s="5" t="n"/>
-      <c r="BW15" s="5" t="n"/>
-      <c r="BX15" s="5" t="n"/>
-      <c r="BY15" s="5" t="n"/>
-      <c r="BZ15" s="5" t="n"/>
-      <c r="CA15" s="5" t="n"/>
-      <c r="CB15" s="5" t="n"/>
-      <c r="CC15" s="5" t="n"/>
-      <c r="CD15" s="8" t="n"/>
+      <c r="AQ15" s="271" t="n"/>
+      <c r="AR15" s="271" t="n"/>
+      <c r="AS15" s="271" t="n"/>
+      <c r="AT15" s="271" t="n"/>
+      <c r="AU15" s="271" t="n"/>
+      <c r="AV15" s="271" t="n"/>
+      <c r="AW15" s="271" t="n"/>
+      <c r="AX15" s="271" t="n"/>
+      <c r="AY15" s="271" t="n"/>
+      <c r="AZ15" s="271" t="n"/>
+      <c r="BA15" s="271" t="n"/>
+      <c r="BB15" s="271" t="n"/>
+      <c r="BC15" s="272" t="n"/>
+      <c r="BD15" s="294" t="n"/>
+      <c r="BE15" s="271" t="n"/>
+      <c r="BF15" s="271" t="n"/>
+      <c r="BG15" s="271" t="n"/>
+      <c r="BH15" s="271" t="n"/>
+      <c r="BI15" s="271" t="n"/>
+      <c r="BJ15" s="271" t="n"/>
+      <c r="BK15" s="271" t="n"/>
+      <c r="BL15" s="271" t="n"/>
+      <c r="BM15" s="271" t="n"/>
+      <c r="BN15" s="271" t="n"/>
+      <c r="BO15" s="271" t="n"/>
+      <c r="BP15" s="271" t="n"/>
+      <c r="BQ15" s="271" t="n"/>
+      <c r="BR15" s="271" t="n"/>
+      <c r="BS15" s="271" t="n"/>
+      <c r="BT15" s="271" t="n"/>
+      <c r="BU15" s="271" t="n"/>
+      <c r="BV15" s="271" t="n"/>
+      <c r="BW15" s="271" t="n"/>
+      <c r="BX15" s="271" t="n"/>
+      <c r="BY15" s="271" t="n"/>
+      <c r="BZ15" s="271" t="n"/>
+      <c r="CA15" s="271" t="n"/>
+      <c r="CB15" s="271" t="n"/>
+      <c r="CC15" s="271" t="n"/>
+      <c r="CD15" s="274" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="682" t="inlineStr">
+      <c r="A16" s="790" t="inlineStr">
         <is>
           <t>Top Abnormality / Revalidation Need</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="12" t="n"/>
-      <c r="S16" s="12" t="n"/>
-      <c r="T16" s="12" t="n"/>
-      <c r="U16" s="12" t="n"/>
-      <c r="V16" s="12" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="12" t="n"/>
-      <c r="Y16" s="12" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="12" t="n"/>
-      <c r="AB16" s="12" t="n"/>
-      <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="12" t="n"/>
-      <c r="AE16" s="12" t="n"/>
-      <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="12" t="n"/>
-      <c r="AH16" s="12" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="12" t="n"/>
-      <c r="AK16" s="12" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="12" t="n"/>
-      <c r="AN16" s="12" t="n"/>
-      <c r="AO16" s="13" t="n"/>
-      <c r="AP16" s="683" t="inlineStr">
+      <c r="B16" s="277" t="n"/>
+      <c r="C16" s="277" t="n"/>
+      <c r="D16" s="277" t="n"/>
+      <c r="E16" s="277" t="n"/>
+      <c r="F16" s="277" t="n"/>
+      <c r="G16" s="277" t="n"/>
+      <c r="H16" s="277" t="n"/>
+      <c r="I16" s="277" t="n"/>
+      <c r="J16" s="277" t="n"/>
+      <c r="K16" s="277" t="n"/>
+      <c r="L16" s="277" t="n"/>
+      <c r="M16" s="277" t="n"/>
+      <c r="N16" s="278" t="n"/>
+      <c r="O16" s="296" t="n"/>
+      <c r="P16" s="277" t="n"/>
+      <c r="Q16" s="277" t="n"/>
+      <c r="R16" s="277" t="n"/>
+      <c r="S16" s="277" t="n"/>
+      <c r="T16" s="277" t="n"/>
+      <c r="U16" s="277" t="n"/>
+      <c r="V16" s="277" t="n"/>
+      <c r="W16" s="277" t="n"/>
+      <c r="X16" s="277" t="n"/>
+      <c r="Y16" s="277" t="n"/>
+      <c r="Z16" s="277" t="n"/>
+      <c r="AA16" s="277" t="n"/>
+      <c r="AB16" s="277" t="n"/>
+      <c r="AC16" s="277" t="n"/>
+      <c r="AD16" s="277" t="n"/>
+      <c r="AE16" s="277" t="n"/>
+      <c r="AF16" s="277" t="n"/>
+      <c r="AG16" s="277" t="n"/>
+      <c r="AH16" s="277" t="n"/>
+      <c r="AI16" s="277" t="n"/>
+      <c r="AJ16" s="277" t="n"/>
+      <c r="AK16" s="277" t="n"/>
+      <c r="AL16" s="277" t="n"/>
+      <c r="AM16" s="277" t="n"/>
+      <c r="AN16" s="277" t="n"/>
+      <c r="AO16" s="278" t="n"/>
+      <c r="AP16" s="791" t="inlineStr">
         <is>
           <t>Next Step</t>
         </is>
       </c>
-      <c r="AQ16" s="12" t="n"/>
-      <c r="AR16" s="12" t="n"/>
-      <c r="AS16" s="12" t="n"/>
-      <c r="AT16" s="12" t="n"/>
-      <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="12" t="n"/>
-      <c r="AW16" s="12" t="n"/>
-      <c r="AX16" s="12" t="n"/>
-      <c r="AY16" s="12" t="n"/>
-      <c r="AZ16" s="12" t="n"/>
-      <c r="BA16" s="12" t="n"/>
-      <c r="BB16" s="12" t="n"/>
-      <c r="BC16" s="13" t="n"/>
-      <c r="BD16" s="14" t="n"/>
-      <c r="BE16" s="12" t="n"/>
-      <c r="BF16" s="12" t="n"/>
-      <c r="BG16" s="12" t="n"/>
-      <c r="BH16" s="12" t="n"/>
-      <c r="BI16" s="12" t="n"/>
-      <c r="BJ16" s="12" t="n"/>
-      <c r="BK16" s="12" t="n"/>
-      <c r="BL16" s="12" t="n"/>
-      <c r="BM16" s="12" t="n"/>
-      <c r="BN16" s="12" t="n"/>
-      <c r="BO16" s="12" t="n"/>
-      <c r="BP16" s="12" t="n"/>
-      <c r="BQ16" s="12" t="n"/>
-      <c r="BR16" s="12" t="n"/>
-      <c r="BS16" s="12" t="n"/>
-      <c r="BT16" s="12" t="n"/>
-      <c r="BU16" s="12" t="n"/>
-      <c r="BV16" s="12" t="n"/>
-      <c r="BW16" s="12" t="n"/>
-      <c r="BX16" s="12" t="n"/>
-      <c r="BY16" s="12" t="n"/>
-      <c r="BZ16" s="12" t="n"/>
-      <c r="CA16" s="12" t="n"/>
-      <c r="CB16" s="12" t="n"/>
-      <c r="CC16" s="12" t="n"/>
-      <c r="CD16" s="15" t="n"/>
+      <c r="AQ16" s="277" t="n"/>
+      <c r="AR16" s="277" t="n"/>
+      <c r="AS16" s="277" t="n"/>
+      <c r="AT16" s="277" t="n"/>
+      <c r="AU16" s="277" t="n"/>
+      <c r="AV16" s="277" t="n"/>
+      <c r="AW16" s="277" t="n"/>
+      <c r="AX16" s="277" t="n"/>
+      <c r="AY16" s="277" t="n"/>
+      <c r="AZ16" s="277" t="n"/>
+      <c r="BA16" s="277" t="n"/>
+      <c r="BB16" s="277" t="n"/>
+      <c r="BC16" s="278" t="n"/>
+      <c r="BD16" s="279" t="n"/>
+      <c r="BE16" s="277" t="n"/>
+      <c r="BF16" s="277" t="n"/>
+      <c r="BG16" s="277" t="n"/>
+      <c r="BH16" s="277" t="n"/>
+      <c r="BI16" s="277" t="n"/>
+      <c r="BJ16" s="277" t="n"/>
+      <c r="BK16" s="277" t="n"/>
+      <c r="BL16" s="277" t="n"/>
+      <c r="BM16" s="277" t="n"/>
+      <c r="BN16" s="277" t="n"/>
+      <c r="BO16" s="277" t="n"/>
+      <c r="BP16" s="277" t="n"/>
+      <c r="BQ16" s="277" t="n"/>
+      <c r="BR16" s="277" t="n"/>
+      <c r="BS16" s="277" t="n"/>
+      <c r="BT16" s="277" t="n"/>
+      <c r="BU16" s="277" t="n"/>
+      <c r="BV16" s="277" t="n"/>
+      <c r="BW16" s="277" t="n"/>
+      <c r="BX16" s="277" t="n"/>
+      <c r="BY16" s="277" t="n"/>
+      <c r="BZ16" s="277" t="n"/>
+      <c r="CA16" s="277" t="n"/>
+      <c r="CB16" s="277" t="n"/>
+      <c r="CC16" s="277" t="n"/>
+      <c r="CD16" s="280" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="682" t="inlineStr">
+      <c r="A17" s="790" t="inlineStr">
         <is>
           <t>Action Owner</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="12" t="n"/>
-      <c r="S17" s="12" t="n"/>
-      <c r="T17" s="12" t="n"/>
-      <c r="U17" s="12" t="n"/>
-      <c r="V17" s="12" t="n"/>
-      <c r="W17" s="12" t="n"/>
-      <c r="X17" s="12" t="n"/>
-      <c r="Y17" s="12" t="n"/>
-      <c r="Z17" s="12" t="n"/>
-      <c r="AA17" s="12" t="n"/>
-      <c r="AB17" s="12" t="n"/>
-      <c r="AC17" s="12" t="n"/>
-      <c r="AD17" s="12" t="n"/>
-      <c r="AE17" s="12" t="n"/>
-      <c r="AF17" s="12" t="n"/>
-      <c r="AG17" s="12" t="n"/>
-      <c r="AH17" s="12" t="n"/>
-      <c r="AI17" s="12" t="n"/>
-      <c r="AJ17" s="12" t="n"/>
-      <c r="AK17" s="12" t="n"/>
-      <c r="AL17" s="12" t="n"/>
-      <c r="AM17" s="12" t="n"/>
-      <c r="AN17" s="12" t="n"/>
-      <c r="AO17" s="13" t="n"/>
-      <c r="AP17" s="683" t="inlineStr">
+      <c r="B17" s="277" t="n"/>
+      <c r="C17" s="277" t="n"/>
+      <c r="D17" s="277" t="n"/>
+      <c r="E17" s="277" t="n"/>
+      <c r="F17" s="277" t="n"/>
+      <c r="G17" s="277" t="n"/>
+      <c r="H17" s="277" t="n"/>
+      <c r="I17" s="277" t="n"/>
+      <c r="J17" s="277" t="n"/>
+      <c r="K17" s="277" t="n"/>
+      <c r="L17" s="277" t="n"/>
+      <c r="M17" s="277" t="n"/>
+      <c r="N17" s="278" t="n"/>
+      <c r="O17" s="296" t="n"/>
+      <c r="P17" s="277" t="n"/>
+      <c r="Q17" s="277" t="n"/>
+      <c r="R17" s="277" t="n"/>
+      <c r="S17" s="277" t="n"/>
+      <c r="T17" s="277" t="n"/>
+      <c r="U17" s="277" t="n"/>
+      <c r="V17" s="277" t="n"/>
+      <c r="W17" s="277" t="n"/>
+      <c r="X17" s="277" t="n"/>
+      <c r="Y17" s="277" t="n"/>
+      <c r="Z17" s="277" t="n"/>
+      <c r="AA17" s="277" t="n"/>
+      <c r="AB17" s="277" t="n"/>
+      <c r="AC17" s="277" t="n"/>
+      <c r="AD17" s="277" t="n"/>
+      <c r="AE17" s="277" t="n"/>
+      <c r="AF17" s="277" t="n"/>
+      <c r="AG17" s="277" t="n"/>
+      <c r="AH17" s="277" t="n"/>
+      <c r="AI17" s="277" t="n"/>
+      <c r="AJ17" s="277" t="n"/>
+      <c r="AK17" s="277" t="n"/>
+      <c r="AL17" s="277" t="n"/>
+      <c r="AM17" s="277" t="n"/>
+      <c r="AN17" s="277" t="n"/>
+      <c r="AO17" s="278" t="n"/>
+      <c r="AP17" s="791" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AQ17" s="12" t="n"/>
-      <c r="AR17" s="12" t="n"/>
-      <c r="AS17" s="12" t="n"/>
-      <c r="AT17" s="12" t="n"/>
-      <c r="AU17" s="12" t="n"/>
-      <c r="AV17" s="12" t="n"/>
-      <c r="AW17" s="12" t="n"/>
-      <c r="AX17" s="12" t="n"/>
-      <c r="AY17" s="12" t="n"/>
-      <c r="AZ17" s="12" t="n"/>
-      <c r="BA17" s="12" t="n"/>
-      <c r="BB17" s="12" t="n"/>
-      <c r="BC17" s="13" t="n"/>
-      <c r="BD17" s="687" t="n"/>
-      <c r="BE17" s="12" t="n"/>
-      <c r="BF17" s="12" t="n"/>
-      <c r="BG17" s="12" t="n"/>
-      <c r="BH17" s="12" t="n"/>
-      <c r="BI17" s="12" t="n"/>
-      <c r="BJ17" s="12" t="n"/>
-      <c r="BK17" s="12" t="n"/>
-      <c r="BL17" s="12" t="n"/>
-      <c r="BM17" s="12" t="n"/>
-      <c r="BN17" s="12" t="n"/>
-      <c r="BO17" s="12" t="n"/>
-      <c r="BP17" s="12" t="n"/>
-      <c r="BQ17" s="12" t="n"/>
-      <c r="BR17" s="12" t="n"/>
-      <c r="BS17" s="12" t="n"/>
-      <c r="BT17" s="12" t="n"/>
-      <c r="BU17" s="12" t="n"/>
-      <c r="BV17" s="12" t="n"/>
-      <c r="BW17" s="12" t="n"/>
-      <c r="BX17" s="12" t="n"/>
-      <c r="BY17" s="12" t="n"/>
-      <c r="BZ17" s="12" t="n"/>
-      <c r="CA17" s="12" t="n"/>
-      <c r="CB17" s="12" t="n"/>
-      <c r="CC17" s="12" t="n"/>
-      <c r="CD17" s="15" t="n"/>
+      <c r="AQ17" s="277" t="n"/>
+      <c r="AR17" s="277" t="n"/>
+      <c r="AS17" s="277" t="n"/>
+      <c r="AT17" s="277" t="n"/>
+      <c r="AU17" s="277" t="n"/>
+      <c r="AV17" s="277" t="n"/>
+      <c r="AW17" s="277" t="n"/>
+      <c r="AX17" s="277" t="n"/>
+      <c r="AY17" s="277" t="n"/>
+      <c r="AZ17" s="277" t="n"/>
+      <c r="BA17" s="277" t="n"/>
+      <c r="BB17" s="277" t="n"/>
+      <c r="BC17" s="278" t="n"/>
+      <c r="BD17" s="334" t="n"/>
+      <c r="BE17" s="277" t="n"/>
+      <c r="BF17" s="277" t="n"/>
+      <c r="BG17" s="277" t="n"/>
+      <c r="BH17" s="277" t="n"/>
+      <c r="BI17" s="277" t="n"/>
+      <c r="BJ17" s="277" t="n"/>
+      <c r="BK17" s="277" t="n"/>
+      <c r="BL17" s="277" t="n"/>
+      <c r="BM17" s="277" t="n"/>
+      <c r="BN17" s="277" t="n"/>
+      <c r="BO17" s="277" t="n"/>
+      <c r="BP17" s="277" t="n"/>
+      <c r="BQ17" s="277" t="n"/>
+      <c r="BR17" s="277" t="n"/>
+      <c r="BS17" s="277" t="n"/>
+      <c r="BT17" s="277" t="n"/>
+      <c r="BU17" s="277" t="n"/>
+      <c r="BV17" s="277" t="n"/>
+      <c r="BW17" s="277" t="n"/>
+      <c r="BX17" s="277" t="n"/>
+      <c r="BY17" s="277" t="n"/>
+      <c r="BZ17" s="277" t="n"/>
+      <c r="CA17" s="277" t="n"/>
+      <c r="CB17" s="277" t="n"/>
+      <c r="CC17" s="277" t="n"/>
+      <c r="CD17" s="280" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="684" t="inlineStr">
+      <c r="A18" s="792" t="inlineStr">
         <is>
           <t>Escalation if Not Released</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="19" t="n"/>
-      <c r="H18" s="19" t="n"/>
-      <c r="I18" s="19" t="n"/>
-      <c r="J18" s="19" t="n"/>
-      <c r="K18" s="19" t="n"/>
-      <c r="L18" s="19" t="n"/>
-      <c r="M18" s="19" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="23" t="n"/>
-      <c r="P18" s="19" t="n"/>
-      <c r="Q18" s="19" t="n"/>
-      <c r="R18" s="19" t="n"/>
-      <c r="S18" s="19" t="n"/>
-      <c r="T18" s="19" t="n"/>
-      <c r="U18" s="19" t="n"/>
-      <c r="V18" s="19" t="n"/>
-      <c r="W18" s="19" t="n"/>
-      <c r="X18" s="19" t="n"/>
-      <c r="Y18" s="19" t="n"/>
-      <c r="Z18" s="19" t="n"/>
-      <c r="AA18" s="19" t="n"/>
-      <c r="AB18" s="19" t="n"/>
-      <c r="AC18" s="19" t="n"/>
-      <c r="AD18" s="19" t="n"/>
-      <c r="AE18" s="19" t="n"/>
-      <c r="AF18" s="19" t="n"/>
-      <c r="AG18" s="19" t="n"/>
-      <c r="AH18" s="19" t="n"/>
-      <c r="AI18" s="19" t="n"/>
-      <c r="AJ18" s="19" t="n"/>
-      <c r="AK18" s="19" t="n"/>
-      <c r="AL18" s="19" t="n"/>
-      <c r="AM18" s="19" t="n"/>
-      <c r="AN18" s="19" t="n"/>
-      <c r="AO18" s="22" t="n"/>
-      <c r="AP18" s="685" t="inlineStr">
+      <c r="B18" s="283" t="n"/>
+      <c r="C18" s="283" t="n"/>
+      <c r="D18" s="283" t="n"/>
+      <c r="E18" s="283" t="n"/>
+      <c r="F18" s="283" t="n"/>
+      <c r="G18" s="283" t="n"/>
+      <c r="H18" s="283" t="n"/>
+      <c r="I18" s="283" t="n"/>
+      <c r="J18" s="283" t="n"/>
+      <c r="K18" s="283" t="n"/>
+      <c r="L18" s="283" t="n"/>
+      <c r="M18" s="283" t="n"/>
+      <c r="N18" s="285" t="n"/>
+      <c r="O18" s="299" t="n"/>
+      <c r="P18" s="283" t="n"/>
+      <c r="Q18" s="283" t="n"/>
+      <c r="R18" s="283" t="n"/>
+      <c r="S18" s="283" t="n"/>
+      <c r="T18" s="283" t="n"/>
+      <c r="U18" s="283" t="n"/>
+      <c r="V18" s="283" t="n"/>
+      <c r="W18" s="283" t="n"/>
+      <c r="X18" s="283" t="n"/>
+      <c r="Y18" s="283" t="n"/>
+      <c r="Z18" s="283" t="n"/>
+      <c r="AA18" s="283" t="n"/>
+      <c r="AB18" s="283" t="n"/>
+      <c r="AC18" s="283" t="n"/>
+      <c r="AD18" s="283" t="n"/>
+      <c r="AE18" s="283" t="n"/>
+      <c r="AF18" s="283" t="n"/>
+      <c r="AG18" s="283" t="n"/>
+      <c r="AH18" s="283" t="n"/>
+      <c r="AI18" s="283" t="n"/>
+      <c r="AJ18" s="283" t="n"/>
+      <c r="AK18" s="283" t="n"/>
+      <c r="AL18" s="283" t="n"/>
+      <c r="AM18" s="283" t="n"/>
+      <c r="AN18" s="283" t="n"/>
+      <c r="AO18" s="285" t="n"/>
+      <c r="AP18" s="793" t="inlineStr">
         <is>
           <t>FAI Status</t>
         </is>
       </c>
-      <c r="AQ18" s="19" t="n"/>
-      <c r="AR18" s="19" t="n"/>
-      <c r="AS18" s="19" t="n"/>
-      <c r="AT18" s="19" t="n"/>
-      <c r="AU18" s="19" t="n"/>
-      <c r="AV18" s="19" t="n"/>
-      <c r="AW18" s="19" t="n"/>
-      <c r="AX18" s="19" t="n"/>
-      <c r="AY18" s="19" t="n"/>
-      <c r="AZ18" s="19" t="n"/>
-      <c r="BA18" s="19" t="n"/>
-      <c r="BB18" s="19" t="n"/>
-      <c r="BC18" s="22" t="n"/>
-      <c r="BD18" s="23" t="n"/>
-      <c r="BE18" s="19" t="n"/>
-      <c r="BF18" s="19" t="n"/>
-      <c r="BG18" s="19" t="n"/>
-      <c r="BH18" s="19" t="n"/>
-      <c r="BI18" s="19" t="n"/>
-      <c r="BJ18" s="19" t="n"/>
-      <c r="BK18" s="19" t="n"/>
-      <c r="BL18" s="19" t="n"/>
-      <c r="BM18" s="19" t="n"/>
-      <c r="BN18" s="19" t="n"/>
-      <c r="BO18" s="19" t="n"/>
-      <c r="BP18" s="19" t="n"/>
-      <c r="BQ18" s="19" t="n"/>
-      <c r="BR18" s="19" t="n"/>
-      <c r="BS18" s="19" t="n"/>
-      <c r="BT18" s="19" t="n"/>
-      <c r="BU18" s="19" t="n"/>
-      <c r="BV18" s="19" t="n"/>
-      <c r="BW18" s="19" t="n"/>
-      <c r="BX18" s="19" t="n"/>
-      <c r="BY18" s="19" t="n"/>
-      <c r="BZ18" s="19" t="n"/>
-      <c r="CA18" s="19" t="n"/>
-      <c r="CB18" s="19" t="n"/>
-      <c r="CC18" s="19" t="n"/>
-      <c r="CD18" s="24" t="n"/>
+      <c r="AQ18" s="283" t="n"/>
+      <c r="AR18" s="283" t="n"/>
+      <c r="AS18" s="283" t="n"/>
+      <c r="AT18" s="283" t="n"/>
+      <c r="AU18" s="283" t="n"/>
+      <c r="AV18" s="283" t="n"/>
+      <c r="AW18" s="283" t="n"/>
+      <c r="AX18" s="283" t="n"/>
+      <c r="AY18" s="283" t="n"/>
+      <c r="AZ18" s="283" t="n"/>
+      <c r="BA18" s="283" t="n"/>
+      <c r="BB18" s="283" t="n"/>
+      <c r="BC18" s="285" t="n"/>
+      <c r="BD18" s="286" t="n"/>
+      <c r="BE18" s="283" t="n"/>
+      <c r="BF18" s="283" t="n"/>
+      <c r="BG18" s="283" t="n"/>
+      <c r="BH18" s="283" t="n"/>
+      <c r="BI18" s="283" t="n"/>
+      <c r="BJ18" s="283" t="n"/>
+      <c r="BK18" s="283" t="n"/>
+      <c r="BL18" s="283" t="n"/>
+      <c r="BM18" s="283" t="n"/>
+      <c r="BN18" s="283" t="n"/>
+      <c r="BO18" s="283" t="n"/>
+      <c r="BP18" s="283" t="n"/>
+      <c r="BQ18" s="283" t="n"/>
+      <c r="BR18" s="283" t="n"/>
+      <c r="BS18" s="283" t="n"/>
+      <c r="BT18" s="283" t="n"/>
+      <c r="BU18" s="283" t="n"/>
+      <c r="BV18" s="283" t="n"/>
+      <c r="BW18" s="283" t="n"/>
+      <c r="BX18" s="283" t="n"/>
+      <c r="BY18" s="283" t="n"/>
+      <c r="BZ18" s="283" t="n"/>
+      <c r="CA18" s="283" t="n"/>
+      <c r="CB18" s="283" t="n"/>
+      <c r="CC18" s="283" t="n"/>
+      <c r="CD18" s="287" t="n"/>
     </row>
     <row r="19" ht="3" customHeight="1">
       <c r="A19" s="686" t="n"/>
@@ -9256,1184 +9270,1184 @@
       <c r="CD19" s="10" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="679" t="inlineStr">
+      <c r="A20" s="787" t="inlineStr">
         <is>
           <t>3.  REVALIDATION TRIGGER SECTION</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="27" t="n"/>
-      <c r="O20" s="27" t="n"/>
-      <c r="P20" s="27" t="n"/>
-      <c r="Q20" s="27" t="n"/>
-      <c r="R20" s="27" t="n"/>
-      <c r="S20" s="27" t="n"/>
-      <c r="T20" s="27" t="n"/>
-      <c r="U20" s="27" t="n"/>
-      <c r="V20" s="27" t="n"/>
-      <c r="W20" s="27" t="n"/>
-      <c r="X20" s="27" t="n"/>
-      <c r="Y20" s="27" t="n"/>
-      <c r="Z20" s="27" t="n"/>
-      <c r="AA20" s="27" t="n"/>
-      <c r="AB20" s="27" t="n"/>
-      <c r="AC20" s="27" t="n"/>
-      <c r="AD20" s="27" t="n"/>
-      <c r="AE20" s="27" t="n"/>
-      <c r="AF20" s="27" t="n"/>
-      <c r="AG20" s="27" t="n"/>
-      <c r="AH20" s="27" t="n"/>
-      <c r="AI20" s="27" t="n"/>
-      <c r="AJ20" s="27" t="n"/>
-      <c r="AK20" s="27" t="n"/>
-      <c r="AL20" s="27" t="n"/>
-      <c r="AM20" s="27" t="n"/>
-      <c r="AN20" s="27" t="n"/>
-      <c r="AO20" s="27" t="n"/>
-      <c r="AP20" s="27" t="n"/>
-      <c r="AQ20" s="27" t="n"/>
-      <c r="AR20" s="27" t="n"/>
-      <c r="AS20" s="27" t="n"/>
-      <c r="AT20" s="27" t="n"/>
-      <c r="AU20" s="27" t="n"/>
-      <c r="AV20" s="27" t="n"/>
-      <c r="AW20" s="27" t="n"/>
-      <c r="AX20" s="27" t="n"/>
-      <c r="AY20" s="27" t="n"/>
-      <c r="AZ20" s="27" t="n"/>
-      <c r="BA20" s="27" t="n"/>
-      <c r="BB20" s="27" t="n"/>
-      <c r="BC20" s="27" t="n"/>
-      <c r="BD20" s="27" t="n"/>
-      <c r="BE20" s="27" t="n"/>
-      <c r="BF20" s="27" t="n"/>
-      <c r="BG20" s="27" t="n"/>
-      <c r="BH20" s="27" t="n"/>
-      <c r="BI20" s="27" t="n"/>
-      <c r="BJ20" s="27" t="n"/>
-      <c r="BK20" s="27" t="n"/>
-      <c r="BL20" s="27" t="n"/>
-      <c r="BM20" s="27" t="n"/>
-      <c r="BN20" s="27" t="n"/>
-      <c r="BO20" s="27" t="n"/>
-      <c r="BP20" s="27" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
-      <c r="BR20" s="27" t="n"/>
-      <c r="BS20" s="27" t="n"/>
-      <c r="BT20" s="27" t="n"/>
-      <c r="BU20" s="27" t="n"/>
-      <c r="BV20" s="27" t="n"/>
-      <c r="BW20" s="27" t="n"/>
-      <c r="BX20" s="27" t="n"/>
-      <c r="BY20" s="27" t="n"/>
-      <c r="BZ20" s="27" t="n"/>
-      <c r="CA20" s="27" t="n"/>
-      <c r="CB20" s="27" t="n"/>
-      <c r="CC20" s="27" t="n"/>
-      <c r="CD20" s="28" t="n"/>
+      <c r="B20" s="289" t="n"/>
+      <c r="C20" s="289" t="n"/>
+      <c r="D20" s="289" t="n"/>
+      <c r="E20" s="289" t="n"/>
+      <c r="F20" s="289" t="n"/>
+      <c r="G20" s="289" t="n"/>
+      <c r="H20" s="289" t="n"/>
+      <c r="I20" s="289" t="n"/>
+      <c r="J20" s="289" t="n"/>
+      <c r="K20" s="289" t="n"/>
+      <c r="L20" s="289" t="n"/>
+      <c r="M20" s="289" t="n"/>
+      <c r="N20" s="289" t="n"/>
+      <c r="O20" s="289" t="n"/>
+      <c r="P20" s="289" t="n"/>
+      <c r="Q20" s="289" t="n"/>
+      <c r="R20" s="289" t="n"/>
+      <c r="S20" s="289" t="n"/>
+      <c r="T20" s="289" t="n"/>
+      <c r="U20" s="289" t="n"/>
+      <c r="V20" s="289" t="n"/>
+      <c r="W20" s="289" t="n"/>
+      <c r="X20" s="289" t="n"/>
+      <c r="Y20" s="289" t="n"/>
+      <c r="Z20" s="289" t="n"/>
+      <c r="AA20" s="289" t="n"/>
+      <c r="AB20" s="289" t="n"/>
+      <c r="AC20" s="289" t="n"/>
+      <c r="AD20" s="289" t="n"/>
+      <c r="AE20" s="289" t="n"/>
+      <c r="AF20" s="289" t="n"/>
+      <c r="AG20" s="289" t="n"/>
+      <c r="AH20" s="289" t="n"/>
+      <c r="AI20" s="289" t="n"/>
+      <c r="AJ20" s="289" t="n"/>
+      <c r="AK20" s="289" t="n"/>
+      <c r="AL20" s="289" t="n"/>
+      <c r="AM20" s="289" t="n"/>
+      <c r="AN20" s="289" t="n"/>
+      <c r="AO20" s="289" t="n"/>
+      <c r="AP20" s="289" t="n"/>
+      <c r="AQ20" s="289" t="n"/>
+      <c r="AR20" s="289" t="n"/>
+      <c r="AS20" s="289" t="n"/>
+      <c r="AT20" s="289" t="n"/>
+      <c r="AU20" s="289" t="n"/>
+      <c r="AV20" s="289" t="n"/>
+      <c r="AW20" s="289" t="n"/>
+      <c r="AX20" s="289" t="n"/>
+      <c r="AY20" s="289" t="n"/>
+      <c r="AZ20" s="289" t="n"/>
+      <c r="BA20" s="289" t="n"/>
+      <c r="BB20" s="289" t="n"/>
+      <c r="BC20" s="289" t="n"/>
+      <c r="BD20" s="289" t="n"/>
+      <c r="BE20" s="289" t="n"/>
+      <c r="BF20" s="289" t="n"/>
+      <c r="BG20" s="289" t="n"/>
+      <c r="BH20" s="289" t="n"/>
+      <c r="BI20" s="289" t="n"/>
+      <c r="BJ20" s="289" t="n"/>
+      <c r="BK20" s="289" t="n"/>
+      <c r="BL20" s="289" t="n"/>
+      <c r="BM20" s="289" t="n"/>
+      <c r="BN20" s="289" t="n"/>
+      <c r="BO20" s="289" t="n"/>
+      <c r="BP20" s="289" t="n"/>
+      <c r="BQ20" s="289" t="n"/>
+      <c r="BR20" s="289" t="n"/>
+      <c r="BS20" s="289" t="n"/>
+      <c r="BT20" s="289" t="n"/>
+      <c r="BU20" s="289" t="n"/>
+      <c r="BV20" s="289" t="n"/>
+      <c r="BW20" s="289" t="n"/>
+      <c r="BX20" s="289" t="n"/>
+      <c r="BY20" s="289" t="n"/>
+      <c r="BZ20" s="289" t="n"/>
+      <c r="CA20" s="289" t="n"/>
+      <c r="CB20" s="289" t="n"/>
+      <c r="CC20" s="289" t="n"/>
+      <c r="CD20" s="290" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="301" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="B21" s="271" t="n"/>
+      <c r="C21" s="271" t="n"/>
+      <c r="D21" s="272" t="n"/>
+      <c r="E21" s="302" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="37" t="inlineStr">
+      <c r="F21" s="271" t="n"/>
+      <c r="G21" s="271" t="n"/>
+      <c r="H21" s="271" t="n"/>
+      <c r="I21" s="271" t="n"/>
+      <c r="J21" s="272" t="n"/>
+      <c r="K21" s="302" t="inlineStr">
         <is>
           <t>Control Item / Check</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-      <c r="Y21" s="5" t="n"/>
-      <c r="Z21" s="5" t="n"/>
-      <c r="AA21" s="5" t="n"/>
-      <c r="AB21" s="5" t="n"/>
-      <c r="AC21" s="5" t="n"/>
-      <c r="AD21" s="5" t="n"/>
-      <c r="AE21" s="5" t="n"/>
-      <c r="AF21" s="5" t="n"/>
-      <c r="AG21" s="5" t="n"/>
-      <c r="AH21" s="5" t="n"/>
-      <c r="AI21" s="5" t="n"/>
-      <c r="AJ21" s="5" t="n"/>
-      <c r="AK21" s="5" t="n"/>
-      <c r="AL21" s="5" t="n"/>
-      <c r="AM21" s="6" t="n"/>
-      <c r="AN21" s="37" t="inlineStr">
+      <c r="L21" s="271" t="n"/>
+      <c r="M21" s="271" t="n"/>
+      <c r="N21" s="271" t="n"/>
+      <c r="O21" s="271" t="n"/>
+      <c r="P21" s="271" t="n"/>
+      <c r="Q21" s="271" t="n"/>
+      <c r="R21" s="271" t="n"/>
+      <c r="S21" s="271" t="n"/>
+      <c r="T21" s="271" t="n"/>
+      <c r="U21" s="271" t="n"/>
+      <c r="V21" s="271" t="n"/>
+      <c r="W21" s="271" t="n"/>
+      <c r="X21" s="271" t="n"/>
+      <c r="Y21" s="271" t="n"/>
+      <c r="Z21" s="271" t="n"/>
+      <c r="AA21" s="271" t="n"/>
+      <c r="AB21" s="271" t="n"/>
+      <c r="AC21" s="271" t="n"/>
+      <c r="AD21" s="271" t="n"/>
+      <c r="AE21" s="271" t="n"/>
+      <c r="AF21" s="271" t="n"/>
+      <c r="AG21" s="271" t="n"/>
+      <c r="AH21" s="271" t="n"/>
+      <c r="AI21" s="271" t="n"/>
+      <c r="AJ21" s="271" t="n"/>
+      <c r="AK21" s="271" t="n"/>
+      <c r="AL21" s="271" t="n"/>
+      <c r="AM21" s="272" t="n"/>
+      <c r="AN21" s="302" t="inlineStr">
         <is>
           <t>Evidence / Acceptance Criteria</t>
         </is>
       </c>
-      <c r="AO21" s="5" t="n"/>
-      <c r="AP21" s="5" t="n"/>
-      <c r="AQ21" s="5" t="n"/>
-      <c r="AR21" s="5" t="n"/>
-      <c r="AS21" s="5" t="n"/>
-      <c r="AT21" s="5" t="n"/>
-      <c r="AU21" s="5" t="n"/>
-      <c r="AV21" s="5" t="n"/>
-      <c r="AW21" s="5" t="n"/>
-      <c r="AX21" s="5" t="n"/>
-      <c r="AY21" s="5" t="n"/>
-      <c r="AZ21" s="5" t="n"/>
-      <c r="BA21" s="5" t="n"/>
-      <c r="BB21" s="5" t="n"/>
-      <c r="BC21" s="5" t="n"/>
-      <c r="BD21" s="5" t="n"/>
-      <c r="BE21" s="5" t="n"/>
-      <c r="BF21" s="5" t="n"/>
-      <c r="BG21" s="5" t="n"/>
-      <c r="BH21" s="5" t="n"/>
-      <c r="BI21" s="5" t="n"/>
-      <c r="BJ21" s="5" t="n"/>
-      <c r="BK21" s="5" t="n"/>
-      <c r="BL21" s="6" t="n"/>
-      <c r="BM21" s="37" t="inlineStr">
+      <c r="AO21" s="271" t="n"/>
+      <c r="AP21" s="271" t="n"/>
+      <c r="AQ21" s="271" t="n"/>
+      <c r="AR21" s="271" t="n"/>
+      <c r="AS21" s="271" t="n"/>
+      <c r="AT21" s="271" t="n"/>
+      <c r="AU21" s="271" t="n"/>
+      <c r="AV21" s="271" t="n"/>
+      <c r="AW21" s="271" t="n"/>
+      <c r="AX21" s="271" t="n"/>
+      <c r="AY21" s="271" t="n"/>
+      <c r="AZ21" s="271" t="n"/>
+      <c r="BA21" s="271" t="n"/>
+      <c r="BB21" s="271" t="n"/>
+      <c r="BC21" s="271" t="n"/>
+      <c r="BD21" s="271" t="n"/>
+      <c r="BE21" s="271" t="n"/>
+      <c r="BF21" s="271" t="n"/>
+      <c r="BG21" s="271" t="n"/>
+      <c r="BH21" s="271" t="n"/>
+      <c r="BI21" s="271" t="n"/>
+      <c r="BJ21" s="271" t="n"/>
+      <c r="BK21" s="271" t="n"/>
+      <c r="BL21" s="272" t="n"/>
+      <c r="BM21" s="302" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="BN21" s="5" t="n"/>
-      <c r="BO21" s="5" t="n"/>
-      <c r="BP21" s="5" t="n"/>
-      <c r="BQ21" s="5" t="n"/>
-      <c r="BR21" s="5" t="n"/>
-      <c r="BS21" s="5" t="n"/>
-      <c r="BT21" s="6" t="n"/>
-      <c r="BU21" s="37" t="inlineStr">
+      <c r="BN21" s="271" t="n"/>
+      <c r="BO21" s="271" t="n"/>
+      <c r="BP21" s="271" t="n"/>
+      <c r="BQ21" s="271" t="n"/>
+      <c r="BR21" s="271" t="n"/>
+      <c r="BS21" s="271" t="n"/>
+      <c r="BT21" s="272" t="n"/>
+      <c r="BU21" s="302" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="BV21" s="5" t="n"/>
-      <c r="BW21" s="5" t="n"/>
-      <c r="BX21" s="5" t="n"/>
-      <c r="BY21" s="5" t="n"/>
-      <c r="BZ21" s="6" t="n"/>
-      <c r="CA21" s="37" t="inlineStr">
+      <c r="BV21" s="271" t="n"/>
+      <c r="BW21" s="271" t="n"/>
+      <c r="BX21" s="271" t="n"/>
+      <c r="BY21" s="271" t="n"/>
+      <c r="BZ21" s="272" t="n"/>
+      <c r="CA21" s="303" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="CB21" s="5" t="n"/>
-      <c r="CC21" s="5" t="n"/>
-      <c r="CD21" s="8" t="n"/>
+      <c r="CB21" s="271" t="n"/>
+      <c r="CC21" s="271" t="n"/>
+      <c r="CD21" s="274" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="688" t="n">
+      <c r="A22" s="794" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="689" t="inlineStr">
+      <c r="B22" s="271" t="n"/>
+      <c r="C22" s="271" t="n"/>
+      <c r="D22" s="272" t="n"/>
+      <c r="E22" s="795" t="inlineStr">
         <is>
           <t>BAS</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="690" t="inlineStr">
+      <c r="F22" s="271" t="n"/>
+      <c r="G22" s="271" t="n"/>
+      <c r="H22" s="271" t="n"/>
+      <c r="I22" s="271" t="n"/>
+      <c r="J22" s="272" t="n"/>
+      <c r="K22" s="796" t="inlineStr">
         <is>
           <t>Released baseline and revision are current.</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-      <c r="Y22" s="5" t="n"/>
-      <c r="Z22" s="5" t="n"/>
-      <c r="AA22" s="5" t="n"/>
-      <c r="AB22" s="5" t="n"/>
-      <c r="AC22" s="5" t="n"/>
-      <c r="AD22" s="5" t="n"/>
-      <c r="AE22" s="5" t="n"/>
-      <c r="AF22" s="5" t="n"/>
-      <c r="AG22" s="5" t="n"/>
-      <c r="AH22" s="5" t="n"/>
-      <c r="AI22" s="5" t="n"/>
-      <c r="AJ22" s="5" t="n"/>
-      <c r="AK22" s="5" t="n"/>
-      <c r="AL22" s="5" t="n"/>
-      <c r="AM22" s="6" t="n"/>
-      <c r="AN22" s="691" t="inlineStr">
+      <c r="L22" s="271" t="n"/>
+      <c r="M22" s="271" t="n"/>
+      <c r="N22" s="271" t="n"/>
+      <c r="O22" s="271" t="n"/>
+      <c r="P22" s="271" t="n"/>
+      <c r="Q22" s="271" t="n"/>
+      <c r="R22" s="271" t="n"/>
+      <c r="S22" s="271" t="n"/>
+      <c r="T22" s="271" t="n"/>
+      <c r="U22" s="271" t="n"/>
+      <c r="V22" s="271" t="n"/>
+      <c r="W22" s="271" t="n"/>
+      <c r="X22" s="271" t="n"/>
+      <c r="Y22" s="271" t="n"/>
+      <c r="Z22" s="271" t="n"/>
+      <c r="AA22" s="271" t="n"/>
+      <c r="AB22" s="271" t="n"/>
+      <c r="AC22" s="271" t="n"/>
+      <c r="AD22" s="271" t="n"/>
+      <c r="AE22" s="271" t="n"/>
+      <c r="AF22" s="271" t="n"/>
+      <c r="AG22" s="271" t="n"/>
+      <c r="AH22" s="271" t="n"/>
+      <c r="AI22" s="271" t="n"/>
+      <c r="AJ22" s="271" t="n"/>
+      <c r="AK22" s="271" t="n"/>
+      <c r="AL22" s="271" t="n"/>
+      <c r="AM22" s="272" t="n"/>
+      <c r="AN22" s="797" t="inlineStr">
         <is>
           <t>FAI is performed against the correct released package.</t>
         </is>
       </c>
-      <c r="AO22" s="5" t="n"/>
-      <c r="AP22" s="5" t="n"/>
-      <c r="AQ22" s="5" t="n"/>
-      <c r="AR22" s="5" t="n"/>
-      <c r="AS22" s="5" t="n"/>
-      <c r="AT22" s="5" t="n"/>
-      <c r="AU22" s="5" t="n"/>
-      <c r="AV22" s="5" t="n"/>
-      <c r="AW22" s="5" t="n"/>
-      <c r="AX22" s="5" t="n"/>
-      <c r="AY22" s="5" t="n"/>
-      <c r="AZ22" s="5" t="n"/>
-      <c r="BA22" s="5" t="n"/>
-      <c r="BB22" s="5" t="n"/>
-      <c r="BC22" s="5" t="n"/>
-      <c r="BD22" s="5" t="n"/>
-      <c r="BE22" s="5" t="n"/>
-      <c r="BF22" s="5" t="n"/>
-      <c r="BG22" s="5" t="n"/>
-      <c r="BH22" s="5" t="n"/>
-      <c r="BI22" s="5" t="n"/>
-      <c r="BJ22" s="5" t="n"/>
-      <c r="BK22" s="5" t="n"/>
-      <c r="BL22" s="6" t="n"/>
-      <c r="BM22" s="690" t="n"/>
-      <c r="BN22" s="5" t="n"/>
-      <c r="BO22" s="5" t="n"/>
-      <c r="BP22" s="5" t="n"/>
-      <c r="BQ22" s="5" t="n"/>
-      <c r="BR22" s="5" t="n"/>
-      <c r="BS22" s="5" t="n"/>
-      <c r="BT22" s="6" t="n"/>
-      <c r="BU22" s="690" t="n"/>
-      <c r="BV22" s="5" t="n"/>
-      <c r="BW22" s="5" t="n"/>
-      <c r="BX22" s="5" t="n"/>
-      <c r="BY22" s="5" t="n"/>
-      <c r="BZ22" s="6" t="n"/>
-      <c r="CA22" s="690" t="n"/>
-      <c r="CB22" s="5" t="n"/>
-      <c r="CC22" s="5" t="n"/>
-      <c r="CD22" s="8" t="n"/>
+      <c r="AO22" s="271" t="n"/>
+      <c r="AP22" s="271" t="n"/>
+      <c r="AQ22" s="271" t="n"/>
+      <c r="AR22" s="271" t="n"/>
+      <c r="AS22" s="271" t="n"/>
+      <c r="AT22" s="271" t="n"/>
+      <c r="AU22" s="271" t="n"/>
+      <c r="AV22" s="271" t="n"/>
+      <c r="AW22" s="271" t="n"/>
+      <c r="AX22" s="271" t="n"/>
+      <c r="AY22" s="271" t="n"/>
+      <c r="AZ22" s="271" t="n"/>
+      <c r="BA22" s="271" t="n"/>
+      <c r="BB22" s="271" t="n"/>
+      <c r="BC22" s="271" t="n"/>
+      <c r="BD22" s="271" t="n"/>
+      <c r="BE22" s="271" t="n"/>
+      <c r="BF22" s="271" t="n"/>
+      <c r="BG22" s="271" t="n"/>
+      <c r="BH22" s="271" t="n"/>
+      <c r="BI22" s="271" t="n"/>
+      <c r="BJ22" s="271" t="n"/>
+      <c r="BK22" s="271" t="n"/>
+      <c r="BL22" s="272" t="n"/>
+      <c r="BM22" s="796" t="n"/>
+      <c r="BN22" s="271" t="n"/>
+      <c r="BO22" s="271" t="n"/>
+      <c r="BP22" s="271" t="n"/>
+      <c r="BQ22" s="271" t="n"/>
+      <c r="BR22" s="271" t="n"/>
+      <c r="BS22" s="271" t="n"/>
+      <c r="BT22" s="272" t="n"/>
+      <c r="BU22" s="796" t="n"/>
+      <c r="BV22" s="271" t="n"/>
+      <c r="BW22" s="271" t="n"/>
+      <c r="BX22" s="271" t="n"/>
+      <c r="BY22" s="271" t="n"/>
+      <c r="BZ22" s="272" t="n"/>
+      <c r="CA22" s="798" t="n"/>
+      <c r="CB22" s="271" t="n"/>
+      <c r="CC22" s="271" t="n"/>
+      <c r="CD22" s="274" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="692" t="n">
+      <c r="A23" s="799" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="693" t="inlineStr">
+      <c r="B23" s="277" t="n"/>
+      <c r="C23" s="277" t="n"/>
+      <c r="D23" s="278" t="n"/>
+      <c r="E23" s="309" t="inlineStr">
         <is>
           <t>CHR</t>
         </is>
       </c>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="694" t="inlineStr">
+      <c r="F23" s="277" t="n"/>
+      <c r="G23" s="277" t="n"/>
+      <c r="H23" s="277" t="n"/>
+      <c r="I23" s="277" t="n"/>
+      <c r="J23" s="278" t="n"/>
+      <c r="K23" s="310" t="inlineStr">
         <is>
           <t>Characteristic list is complete and traceable.</t>
         </is>
       </c>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="12" t="n"/>
-      <c r="R23" s="12" t="n"/>
-      <c r="S23" s="12" t="n"/>
-      <c r="T23" s="12" t="n"/>
-      <c r="U23" s="12" t="n"/>
-      <c r="V23" s="12" t="n"/>
-      <c r="W23" s="12" t="n"/>
-      <c r="X23" s="12" t="n"/>
-      <c r="Y23" s="12" t="n"/>
-      <c r="Z23" s="12" t="n"/>
-      <c r="AA23" s="12" t="n"/>
-      <c r="AB23" s="12" t="n"/>
-      <c r="AC23" s="12" t="n"/>
-      <c r="AD23" s="12" t="n"/>
-      <c r="AE23" s="12" t="n"/>
-      <c r="AF23" s="12" t="n"/>
-      <c r="AG23" s="12" t="n"/>
-      <c r="AH23" s="12" t="n"/>
-      <c r="AI23" s="12" t="n"/>
-      <c r="AJ23" s="12" t="n"/>
-      <c r="AK23" s="12" t="n"/>
-      <c r="AL23" s="12" t="n"/>
-      <c r="AM23" s="13" t="n"/>
-      <c r="AN23" s="695" t="inlineStr">
+      <c r="L23" s="277" t="n"/>
+      <c r="M23" s="277" t="n"/>
+      <c r="N23" s="277" t="n"/>
+      <c r="O23" s="277" t="n"/>
+      <c r="P23" s="277" t="n"/>
+      <c r="Q23" s="277" t="n"/>
+      <c r="R23" s="277" t="n"/>
+      <c r="S23" s="277" t="n"/>
+      <c r="T23" s="277" t="n"/>
+      <c r="U23" s="277" t="n"/>
+      <c r="V23" s="277" t="n"/>
+      <c r="W23" s="277" t="n"/>
+      <c r="X23" s="277" t="n"/>
+      <c r="Y23" s="277" t="n"/>
+      <c r="Z23" s="277" t="n"/>
+      <c r="AA23" s="277" t="n"/>
+      <c r="AB23" s="277" t="n"/>
+      <c r="AC23" s="277" t="n"/>
+      <c r="AD23" s="277" t="n"/>
+      <c r="AE23" s="277" t="n"/>
+      <c r="AF23" s="277" t="n"/>
+      <c r="AG23" s="277" t="n"/>
+      <c r="AH23" s="277" t="n"/>
+      <c r="AI23" s="277" t="n"/>
+      <c r="AJ23" s="277" t="n"/>
+      <c r="AK23" s="277" t="n"/>
+      <c r="AL23" s="277" t="n"/>
+      <c r="AM23" s="278" t="n"/>
+      <c r="AN23" s="307" t="inlineStr">
         <is>
           <t>Balloon or requirement linkage is unique.</t>
         </is>
       </c>
-      <c r="AO23" s="12" t="n"/>
-      <c r="AP23" s="12" t="n"/>
-      <c r="AQ23" s="12" t="n"/>
-      <c r="AR23" s="12" t="n"/>
-      <c r="AS23" s="12" t="n"/>
-      <c r="AT23" s="12" t="n"/>
-      <c r="AU23" s="12" t="n"/>
-      <c r="AV23" s="12" t="n"/>
-      <c r="AW23" s="12" t="n"/>
-      <c r="AX23" s="12" t="n"/>
-      <c r="AY23" s="12" t="n"/>
-      <c r="AZ23" s="12" t="n"/>
-      <c r="BA23" s="12" t="n"/>
-      <c r="BB23" s="12" t="n"/>
-      <c r="BC23" s="12" t="n"/>
-      <c r="BD23" s="12" t="n"/>
-      <c r="BE23" s="12" t="n"/>
-      <c r="BF23" s="12" t="n"/>
-      <c r="BG23" s="12" t="n"/>
-      <c r="BH23" s="12" t="n"/>
-      <c r="BI23" s="12" t="n"/>
-      <c r="BJ23" s="12" t="n"/>
-      <c r="BK23" s="12" t="n"/>
-      <c r="BL23" s="13" t="n"/>
-      <c r="BM23" s="696" t="n"/>
-      <c r="BN23" s="12" t="n"/>
-      <c r="BO23" s="12" t="n"/>
-      <c r="BP23" s="12" t="n"/>
-      <c r="BQ23" s="12" t="n"/>
-      <c r="BR23" s="12" t="n"/>
-      <c r="BS23" s="12" t="n"/>
-      <c r="BT23" s="13" t="n"/>
-      <c r="BU23" s="696" t="n"/>
-      <c r="BV23" s="12" t="n"/>
-      <c r="BW23" s="12" t="n"/>
-      <c r="BX23" s="12" t="n"/>
-      <c r="BY23" s="12" t="n"/>
-      <c r="BZ23" s="13" t="n"/>
-      <c r="CA23" s="696" t="n"/>
-      <c r="CB23" s="12" t="n"/>
-      <c r="CC23" s="12" t="n"/>
-      <c r="CD23" s="15" t="n"/>
+      <c r="AO23" s="277" t="n"/>
+      <c r="AP23" s="277" t="n"/>
+      <c r="AQ23" s="277" t="n"/>
+      <c r="AR23" s="277" t="n"/>
+      <c r="AS23" s="277" t="n"/>
+      <c r="AT23" s="277" t="n"/>
+      <c r="AU23" s="277" t="n"/>
+      <c r="AV23" s="277" t="n"/>
+      <c r="AW23" s="277" t="n"/>
+      <c r="AX23" s="277" t="n"/>
+      <c r="AY23" s="277" t="n"/>
+      <c r="AZ23" s="277" t="n"/>
+      <c r="BA23" s="277" t="n"/>
+      <c r="BB23" s="277" t="n"/>
+      <c r="BC23" s="277" t="n"/>
+      <c r="BD23" s="277" t="n"/>
+      <c r="BE23" s="277" t="n"/>
+      <c r="BF23" s="277" t="n"/>
+      <c r="BG23" s="277" t="n"/>
+      <c r="BH23" s="277" t="n"/>
+      <c r="BI23" s="277" t="n"/>
+      <c r="BJ23" s="277" t="n"/>
+      <c r="BK23" s="277" t="n"/>
+      <c r="BL23" s="278" t="n"/>
+      <c r="BM23" s="306" t="n"/>
+      <c r="BN23" s="277" t="n"/>
+      <c r="BO23" s="277" t="n"/>
+      <c r="BP23" s="277" t="n"/>
+      <c r="BQ23" s="277" t="n"/>
+      <c r="BR23" s="277" t="n"/>
+      <c r="BS23" s="277" t="n"/>
+      <c r="BT23" s="278" t="n"/>
+      <c r="BU23" s="306" t="n"/>
+      <c r="BV23" s="277" t="n"/>
+      <c r="BW23" s="277" t="n"/>
+      <c r="BX23" s="277" t="n"/>
+      <c r="BY23" s="277" t="n"/>
+      <c r="BZ23" s="278" t="n"/>
+      <c r="CA23" s="800" t="n"/>
+      <c r="CB23" s="277" t="n"/>
+      <c r="CC23" s="277" t="n"/>
+      <c r="CD23" s="280" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="692" t="n">
+      <c r="A24" s="799" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="697" t="inlineStr">
+      <c r="B24" s="277" t="n"/>
+      <c r="C24" s="277" t="n"/>
+      <c r="D24" s="278" t="n"/>
+      <c r="E24" s="311" t="inlineStr">
         <is>
           <t>PRG</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="696" t="inlineStr">
+      <c r="F24" s="277" t="n"/>
+      <c r="G24" s="277" t="n"/>
+      <c r="H24" s="277" t="n"/>
+      <c r="I24" s="277" t="n"/>
+      <c r="J24" s="278" t="n"/>
+      <c r="K24" s="306" t="inlineStr">
         <is>
           <t>Inspection program / method is aligned.</t>
         </is>
       </c>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="12" t="n"/>
-      <c r="R24" s="12" t="n"/>
-      <c r="S24" s="12" t="n"/>
-      <c r="T24" s="12" t="n"/>
-      <c r="U24" s="12" t="n"/>
-      <c r="V24" s="12" t="n"/>
-      <c r="W24" s="12" t="n"/>
-      <c r="X24" s="12" t="n"/>
-      <c r="Y24" s="12" t="n"/>
-      <c r="Z24" s="12" t="n"/>
-      <c r="AA24" s="12" t="n"/>
-      <c r="AB24" s="12" t="n"/>
-      <c r="AC24" s="12" t="n"/>
-      <c r="AD24" s="12" t="n"/>
-      <c r="AE24" s="12" t="n"/>
-      <c r="AF24" s="12" t="n"/>
-      <c r="AG24" s="12" t="n"/>
-      <c r="AH24" s="12" t="n"/>
-      <c r="AI24" s="12" t="n"/>
-      <c r="AJ24" s="12" t="n"/>
-      <c r="AK24" s="12" t="n"/>
-      <c r="AL24" s="12" t="n"/>
-      <c r="AM24" s="13" t="n"/>
-      <c r="AN24" s="695" t="inlineStr">
+      <c r="L24" s="277" t="n"/>
+      <c r="M24" s="277" t="n"/>
+      <c r="N24" s="277" t="n"/>
+      <c r="O24" s="277" t="n"/>
+      <c r="P24" s="277" t="n"/>
+      <c r="Q24" s="277" t="n"/>
+      <c r="R24" s="277" t="n"/>
+      <c r="S24" s="277" t="n"/>
+      <c r="T24" s="277" t="n"/>
+      <c r="U24" s="277" t="n"/>
+      <c r="V24" s="277" t="n"/>
+      <c r="W24" s="277" t="n"/>
+      <c r="X24" s="277" t="n"/>
+      <c r="Y24" s="277" t="n"/>
+      <c r="Z24" s="277" t="n"/>
+      <c r="AA24" s="277" t="n"/>
+      <c r="AB24" s="277" t="n"/>
+      <c r="AC24" s="277" t="n"/>
+      <c r="AD24" s="277" t="n"/>
+      <c r="AE24" s="277" t="n"/>
+      <c r="AF24" s="277" t="n"/>
+      <c r="AG24" s="277" t="n"/>
+      <c r="AH24" s="277" t="n"/>
+      <c r="AI24" s="277" t="n"/>
+      <c r="AJ24" s="277" t="n"/>
+      <c r="AK24" s="277" t="n"/>
+      <c r="AL24" s="277" t="n"/>
+      <c r="AM24" s="278" t="n"/>
+      <c r="AN24" s="307" t="inlineStr">
         <is>
           <t>Method / program rev matches the baseline.</t>
         </is>
       </c>
-      <c r="AO24" s="12" t="n"/>
-      <c r="AP24" s="12" t="n"/>
-      <c r="AQ24" s="12" t="n"/>
-      <c r="AR24" s="12" t="n"/>
-      <c r="AS24" s="12" t="n"/>
-      <c r="AT24" s="12" t="n"/>
-      <c r="AU24" s="12" t="n"/>
-      <c r="AV24" s="12" t="n"/>
-      <c r="AW24" s="12" t="n"/>
-      <c r="AX24" s="12" t="n"/>
-      <c r="AY24" s="12" t="n"/>
-      <c r="AZ24" s="12" t="n"/>
-      <c r="BA24" s="12" t="n"/>
-      <c r="BB24" s="12" t="n"/>
-      <c r="BC24" s="12" t="n"/>
-      <c r="BD24" s="12" t="n"/>
-      <c r="BE24" s="12" t="n"/>
-      <c r="BF24" s="12" t="n"/>
-      <c r="BG24" s="12" t="n"/>
-      <c r="BH24" s="12" t="n"/>
-      <c r="BI24" s="12" t="n"/>
-      <c r="BJ24" s="12" t="n"/>
-      <c r="BK24" s="12" t="n"/>
-      <c r="BL24" s="13" t="n"/>
-      <c r="BM24" s="696" t="n"/>
-      <c r="BN24" s="12" t="n"/>
-      <c r="BO24" s="12" t="n"/>
-      <c r="BP24" s="12" t="n"/>
-      <c r="BQ24" s="12" t="n"/>
-      <c r="BR24" s="12" t="n"/>
-      <c r="BS24" s="12" t="n"/>
-      <c r="BT24" s="13" t="n"/>
-      <c r="BU24" s="696" t="n"/>
-      <c r="BV24" s="12" t="n"/>
-      <c r="BW24" s="12" t="n"/>
-      <c r="BX24" s="12" t="n"/>
-      <c r="BY24" s="12" t="n"/>
-      <c r="BZ24" s="13" t="n"/>
-      <c r="CA24" s="696" t="n"/>
-      <c r="CB24" s="12" t="n"/>
-      <c r="CC24" s="12" t="n"/>
-      <c r="CD24" s="15" t="n"/>
+      <c r="AO24" s="277" t="n"/>
+      <c r="AP24" s="277" t="n"/>
+      <c r="AQ24" s="277" t="n"/>
+      <c r="AR24" s="277" t="n"/>
+      <c r="AS24" s="277" t="n"/>
+      <c r="AT24" s="277" t="n"/>
+      <c r="AU24" s="277" t="n"/>
+      <c r="AV24" s="277" t="n"/>
+      <c r="AW24" s="277" t="n"/>
+      <c r="AX24" s="277" t="n"/>
+      <c r="AY24" s="277" t="n"/>
+      <c r="AZ24" s="277" t="n"/>
+      <c r="BA24" s="277" t="n"/>
+      <c r="BB24" s="277" t="n"/>
+      <c r="BC24" s="277" t="n"/>
+      <c r="BD24" s="277" t="n"/>
+      <c r="BE24" s="277" t="n"/>
+      <c r="BF24" s="277" t="n"/>
+      <c r="BG24" s="277" t="n"/>
+      <c r="BH24" s="277" t="n"/>
+      <c r="BI24" s="277" t="n"/>
+      <c r="BJ24" s="277" t="n"/>
+      <c r="BK24" s="277" t="n"/>
+      <c r="BL24" s="278" t="n"/>
+      <c r="BM24" s="306" t="n"/>
+      <c r="BN24" s="277" t="n"/>
+      <c r="BO24" s="277" t="n"/>
+      <c r="BP24" s="277" t="n"/>
+      <c r="BQ24" s="277" t="n"/>
+      <c r="BR24" s="277" t="n"/>
+      <c r="BS24" s="277" t="n"/>
+      <c r="BT24" s="278" t="n"/>
+      <c r="BU24" s="306" t="n"/>
+      <c r="BV24" s="277" t="n"/>
+      <c r="BW24" s="277" t="n"/>
+      <c r="BX24" s="277" t="n"/>
+      <c r="BY24" s="277" t="n"/>
+      <c r="BZ24" s="278" t="n"/>
+      <c r="CA24" s="800" t="n"/>
+      <c r="CB24" s="277" t="n"/>
+      <c r="CC24" s="277" t="n"/>
+      <c r="CD24" s="280" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="692" t="n">
+      <c r="A25" s="799" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="698" t="inlineStr">
+      <c r="B25" s="277" t="n"/>
+      <c r="C25" s="277" t="n"/>
+      <c r="D25" s="278" t="n"/>
+      <c r="E25" s="312" t="inlineStr">
         <is>
           <t>MAT</t>
         </is>
       </c>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="694" t="inlineStr">
+      <c r="F25" s="277" t="n"/>
+      <c r="G25" s="277" t="n"/>
+      <c r="H25" s="277" t="n"/>
+      <c r="I25" s="277" t="n"/>
+      <c r="J25" s="278" t="n"/>
+      <c r="K25" s="310" t="inlineStr">
         <is>
           <t>Material and process evidence are available.</t>
         </is>
       </c>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="12" t="n"/>
-      <c r="R25" s="12" t="n"/>
-      <c r="S25" s="12" t="n"/>
-      <c r="T25" s="12" t="n"/>
-      <c r="U25" s="12" t="n"/>
-      <c r="V25" s="12" t="n"/>
-      <c r="W25" s="12" t="n"/>
-      <c r="X25" s="12" t="n"/>
-      <c r="Y25" s="12" t="n"/>
-      <c r="Z25" s="12" t="n"/>
-      <c r="AA25" s="12" t="n"/>
-      <c r="AB25" s="12" t="n"/>
-      <c r="AC25" s="12" t="n"/>
-      <c r="AD25" s="12" t="n"/>
-      <c r="AE25" s="12" t="n"/>
-      <c r="AF25" s="12" t="n"/>
-      <c r="AG25" s="12" t="n"/>
-      <c r="AH25" s="12" t="n"/>
-      <c r="AI25" s="12" t="n"/>
-      <c r="AJ25" s="12" t="n"/>
-      <c r="AK25" s="12" t="n"/>
-      <c r="AL25" s="12" t="n"/>
-      <c r="AM25" s="13" t="n"/>
-      <c r="AN25" s="695" t="inlineStr">
+      <c r="L25" s="277" t="n"/>
+      <c r="M25" s="277" t="n"/>
+      <c r="N25" s="277" t="n"/>
+      <c r="O25" s="277" t="n"/>
+      <c r="P25" s="277" t="n"/>
+      <c r="Q25" s="277" t="n"/>
+      <c r="R25" s="277" t="n"/>
+      <c r="S25" s="277" t="n"/>
+      <c r="T25" s="277" t="n"/>
+      <c r="U25" s="277" t="n"/>
+      <c r="V25" s="277" t="n"/>
+      <c r="W25" s="277" t="n"/>
+      <c r="X25" s="277" t="n"/>
+      <c r="Y25" s="277" t="n"/>
+      <c r="Z25" s="277" t="n"/>
+      <c r="AA25" s="277" t="n"/>
+      <c r="AB25" s="277" t="n"/>
+      <c r="AC25" s="277" t="n"/>
+      <c r="AD25" s="277" t="n"/>
+      <c r="AE25" s="277" t="n"/>
+      <c r="AF25" s="277" t="n"/>
+      <c r="AG25" s="277" t="n"/>
+      <c r="AH25" s="277" t="n"/>
+      <c r="AI25" s="277" t="n"/>
+      <c r="AJ25" s="277" t="n"/>
+      <c r="AK25" s="277" t="n"/>
+      <c r="AL25" s="277" t="n"/>
+      <c r="AM25" s="278" t="n"/>
+      <c r="AN25" s="307" t="inlineStr">
         <is>
           <t>Certifications or special-process evidence are linked.</t>
         </is>
       </c>
-      <c r="AO25" s="12" t="n"/>
-      <c r="AP25" s="12" t="n"/>
-      <c r="AQ25" s="12" t="n"/>
-      <c r="AR25" s="12" t="n"/>
-      <c r="AS25" s="12" t="n"/>
-      <c r="AT25" s="12" t="n"/>
-      <c r="AU25" s="12" t="n"/>
-      <c r="AV25" s="12" t="n"/>
-      <c r="AW25" s="12" t="n"/>
-      <c r="AX25" s="12" t="n"/>
-      <c r="AY25" s="12" t="n"/>
-      <c r="AZ25" s="12" t="n"/>
-      <c r="BA25" s="12" t="n"/>
-      <c r="BB25" s="12" t="n"/>
-      <c r="BC25" s="12" t="n"/>
-      <c r="BD25" s="12" t="n"/>
-      <c r="BE25" s="12" t="n"/>
-      <c r="BF25" s="12" t="n"/>
-      <c r="BG25" s="12" t="n"/>
-      <c r="BH25" s="12" t="n"/>
-      <c r="BI25" s="12" t="n"/>
-      <c r="BJ25" s="12" t="n"/>
-      <c r="BK25" s="12" t="n"/>
-      <c r="BL25" s="13" t="n"/>
-      <c r="BM25" s="696" t="n"/>
-      <c r="BN25" s="12" t="n"/>
-      <c r="BO25" s="12" t="n"/>
-      <c r="BP25" s="12" t="n"/>
-      <c r="BQ25" s="12" t="n"/>
-      <c r="BR25" s="12" t="n"/>
-      <c r="BS25" s="12" t="n"/>
-      <c r="BT25" s="13" t="n"/>
-      <c r="BU25" s="696" t="n"/>
-      <c r="BV25" s="12" t="n"/>
-      <c r="BW25" s="12" t="n"/>
-      <c r="BX25" s="12" t="n"/>
-      <c r="BY25" s="12" t="n"/>
-      <c r="BZ25" s="13" t="n"/>
-      <c r="CA25" s="696" t="n"/>
-      <c r="CB25" s="12" t="n"/>
-      <c r="CC25" s="12" t="n"/>
-      <c r="CD25" s="15" t="n"/>
+      <c r="AO25" s="277" t="n"/>
+      <c r="AP25" s="277" t="n"/>
+      <c r="AQ25" s="277" t="n"/>
+      <c r="AR25" s="277" t="n"/>
+      <c r="AS25" s="277" t="n"/>
+      <c r="AT25" s="277" t="n"/>
+      <c r="AU25" s="277" t="n"/>
+      <c r="AV25" s="277" t="n"/>
+      <c r="AW25" s="277" t="n"/>
+      <c r="AX25" s="277" t="n"/>
+      <c r="AY25" s="277" t="n"/>
+      <c r="AZ25" s="277" t="n"/>
+      <c r="BA25" s="277" t="n"/>
+      <c r="BB25" s="277" t="n"/>
+      <c r="BC25" s="277" t="n"/>
+      <c r="BD25" s="277" t="n"/>
+      <c r="BE25" s="277" t="n"/>
+      <c r="BF25" s="277" t="n"/>
+      <c r="BG25" s="277" t="n"/>
+      <c r="BH25" s="277" t="n"/>
+      <c r="BI25" s="277" t="n"/>
+      <c r="BJ25" s="277" t="n"/>
+      <c r="BK25" s="277" t="n"/>
+      <c r="BL25" s="278" t="n"/>
+      <c r="BM25" s="306" t="n"/>
+      <c r="BN25" s="277" t="n"/>
+      <c r="BO25" s="277" t="n"/>
+      <c r="BP25" s="277" t="n"/>
+      <c r="BQ25" s="277" t="n"/>
+      <c r="BR25" s="277" t="n"/>
+      <c r="BS25" s="277" t="n"/>
+      <c r="BT25" s="278" t="n"/>
+      <c r="BU25" s="306" t="n"/>
+      <c r="BV25" s="277" t="n"/>
+      <c r="BW25" s="277" t="n"/>
+      <c r="BX25" s="277" t="n"/>
+      <c r="BY25" s="277" t="n"/>
+      <c r="BZ25" s="278" t="n"/>
+      <c r="CA25" s="800" t="n"/>
+      <c r="CB25" s="277" t="n"/>
+      <c r="CC25" s="277" t="n"/>
+      <c r="CD25" s="280" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="692" t="n">
+      <c r="A26" s="799" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="699" t="inlineStr">
+      <c r="B26" s="277" t="n"/>
+      <c r="C26" s="277" t="n"/>
+      <c r="D26" s="278" t="n"/>
+      <c r="E26" s="313" t="inlineStr">
         <is>
           <t>GAG</t>
         </is>
       </c>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="696" t="inlineStr">
+      <c r="F26" s="277" t="n"/>
+      <c r="G26" s="277" t="n"/>
+      <c r="H26" s="277" t="n"/>
+      <c r="I26" s="277" t="n"/>
+      <c r="J26" s="278" t="n"/>
+      <c r="K26" s="306" t="inlineStr">
         <is>
           <t>Gages and measuring resources are verified.</t>
         </is>
       </c>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="12" t="n"/>
-      <c r="R26" s="12" t="n"/>
-      <c r="S26" s="12" t="n"/>
-      <c r="T26" s="12" t="n"/>
-      <c r="U26" s="12" t="n"/>
-      <c r="V26" s="12" t="n"/>
-      <c r="W26" s="12" t="n"/>
-      <c r="X26" s="12" t="n"/>
-      <c r="Y26" s="12" t="n"/>
-      <c r="Z26" s="12" t="n"/>
-      <c r="AA26" s="12" t="n"/>
-      <c r="AB26" s="12" t="n"/>
-      <c r="AC26" s="12" t="n"/>
-      <c r="AD26" s="12" t="n"/>
-      <c r="AE26" s="12" t="n"/>
-      <c r="AF26" s="12" t="n"/>
-      <c r="AG26" s="12" t="n"/>
-      <c r="AH26" s="12" t="n"/>
-      <c r="AI26" s="12" t="n"/>
-      <c r="AJ26" s="12" t="n"/>
-      <c r="AK26" s="12" t="n"/>
-      <c r="AL26" s="12" t="n"/>
-      <c r="AM26" s="13" t="n"/>
-      <c r="AN26" s="695" t="inlineStr">
+      <c r="L26" s="277" t="n"/>
+      <c r="M26" s="277" t="n"/>
+      <c r="N26" s="277" t="n"/>
+      <c r="O26" s="277" t="n"/>
+      <c r="P26" s="277" t="n"/>
+      <c r="Q26" s="277" t="n"/>
+      <c r="R26" s="277" t="n"/>
+      <c r="S26" s="277" t="n"/>
+      <c r="T26" s="277" t="n"/>
+      <c r="U26" s="277" t="n"/>
+      <c r="V26" s="277" t="n"/>
+      <c r="W26" s="277" t="n"/>
+      <c r="X26" s="277" t="n"/>
+      <c r="Y26" s="277" t="n"/>
+      <c r="Z26" s="277" t="n"/>
+      <c r="AA26" s="277" t="n"/>
+      <c r="AB26" s="277" t="n"/>
+      <c r="AC26" s="277" t="n"/>
+      <c r="AD26" s="277" t="n"/>
+      <c r="AE26" s="277" t="n"/>
+      <c r="AF26" s="277" t="n"/>
+      <c r="AG26" s="277" t="n"/>
+      <c r="AH26" s="277" t="n"/>
+      <c r="AI26" s="277" t="n"/>
+      <c r="AJ26" s="277" t="n"/>
+      <c r="AK26" s="277" t="n"/>
+      <c r="AL26" s="277" t="n"/>
+      <c r="AM26" s="278" t="n"/>
+      <c r="AN26" s="307" t="inlineStr">
         <is>
           <t>Measurement resources are current and suitable.</t>
         </is>
       </c>
-      <c r="AO26" s="12" t="n"/>
-      <c r="AP26" s="12" t="n"/>
-      <c r="AQ26" s="12" t="n"/>
-      <c r="AR26" s="12" t="n"/>
-      <c r="AS26" s="12" t="n"/>
-      <c r="AT26" s="12" t="n"/>
-      <c r="AU26" s="12" t="n"/>
-      <c r="AV26" s="12" t="n"/>
-      <c r="AW26" s="12" t="n"/>
-      <c r="AX26" s="12" t="n"/>
-      <c r="AY26" s="12" t="n"/>
-      <c r="AZ26" s="12" t="n"/>
-      <c r="BA26" s="12" t="n"/>
-      <c r="BB26" s="12" t="n"/>
-      <c r="BC26" s="12" t="n"/>
-      <c r="BD26" s="12" t="n"/>
-      <c r="BE26" s="12" t="n"/>
-      <c r="BF26" s="12" t="n"/>
-      <c r="BG26" s="12" t="n"/>
-      <c r="BH26" s="12" t="n"/>
-      <c r="BI26" s="12" t="n"/>
-      <c r="BJ26" s="12" t="n"/>
-      <c r="BK26" s="12" t="n"/>
-      <c r="BL26" s="13" t="n"/>
-      <c r="BM26" s="696" t="n"/>
-      <c r="BN26" s="12" t="n"/>
-      <c r="BO26" s="12" t="n"/>
-      <c r="BP26" s="12" t="n"/>
-      <c r="BQ26" s="12" t="n"/>
-      <c r="BR26" s="12" t="n"/>
-      <c r="BS26" s="12" t="n"/>
-      <c r="BT26" s="13" t="n"/>
-      <c r="BU26" s="696" t="n"/>
-      <c r="BV26" s="12" t="n"/>
-      <c r="BW26" s="12" t="n"/>
-      <c r="BX26" s="12" t="n"/>
-      <c r="BY26" s="12" t="n"/>
-      <c r="BZ26" s="13" t="n"/>
-      <c r="CA26" s="696" t="n"/>
-      <c r="CB26" s="12" t="n"/>
-      <c r="CC26" s="12" t="n"/>
-      <c r="CD26" s="15" t="n"/>
+      <c r="AO26" s="277" t="n"/>
+      <c r="AP26" s="277" t="n"/>
+      <c r="AQ26" s="277" t="n"/>
+      <c r="AR26" s="277" t="n"/>
+      <c r="AS26" s="277" t="n"/>
+      <c r="AT26" s="277" t="n"/>
+      <c r="AU26" s="277" t="n"/>
+      <c r="AV26" s="277" t="n"/>
+      <c r="AW26" s="277" t="n"/>
+      <c r="AX26" s="277" t="n"/>
+      <c r="AY26" s="277" t="n"/>
+      <c r="AZ26" s="277" t="n"/>
+      <c r="BA26" s="277" t="n"/>
+      <c r="BB26" s="277" t="n"/>
+      <c r="BC26" s="277" t="n"/>
+      <c r="BD26" s="277" t="n"/>
+      <c r="BE26" s="277" t="n"/>
+      <c r="BF26" s="277" t="n"/>
+      <c r="BG26" s="277" t="n"/>
+      <c r="BH26" s="277" t="n"/>
+      <c r="BI26" s="277" t="n"/>
+      <c r="BJ26" s="277" t="n"/>
+      <c r="BK26" s="277" t="n"/>
+      <c r="BL26" s="278" t="n"/>
+      <c r="BM26" s="306" t="n"/>
+      <c r="BN26" s="277" t="n"/>
+      <c r="BO26" s="277" t="n"/>
+      <c r="BP26" s="277" t="n"/>
+      <c r="BQ26" s="277" t="n"/>
+      <c r="BR26" s="277" t="n"/>
+      <c r="BS26" s="277" t="n"/>
+      <c r="BT26" s="278" t="n"/>
+      <c r="BU26" s="306" t="n"/>
+      <c r="BV26" s="277" t="n"/>
+      <c r="BW26" s="277" t="n"/>
+      <c r="BX26" s="277" t="n"/>
+      <c r="BY26" s="277" t="n"/>
+      <c r="BZ26" s="278" t="n"/>
+      <c r="CA26" s="800" t="n"/>
+      <c r="CB26" s="277" t="n"/>
+      <c r="CC26" s="277" t="n"/>
+      <c r="CD26" s="280" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="692" t="n">
+      <c r="A27" s="799" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="700" t="inlineStr">
+      <c r="B27" s="277" t="n"/>
+      <c r="C27" s="277" t="n"/>
+      <c r="D27" s="278" t="n"/>
+      <c r="E27" s="314" t="inlineStr">
         <is>
           <t>TRC</t>
         </is>
       </c>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="694" t="inlineStr">
+      <c r="F27" s="277" t="n"/>
+      <c r="G27" s="277" t="n"/>
+      <c r="H27" s="277" t="n"/>
+      <c r="I27" s="277" t="n"/>
+      <c r="J27" s="278" t="n"/>
+      <c r="K27" s="310" t="inlineStr">
         <is>
           <t>Sample / lot traceability is maintained.</t>
         </is>
       </c>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="12" t="n"/>
-      <c r="R27" s="12" t="n"/>
-      <c r="S27" s="12" t="n"/>
-      <c r="T27" s="12" t="n"/>
-      <c r="U27" s="12" t="n"/>
-      <c r="V27" s="12" t="n"/>
-      <c r="W27" s="12" t="n"/>
-      <c r="X27" s="12" t="n"/>
-      <c r="Y27" s="12" t="n"/>
-      <c r="Z27" s="12" t="n"/>
-      <c r="AA27" s="12" t="n"/>
-      <c r="AB27" s="12" t="n"/>
-      <c r="AC27" s="12" t="n"/>
-      <c r="AD27" s="12" t="n"/>
-      <c r="AE27" s="12" t="n"/>
-      <c r="AF27" s="12" t="n"/>
-      <c r="AG27" s="12" t="n"/>
-      <c r="AH27" s="12" t="n"/>
-      <c r="AI27" s="12" t="n"/>
-      <c r="AJ27" s="12" t="n"/>
-      <c r="AK27" s="12" t="n"/>
-      <c r="AL27" s="12" t="n"/>
-      <c r="AM27" s="13" t="n"/>
-      <c r="AN27" s="695" t="inlineStr">
+      <c r="L27" s="277" t="n"/>
+      <c r="M27" s="277" t="n"/>
+      <c r="N27" s="277" t="n"/>
+      <c r="O27" s="277" t="n"/>
+      <c r="P27" s="277" t="n"/>
+      <c r="Q27" s="277" t="n"/>
+      <c r="R27" s="277" t="n"/>
+      <c r="S27" s="277" t="n"/>
+      <c r="T27" s="277" t="n"/>
+      <c r="U27" s="277" t="n"/>
+      <c r="V27" s="277" t="n"/>
+      <c r="W27" s="277" t="n"/>
+      <c r="X27" s="277" t="n"/>
+      <c r="Y27" s="277" t="n"/>
+      <c r="Z27" s="277" t="n"/>
+      <c r="AA27" s="277" t="n"/>
+      <c r="AB27" s="277" t="n"/>
+      <c r="AC27" s="277" t="n"/>
+      <c r="AD27" s="277" t="n"/>
+      <c r="AE27" s="277" t="n"/>
+      <c r="AF27" s="277" t="n"/>
+      <c r="AG27" s="277" t="n"/>
+      <c r="AH27" s="277" t="n"/>
+      <c r="AI27" s="277" t="n"/>
+      <c r="AJ27" s="277" t="n"/>
+      <c r="AK27" s="277" t="n"/>
+      <c r="AL27" s="277" t="n"/>
+      <c r="AM27" s="278" t="n"/>
+      <c r="AN27" s="307" t="inlineStr">
         <is>
           <t>First-article sample identity is unique.</t>
         </is>
       </c>
-      <c r="AO27" s="12" t="n"/>
-      <c r="AP27" s="12" t="n"/>
-      <c r="AQ27" s="12" t="n"/>
-      <c r="AR27" s="12" t="n"/>
-      <c r="AS27" s="12" t="n"/>
-      <c r="AT27" s="12" t="n"/>
-      <c r="AU27" s="12" t="n"/>
-      <c r="AV27" s="12" t="n"/>
-      <c r="AW27" s="12" t="n"/>
-      <c r="AX27" s="12" t="n"/>
-      <c r="AY27" s="12" t="n"/>
-      <c r="AZ27" s="12" t="n"/>
-      <c r="BA27" s="12" t="n"/>
-      <c r="BB27" s="12" t="n"/>
-      <c r="BC27" s="12" t="n"/>
-      <c r="BD27" s="12" t="n"/>
-      <c r="BE27" s="12" t="n"/>
-      <c r="BF27" s="12" t="n"/>
-      <c r="BG27" s="12" t="n"/>
-      <c r="BH27" s="12" t="n"/>
-      <c r="BI27" s="12" t="n"/>
-      <c r="BJ27" s="12" t="n"/>
-      <c r="BK27" s="12" t="n"/>
-      <c r="BL27" s="13" t="n"/>
-      <c r="BM27" s="696" t="n"/>
-      <c r="BN27" s="12" t="n"/>
-      <c r="BO27" s="12" t="n"/>
-      <c r="BP27" s="12" t="n"/>
-      <c r="BQ27" s="12" t="n"/>
-      <c r="BR27" s="12" t="n"/>
-      <c r="BS27" s="12" t="n"/>
-      <c r="BT27" s="13" t="n"/>
-      <c r="BU27" s="696" t="n"/>
-      <c r="BV27" s="12" t="n"/>
-      <c r="BW27" s="12" t="n"/>
-      <c r="BX27" s="12" t="n"/>
-      <c r="BY27" s="12" t="n"/>
-      <c r="BZ27" s="13" t="n"/>
-      <c r="CA27" s="696" t="n"/>
-      <c r="CB27" s="12" t="n"/>
-      <c r="CC27" s="12" t="n"/>
-      <c r="CD27" s="15" t="n"/>
+      <c r="AO27" s="277" t="n"/>
+      <c r="AP27" s="277" t="n"/>
+      <c r="AQ27" s="277" t="n"/>
+      <c r="AR27" s="277" t="n"/>
+      <c r="AS27" s="277" t="n"/>
+      <c r="AT27" s="277" t="n"/>
+      <c r="AU27" s="277" t="n"/>
+      <c r="AV27" s="277" t="n"/>
+      <c r="AW27" s="277" t="n"/>
+      <c r="AX27" s="277" t="n"/>
+      <c r="AY27" s="277" t="n"/>
+      <c r="AZ27" s="277" t="n"/>
+      <c r="BA27" s="277" t="n"/>
+      <c r="BB27" s="277" t="n"/>
+      <c r="BC27" s="277" t="n"/>
+      <c r="BD27" s="277" t="n"/>
+      <c r="BE27" s="277" t="n"/>
+      <c r="BF27" s="277" t="n"/>
+      <c r="BG27" s="277" t="n"/>
+      <c r="BH27" s="277" t="n"/>
+      <c r="BI27" s="277" t="n"/>
+      <c r="BJ27" s="277" t="n"/>
+      <c r="BK27" s="277" t="n"/>
+      <c r="BL27" s="278" t="n"/>
+      <c r="BM27" s="306" t="n"/>
+      <c r="BN27" s="277" t="n"/>
+      <c r="BO27" s="277" t="n"/>
+      <c r="BP27" s="277" t="n"/>
+      <c r="BQ27" s="277" t="n"/>
+      <c r="BR27" s="277" t="n"/>
+      <c r="BS27" s="277" t="n"/>
+      <c r="BT27" s="278" t="n"/>
+      <c r="BU27" s="306" t="n"/>
+      <c r="BV27" s="277" t="n"/>
+      <c r="BW27" s="277" t="n"/>
+      <c r="BX27" s="277" t="n"/>
+      <c r="BY27" s="277" t="n"/>
+      <c r="BZ27" s="278" t="n"/>
+      <c r="CA27" s="800" t="n"/>
+      <c r="CB27" s="277" t="n"/>
+      <c r="CC27" s="277" t="n"/>
+      <c r="CD27" s="280" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="692" t="n">
+      <c r="A28" s="799" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="697" t="inlineStr">
+      <c r="B28" s="277" t="n"/>
+      <c r="C28" s="277" t="n"/>
+      <c r="D28" s="278" t="n"/>
+      <c r="E28" s="311" t="inlineStr">
         <is>
           <t>ABN</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="696" t="inlineStr">
+      <c r="F28" s="277" t="n"/>
+      <c r="G28" s="277" t="n"/>
+      <c r="H28" s="277" t="n"/>
+      <c r="I28" s="277" t="n"/>
+      <c r="J28" s="278" t="n"/>
+      <c r="K28" s="306" t="inlineStr">
         <is>
           <t>Abnormal results and concessions are linked.</t>
         </is>
       </c>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="12" t="n"/>
-      <c r="R28" s="12" t="n"/>
-      <c r="S28" s="12" t="n"/>
-      <c r="T28" s="12" t="n"/>
-      <c r="U28" s="12" t="n"/>
-      <c r="V28" s="12" t="n"/>
-      <c r="W28" s="12" t="n"/>
-      <c r="X28" s="12" t="n"/>
-      <c r="Y28" s="12" t="n"/>
-      <c r="Z28" s="12" t="n"/>
-      <c r="AA28" s="12" t="n"/>
-      <c r="AB28" s="12" t="n"/>
-      <c r="AC28" s="12" t="n"/>
-      <c r="AD28" s="12" t="n"/>
-      <c r="AE28" s="12" t="n"/>
-      <c r="AF28" s="12" t="n"/>
-      <c r="AG28" s="12" t="n"/>
-      <c r="AH28" s="12" t="n"/>
-      <c r="AI28" s="12" t="n"/>
-      <c r="AJ28" s="12" t="n"/>
-      <c r="AK28" s="12" t="n"/>
-      <c r="AL28" s="12" t="n"/>
-      <c r="AM28" s="13" t="n"/>
-      <c r="AN28" s="695" t="inlineStr">
+      <c r="L28" s="277" t="n"/>
+      <c r="M28" s="277" t="n"/>
+      <c r="N28" s="277" t="n"/>
+      <c r="O28" s="277" t="n"/>
+      <c r="P28" s="277" t="n"/>
+      <c r="Q28" s="277" t="n"/>
+      <c r="R28" s="277" t="n"/>
+      <c r="S28" s="277" t="n"/>
+      <c r="T28" s="277" t="n"/>
+      <c r="U28" s="277" t="n"/>
+      <c r="V28" s="277" t="n"/>
+      <c r="W28" s="277" t="n"/>
+      <c r="X28" s="277" t="n"/>
+      <c r="Y28" s="277" t="n"/>
+      <c r="Z28" s="277" t="n"/>
+      <c r="AA28" s="277" t="n"/>
+      <c r="AB28" s="277" t="n"/>
+      <c r="AC28" s="277" t="n"/>
+      <c r="AD28" s="277" t="n"/>
+      <c r="AE28" s="277" t="n"/>
+      <c r="AF28" s="277" t="n"/>
+      <c r="AG28" s="277" t="n"/>
+      <c r="AH28" s="277" t="n"/>
+      <c r="AI28" s="277" t="n"/>
+      <c r="AJ28" s="277" t="n"/>
+      <c r="AK28" s="277" t="n"/>
+      <c r="AL28" s="277" t="n"/>
+      <c r="AM28" s="278" t="n"/>
+      <c r="AN28" s="307" t="inlineStr">
         <is>
           <t>Any discrepancy has hold or concession logic.</t>
         </is>
       </c>
-      <c r="AO28" s="12" t="n"/>
-      <c r="AP28" s="12" t="n"/>
-      <c r="AQ28" s="12" t="n"/>
-      <c r="AR28" s="12" t="n"/>
-      <c r="AS28" s="12" t="n"/>
-      <c r="AT28" s="12" t="n"/>
-      <c r="AU28" s="12" t="n"/>
-      <c r="AV28" s="12" t="n"/>
-      <c r="AW28" s="12" t="n"/>
-      <c r="AX28" s="12" t="n"/>
-      <c r="AY28" s="12" t="n"/>
-      <c r="AZ28" s="12" t="n"/>
-      <c r="BA28" s="12" t="n"/>
-      <c r="BB28" s="12" t="n"/>
-      <c r="BC28" s="12" t="n"/>
-      <c r="BD28" s="12" t="n"/>
-      <c r="BE28" s="12" t="n"/>
-      <c r="BF28" s="12" t="n"/>
-      <c r="BG28" s="12" t="n"/>
-      <c r="BH28" s="12" t="n"/>
-      <c r="BI28" s="12" t="n"/>
-      <c r="BJ28" s="12" t="n"/>
-      <c r="BK28" s="12" t="n"/>
-      <c r="BL28" s="13" t="n"/>
-      <c r="BM28" s="696" t="n"/>
-      <c r="BN28" s="12" t="n"/>
-      <c r="BO28" s="12" t="n"/>
-      <c r="BP28" s="12" t="n"/>
-      <c r="BQ28" s="12" t="n"/>
-      <c r="BR28" s="12" t="n"/>
-      <c r="BS28" s="12" t="n"/>
-      <c r="BT28" s="13" t="n"/>
-      <c r="BU28" s="696" t="n"/>
-      <c r="BV28" s="12" t="n"/>
-      <c r="BW28" s="12" t="n"/>
-      <c r="BX28" s="12" t="n"/>
-      <c r="BY28" s="12" t="n"/>
-      <c r="BZ28" s="13" t="n"/>
-      <c r="CA28" s="696" t="n"/>
-      <c r="CB28" s="12" t="n"/>
-      <c r="CC28" s="12" t="n"/>
-      <c r="CD28" s="15" t="n"/>
+      <c r="AO28" s="277" t="n"/>
+      <c r="AP28" s="277" t="n"/>
+      <c r="AQ28" s="277" t="n"/>
+      <c r="AR28" s="277" t="n"/>
+      <c r="AS28" s="277" t="n"/>
+      <c r="AT28" s="277" t="n"/>
+      <c r="AU28" s="277" t="n"/>
+      <c r="AV28" s="277" t="n"/>
+      <c r="AW28" s="277" t="n"/>
+      <c r="AX28" s="277" t="n"/>
+      <c r="AY28" s="277" t="n"/>
+      <c r="AZ28" s="277" t="n"/>
+      <c r="BA28" s="277" t="n"/>
+      <c r="BB28" s="277" t="n"/>
+      <c r="BC28" s="277" t="n"/>
+      <c r="BD28" s="277" t="n"/>
+      <c r="BE28" s="277" t="n"/>
+      <c r="BF28" s="277" t="n"/>
+      <c r="BG28" s="277" t="n"/>
+      <c r="BH28" s="277" t="n"/>
+      <c r="BI28" s="277" t="n"/>
+      <c r="BJ28" s="277" t="n"/>
+      <c r="BK28" s="277" t="n"/>
+      <c r="BL28" s="278" t="n"/>
+      <c r="BM28" s="306" t="n"/>
+      <c r="BN28" s="277" t="n"/>
+      <c r="BO28" s="277" t="n"/>
+      <c r="BP28" s="277" t="n"/>
+      <c r="BQ28" s="277" t="n"/>
+      <c r="BR28" s="277" t="n"/>
+      <c r="BS28" s="277" t="n"/>
+      <c r="BT28" s="278" t="n"/>
+      <c r="BU28" s="306" t="n"/>
+      <c r="BV28" s="277" t="n"/>
+      <c r="BW28" s="277" t="n"/>
+      <c r="BX28" s="277" t="n"/>
+      <c r="BY28" s="277" t="n"/>
+      <c r="BZ28" s="278" t="n"/>
+      <c r="CA28" s="800" t="n"/>
+      <c r="CB28" s="277" t="n"/>
+      <c r="CC28" s="277" t="n"/>
+      <c r="CD28" s="280" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="692" t="n">
+      <c r="A29" s="799" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="701" t="inlineStr">
+      <c r="B29" s="277" t="n"/>
+      <c r="C29" s="277" t="n"/>
+      <c r="D29" s="278" t="n"/>
+      <c r="E29" s="315" t="inlineStr">
         <is>
           <t>REV</t>
         </is>
       </c>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="694" t="inlineStr">
+      <c r="F29" s="277" t="n"/>
+      <c r="G29" s="277" t="n"/>
+      <c r="H29" s="277" t="n"/>
+      <c r="I29" s="277" t="n"/>
+      <c r="J29" s="278" t="n"/>
+      <c r="K29" s="310" t="inlineStr">
         <is>
           <t>Revalidation trigger is assessed.</t>
         </is>
       </c>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="12" t="n"/>
-      <c r="R29" s="12" t="n"/>
-      <c r="S29" s="12" t="n"/>
-      <c r="T29" s="12" t="n"/>
-      <c r="U29" s="12" t="n"/>
-      <c r="V29" s="12" t="n"/>
-      <c r="W29" s="12" t="n"/>
-      <c r="X29" s="12" t="n"/>
-      <c r="Y29" s="12" t="n"/>
-      <c r="Z29" s="12" t="n"/>
-      <c r="AA29" s="12" t="n"/>
-      <c r="AB29" s="12" t="n"/>
-      <c r="AC29" s="12" t="n"/>
-      <c r="AD29" s="12" t="n"/>
-      <c r="AE29" s="12" t="n"/>
-      <c r="AF29" s="12" t="n"/>
-      <c r="AG29" s="12" t="n"/>
-      <c r="AH29" s="12" t="n"/>
-      <c r="AI29" s="12" t="n"/>
-      <c r="AJ29" s="12" t="n"/>
-      <c r="AK29" s="12" t="n"/>
-      <c r="AL29" s="12" t="n"/>
-      <c r="AM29" s="13" t="n"/>
-      <c r="AN29" s="695" t="inlineStr">
+      <c r="L29" s="277" t="n"/>
+      <c r="M29" s="277" t="n"/>
+      <c r="N29" s="277" t="n"/>
+      <c r="O29" s="277" t="n"/>
+      <c r="P29" s="277" t="n"/>
+      <c r="Q29" s="277" t="n"/>
+      <c r="R29" s="277" t="n"/>
+      <c r="S29" s="277" t="n"/>
+      <c r="T29" s="277" t="n"/>
+      <c r="U29" s="277" t="n"/>
+      <c r="V29" s="277" t="n"/>
+      <c r="W29" s="277" t="n"/>
+      <c r="X29" s="277" t="n"/>
+      <c r="Y29" s="277" t="n"/>
+      <c r="Z29" s="277" t="n"/>
+      <c r="AA29" s="277" t="n"/>
+      <c r="AB29" s="277" t="n"/>
+      <c r="AC29" s="277" t="n"/>
+      <c r="AD29" s="277" t="n"/>
+      <c r="AE29" s="277" t="n"/>
+      <c r="AF29" s="277" t="n"/>
+      <c r="AG29" s="277" t="n"/>
+      <c r="AH29" s="277" t="n"/>
+      <c r="AI29" s="277" t="n"/>
+      <c r="AJ29" s="277" t="n"/>
+      <c r="AK29" s="277" t="n"/>
+      <c r="AL29" s="277" t="n"/>
+      <c r="AM29" s="278" t="n"/>
+      <c r="AN29" s="307" t="inlineStr">
         <is>
           <t>Future change conditions are explicit.</t>
         </is>
       </c>
-      <c r="AO29" s="12" t="n"/>
-      <c r="AP29" s="12" t="n"/>
-      <c r="AQ29" s="12" t="n"/>
-      <c r="AR29" s="12" t="n"/>
-      <c r="AS29" s="12" t="n"/>
-      <c r="AT29" s="12" t="n"/>
-      <c r="AU29" s="12" t="n"/>
-      <c r="AV29" s="12" t="n"/>
-      <c r="AW29" s="12" t="n"/>
-      <c r="AX29" s="12" t="n"/>
-      <c r="AY29" s="12" t="n"/>
-      <c r="AZ29" s="12" t="n"/>
-      <c r="BA29" s="12" t="n"/>
-      <c r="BB29" s="12" t="n"/>
-      <c r="BC29" s="12" t="n"/>
-      <c r="BD29" s="12" t="n"/>
-      <c r="BE29" s="12" t="n"/>
-      <c r="BF29" s="12" t="n"/>
-      <c r="BG29" s="12" t="n"/>
-      <c r="BH29" s="12" t="n"/>
-      <c r="BI29" s="12" t="n"/>
-      <c r="BJ29" s="12" t="n"/>
-      <c r="BK29" s="12" t="n"/>
-      <c r="BL29" s="13" t="n"/>
-      <c r="BM29" s="696" t="n"/>
-      <c r="BN29" s="12" t="n"/>
-      <c r="BO29" s="12" t="n"/>
-      <c r="BP29" s="12" t="n"/>
-      <c r="BQ29" s="12" t="n"/>
-      <c r="BR29" s="12" t="n"/>
-      <c r="BS29" s="12" t="n"/>
-      <c r="BT29" s="13" t="n"/>
-      <c r="BU29" s="696" t="n"/>
-      <c r="BV29" s="12" t="n"/>
-      <c r="BW29" s="12" t="n"/>
-      <c r="BX29" s="12" t="n"/>
-      <c r="BY29" s="12" t="n"/>
-      <c r="BZ29" s="13" t="n"/>
-      <c r="CA29" s="696" t="n"/>
-      <c r="CB29" s="12" t="n"/>
-      <c r="CC29" s="12" t="n"/>
-      <c r="CD29" s="15" t="n"/>
+      <c r="AO29" s="277" t="n"/>
+      <c r="AP29" s="277" t="n"/>
+      <c r="AQ29" s="277" t="n"/>
+      <c r="AR29" s="277" t="n"/>
+      <c r="AS29" s="277" t="n"/>
+      <c r="AT29" s="277" t="n"/>
+      <c r="AU29" s="277" t="n"/>
+      <c r="AV29" s="277" t="n"/>
+      <c r="AW29" s="277" t="n"/>
+      <c r="AX29" s="277" t="n"/>
+      <c r="AY29" s="277" t="n"/>
+      <c r="AZ29" s="277" t="n"/>
+      <c r="BA29" s="277" t="n"/>
+      <c r="BB29" s="277" t="n"/>
+      <c r="BC29" s="277" t="n"/>
+      <c r="BD29" s="277" t="n"/>
+      <c r="BE29" s="277" t="n"/>
+      <c r="BF29" s="277" t="n"/>
+      <c r="BG29" s="277" t="n"/>
+      <c r="BH29" s="277" t="n"/>
+      <c r="BI29" s="277" t="n"/>
+      <c r="BJ29" s="277" t="n"/>
+      <c r="BK29" s="277" t="n"/>
+      <c r="BL29" s="278" t="n"/>
+      <c r="BM29" s="306" t="n"/>
+      <c r="BN29" s="277" t="n"/>
+      <c r="BO29" s="277" t="n"/>
+      <c r="BP29" s="277" t="n"/>
+      <c r="BQ29" s="277" t="n"/>
+      <c r="BR29" s="277" t="n"/>
+      <c r="BS29" s="277" t="n"/>
+      <c r="BT29" s="278" t="n"/>
+      <c r="BU29" s="306" t="n"/>
+      <c r="BV29" s="277" t="n"/>
+      <c r="BW29" s="277" t="n"/>
+      <c r="BX29" s="277" t="n"/>
+      <c r="BY29" s="277" t="n"/>
+      <c r="BZ29" s="278" t="n"/>
+      <c r="CA29" s="800" t="n"/>
+      <c r="CB29" s="277" t="n"/>
+      <c r="CC29" s="277" t="n"/>
+      <c r="CD29" s="280" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="692" t="n">
+      <c r="A30" s="799" t="n">
         <v>9</v>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="697" t="inlineStr">
+      <c r="B30" s="277" t="n"/>
+      <c r="C30" s="277" t="n"/>
+      <c r="D30" s="278" t="n"/>
+      <c r="E30" s="311" t="inlineStr">
         <is>
           <t>EVD</t>
         </is>
       </c>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="696" t="inlineStr">
+      <c r="F30" s="277" t="n"/>
+      <c r="G30" s="277" t="n"/>
+      <c r="H30" s="277" t="n"/>
+      <c r="I30" s="277" t="n"/>
+      <c r="J30" s="278" t="n"/>
+      <c r="K30" s="306" t="inlineStr">
         <is>
           <t>Evidence package and result log are complete.</t>
         </is>
       </c>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="12" t="n"/>
-      <c r="R30" s="12" t="n"/>
-      <c r="S30" s="12" t="n"/>
-      <c r="T30" s="12" t="n"/>
-      <c r="U30" s="12" t="n"/>
-      <c r="V30" s="12" t="n"/>
-      <c r="W30" s="12" t="n"/>
-      <c r="X30" s="12" t="n"/>
-      <c r="Y30" s="12" t="n"/>
-      <c r="Z30" s="12" t="n"/>
-      <c r="AA30" s="12" t="n"/>
-      <c r="AB30" s="12" t="n"/>
-      <c r="AC30" s="12" t="n"/>
-      <c r="AD30" s="12" t="n"/>
-      <c r="AE30" s="12" t="n"/>
-      <c r="AF30" s="12" t="n"/>
-      <c r="AG30" s="12" t="n"/>
-      <c r="AH30" s="12" t="n"/>
-      <c r="AI30" s="12" t="n"/>
-      <c r="AJ30" s="12" t="n"/>
-      <c r="AK30" s="12" t="n"/>
-      <c r="AL30" s="12" t="n"/>
-      <c r="AM30" s="13" t="n"/>
-      <c r="AN30" s="695" t="inlineStr">
+      <c r="L30" s="277" t="n"/>
+      <c r="M30" s="277" t="n"/>
+      <c r="N30" s="277" t="n"/>
+      <c r="O30" s="277" t="n"/>
+      <c r="P30" s="277" t="n"/>
+      <c r="Q30" s="277" t="n"/>
+      <c r="R30" s="277" t="n"/>
+      <c r="S30" s="277" t="n"/>
+      <c r="T30" s="277" t="n"/>
+      <c r="U30" s="277" t="n"/>
+      <c r="V30" s="277" t="n"/>
+      <c r="W30" s="277" t="n"/>
+      <c r="X30" s="277" t="n"/>
+      <c r="Y30" s="277" t="n"/>
+      <c r="Z30" s="277" t="n"/>
+      <c r="AA30" s="277" t="n"/>
+      <c r="AB30" s="277" t="n"/>
+      <c r="AC30" s="277" t="n"/>
+      <c r="AD30" s="277" t="n"/>
+      <c r="AE30" s="277" t="n"/>
+      <c r="AF30" s="277" t="n"/>
+      <c r="AG30" s="277" t="n"/>
+      <c r="AH30" s="277" t="n"/>
+      <c r="AI30" s="277" t="n"/>
+      <c r="AJ30" s="277" t="n"/>
+      <c r="AK30" s="277" t="n"/>
+      <c r="AL30" s="277" t="n"/>
+      <c r="AM30" s="278" t="n"/>
+      <c r="AN30" s="307" t="inlineStr">
         <is>
           <t>Result records are uniquely recoverable.</t>
         </is>
       </c>
-      <c r="AO30" s="12" t="n"/>
-      <c r="AP30" s="12" t="n"/>
-      <c r="AQ30" s="12" t="n"/>
-      <c r="AR30" s="12" t="n"/>
-      <c r="AS30" s="12" t="n"/>
-      <c r="AT30" s="12" t="n"/>
-      <c r="AU30" s="12" t="n"/>
-      <c r="AV30" s="12" t="n"/>
-      <c r="AW30" s="12" t="n"/>
-      <c r="AX30" s="12" t="n"/>
-      <c r="AY30" s="12" t="n"/>
-      <c r="AZ30" s="12" t="n"/>
-      <c r="BA30" s="12" t="n"/>
-      <c r="BB30" s="12" t="n"/>
-      <c r="BC30" s="12" t="n"/>
-      <c r="BD30" s="12" t="n"/>
-      <c r="BE30" s="12" t="n"/>
-      <c r="BF30" s="12" t="n"/>
-      <c r="BG30" s="12" t="n"/>
-      <c r="BH30" s="12" t="n"/>
-      <c r="BI30" s="12" t="n"/>
-      <c r="BJ30" s="12" t="n"/>
-      <c r="BK30" s="12" t="n"/>
-      <c r="BL30" s="13" t="n"/>
-      <c r="BM30" s="696" t="n"/>
-      <c r="BN30" s="12" t="n"/>
-      <c r="BO30" s="12" t="n"/>
-      <c r="BP30" s="12" t="n"/>
-      <c r="BQ30" s="12" t="n"/>
-      <c r="BR30" s="12" t="n"/>
-      <c r="BS30" s="12" t="n"/>
-      <c r="BT30" s="13" t="n"/>
-      <c r="BU30" s="696" t="n"/>
-      <c r="BV30" s="12" t="n"/>
-      <c r="BW30" s="12" t="n"/>
-      <c r="BX30" s="12" t="n"/>
-      <c r="BY30" s="12" t="n"/>
-      <c r="BZ30" s="13" t="n"/>
-      <c r="CA30" s="696" t="n"/>
-      <c r="CB30" s="12" t="n"/>
-      <c r="CC30" s="12" t="n"/>
-      <c r="CD30" s="15" t="n"/>
+      <c r="AO30" s="277" t="n"/>
+      <c r="AP30" s="277" t="n"/>
+      <c r="AQ30" s="277" t="n"/>
+      <c r="AR30" s="277" t="n"/>
+      <c r="AS30" s="277" t="n"/>
+      <c r="AT30" s="277" t="n"/>
+      <c r="AU30" s="277" t="n"/>
+      <c r="AV30" s="277" t="n"/>
+      <c r="AW30" s="277" t="n"/>
+      <c r="AX30" s="277" t="n"/>
+      <c r="AY30" s="277" t="n"/>
+      <c r="AZ30" s="277" t="n"/>
+      <c r="BA30" s="277" t="n"/>
+      <c r="BB30" s="277" t="n"/>
+      <c r="BC30" s="277" t="n"/>
+      <c r="BD30" s="277" t="n"/>
+      <c r="BE30" s="277" t="n"/>
+      <c r="BF30" s="277" t="n"/>
+      <c r="BG30" s="277" t="n"/>
+      <c r="BH30" s="277" t="n"/>
+      <c r="BI30" s="277" t="n"/>
+      <c r="BJ30" s="277" t="n"/>
+      <c r="BK30" s="277" t="n"/>
+      <c r="BL30" s="278" t="n"/>
+      <c r="BM30" s="306" t="n"/>
+      <c r="BN30" s="277" t="n"/>
+      <c r="BO30" s="277" t="n"/>
+      <c r="BP30" s="277" t="n"/>
+      <c r="BQ30" s="277" t="n"/>
+      <c r="BR30" s="277" t="n"/>
+      <c r="BS30" s="277" t="n"/>
+      <c r="BT30" s="278" t="n"/>
+      <c r="BU30" s="306" t="n"/>
+      <c r="BV30" s="277" t="n"/>
+      <c r="BW30" s="277" t="n"/>
+      <c r="BX30" s="277" t="n"/>
+      <c r="BY30" s="277" t="n"/>
+      <c r="BZ30" s="278" t="n"/>
+      <c r="CA30" s="800" t="n"/>
+      <c r="CB30" s="277" t="n"/>
+      <c r="CC30" s="277" t="n"/>
+      <c r="CD30" s="280" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="702" t="n">
+      <c r="A31" s="801" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="703" t="inlineStr">
+      <c r="B31" s="283" t="n"/>
+      <c r="C31" s="283" t="n"/>
+      <c r="D31" s="285" t="n"/>
+      <c r="E31" s="316" t="inlineStr">
         <is>
           <t>REL</t>
         </is>
       </c>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="704" t="inlineStr">
+      <c r="F31" s="283" t="n"/>
+      <c r="G31" s="283" t="n"/>
+      <c r="H31" s="283" t="n"/>
+      <c r="I31" s="283" t="n"/>
+      <c r="J31" s="285" t="n"/>
+      <c r="K31" s="317" t="inlineStr">
         <is>
           <t>Disposition authority is explicit.</t>
         </is>
       </c>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="19" t="n"/>
-      <c r="P31" s="19" t="n"/>
-      <c r="Q31" s="19" t="n"/>
-      <c r="R31" s="19" t="n"/>
-      <c r="S31" s="19" t="n"/>
-      <c r="T31" s="19" t="n"/>
-      <c r="U31" s="19" t="n"/>
-      <c r="V31" s="19" t="n"/>
-      <c r="W31" s="19" t="n"/>
-      <c r="X31" s="19" t="n"/>
-      <c r="Y31" s="19" t="n"/>
-      <c r="Z31" s="19" t="n"/>
-      <c r="AA31" s="19" t="n"/>
-      <c r="AB31" s="19" t="n"/>
-      <c r="AC31" s="19" t="n"/>
-      <c r="AD31" s="19" t="n"/>
-      <c r="AE31" s="19" t="n"/>
-      <c r="AF31" s="19" t="n"/>
-      <c r="AG31" s="19" t="n"/>
-      <c r="AH31" s="19" t="n"/>
-      <c r="AI31" s="19" t="n"/>
-      <c r="AJ31" s="19" t="n"/>
-      <c r="AK31" s="19" t="n"/>
-      <c r="AL31" s="19" t="n"/>
-      <c r="AM31" s="22" t="n"/>
-      <c r="AN31" s="705" t="inlineStr">
+      <c r="L31" s="283" t="n"/>
+      <c r="M31" s="283" t="n"/>
+      <c r="N31" s="283" t="n"/>
+      <c r="O31" s="283" t="n"/>
+      <c r="P31" s="283" t="n"/>
+      <c r="Q31" s="283" t="n"/>
+      <c r="R31" s="283" t="n"/>
+      <c r="S31" s="283" t="n"/>
+      <c r="T31" s="283" t="n"/>
+      <c r="U31" s="283" t="n"/>
+      <c r="V31" s="283" t="n"/>
+      <c r="W31" s="283" t="n"/>
+      <c r="X31" s="283" t="n"/>
+      <c r="Y31" s="283" t="n"/>
+      <c r="Z31" s="283" t="n"/>
+      <c r="AA31" s="283" t="n"/>
+      <c r="AB31" s="283" t="n"/>
+      <c r="AC31" s="283" t="n"/>
+      <c r="AD31" s="283" t="n"/>
+      <c r="AE31" s="283" t="n"/>
+      <c r="AF31" s="283" t="n"/>
+      <c r="AG31" s="283" t="n"/>
+      <c r="AH31" s="283" t="n"/>
+      <c r="AI31" s="283" t="n"/>
+      <c r="AJ31" s="283" t="n"/>
+      <c r="AK31" s="283" t="n"/>
+      <c r="AL31" s="283" t="n"/>
+      <c r="AM31" s="285" t="n"/>
+      <c r="AN31" s="318" t="inlineStr">
         <is>
           <t>Final FAI release or hold matches authority matrix.</t>
         </is>
       </c>
-      <c r="AO31" s="19" t="n"/>
-      <c r="AP31" s="19" t="n"/>
-      <c r="AQ31" s="19" t="n"/>
-      <c r="AR31" s="19" t="n"/>
-      <c r="AS31" s="19" t="n"/>
-      <c r="AT31" s="19" t="n"/>
-      <c r="AU31" s="19" t="n"/>
-      <c r="AV31" s="19" t="n"/>
-      <c r="AW31" s="19" t="n"/>
-      <c r="AX31" s="19" t="n"/>
-      <c r="AY31" s="19" t="n"/>
-      <c r="AZ31" s="19" t="n"/>
-      <c r="BA31" s="19" t="n"/>
-      <c r="BB31" s="19" t="n"/>
-      <c r="BC31" s="19" t="n"/>
-      <c r="BD31" s="19" t="n"/>
-      <c r="BE31" s="19" t="n"/>
-      <c r="BF31" s="19" t="n"/>
-      <c r="BG31" s="19" t="n"/>
-      <c r="BH31" s="19" t="n"/>
-      <c r="BI31" s="19" t="n"/>
-      <c r="BJ31" s="19" t="n"/>
-      <c r="BK31" s="19" t="n"/>
-      <c r="BL31" s="22" t="n"/>
-      <c r="BM31" s="706" t="n"/>
-      <c r="BN31" s="19" t="n"/>
-      <c r="BO31" s="19" t="n"/>
-      <c r="BP31" s="19" t="n"/>
-      <c r="BQ31" s="19" t="n"/>
-      <c r="BR31" s="19" t="n"/>
-      <c r="BS31" s="19" t="n"/>
-      <c r="BT31" s="22" t="n"/>
-      <c r="BU31" s="706" t="n"/>
-      <c r="BV31" s="19" t="n"/>
-      <c r="BW31" s="19" t="n"/>
-      <c r="BX31" s="19" t="n"/>
-      <c r="BY31" s="19" t="n"/>
-      <c r="BZ31" s="22" t="n"/>
-      <c r="CA31" s="706" t="n"/>
-      <c r="CB31" s="19" t="n"/>
-      <c r="CC31" s="19" t="n"/>
-      <c r="CD31" s="24" t="n"/>
+      <c r="AO31" s="283" t="n"/>
+      <c r="AP31" s="283" t="n"/>
+      <c r="AQ31" s="283" t="n"/>
+      <c r="AR31" s="283" t="n"/>
+      <c r="AS31" s="283" t="n"/>
+      <c r="AT31" s="283" t="n"/>
+      <c r="AU31" s="283" t="n"/>
+      <c r="AV31" s="283" t="n"/>
+      <c r="AW31" s="283" t="n"/>
+      <c r="AX31" s="283" t="n"/>
+      <c r="AY31" s="283" t="n"/>
+      <c r="AZ31" s="283" t="n"/>
+      <c r="BA31" s="283" t="n"/>
+      <c r="BB31" s="283" t="n"/>
+      <c r="BC31" s="283" t="n"/>
+      <c r="BD31" s="283" t="n"/>
+      <c r="BE31" s="283" t="n"/>
+      <c r="BF31" s="283" t="n"/>
+      <c r="BG31" s="283" t="n"/>
+      <c r="BH31" s="283" t="n"/>
+      <c r="BI31" s="283" t="n"/>
+      <c r="BJ31" s="283" t="n"/>
+      <c r="BK31" s="283" t="n"/>
+      <c r="BL31" s="285" t="n"/>
+      <c r="BM31" s="802" t="n"/>
+      <c r="BN31" s="283" t="n"/>
+      <c r="BO31" s="283" t="n"/>
+      <c r="BP31" s="283" t="n"/>
+      <c r="BQ31" s="283" t="n"/>
+      <c r="BR31" s="283" t="n"/>
+      <c r="BS31" s="283" t="n"/>
+      <c r="BT31" s="285" t="n"/>
+      <c r="BU31" s="802" t="n"/>
+      <c r="BV31" s="283" t="n"/>
+      <c r="BW31" s="283" t="n"/>
+      <c r="BX31" s="283" t="n"/>
+      <c r="BY31" s="283" t="n"/>
+      <c r="BZ31" s="285" t="n"/>
+      <c r="CA31" s="803" t="n"/>
+      <c r="CB31" s="283" t="n"/>
+      <c r="CC31" s="283" t="n"/>
+      <c r="CD31" s="287" t="n"/>
     </row>
     <row r="32" ht="3" customHeight="1">
       <c r="A32" s="686" t="n"/>
@@ -10520,634 +10534,634 @@
       <c r="CD32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="679" t="inlineStr">
+      <c r="A33" s="787" t="inlineStr">
         <is>
           <t>4.  DISPOSITION AND APPROVAL SECTION WITH LINKED NCR / CONCESSION IF APPLICABLE.</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-      <c r="Q33" s="27" t="n"/>
-      <c r="R33" s="27" t="n"/>
-      <c r="S33" s="27" t="n"/>
-      <c r="T33" s="27" t="n"/>
-      <c r="U33" s="27" t="n"/>
-      <c r="V33" s="27" t="n"/>
-      <c r="W33" s="27" t="n"/>
-      <c r="X33" s="27" t="n"/>
-      <c r="Y33" s="27" t="n"/>
-      <c r="Z33" s="27" t="n"/>
-      <c r="AA33" s="27" t="n"/>
-      <c r="AB33" s="27" t="n"/>
-      <c r="AC33" s="27" t="n"/>
-      <c r="AD33" s="27" t="n"/>
-      <c r="AE33" s="27" t="n"/>
-      <c r="AF33" s="27" t="n"/>
-      <c r="AG33" s="27" t="n"/>
-      <c r="AH33" s="27" t="n"/>
-      <c r="AI33" s="27" t="n"/>
-      <c r="AJ33" s="27" t="n"/>
-      <c r="AK33" s="27" t="n"/>
-      <c r="AL33" s="27" t="n"/>
-      <c r="AM33" s="27" t="n"/>
-      <c r="AN33" s="27" t="n"/>
-      <c r="AO33" s="27" t="n"/>
-      <c r="AP33" s="27" t="n"/>
-      <c r="AQ33" s="27" t="n"/>
-      <c r="AR33" s="27" t="n"/>
-      <c r="AS33" s="27" t="n"/>
-      <c r="AT33" s="27" t="n"/>
-      <c r="AU33" s="27" t="n"/>
-      <c r="AV33" s="27" t="n"/>
-      <c r="AW33" s="27" t="n"/>
-      <c r="AX33" s="27" t="n"/>
-      <c r="AY33" s="27" t="n"/>
-      <c r="AZ33" s="27" t="n"/>
-      <c r="BA33" s="27" t="n"/>
-      <c r="BB33" s="27" t="n"/>
-      <c r="BC33" s="27" t="n"/>
-      <c r="BD33" s="27" t="n"/>
-      <c r="BE33" s="27" t="n"/>
-      <c r="BF33" s="27" t="n"/>
-      <c r="BG33" s="27" t="n"/>
-      <c r="BH33" s="27" t="n"/>
-      <c r="BI33" s="27" t="n"/>
-      <c r="BJ33" s="27" t="n"/>
-      <c r="BK33" s="27" t="n"/>
-      <c r="BL33" s="27" t="n"/>
-      <c r="BM33" s="27" t="n"/>
-      <c r="BN33" s="27" t="n"/>
-      <c r="BO33" s="27" t="n"/>
-      <c r="BP33" s="27" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
-      <c r="BR33" s="27" t="n"/>
-      <c r="BS33" s="27" t="n"/>
-      <c r="BT33" s="27" t="n"/>
-      <c r="BU33" s="27" t="n"/>
-      <c r="BV33" s="27" t="n"/>
-      <c r="BW33" s="27" t="n"/>
-      <c r="BX33" s="27" t="n"/>
-      <c r="BY33" s="27" t="n"/>
-      <c r="BZ33" s="27" t="n"/>
-      <c r="CA33" s="27" t="n"/>
-      <c r="CB33" s="27" t="n"/>
-      <c r="CC33" s="27" t="n"/>
-      <c r="CD33" s="28" t="n"/>
+      <c r="B33" s="289" t="n"/>
+      <c r="C33" s="289" t="n"/>
+      <c r="D33" s="289" t="n"/>
+      <c r="E33" s="289" t="n"/>
+      <c r="F33" s="289" t="n"/>
+      <c r="G33" s="289" t="n"/>
+      <c r="H33" s="289" t="n"/>
+      <c r="I33" s="289" t="n"/>
+      <c r="J33" s="289" t="n"/>
+      <c r="K33" s="289" t="n"/>
+      <c r="L33" s="289" t="n"/>
+      <c r="M33" s="289" t="n"/>
+      <c r="N33" s="289" t="n"/>
+      <c r="O33" s="289" t="n"/>
+      <c r="P33" s="289" t="n"/>
+      <c r="Q33" s="289" t="n"/>
+      <c r="R33" s="289" t="n"/>
+      <c r="S33" s="289" t="n"/>
+      <c r="T33" s="289" t="n"/>
+      <c r="U33" s="289" t="n"/>
+      <c r="V33" s="289" t="n"/>
+      <c r="W33" s="289" t="n"/>
+      <c r="X33" s="289" t="n"/>
+      <c r="Y33" s="289" t="n"/>
+      <c r="Z33" s="289" t="n"/>
+      <c r="AA33" s="289" t="n"/>
+      <c r="AB33" s="289" t="n"/>
+      <c r="AC33" s="289" t="n"/>
+      <c r="AD33" s="289" t="n"/>
+      <c r="AE33" s="289" t="n"/>
+      <c r="AF33" s="289" t="n"/>
+      <c r="AG33" s="289" t="n"/>
+      <c r="AH33" s="289" t="n"/>
+      <c r="AI33" s="289" t="n"/>
+      <c r="AJ33" s="289" t="n"/>
+      <c r="AK33" s="289" t="n"/>
+      <c r="AL33" s="289" t="n"/>
+      <c r="AM33" s="289" t="n"/>
+      <c r="AN33" s="289" t="n"/>
+      <c r="AO33" s="289" t="n"/>
+      <c r="AP33" s="289" t="n"/>
+      <c r="AQ33" s="289" t="n"/>
+      <c r="AR33" s="289" t="n"/>
+      <c r="AS33" s="289" t="n"/>
+      <c r="AT33" s="289" t="n"/>
+      <c r="AU33" s="289" t="n"/>
+      <c r="AV33" s="289" t="n"/>
+      <c r="AW33" s="289" t="n"/>
+      <c r="AX33" s="289" t="n"/>
+      <c r="AY33" s="289" t="n"/>
+      <c r="AZ33" s="289" t="n"/>
+      <c r="BA33" s="289" t="n"/>
+      <c r="BB33" s="289" t="n"/>
+      <c r="BC33" s="289" t="n"/>
+      <c r="BD33" s="289" t="n"/>
+      <c r="BE33" s="289" t="n"/>
+      <c r="BF33" s="289" t="n"/>
+      <c r="BG33" s="289" t="n"/>
+      <c r="BH33" s="289" t="n"/>
+      <c r="BI33" s="289" t="n"/>
+      <c r="BJ33" s="289" t="n"/>
+      <c r="BK33" s="289" t="n"/>
+      <c r="BL33" s="289" t="n"/>
+      <c r="BM33" s="289" t="n"/>
+      <c r="BN33" s="289" t="n"/>
+      <c r="BO33" s="289" t="n"/>
+      <c r="BP33" s="289" t="n"/>
+      <c r="BQ33" s="289" t="n"/>
+      <c r="BR33" s="289" t="n"/>
+      <c r="BS33" s="289" t="n"/>
+      <c r="BT33" s="289" t="n"/>
+      <c r="BU33" s="289" t="n"/>
+      <c r="BV33" s="289" t="n"/>
+      <c r="BW33" s="289" t="n"/>
+      <c r="BX33" s="289" t="n"/>
+      <c r="BY33" s="289" t="n"/>
+      <c r="BZ33" s="289" t="n"/>
+      <c r="CA33" s="289" t="n"/>
+      <c r="CB33" s="289" t="n"/>
+      <c r="CC33" s="289" t="n"/>
+      <c r="CD33" s="290" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="301" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="37" t="inlineStr">
+      <c r="B34" s="271" t="n"/>
+      <c r="C34" s="271" t="n"/>
+      <c r="D34" s="272" t="n"/>
+      <c r="E34" s="302" t="inlineStr">
         <is>
           <t>Issue / Condition</t>
         </is>
       </c>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="5" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="6" t="n"/>
-      <c r="Y34" s="37" t="inlineStr">
+      <c r="F34" s="271" t="n"/>
+      <c r="G34" s="271" t="n"/>
+      <c r="H34" s="271" t="n"/>
+      <c r="I34" s="271" t="n"/>
+      <c r="J34" s="271" t="n"/>
+      <c r="K34" s="271" t="n"/>
+      <c r="L34" s="271" t="n"/>
+      <c r="M34" s="271" t="n"/>
+      <c r="N34" s="271" t="n"/>
+      <c r="O34" s="271" t="n"/>
+      <c r="P34" s="271" t="n"/>
+      <c r="Q34" s="271" t="n"/>
+      <c r="R34" s="271" t="n"/>
+      <c r="S34" s="271" t="n"/>
+      <c r="T34" s="271" t="n"/>
+      <c r="U34" s="271" t="n"/>
+      <c r="V34" s="271" t="n"/>
+      <c r="W34" s="271" t="n"/>
+      <c r="X34" s="272" t="n"/>
+      <c r="Y34" s="302" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="Z34" s="5" t="n"/>
-      <c r="AA34" s="5" t="n"/>
-      <c r="AB34" s="5" t="n"/>
-      <c r="AC34" s="5" t="n"/>
-      <c r="AD34" s="5" t="n"/>
-      <c r="AE34" s="5" t="n"/>
-      <c r="AF34" s="5" t="n"/>
-      <c r="AG34" s="5" t="n"/>
-      <c r="AH34" s="5" t="n"/>
-      <c r="AI34" s="5" t="n"/>
-      <c r="AJ34" s="5" t="n"/>
-      <c r="AK34" s="5" t="n"/>
-      <c r="AL34" s="5" t="n"/>
-      <c r="AM34" s="5" t="n"/>
-      <c r="AN34" s="5" t="n"/>
-      <c r="AO34" s="5" t="n"/>
-      <c r="AP34" s="5" t="n"/>
-      <c r="AQ34" s="5" t="n"/>
-      <c r="AR34" s="5" t="n"/>
-      <c r="AS34" s="5" t="n"/>
-      <c r="AT34" s="5" t="n"/>
-      <c r="AU34" s="5" t="n"/>
-      <c r="AV34" s="5" t="n"/>
-      <c r="AW34" s="6" t="n"/>
-      <c r="AX34" s="37" t="inlineStr">
+      <c r="Z34" s="271" t="n"/>
+      <c r="AA34" s="271" t="n"/>
+      <c r="AB34" s="271" t="n"/>
+      <c r="AC34" s="271" t="n"/>
+      <c r="AD34" s="271" t="n"/>
+      <c r="AE34" s="271" t="n"/>
+      <c r="AF34" s="271" t="n"/>
+      <c r="AG34" s="271" t="n"/>
+      <c r="AH34" s="271" t="n"/>
+      <c r="AI34" s="271" t="n"/>
+      <c r="AJ34" s="271" t="n"/>
+      <c r="AK34" s="271" t="n"/>
+      <c r="AL34" s="271" t="n"/>
+      <c r="AM34" s="271" t="n"/>
+      <c r="AN34" s="271" t="n"/>
+      <c r="AO34" s="271" t="n"/>
+      <c r="AP34" s="271" t="n"/>
+      <c r="AQ34" s="271" t="n"/>
+      <c r="AR34" s="271" t="n"/>
+      <c r="AS34" s="271" t="n"/>
+      <c r="AT34" s="271" t="n"/>
+      <c r="AU34" s="271" t="n"/>
+      <c r="AV34" s="271" t="n"/>
+      <c r="AW34" s="272" t="n"/>
+      <c r="AX34" s="302" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AY34" s="5" t="n"/>
-      <c r="AZ34" s="5" t="n"/>
-      <c r="BA34" s="5" t="n"/>
-      <c r="BB34" s="5" t="n"/>
-      <c r="BC34" s="5" t="n"/>
-      <c r="BD34" s="5" t="n"/>
-      <c r="BE34" s="5" t="n"/>
-      <c r="BF34" s="5" t="n"/>
-      <c r="BG34" s="6" t="n"/>
-      <c r="BH34" s="37" t="inlineStr">
+      <c r="AY34" s="271" t="n"/>
+      <c r="AZ34" s="271" t="n"/>
+      <c r="BA34" s="271" t="n"/>
+      <c r="BB34" s="271" t="n"/>
+      <c r="BC34" s="271" t="n"/>
+      <c r="BD34" s="271" t="n"/>
+      <c r="BE34" s="271" t="n"/>
+      <c r="BF34" s="271" t="n"/>
+      <c r="BG34" s="272" t="n"/>
+      <c r="BH34" s="302" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="BI34" s="5" t="n"/>
-      <c r="BJ34" s="5" t="n"/>
-      <c r="BK34" s="5" t="n"/>
-      <c r="BL34" s="5" t="n"/>
-      <c r="BM34" s="5" t="n"/>
-      <c r="BN34" s="5" t="n"/>
-      <c r="BO34" s="5" t="n"/>
-      <c r="BP34" s="5" t="n"/>
-      <c r="BQ34" s="6" t="n"/>
-      <c r="BR34" s="37" t="inlineStr">
+      <c r="BI34" s="271" t="n"/>
+      <c r="BJ34" s="271" t="n"/>
+      <c r="BK34" s="271" t="n"/>
+      <c r="BL34" s="271" t="n"/>
+      <c r="BM34" s="271" t="n"/>
+      <c r="BN34" s="271" t="n"/>
+      <c r="BO34" s="271" t="n"/>
+      <c r="BP34" s="271" t="n"/>
+      <c r="BQ34" s="272" t="n"/>
+      <c r="BR34" s="302" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="BS34" s="5" t="n"/>
-      <c r="BT34" s="5" t="n"/>
-      <c r="BU34" s="5" t="n"/>
-      <c r="BV34" s="5" t="n"/>
-      <c r="BW34" s="5" t="n"/>
-      <c r="BX34" s="6" t="n"/>
-      <c r="BY34" s="37" t="inlineStr">
+      <c r="BS34" s="271" t="n"/>
+      <c r="BT34" s="271" t="n"/>
+      <c r="BU34" s="271" t="n"/>
+      <c r="BV34" s="271" t="n"/>
+      <c r="BW34" s="271" t="n"/>
+      <c r="BX34" s="272" t="n"/>
+      <c r="BY34" s="303" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="BZ34" s="5" t="n"/>
-      <c r="CA34" s="5" t="n"/>
-      <c r="CB34" s="5" t="n"/>
-      <c r="CC34" s="5" t="n"/>
-      <c r="CD34" s="8" t="n"/>
+      <c r="BZ34" s="271" t="n"/>
+      <c r="CA34" s="271" t="n"/>
+      <c r="CB34" s="271" t="n"/>
+      <c r="CC34" s="271" t="n"/>
+      <c r="CD34" s="274" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="707" t="n">
+      <c r="A35" s="804" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="690" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="5" t="n"/>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="5" t="n"/>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="5" t="n"/>
-      <c r="X35" s="6" t="n"/>
-      <c r="Y35" s="690" t="n"/>
-      <c r="Z35" s="5" t="n"/>
-      <c r="AA35" s="5" t="n"/>
-      <c r="AB35" s="5" t="n"/>
-      <c r="AC35" s="5" t="n"/>
-      <c r="AD35" s="5" t="n"/>
-      <c r="AE35" s="5" t="n"/>
-      <c r="AF35" s="5" t="n"/>
-      <c r="AG35" s="5" t="n"/>
-      <c r="AH35" s="5" t="n"/>
-      <c r="AI35" s="5" t="n"/>
-      <c r="AJ35" s="5" t="n"/>
-      <c r="AK35" s="5" t="n"/>
-      <c r="AL35" s="5" t="n"/>
-      <c r="AM35" s="5" t="n"/>
-      <c r="AN35" s="5" t="n"/>
-      <c r="AO35" s="5" t="n"/>
-      <c r="AP35" s="5" t="n"/>
-      <c r="AQ35" s="5" t="n"/>
-      <c r="AR35" s="5" t="n"/>
-      <c r="AS35" s="5" t="n"/>
-      <c r="AT35" s="5" t="n"/>
-      <c r="AU35" s="5" t="n"/>
-      <c r="AV35" s="5" t="n"/>
-      <c r="AW35" s="6" t="n"/>
-      <c r="AX35" s="690" t="n"/>
-      <c r="AY35" s="5" t="n"/>
-      <c r="AZ35" s="5" t="n"/>
-      <c r="BA35" s="5" t="n"/>
-      <c r="BB35" s="5" t="n"/>
-      <c r="BC35" s="5" t="n"/>
-      <c r="BD35" s="5" t="n"/>
-      <c r="BE35" s="5" t="n"/>
-      <c r="BF35" s="5" t="n"/>
-      <c r="BG35" s="6" t="n"/>
-      <c r="BH35" s="708" t="n"/>
-      <c r="BI35" s="5" t="n"/>
-      <c r="BJ35" s="5" t="n"/>
-      <c r="BK35" s="5" t="n"/>
-      <c r="BL35" s="5" t="n"/>
-      <c r="BM35" s="5" t="n"/>
-      <c r="BN35" s="5" t="n"/>
-      <c r="BO35" s="5" t="n"/>
-      <c r="BP35" s="5" t="n"/>
-      <c r="BQ35" s="6" t="n"/>
-      <c r="BR35" s="690" t="n"/>
-      <c r="BS35" s="5" t="n"/>
-      <c r="BT35" s="5" t="n"/>
-      <c r="BU35" s="5" t="n"/>
-      <c r="BV35" s="5" t="n"/>
-      <c r="BW35" s="5" t="n"/>
-      <c r="BX35" s="6" t="n"/>
-      <c r="BY35" s="690" t="n"/>
-      <c r="BZ35" s="5" t="n"/>
-      <c r="CA35" s="5" t="n"/>
-      <c r="CB35" s="5" t="n"/>
-      <c r="CC35" s="5" t="n"/>
-      <c r="CD35" s="8" t="n"/>
+      <c r="B35" s="271" t="n"/>
+      <c r="C35" s="271" t="n"/>
+      <c r="D35" s="272" t="n"/>
+      <c r="E35" s="796" t="n"/>
+      <c r="F35" s="271" t="n"/>
+      <c r="G35" s="271" t="n"/>
+      <c r="H35" s="271" t="n"/>
+      <c r="I35" s="271" t="n"/>
+      <c r="J35" s="271" t="n"/>
+      <c r="K35" s="271" t="n"/>
+      <c r="L35" s="271" t="n"/>
+      <c r="M35" s="271" t="n"/>
+      <c r="N35" s="271" t="n"/>
+      <c r="O35" s="271" t="n"/>
+      <c r="P35" s="271" t="n"/>
+      <c r="Q35" s="271" t="n"/>
+      <c r="R35" s="271" t="n"/>
+      <c r="S35" s="271" t="n"/>
+      <c r="T35" s="271" t="n"/>
+      <c r="U35" s="271" t="n"/>
+      <c r="V35" s="271" t="n"/>
+      <c r="W35" s="271" t="n"/>
+      <c r="X35" s="272" t="n"/>
+      <c r="Y35" s="796" t="n"/>
+      <c r="Z35" s="271" t="n"/>
+      <c r="AA35" s="271" t="n"/>
+      <c r="AB35" s="271" t="n"/>
+      <c r="AC35" s="271" t="n"/>
+      <c r="AD35" s="271" t="n"/>
+      <c r="AE35" s="271" t="n"/>
+      <c r="AF35" s="271" t="n"/>
+      <c r="AG35" s="271" t="n"/>
+      <c r="AH35" s="271" t="n"/>
+      <c r="AI35" s="271" t="n"/>
+      <c r="AJ35" s="271" t="n"/>
+      <c r="AK35" s="271" t="n"/>
+      <c r="AL35" s="271" t="n"/>
+      <c r="AM35" s="271" t="n"/>
+      <c r="AN35" s="271" t="n"/>
+      <c r="AO35" s="271" t="n"/>
+      <c r="AP35" s="271" t="n"/>
+      <c r="AQ35" s="271" t="n"/>
+      <c r="AR35" s="271" t="n"/>
+      <c r="AS35" s="271" t="n"/>
+      <c r="AT35" s="271" t="n"/>
+      <c r="AU35" s="271" t="n"/>
+      <c r="AV35" s="271" t="n"/>
+      <c r="AW35" s="272" t="n"/>
+      <c r="AX35" s="796" t="n"/>
+      <c r="AY35" s="271" t="n"/>
+      <c r="AZ35" s="271" t="n"/>
+      <c r="BA35" s="271" t="n"/>
+      <c r="BB35" s="271" t="n"/>
+      <c r="BC35" s="271" t="n"/>
+      <c r="BD35" s="271" t="n"/>
+      <c r="BE35" s="271" t="n"/>
+      <c r="BF35" s="271" t="n"/>
+      <c r="BG35" s="272" t="n"/>
+      <c r="BH35" s="805" t="n"/>
+      <c r="BI35" s="271" t="n"/>
+      <c r="BJ35" s="271" t="n"/>
+      <c r="BK35" s="271" t="n"/>
+      <c r="BL35" s="271" t="n"/>
+      <c r="BM35" s="271" t="n"/>
+      <c r="BN35" s="271" t="n"/>
+      <c r="BO35" s="271" t="n"/>
+      <c r="BP35" s="271" t="n"/>
+      <c r="BQ35" s="272" t="n"/>
+      <c r="BR35" s="796" t="n"/>
+      <c r="BS35" s="271" t="n"/>
+      <c r="BT35" s="271" t="n"/>
+      <c r="BU35" s="271" t="n"/>
+      <c r="BV35" s="271" t="n"/>
+      <c r="BW35" s="271" t="n"/>
+      <c r="BX35" s="272" t="n"/>
+      <c r="BY35" s="798" t="n"/>
+      <c r="BZ35" s="271" t="n"/>
+      <c r="CA35" s="271" t="n"/>
+      <c r="CB35" s="271" t="n"/>
+      <c r="CC35" s="271" t="n"/>
+      <c r="CD35" s="274" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="709" t="n">
+      <c r="A36" s="806" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="696" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="12" t="n"/>
-      <c r="R36" s="12" t="n"/>
-      <c r="S36" s="12" t="n"/>
-      <c r="T36" s="12" t="n"/>
-      <c r="U36" s="12" t="n"/>
-      <c r="V36" s="12" t="n"/>
-      <c r="W36" s="12" t="n"/>
-      <c r="X36" s="13" t="n"/>
-      <c r="Y36" s="696" t="n"/>
-      <c r="Z36" s="12" t="n"/>
-      <c r="AA36" s="12" t="n"/>
-      <c r="AB36" s="12" t="n"/>
-      <c r="AC36" s="12" t="n"/>
-      <c r="AD36" s="12" t="n"/>
-      <c r="AE36" s="12" t="n"/>
-      <c r="AF36" s="12" t="n"/>
-      <c r="AG36" s="12" t="n"/>
-      <c r="AH36" s="12" t="n"/>
-      <c r="AI36" s="12" t="n"/>
-      <c r="AJ36" s="12" t="n"/>
-      <c r="AK36" s="12" t="n"/>
-      <c r="AL36" s="12" t="n"/>
-      <c r="AM36" s="12" t="n"/>
-      <c r="AN36" s="12" t="n"/>
-      <c r="AO36" s="12" t="n"/>
-      <c r="AP36" s="12" t="n"/>
-      <c r="AQ36" s="12" t="n"/>
-      <c r="AR36" s="12" t="n"/>
-      <c r="AS36" s="12" t="n"/>
-      <c r="AT36" s="12" t="n"/>
-      <c r="AU36" s="12" t="n"/>
-      <c r="AV36" s="12" t="n"/>
-      <c r="AW36" s="13" t="n"/>
-      <c r="AX36" s="696" t="n"/>
-      <c r="AY36" s="12" t="n"/>
-      <c r="AZ36" s="12" t="n"/>
-      <c r="BA36" s="12" t="n"/>
-      <c r="BB36" s="12" t="n"/>
-      <c r="BC36" s="12" t="n"/>
-      <c r="BD36" s="12" t="n"/>
-      <c r="BE36" s="12" t="n"/>
-      <c r="BF36" s="12" t="n"/>
-      <c r="BG36" s="13" t="n"/>
-      <c r="BH36" s="710" t="n"/>
-      <c r="BI36" s="12" t="n"/>
-      <c r="BJ36" s="12" t="n"/>
-      <c r="BK36" s="12" t="n"/>
-      <c r="BL36" s="12" t="n"/>
-      <c r="BM36" s="12" t="n"/>
-      <c r="BN36" s="12" t="n"/>
-      <c r="BO36" s="12" t="n"/>
-      <c r="BP36" s="12" t="n"/>
-      <c r="BQ36" s="13" t="n"/>
-      <c r="BR36" s="696" t="n"/>
-      <c r="BS36" s="12" t="n"/>
-      <c r="BT36" s="12" t="n"/>
-      <c r="BU36" s="12" t="n"/>
-      <c r="BV36" s="12" t="n"/>
-      <c r="BW36" s="12" t="n"/>
-      <c r="BX36" s="13" t="n"/>
-      <c r="BY36" s="696" t="n"/>
-      <c r="BZ36" s="12" t="n"/>
-      <c r="CA36" s="12" t="n"/>
-      <c r="CB36" s="12" t="n"/>
-      <c r="CC36" s="12" t="n"/>
-      <c r="CD36" s="15" t="n"/>
+      <c r="B36" s="277" t="n"/>
+      <c r="C36" s="277" t="n"/>
+      <c r="D36" s="278" t="n"/>
+      <c r="E36" s="306" t="n"/>
+      <c r="F36" s="277" t="n"/>
+      <c r="G36" s="277" t="n"/>
+      <c r="H36" s="277" t="n"/>
+      <c r="I36" s="277" t="n"/>
+      <c r="J36" s="277" t="n"/>
+      <c r="K36" s="277" t="n"/>
+      <c r="L36" s="277" t="n"/>
+      <c r="M36" s="277" t="n"/>
+      <c r="N36" s="277" t="n"/>
+      <c r="O36" s="277" t="n"/>
+      <c r="P36" s="277" t="n"/>
+      <c r="Q36" s="277" t="n"/>
+      <c r="R36" s="277" t="n"/>
+      <c r="S36" s="277" t="n"/>
+      <c r="T36" s="277" t="n"/>
+      <c r="U36" s="277" t="n"/>
+      <c r="V36" s="277" t="n"/>
+      <c r="W36" s="277" t="n"/>
+      <c r="X36" s="278" t="n"/>
+      <c r="Y36" s="306" t="n"/>
+      <c r="Z36" s="277" t="n"/>
+      <c r="AA36" s="277" t="n"/>
+      <c r="AB36" s="277" t="n"/>
+      <c r="AC36" s="277" t="n"/>
+      <c r="AD36" s="277" t="n"/>
+      <c r="AE36" s="277" t="n"/>
+      <c r="AF36" s="277" t="n"/>
+      <c r="AG36" s="277" t="n"/>
+      <c r="AH36" s="277" t="n"/>
+      <c r="AI36" s="277" t="n"/>
+      <c r="AJ36" s="277" t="n"/>
+      <c r="AK36" s="277" t="n"/>
+      <c r="AL36" s="277" t="n"/>
+      <c r="AM36" s="277" t="n"/>
+      <c r="AN36" s="277" t="n"/>
+      <c r="AO36" s="277" t="n"/>
+      <c r="AP36" s="277" t="n"/>
+      <c r="AQ36" s="277" t="n"/>
+      <c r="AR36" s="277" t="n"/>
+      <c r="AS36" s="277" t="n"/>
+      <c r="AT36" s="277" t="n"/>
+      <c r="AU36" s="277" t="n"/>
+      <c r="AV36" s="277" t="n"/>
+      <c r="AW36" s="278" t="n"/>
+      <c r="AX36" s="306" t="n"/>
+      <c r="AY36" s="277" t="n"/>
+      <c r="AZ36" s="277" t="n"/>
+      <c r="BA36" s="277" t="n"/>
+      <c r="BB36" s="277" t="n"/>
+      <c r="BC36" s="277" t="n"/>
+      <c r="BD36" s="277" t="n"/>
+      <c r="BE36" s="277" t="n"/>
+      <c r="BF36" s="277" t="n"/>
+      <c r="BG36" s="278" t="n"/>
+      <c r="BH36" s="807" t="n"/>
+      <c r="BI36" s="277" t="n"/>
+      <c r="BJ36" s="277" t="n"/>
+      <c r="BK36" s="277" t="n"/>
+      <c r="BL36" s="277" t="n"/>
+      <c r="BM36" s="277" t="n"/>
+      <c r="BN36" s="277" t="n"/>
+      <c r="BO36" s="277" t="n"/>
+      <c r="BP36" s="277" t="n"/>
+      <c r="BQ36" s="278" t="n"/>
+      <c r="BR36" s="306" t="n"/>
+      <c r="BS36" s="277" t="n"/>
+      <c r="BT36" s="277" t="n"/>
+      <c r="BU36" s="277" t="n"/>
+      <c r="BV36" s="277" t="n"/>
+      <c r="BW36" s="277" t="n"/>
+      <c r="BX36" s="278" t="n"/>
+      <c r="BY36" s="800" t="n"/>
+      <c r="BZ36" s="277" t="n"/>
+      <c r="CA36" s="277" t="n"/>
+      <c r="CB36" s="277" t="n"/>
+      <c r="CC36" s="277" t="n"/>
+      <c r="CD36" s="280" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="709" t="n">
+      <c r="A37" s="806" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="696" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="12" t="n"/>
-      <c r="R37" s="12" t="n"/>
-      <c r="S37" s="12" t="n"/>
-      <c r="T37" s="12" t="n"/>
-      <c r="U37" s="12" t="n"/>
-      <c r="V37" s="12" t="n"/>
-      <c r="W37" s="12" t="n"/>
-      <c r="X37" s="13" t="n"/>
-      <c r="Y37" s="696" t="n"/>
-      <c r="Z37" s="12" t="n"/>
-      <c r="AA37" s="12" t="n"/>
-      <c r="AB37" s="12" t="n"/>
-      <c r="AC37" s="12" t="n"/>
-      <c r="AD37" s="12" t="n"/>
-      <c r="AE37" s="12" t="n"/>
-      <c r="AF37" s="12" t="n"/>
-      <c r="AG37" s="12" t="n"/>
-      <c r="AH37" s="12" t="n"/>
-      <c r="AI37" s="12" t="n"/>
-      <c r="AJ37" s="12" t="n"/>
-      <c r="AK37" s="12" t="n"/>
-      <c r="AL37" s="12" t="n"/>
-      <c r="AM37" s="12" t="n"/>
-      <c r="AN37" s="12" t="n"/>
-      <c r="AO37" s="12" t="n"/>
-      <c r="AP37" s="12" t="n"/>
-      <c r="AQ37" s="12" t="n"/>
-      <c r="AR37" s="12" t="n"/>
-      <c r="AS37" s="12" t="n"/>
-      <c r="AT37" s="12" t="n"/>
-      <c r="AU37" s="12" t="n"/>
-      <c r="AV37" s="12" t="n"/>
-      <c r="AW37" s="13" t="n"/>
-      <c r="AX37" s="696" t="n"/>
-      <c r="AY37" s="12" t="n"/>
-      <c r="AZ37" s="12" t="n"/>
-      <c r="BA37" s="12" t="n"/>
-      <c r="BB37" s="12" t="n"/>
-      <c r="BC37" s="12" t="n"/>
-      <c r="BD37" s="12" t="n"/>
-      <c r="BE37" s="12" t="n"/>
-      <c r="BF37" s="12" t="n"/>
-      <c r="BG37" s="13" t="n"/>
-      <c r="BH37" s="710" t="n"/>
-      <c r="BI37" s="12" t="n"/>
-      <c r="BJ37" s="12" t="n"/>
-      <c r="BK37" s="12" t="n"/>
-      <c r="BL37" s="12" t="n"/>
-      <c r="BM37" s="12" t="n"/>
-      <c r="BN37" s="12" t="n"/>
-      <c r="BO37" s="12" t="n"/>
-      <c r="BP37" s="12" t="n"/>
-      <c r="BQ37" s="13" t="n"/>
-      <c r="BR37" s="696" t="n"/>
-      <c r="BS37" s="12" t="n"/>
-      <c r="BT37" s="12" t="n"/>
-      <c r="BU37" s="12" t="n"/>
-      <c r="BV37" s="12" t="n"/>
-      <c r="BW37" s="12" t="n"/>
-      <c r="BX37" s="13" t="n"/>
-      <c r="BY37" s="696" t="n"/>
-      <c r="BZ37" s="12" t="n"/>
-      <c r="CA37" s="12" t="n"/>
-      <c r="CB37" s="12" t="n"/>
-      <c r="CC37" s="12" t="n"/>
-      <c r="CD37" s="15" t="n"/>
+      <c r="B37" s="277" t="n"/>
+      <c r="C37" s="277" t="n"/>
+      <c r="D37" s="278" t="n"/>
+      <c r="E37" s="306" t="n"/>
+      <c r="F37" s="277" t="n"/>
+      <c r="G37" s="277" t="n"/>
+      <c r="H37" s="277" t="n"/>
+      <c r="I37" s="277" t="n"/>
+      <c r="J37" s="277" t="n"/>
+      <c r="K37" s="277" t="n"/>
+      <c r="L37" s="277" t="n"/>
+      <c r="M37" s="277" t="n"/>
+      <c r="N37" s="277" t="n"/>
+      <c r="O37" s="277" t="n"/>
+      <c r="P37" s="277" t="n"/>
+      <c r="Q37" s="277" t="n"/>
+      <c r="R37" s="277" t="n"/>
+      <c r="S37" s="277" t="n"/>
+      <c r="T37" s="277" t="n"/>
+      <c r="U37" s="277" t="n"/>
+      <c r="V37" s="277" t="n"/>
+      <c r="W37" s="277" t="n"/>
+      <c r="X37" s="278" t="n"/>
+      <c r="Y37" s="306" t="n"/>
+      <c r="Z37" s="277" t="n"/>
+      <c r="AA37" s="277" t="n"/>
+      <c r="AB37" s="277" t="n"/>
+      <c r="AC37" s="277" t="n"/>
+      <c r="AD37" s="277" t="n"/>
+      <c r="AE37" s="277" t="n"/>
+      <c r="AF37" s="277" t="n"/>
+      <c r="AG37" s="277" t="n"/>
+      <c r="AH37" s="277" t="n"/>
+      <c r="AI37" s="277" t="n"/>
+      <c r="AJ37" s="277" t="n"/>
+      <c r="AK37" s="277" t="n"/>
+      <c r="AL37" s="277" t="n"/>
+      <c r="AM37" s="277" t="n"/>
+      <c r="AN37" s="277" t="n"/>
+      <c r="AO37" s="277" t="n"/>
+      <c r="AP37" s="277" t="n"/>
+      <c r="AQ37" s="277" t="n"/>
+      <c r="AR37" s="277" t="n"/>
+      <c r="AS37" s="277" t="n"/>
+      <c r="AT37" s="277" t="n"/>
+      <c r="AU37" s="277" t="n"/>
+      <c r="AV37" s="277" t="n"/>
+      <c r="AW37" s="278" t="n"/>
+      <c r="AX37" s="306" t="n"/>
+      <c r="AY37" s="277" t="n"/>
+      <c r="AZ37" s="277" t="n"/>
+      <c r="BA37" s="277" t="n"/>
+      <c r="BB37" s="277" t="n"/>
+      <c r="BC37" s="277" t="n"/>
+      <c r="BD37" s="277" t="n"/>
+      <c r="BE37" s="277" t="n"/>
+      <c r="BF37" s="277" t="n"/>
+      <c r="BG37" s="278" t="n"/>
+      <c r="BH37" s="807" t="n"/>
+      <c r="BI37" s="277" t="n"/>
+      <c r="BJ37" s="277" t="n"/>
+      <c r="BK37" s="277" t="n"/>
+      <c r="BL37" s="277" t="n"/>
+      <c r="BM37" s="277" t="n"/>
+      <c r="BN37" s="277" t="n"/>
+      <c r="BO37" s="277" t="n"/>
+      <c r="BP37" s="277" t="n"/>
+      <c r="BQ37" s="278" t="n"/>
+      <c r="BR37" s="306" t="n"/>
+      <c r="BS37" s="277" t="n"/>
+      <c r="BT37" s="277" t="n"/>
+      <c r="BU37" s="277" t="n"/>
+      <c r="BV37" s="277" t="n"/>
+      <c r="BW37" s="277" t="n"/>
+      <c r="BX37" s="278" t="n"/>
+      <c r="BY37" s="800" t="n"/>
+      <c r="BZ37" s="277" t="n"/>
+      <c r="CA37" s="277" t="n"/>
+      <c r="CB37" s="277" t="n"/>
+      <c r="CC37" s="277" t="n"/>
+      <c r="CD37" s="280" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="709" t="n">
+      <c r="A38" s="806" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="696" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="12" t="n"/>
-      <c r="R38" s="12" t="n"/>
-      <c r="S38" s="12" t="n"/>
-      <c r="T38" s="12" t="n"/>
-      <c r="U38" s="12" t="n"/>
-      <c r="V38" s="12" t="n"/>
-      <c r="W38" s="12" t="n"/>
-      <c r="X38" s="13" t="n"/>
-      <c r="Y38" s="696" t="n"/>
-      <c r="Z38" s="12" t="n"/>
-      <c r="AA38" s="12" t="n"/>
-      <c r="AB38" s="12" t="n"/>
-      <c r="AC38" s="12" t="n"/>
-      <c r="AD38" s="12" t="n"/>
-      <c r="AE38" s="12" t="n"/>
-      <c r="AF38" s="12" t="n"/>
-      <c r="AG38" s="12" t="n"/>
-      <c r="AH38" s="12" t="n"/>
-      <c r="AI38" s="12" t="n"/>
-      <c r="AJ38" s="12" t="n"/>
-      <c r="AK38" s="12" t="n"/>
-      <c r="AL38" s="12" t="n"/>
-      <c r="AM38" s="12" t="n"/>
-      <c r="AN38" s="12" t="n"/>
-      <c r="AO38" s="12" t="n"/>
-      <c r="AP38" s="12" t="n"/>
-      <c r="AQ38" s="12" t="n"/>
-      <c r="AR38" s="12" t="n"/>
-      <c r="AS38" s="12" t="n"/>
-      <c r="AT38" s="12" t="n"/>
-      <c r="AU38" s="12" t="n"/>
-      <c r="AV38" s="12" t="n"/>
-      <c r="AW38" s="13" t="n"/>
-      <c r="AX38" s="696" t="n"/>
-      <c r="AY38" s="12" t="n"/>
-      <c r="AZ38" s="12" t="n"/>
-      <c r="BA38" s="12" t="n"/>
-      <c r="BB38" s="12" t="n"/>
-      <c r="BC38" s="12" t="n"/>
-      <c r="BD38" s="12" t="n"/>
-      <c r="BE38" s="12" t="n"/>
-      <c r="BF38" s="12" t="n"/>
-      <c r="BG38" s="13" t="n"/>
-      <c r="BH38" s="710" t="n"/>
-      <c r="BI38" s="12" t="n"/>
-      <c r="BJ38" s="12" t="n"/>
-      <c r="BK38" s="12" t="n"/>
-      <c r="BL38" s="12" t="n"/>
-      <c r="BM38" s="12" t="n"/>
-      <c r="BN38" s="12" t="n"/>
-      <c r="BO38" s="12" t="n"/>
-      <c r="BP38" s="12" t="n"/>
-      <c r="BQ38" s="13" t="n"/>
-      <c r="BR38" s="696" t="n"/>
-      <c r="BS38" s="12" t="n"/>
-      <c r="BT38" s="12" t="n"/>
-      <c r="BU38" s="12" t="n"/>
-      <c r="BV38" s="12" t="n"/>
-      <c r="BW38" s="12" t="n"/>
-      <c r="BX38" s="13" t="n"/>
-      <c r="BY38" s="696" t="n"/>
-      <c r="BZ38" s="12" t="n"/>
-      <c r="CA38" s="12" t="n"/>
-      <c r="CB38" s="12" t="n"/>
-      <c r="CC38" s="12" t="n"/>
-      <c r="CD38" s="15" t="n"/>
+      <c r="B38" s="277" t="n"/>
+      <c r="C38" s="277" t="n"/>
+      <c r="D38" s="278" t="n"/>
+      <c r="E38" s="306" t="n"/>
+      <c r="F38" s="277" t="n"/>
+      <c r="G38" s="277" t="n"/>
+      <c r="H38" s="277" t="n"/>
+      <c r="I38" s="277" t="n"/>
+      <c r="J38" s="277" t="n"/>
+      <c r="K38" s="277" t="n"/>
+      <c r="L38" s="277" t="n"/>
+      <c r="M38" s="277" t="n"/>
+      <c r="N38" s="277" t="n"/>
+      <c r="O38" s="277" t="n"/>
+      <c r="P38" s="277" t="n"/>
+      <c r="Q38" s="277" t="n"/>
+      <c r="R38" s="277" t="n"/>
+      <c r="S38" s="277" t="n"/>
+      <c r="T38" s="277" t="n"/>
+      <c r="U38" s="277" t="n"/>
+      <c r="V38" s="277" t="n"/>
+      <c r="W38" s="277" t="n"/>
+      <c r="X38" s="278" t="n"/>
+      <c r="Y38" s="306" t="n"/>
+      <c r="Z38" s="277" t="n"/>
+      <c r="AA38" s="277" t="n"/>
+      <c r="AB38" s="277" t="n"/>
+      <c r="AC38" s="277" t="n"/>
+      <c r="AD38" s="277" t="n"/>
+      <c r="AE38" s="277" t="n"/>
+      <c r="AF38" s="277" t="n"/>
+      <c r="AG38" s="277" t="n"/>
+      <c r="AH38" s="277" t="n"/>
+      <c r="AI38" s="277" t="n"/>
+      <c r="AJ38" s="277" t="n"/>
+      <c r="AK38" s="277" t="n"/>
+      <c r="AL38" s="277" t="n"/>
+      <c r="AM38" s="277" t="n"/>
+      <c r="AN38" s="277" t="n"/>
+      <c r="AO38" s="277" t="n"/>
+      <c r="AP38" s="277" t="n"/>
+      <c r="AQ38" s="277" t="n"/>
+      <c r="AR38" s="277" t="n"/>
+      <c r="AS38" s="277" t="n"/>
+      <c r="AT38" s="277" t="n"/>
+      <c r="AU38" s="277" t="n"/>
+      <c r="AV38" s="277" t="n"/>
+      <c r="AW38" s="278" t="n"/>
+      <c r="AX38" s="306" t="n"/>
+      <c r="AY38" s="277" t="n"/>
+      <c r="AZ38" s="277" t="n"/>
+      <c r="BA38" s="277" t="n"/>
+      <c r="BB38" s="277" t="n"/>
+      <c r="BC38" s="277" t="n"/>
+      <c r="BD38" s="277" t="n"/>
+      <c r="BE38" s="277" t="n"/>
+      <c r="BF38" s="277" t="n"/>
+      <c r="BG38" s="278" t="n"/>
+      <c r="BH38" s="807" t="n"/>
+      <c r="BI38" s="277" t="n"/>
+      <c r="BJ38" s="277" t="n"/>
+      <c r="BK38" s="277" t="n"/>
+      <c r="BL38" s="277" t="n"/>
+      <c r="BM38" s="277" t="n"/>
+      <c r="BN38" s="277" t="n"/>
+      <c r="BO38" s="277" t="n"/>
+      <c r="BP38" s="277" t="n"/>
+      <c r="BQ38" s="278" t="n"/>
+      <c r="BR38" s="306" t="n"/>
+      <c r="BS38" s="277" t="n"/>
+      <c r="BT38" s="277" t="n"/>
+      <c r="BU38" s="277" t="n"/>
+      <c r="BV38" s="277" t="n"/>
+      <c r="BW38" s="277" t="n"/>
+      <c r="BX38" s="278" t="n"/>
+      <c r="BY38" s="800" t="n"/>
+      <c r="BZ38" s="277" t="n"/>
+      <c r="CA38" s="277" t="n"/>
+      <c r="CB38" s="277" t="n"/>
+      <c r="CC38" s="277" t="n"/>
+      <c r="CD38" s="280" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="711" t="n">
+      <c r="A39" s="808" t="n">
         <v>5</v>
       </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="706" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-      <c r="L39" s="19" t="n"/>
-      <c r="M39" s="19" t="n"/>
-      <c r="N39" s="19" t="n"/>
-      <c r="O39" s="19" t="n"/>
-      <c r="P39" s="19" t="n"/>
-      <c r="Q39" s="19" t="n"/>
-      <c r="R39" s="19" t="n"/>
-      <c r="S39" s="19" t="n"/>
-      <c r="T39" s="19" t="n"/>
-      <c r="U39" s="19" t="n"/>
-      <c r="V39" s="19" t="n"/>
-      <c r="W39" s="19" t="n"/>
-      <c r="X39" s="22" t="n"/>
-      <c r="Y39" s="706" t="n"/>
-      <c r="Z39" s="19" t="n"/>
-      <c r="AA39" s="19" t="n"/>
-      <c r="AB39" s="19" t="n"/>
-      <c r="AC39" s="19" t="n"/>
-      <c r="AD39" s="19" t="n"/>
-      <c r="AE39" s="19" t="n"/>
-      <c r="AF39" s="19" t="n"/>
-      <c r="AG39" s="19" t="n"/>
-      <c r="AH39" s="19" t="n"/>
-      <c r="AI39" s="19" t="n"/>
-      <c r="AJ39" s="19" t="n"/>
-      <c r="AK39" s="19" t="n"/>
-      <c r="AL39" s="19" t="n"/>
-      <c r="AM39" s="19" t="n"/>
-      <c r="AN39" s="19" t="n"/>
-      <c r="AO39" s="19" t="n"/>
-      <c r="AP39" s="19" t="n"/>
-      <c r="AQ39" s="19" t="n"/>
-      <c r="AR39" s="19" t="n"/>
-      <c r="AS39" s="19" t="n"/>
-      <c r="AT39" s="19" t="n"/>
-      <c r="AU39" s="19" t="n"/>
-      <c r="AV39" s="19" t="n"/>
-      <c r="AW39" s="22" t="n"/>
-      <c r="AX39" s="706" t="n"/>
-      <c r="AY39" s="19" t="n"/>
-      <c r="AZ39" s="19" t="n"/>
-      <c r="BA39" s="19" t="n"/>
-      <c r="BB39" s="19" t="n"/>
-      <c r="BC39" s="19" t="n"/>
-      <c r="BD39" s="19" t="n"/>
-      <c r="BE39" s="19" t="n"/>
-      <c r="BF39" s="19" t="n"/>
-      <c r="BG39" s="22" t="n"/>
-      <c r="BH39" s="712" t="n"/>
-      <c r="BI39" s="19" t="n"/>
-      <c r="BJ39" s="19" t="n"/>
-      <c r="BK39" s="19" t="n"/>
-      <c r="BL39" s="19" t="n"/>
-      <c r="BM39" s="19" t="n"/>
-      <c r="BN39" s="19" t="n"/>
-      <c r="BO39" s="19" t="n"/>
-      <c r="BP39" s="19" t="n"/>
-      <c r="BQ39" s="22" t="n"/>
-      <c r="BR39" s="706" t="n"/>
-      <c r="BS39" s="19" t="n"/>
-      <c r="BT39" s="19" t="n"/>
-      <c r="BU39" s="19" t="n"/>
-      <c r="BV39" s="19" t="n"/>
-      <c r="BW39" s="19" t="n"/>
-      <c r="BX39" s="22" t="n"/>
-      <c r="BY39" s="706" t="n"/>
-      <c r="BZ39" s="19" t="n"/>
-      <c r="CA39" s="19" t="n"/>
-      <c r="CB39" s="19" t="n"/>
-      <c r="CC39" s="19" t="n"/>
-      <c r="CD39" s="24" t="n"/>
+      <c r="B39" s="283" t="n"/>
+      <c r="C39" s="283" t="n"/>
+      <c r="D39" s="285" t="n"/>
+      <c r="E39" s="802" t="n"/>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="n"/>
+      <c r="J39" s="283" t="n"/>
+      <c r="K39" s="283" t="n"/>
+      <c r="L39" s="283" t="n"/>
+      <c r="M39" s="283" t="n"/>
+      <c r="N39" s="283" t="n"/>
+      <c r="O39" s="283" t="n"/>
+      <c r="P39" s="283" t="n"/>
+      <c r="Q39" s="283" t="n"/>
+      <c r="R39" s="283" t="n"/>
+      <c r="S39" s="283" t="n"/>
+      <c r="T39" s="283" t="n"/>
+      <c r="U39" s="283" t="n"/>
+      <c r="V39" s="283" t="n"/>
+      <c r="W39" s="283" t="n"/>
+      <c r="X39" s="285" t="n"/>
+      <c r="Y39" s="802" t="n"/>
+      <c r="Z39" s="283" t="n"/>
+      <c r="AA39" s="283" t="n"/>
+      <c r="AB39" s="283" t="n"/>
+      <c r="AC39" s="283" t="n"/>
+      <c r="AD39" s="283" t="n"/>
+      <c r="AE39" s="283" t="n"/>
+      <c r="AF39" s="283" t="n"/>
+      <c r="AG39" s="283" t="n"/>
+      <c r="AH39" s="283" t="n"/>
+      <c r="AI39" s="283" t="n"/>
+      <c r="AJ39" s="283" t="n"/>
+      <c r="AK39" s="283" t="n"/>
+      <c r="AL39" s="283" t="n"/>
+      <c r="AM39" s="283" t="n"/>
+      <c r="AN39" s="283" t="n"/>
+      <c r="AO39" s="283" t="n"/>
+      <c r="AP39" s="283" t="n"/>
+      <c r="AQ39" s="283" t="n"/>
+      <c r="AR39" s="283" t="n"/>
+      <c r="AS39" s="283" t="n"/>
+      <c r="AT39" s="283" t="n"/>
+      <c r="AU39" s="283" t="n"/>
+      <c r="AV39" s="283" t="n"/>
+      <c r="AW39" s="285" t="n"/>
+      <c r="AX39" s="802" t="n"/>
+      <c r="AY39" s="283" t="n"/>
+      <c r="AZ39" s="283" t="n"/>
+      <c r="BA39" s="283" t="n"/>
+      <c r="BB39" s="283" t="n"/>
+      <c r="BC39" s="283" t="n"/>
+      <c r="BD39" s="283" t="n"/>
+      <c r="BE39" s="283" t="n"/>
+      <c r="BF39" s="283" t="n"/>
+      <c r="BG39" s="285" t="n"/>
+      <c r="BH39" s="809" t="n"/>
+      <c r="BI39" s="283" t="n"/>
+      <c r="BJ39" s="283" t="n"/>
+      <c r="BK39" s="283" t="n"/>
+      <c r="BL39" s="283" t="n"/>
+      <c r="BM39" s="283" t="n"/>
+      <c r="BN39" s="283" t="n"/>
+      <c r="BO39" s="283" t="n"/>
+      <c r="BP39" s="283" t="n"/>
+      <c r="BQ39" s="285" t="n"/>
+      <c r="BR39" s="802" t="n"/>
+      <c r="BS39" s="283" t="n"/>
+      <c r="BT39" s="283" t="n"/>
+      <c r="BU39" s="283" t="n"/>
+      <c r="BV39" s="283" t="n"/>
+      <c r="BW39" s="283" t="n"/>
+      <c r="BX39" s="285" t="n"/>
+      <c r="BY39" s="803" t="n"/>
+      <c r="BZ39" s="283" t="n"/>
+      <c r="CA39" s="283" t="n"/>
+      <c r="CB39" s="283" t="n"/>
+      <c r="CC39" s="283" t="n"/>
+      <c r="CD39" s="287" t="n"/>
     </row>
     <row r="40" ht="3" customHeight="1">
       <c r="A40" s="686" t="n"/>
@@ -11234,452 +11248,298 @@
       <c r="CD40" s="10" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="679" t="inlineStr">
+      <c r="A41" s="787" t="inlineStr">
         <is>
           <t>5.  REVIEW / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="27" t="n"/>
-      <c r="K41" s="27" t="n"/>
-      <c r="L41" s="27" t="n"/>
-      <c r="M41" s="27" t="n"/>
-      <c r="N41" s="27" t="n"/>
-      <c r="O41" s="27" t="n"/>
-      <c r="P41" s="27" t="n"/>
-      <c r="Q41" s="27" t="n"/>
-      <c r="R41" s="27" t="n"/>
-      <c r="S41" s="27" t="n"/>
-      <c r="T41" s="27" t="n"/>
-      <c r="U41" s="27" t="n"/>
-      <c r="V41" s="27" t="n"/>
-      <c r="W41" s="27" t="n"/>
-      <c r="X41" s="27" t="n"/>
-      <c r="Y41" s="27" t="n"/>
-      <c r="Z41" s="27" t="n"/>
-      <c r="AA41" s="27" t="n"/>
-      <c r="AB41" s="27" t="n"/>
-      <c r="AC41" s="27" t="n"/>
-      <c r="AD41" s="27" t="n"/>
-      <c r="AE41" s="27" t="n"/>
-      <c r="AF41" s="27" t="n"/>
-      <c r="AG41" s="27" t="n"/>
-      <c r="AH41" s="27" t="n"/>
-      <c r="AI41" s="27" t="n"/>
-      <c r="AJ41" s="27" t="n"/>
-      <c r="AK41" s="27" t="n"/>
-      <c r="AL41" s="27" t="n"/>
-      <c r="AM41" s="27" t="n"/>
-      <c r="AN41" s="27" t="n"/>
-      <c r="AO41" s="27" t="n"/>
-      <c r="AP41" s="27" t="n"/>
-      <c r="AQ41" s="27" t="n"/>
-      <c r="AR41" s="27" t="n"/>
-      <c r="AS41" s="27" t="n"/>
-      <c r="AT41" s="27" t="n"/>
-      <c r="AU41" s="27" t="n"/>
-      <c r="AV41" s="27" t="n"/>
-      <c r="AW41" s="27" t="n"/>
-      <c r="AX41" s="27" t="n"/>
-      <c r="AY41" s="27" t="n"/>
-      <c r="AZ41" s="27" t="n"/>
-      <c r="BA41" s="27" t="n"/>
-      <c r="BB41" s="27" t="n"/>
-      <c r="BC41" s="27" t="n"/>
-      <c r="BD41" s="27" t="n"/>
-      <c r="BE41" s="27" t="n"/>
-      <c r="BF41" s="27" t="n"/>
-      <c r="BG41" s="27" t="n"/>
-      <c r="BH41" s="27" t="n"/>
-      <c r="BI41" s="27" t="n"/>
-      <c r="BJ41" s="27" t="n"/>
-      <c r="BK41" s="27" t="n"/>
-      <c r="BL41" s="27" t="n"/>
-      <c r="BM41" s="27" t="n"/>
-      <c r="BN41" s="27" t="n"/>
-      <c r="BO41" s="27" t="n"/>
-      <c r="BP41" s="27" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="27" t="n"/>
-      <c r="BS41" s="27" t="n"/>
-      <c r="BT41" s="27" t="n"/>
-      <c r="BU41" s="27" t="n"/>
-      <c r="BV41" s="27" t="n"/>
-      <c r="BW41" s="27" t="n"/>
-      <c r="BX41" s="27" t="n"/>
-      <c r="BY41" s="27" t="n"/>
-      <c r="BZ41" s="27" t="n"/>
-      <c r="CA41" s="27" t="n"/>
-      <c r="CB41" s="27" t="n"/>
-      <c r="CC41" s="27" t="n"/>
-      <c r="CD41" s="28" t="n"/>
+      <c r="B41" s="289" t="n"/>
+      <c r="C41" s="289" t="n"/>
+      <c r="D41" s="289" t="n"/>
+      <c r="E41" s="289" t="n"/>
+      <c r="F41" s="289" t="n"/>
+      <c r="G41" s="289" t="n"/>
+      <c r="H41" s="289" t="n"/>
+      <c r="I41" s="289" t="n"/>
+      <c r="J41" s="289" t="n"/>
+      <c r="K41" s="289" t="n"/>
+      <c r="L41" s="289" t="n"/>
+      <c r="M41" s="289" t="n"/>
+      <c r="N41" s="289" t="n"/>
+      <c r="O41" s="289" t="n"/>
+      <c r="P41" s="289" t="n"/>
+      <c r="Q41" s="289" t="n"/>
+      <c r="R41" s="289" t="n"/>
+      <c r="S41" s="289" t="n"/>
+      <c r="T41" s="289" t="n"/>
+      <c r="U41" s="289" t="n"/>
+      <c r="V41" s="289" t="n"/>
+      <c r="W41" s="289" t="n"/>
+      <c r="X41" s="289" t="n"/>
+      <c r="Y41" s="289" t="n"/>
+      <c r="Z41" s="289" t="n"/>
+      <c r="AA41" s="289" t="n"/>
+      <c r="AB41" s="289" t="n"/>
+      <c r="AC41" s="289" t="n"/>
+      <c r="AD41" s="289" t="n"/>
+      <c r="AE41" s="289" t="n"/>
+      <c r="AF41" s="289" t="n"/>
+      <c r="AG41" s="289" t="n"/>
+      <c r="AH41" s="289" t="n"/>
+      <c r="AI41" s="289" t="n"/>
+      <c r="AJ41" s="289" t="n"/>
+      <c r="AK41" s="289" t="n"/>
+      <c r="AL41" s="289" t="n"/>
+      <c r="AM41" s="289" t="n"/>
+      <c r="AN41" s="289" t="n"/>
+      <c r="AO41" s="289" t="n"/>
+      <c r="AP41" s="289" t="n"/>
+      <c r="AQ41" s="289" t="n"/>
+      <c r="AR41" s="289" t="n"/>
+      <c r="AS41" s="289" t="n"/>
+      <c r="AT41" s="289" t="n"/>
+      <c r="AU41" s="289" t="n"/>
+      <c r="AV41" s="289" t="n"/>
+      <c r="AW41" s="289" t="n"/>
+      <c r="AX41" s="289" t="n"/>
+      <c r="AY41" s="289" t="n"/>
+      <c r="AZ41" s="289" t="n"/>
+      <c r="BA41" s="289" t="n"/>
+      <c r="BB41" s="289" t="n"/>
+      <c r="BC41" s="289" t="n"/>
+      <c r="BD41" s="289" t="n"/>
+      <c r="BE41" s="289" t="n"/>
+      <c r="BF41" s="289" t="n"/>
+      <c r="BG41" s="289" t="n"/>
+      <c r="BH41" s="289" t="n"/>
+      <c r="BI41" s="289" t="n"/>
+      <c r="BJ41" s="289" t="n"/>
+      <c r="BK41" s="289" t="n"/>
+      <c r="BL41" s="289" t="n"/>
+      <c r="BM41" s="289" t="n"/>
+      <c r="BN41" s="289" t="n"/>
+      <c r="BO41" s="289" t="n"/>
+      <c r="BP41" s="289" t="n"/>
+      <c r="BQ41" s="289" t="n"/>
+      <c r="BR41" s="289" t="n"/>
+      <c r="BS41" s="289" t="n"/>
+      <c r="BT41" s="289" t="n"/>
+      <c r="BU41" s="289" t="n"/>
+      <c r="BV41" s="289" t="n"/>
+      <c r="BW41" s="289" t="n"/>
+      <c r="BX41" s="289" t="n"/>
+      <c r="BY41" s="289" t="n"/>
+      <c r="BZ41" s="289" t="n"/>
+      <c r="CA41" s="289" t="n"/>
+      <c r="CB41" s="289" t="n"/>
+      <c r="CC41" s="289" t="n"/>
+      <c r="CD41" s="290" t="n"/>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="688" t="inlineStr">
+      <c r="A42" s="794" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="5" t="n"/>
-      <c r="T42" s="5" t="n"/>
-      <c r="U42" s="5" t="n"/>
-      <c r="V42" s="5" t="n"/>
-      <c r="W42" s="5" t="n"/>
-      <c r="X42" s="5" t="n"/>
-      <c r="Y42" s="5" t="n"/>
-      <c r="Z42" s="5" t="n"/>
-      <c r="AA42" s="6" t="n"/>
-      <c r="AB42" s="713" t="inlineStr">
+      <c r="B42" s="271" t="n"/>
+      <c r="C42" s="271" t="n"/>
+      <c r="D42" s="271" t="n"/>
+      <c r="E42" s="271" t="n"/>
+      <c r="F42" s="271" t="n"/>
+      <c r="G42" s="271" t="n"/>
+      <c r="H42" s="271" t="n"/>
+      <c r="I42" s="271" t="n"/>
+      <c r="J42" s="271" t="n"/>
+      <c r="K42" s="271" t="n"/>
+      <c r="L42" s="271" t="n"/>
+      <c r="M42" s="271" t="n"/>
+      <c r="N42" s="271" t="n"/>
+      <c r="O42" s="271" t="n"/>
+      <c r="P42" s="271" t="n"/>
+      <c r="Q42" s="271" t="n"/>
+      <c r="R42" s="271" t="n"/>
+      <c r="S42" s="271" t="n"/>
+      <c r="T42" s="271" t="n"/>
+      <c r="U42" s="271" t="n"/>
+      <c r="V42" s="271" t="n"/>
+      <c r="W42" s="271" t="n"/>
+      <c r="X42" s="271" t="n"/>
+      <c r="Y42" s="271" t="n"/>
+      <c r="Z42" s="271" t="n"/>
+      <c r="AA42" s="272" t="n"/>
+      <c r="AB42" s="810" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="AC42" s="5" t="n"/>
-      <c r="AD42" s="5" t="n"/>
-      <c r="AE42" s="5" t="n"/>
-      <c r="AF42" s="5" t="n"/>
-      <c r="AG42" s="5" t="n"/>
-      <c r="AH42" s="5" t="n"/>
-      <c r="AI42" s="5" t="n"/>
-      <c r="AJ42" s="5" t="n"/>
-      <c r="AK42" s="5" t="n"/>
-      <c r="AL42" s="5" t="n"/>
-      <c r="AM42" s="5" t="n"/>
-      <c r="AN42" s="5" t="n"/>
-      <c r="AO42" s="5" t="n"/>
-      <c r="AP42" s="5" t="n"/>
-      <c r="AQ42" s="5" t="n"/>
-      <c r="AR42" s="5" t="n"/>
-      <c r="AS42" s="5" t="n"/>
-      <c r="AT42" s="5" t="n"/>
-      <c r="AU42" s="5" t="n"/>
-      <c r="AV42" s="5" t="n"/>
-      <c r="AW42" s="5" t="n"/>
-      <c r="AX42" s="5" t="n"/>
-      <c r="AY42" s="5" t="n"/>
-      <c r="AZ42" s="5" t="n"/>
-      <c r="BA42" s="5" t="n"/>
-      <c r="BB42" s="6" t="n"/>
-      <c r="BC42" s="713" t="inlineStr">
+      <c r="AC42" s="271" t="n"/>
+      <c r="AD42" s="271" t="n"/>
+      <c r="AE42" s="271" t="n"/>
+      <c r="AF42" s="271" t="n"/>
+      <c r="AG42" s="271" t="n"/>
+      <c r="AH42" s="271" t="n"/>
+      <c r="AI42" s="271" t="n"/>
+      <c r="AJ42" s="271" t="n"/>
+      <c r="AK42" s="271" t="n"/>
+      <c r="AL42" s="271" t="n"/>
+      <c r="AM42" s="271" t="n"/>
+      <c r="AN42" s="271" t="n"/>
+      <c r="AO42" s="271" t="n"/>
+      <c r="AP42" s="271" t="n"/>
+      <c r="AQ42" s="271" t="n"/>
+      <c r="AR42" s="271" t="n"/>
+      <c r="AS42" s="271" t="n"/>
+      <c r="AT42" s="271" t="n"/>
+      <c r="AU42" s="271" t="n"/>
+      <c r="AV42" s="271" t="n"/>
+      <c r="AW42" s="271" t="n"/>
+      <c r="AX42" s="271" t="n"/>
+      <c r="AY42" s="271" t="n"/>
+      <c r="AZ42" s="271" t="n"/>
+      <c r="BA42" s="271" t="n"/>
+      <c r="BB42" s="272" t="n"/>
+      <c r="BC42" s="811" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="BD42" s="5" t="n"/>
-      <c r="BE42" s="5" t="n"/>
-      <c r="BF42" s="5" t="n"/>
-      <c r="BG42" s="5" t="n"/>
-      <c r="BH42" s="5" t="n"/>
-      <c r="BI42" s="5" t="n"/>
-      <c r="BJ42" s="5" t="n"/>
-      <c r="BK42" s="5" t="n"/>
-      <c r="BL42" s="5" t="n"/>
-      <c r="BM42" s="5" t="n"/>
-      <c r="BN42" s="5" t="n"/>
-      <c r="BO42" s="5" t="n"/>
-      <c r="BP42" s="5" t="n"/>
-      <c r="BQ42" s="5" t="n"/>
-      <c r="BR42" s="5" t="n"/>
-      <c r="BS42" s="5" t="n"/>
-      <c r="BT42" s="5" t="n"/>
-      <c r="BU42" s="5" t="n"/>
-      <c r="BV42" s="5" t="n"/>
-      <c r="BW42" s="5" t="n"/>
-      <c r="BX42" s="5" t="n"/>
-      <c r="BY42" s="5" t="n"/>
-      <c r="BZ42" s="5" t="n"/>
-      <c r="CA42" s="5" t="n"/>
-      <c r="CB42" s="5" t="n"/>
-      <c r="CC42" s="5" t="n"/>
-      <c r="CD42" s="8" t="n"/>
+      <c r="BD42" s="271" t="n"/>
+      <c r="BE42" s="271" t="n"/>
+      <c r="BF42" s="271" t="n"/>
+      <c r="BG42" s="271" t="n"/>
+      <c r="BH42" s="271" t="n"/>
+      <c r="BI42" s="271" t="n"/>
+      <c r="BJ42" s="271" t="n"/>
+      <c r="BK42" s="271" t="n"/>
+      <c r="BL42" s="271" t="n"/>
+      <c r="BM42" s="271" t="n"/>
+      <c r="BN42" s="271" t="n"/>
+      <c r="BO42" s="271" t="n"/>
+      <c r="BP42" s="271" t="n"/>
+      <c r="BQ42" s="271" t="n"/>
+      <c r="BR42" s="271" t="n"/>
+      <c r="BS42" s="271" t="n"/>
+      <c r="BT42" s="271" t="n"/>
+      <c r="BU42" s="271" t="n"/>
+      <c r="BV42" s="271" t="n"/>
+      <c r="BW42" s="271" t="n"/>
+      <c r="BX42" s="271" t="n"/>
+      <c r="BY42" s="271" t="n"/>
+      <c r="BZ42" s="271" t="n"/>
+      <c r="CA42" s="271" t="n"/>
+      <c r="CB42" s="271" t="n"/>
+      <c r="CC42" s="271" t="n"/>
+      <c r="CD42" s="274" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="714" t="inlineStr">
+      <c r="A43" s="812" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="12" t="n"/>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="12" t="n"/>
-      <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="12" t="n"/>
-      <c r="R43" s="12" t="n"/>
-      <c r="S43" s="12" t="n"/>
-      <c r="T43" s="12" t="n"/>
-      <c r="U43" s="12" t="n"/>
-      <c r="V43" s="12" t="n"/>
-      <c r="W43" s="12" t="n"/>
-      <c r="X43" s="12" t="n"/>
-      <c r="Y43" s="12" t="n"/>
-      <c r="Z43" s="12" t="n"/>
-      <c r="AA43" s="13" t="n"/>
-      <c r="AB43" s="715" t="inlineStr">
+      <c r="AA43" s="813" t="n"/>
+      <c r="AB43" s="814" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AC43" s="12" t="n"/>
-      <c r="AD43" s="12" t="n"/>
-      <c r="AE43" s="12" t="n"/>
-      <c r="AF43" s="12" t="n"/>
-      <c r="AG43" s="12" t="n"/>
-      <c r="AH43" s="12" t="n"/>
-      <c r="AI43" s="12" t="n"/>
-      <c r="AJ43" s="12" t="n"/>
-      <c r="AK43" s="12" t="n"/>
-      <c r="AL43" s="12" t="n"/>
-      <c r="AM43" s="12" t="n"/>
-      <c r="AN43" s="12" t="n"/>
-      <c r="AO43" s="12" t="n"/>
-      <c r="AP43" s="12" t="n"/>
-      <c r="AQ43" s="12" t="n"/>
-      <c r="AR43" s="12" t="n"/>
-      <c r="AS43" s="12" t="n"/>
-      <c r="AT43" s="12" t="n"/>
-      <c r="AU43" s="12" t="n"/>
-      <c r="AV43" s="12" t="n"/>
-      <c r="AW43" s="12" t="n"/>
-      <c r="AX43" s="12" t="n"/>
-      <c r="AY43" s="12" t="n"/>
-      <c r="AZ43" s="12" t="n"/>
-      <c r="BA43" s="12" t="n"/>
-      <c r="BB43" s="13" t="n"/>
-      <c r="BC43" s="715" t="inlineStr">
+      <c r="BB43" s="813" t="n"/>
+      <c r="BC43" s="815" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="BD43" s="12" t="n"/>
-      <c r="BE43" s="12" t="n"/>
-      <c r="BF43" s="12" t="n"/>
-      <c r="BG43" s="12" t="n"/>
-      <c r="BH43" s="12" t="n"/>
-      <c r="BI43" s="12" t="n"/>
-      <c r="BJ43" s="12" t="n"/>
-      <c r="BK43" s="12" t="n"/>
-      <c r="BL43" s="12" t="n"/>
-      <c r="BM43" s="12" t="n"/>
-      <c r="BN43" s="12" t="n"/>
-      <c r="BO43" s="12" t="n"/>
-      <c r="BP43" s="12" t="n"/>
-      <c r="BQ43" s="12" t="n"/>
-      <c r="BR43" s="12" t="n"/>
-      <c r="BS43" s="12" t="n"/>
-      <c r="BT43" s="12" t="n"/>
-      <c r="BU43" s="12" t="n"/>
-      <c r="BV43" s="12" t="n"/>
-      <c r="BW43" s="12" t="n"/>
-      <c r="BX43" s="12" t="n"/>
-      <c r="BY43" s="12" t="n"/>
-      <c r="BZ43" s="12" t="n"/>
-      <c r="CA43" s="12" t="n"/>
-      <c r="CB43" s="12" t="n"/>
-      <c r="CC43" s="12" t="n"/>
-      <c r="CD43" s="15" t="n"/>
+      <c r="CD43" s="326" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="12" t="n"/>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="12" t="n"/>
-      <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="12" t="n"/>
-      <c r="R44" s="12" t="n"/>
-      <c r="S44" s="12" t="n"/>
-      <c r="T44" s="12" t="n"/>
-      <c r="U44" s="12" t="n"/>
-      <c r="V44" s="12" t="n"/>
-      <c r="W44" s="12" t="n"/>
-      <c r="X44" s="12" t="n"/>
-      <c r="Y44" s="12" t="n"/>
-      <c r="Z44" s="12" t="n"/>
-      <c r="AA44" s="13" t="n"/>
-      <c r="AB44" s="12" t="n"/>
-      <c r="AC44" s="12" t="n"/>
-      <c r="AD44" s="12" t="n"/>
-      <c r="AE44" s="12" t="n"/>
-      <c r="AF44" s="12" t="n"/>
-      <c r="AG44" s="12" t="n"/>
-      <c r="AH44" s="12" t="n"/>
-      <c r="AI44" s="12" t="n"/>
-      <c r="AJ44" s="12" t="n"/>
-      <c r="AK44" s="12" t="n"/>
-      <c r="AL44" s="12" t="n"/>
-      <c r="AM44" s="12" t="n"/>
-      <c r="AN44" s="12" t="n"/>
-      <c r="AO44" s="12" t="n"/>
-      <c r="AP44" s="12" t="n"/>
-      <c r="AQ44" s="12" t="n"/>
-      <c r="AR44" s="12" t="n"/>
-      <c r="AS44" s="12" t="n"/>
-      <c r="AT44" s="12" t="n"/>
-      <c r="AU44" s="12" t="n"/>
-      <c r="AV44" s="12" t="n"/>
-      <c r="AW44" s="12" t="n"/>
-      <c r="AX44" s="12" t="n"/>
-      <c r="AY44" s="12" t="n"/>
-      <c r="AZ44" s="12" t="n"/>
-      <c r="BA44" s="12" t="n"/>
-      <c r="BB44" s="13" t="n"/>
-      <c r="BC44" s="12" t="n"/>
-      <c r="BD44" s="12" t="n"/>
-      <c r="BE44" s="12" t="n"/>
-      <c r="BF44" s="12" t="n"/>
-      <c r="BG44" s="12" t="n"/>
-      <c r="BH44" s="12" t="n"/>
-      <c r="BI44" s="12" t="n"/>
-      <c r="BJ44" s="12" t="n"/>
-      <c r="BK44" s="12" t="n"/>
-      <c r="BL44" s="12" t="n"/>
-      <c r="BM44" s="12" t="n"/>
-      <c r="BN44" s="12" t="n"/>
-      <c r="BO44" s="12" t="n"/>
-      <c r="BP44" s="12" t="n"/>
-      <c r="BQ44" s="12" t="n"/>
-      <c r="BR44" s="12" t="n"/>
-      <c r="BS44" s="12" t="n"/>
-      <c r="BT44" s="12" t="n"/>
-      <c r="BU44" s="12" t="n"/>
-      <c r="BV44" s="12" t="n"/>
-      <c r="BW44" s="12" t="n"/>
-      <c r="BX44" s="12" t="n"/>
-      <c r="BY44" s="12" t="n"/>
-      <c r="BZ44" s="12" t="n"/>
-      <c r="CA44" s="12" t="n"/>
-      <c r="CB44" s="12" t="n"/>
-      <c r="CC44" s="12" t="n"/>
-      <c r="CD44" s="15" t="n"/>
+      <c r="A44" s="275" t="n"/>
+      <c r="AA44" s="813" t="n"/>
+      <c r="BB44" s="813" t="n"/>
+      <c r="CD44" s="326" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="18" t="n"/>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="19" t="n"/>
-      <c r="K45" s="19" t="n"/>
-      <c r="L45" s="19" t="n"/>
-      <c r="M45" s="19" t="n"/>
-      <c r="N45" s="19" t="n"/>
-      <c r="O45" s="19" t="n"/>
-      <c r="P45" s="19" t="n"/>
-      <c r="Q45" s="19" t="n"/>
-      <c r="R45" s="19" t="n"/>
-      <c r="S45" s="19" t="n"/>
-      <c r="T45" s="19" t="n"/>
-      <c r="U45" s="19" t="n"/>
-      <c r="V45" s="19" t="n"/>
-      <c r="W45" s="19" t="n"/>
-      <c r="X45" s="19" t="n"/>
-      <c r="Y45" s="19" t="n"/>
-      <c r="Z45" s="19" t="n"/>
-      <c r="AA45" s="22" t="n"/>
-      <c r="AB45" s="19" t="n"/>
-      <c r="AC45" s="19" t="n"/>
-      <c r="AD45" s="19" t="n"/>
-      <c r="AE45" s="19" t="n"/>
-      <c r="AF45" s="19" t="n"/>
-      <c r="AG45" s="19" t="n"/>
-      <c r="AH45" s="19" t="n"/>
-      <c r="AI45" s="19" t="n"/>
-      <c r="AJ45" s="19" t="n"/>
-      <c r="AK45" s="19" t="n"/>
-      <c r="AL45" s="19" t="n"/>
-      <c r="AM45" s="19" t="n"/>
-      <c r="AN45" s="19" t="n"/>
-      <c r="AO45" s="19" t="n"/>
-      <c r="AP45" s="19" t="n"/>
-      <c r="AQ45" s="19" t="n"/>
-      <c r="AR45" s="19" t="n"/>
-      <c r="AS45" s="19" t="n"/>
-      <c r="AT45" s="19" t="n"/>
-      <c r="AU45" s="19" t="n"/>
-      <c r="AV45" s="19" t="n"/>
-      <c r="AW45" s="19" t="n"/>
-      <c r="AX45" s="19" t="n"/>
-      <c r="AY45" s="19" t="n"/>
-      <c r="AZ45" s="19" t="n"/>
-      <c r="BA45" s="19" t="n"/>
-      <c r="BB45" s="22" t="n"/>
-      <c r="BC45" s="19" t="n"/>
-      <c r="BD45" s="19" t="n"/>
-      <c r="BE45" s="19" t="n"/>
-      <c r="BF45" s="19" t="n"/>
-      <c r="BG45" s="19" t="n"/>
-      <c r="BH45" s="19" t="n"/>
-      <c r="BI45" s="19" t="n"/>
-      <c r="BJ45" s="19" t="n"/>
-      <c r="BK45" s="19" t="n"/>
-      <c r="BL45" s="19" t="n"/>
-      <c r="BM45" s="19" t="n"/>
-      <c r="BN45" s="19" t="n"/>
-      <c r="BO45" s="19" t="n"/>
-      <c r="BP45" s="19" t="n"/>
-      <c r="BQ45" s="19" t="n"/>
-      <c r="BR45" s="19" t="n"/>
-      <c r="BS45" s="19" t="n"/>
-      <c r="BT45" s="19" t="n"/>
-      <c r="BU45" s="19" t="n"/>
-      <c r="BV45" s="19" t="n"/>
-      <c r="BW45" s="19" t="n"/>
-      <c r="BX45" s="19" t="n"/>
-      <c r="BY45" s="19" t="n"/>
-      <c r="BZ45" s="19" t="n"/>
-      <c r="CA45" s="19" t="n"/>
-      <c r="CB45" s="19" t="n"/>
-      <c r="CC45" s="19" t="n"/>
-      <c r="CD45" s="24" t="n"/>
+      <c r="A45" s="281" t="n"/>
+      <c r="B45" s="277" t="n"/>
+      <c r="C45" s="277" t="n"/>
+      <c r="D45" s="277" t="n"/>
+      <c r="E45" s="277" t="n"/>
+      <c r="F45" s="277" t="n"/>
+      <c r="G45" s="277" t="n"/>
+      <c r="H45" s="277" t="n"/>
+      <c r="I45" s="277" t="n"/>
+      <c r="J45" s="277" t="n"/>
+      <c r="K45" s="277" t="n"/>
+      <c r="L45" s="277" t="n"/>
+      <c r="M45" s="277" t="n"/>
+      <c r="N45" s="277" t="n"/>
+      <c r="O45" s="277" t="n"/>
+      <c r="P45" s="277" t="n"/>
+      <c r="Q45" s="277" t="n"/>
+      <c r="R45" s="277" t="n"/>
+      <c r="S45" s="277" t="n"/>
+      <c r="T45" s="277" t="n"/>
+      <c r="U45" s="277" t="n"/>
+      <c r="V45" s="277" t="n"/>
+      <c r="W45" s="277" t="n"/>
+      <c r="X45" s="277" t="n"/>
+      <c r="Y45" s="277" t="n"/>
+      <c r="Z45" s="277" t="n"/>
+      <c r="AA45" s="278" t="n"/>
+      <c r="AB45" s="277" t="n"/>
+      <c r="AC45" s="277" t="n"/>
+      <c r="AD45" s="277" t="n"/>
+      <c r="AE45" s="277" t="n"/>
+      <c r="AF45" s="277" t="n"/>
+      <c r="AG45" s="277" t="n"/>
+      <c r="AH45" s="277" t="n"/>
+      <c r="AI45" s="277" t="n"/>
+      <c r="AJ45" s="277" t="n"/>
+      <c r="AK45" s="277" t="n"/>
+      <c r="AL45" s="277" t="n"/>
+      <c r="AM45" s="277" t="n"/>
+      <c r="AN45" s="277" t="n"/>
+      <c r="AO45" s="277" t="n"/>
+      <c r="AP45" s="277" t="n"/>
+      <c r="AQ45" s="277" t="n"/>
+      <c r="AR45" s="277" t="n"/>
+      <c r="AS45" s="277" t="n"/>
+      <c r="AT45" s="277" t="n"/>
+      <c r="AU45" s="277" t="n"/>
+      <c r="AV45" s="277" t="n"/>
+      <c r="AW45" s="277" t="n"/>
+      <c r="AX45" s="277" t="n"/>
+      <c r="AY45" s="277" t="n"/>
+      <c r="AZ45" s="277" t="n"/>
+      <c r="BA45" s="277" t="n"/>
+      <c r="BB45" s="278" t="n"/>
+      <c r="BC45" s="277" t="n"/>
+      <c r="BD45" s="277" t="n"/>
+      <c r="BE45" s="277" t="n"/>
+      <c r="BF45" s="277" t="n"/>
+      <c r="BG45" s="277" t="n"/>
+      <c r="BH45" s="277" t="n"/>
+      <c r="BI45" s="277" t="n"/>
+      <c r="BJ45" s="277" t="n"/>
+      <c r="BK45" s="277" t="n"/>
+      <c r="BL45" s="277" t="n"/>
+      <c r="BM45" s="277" t="n"/>
+      <c r="BN45" s="277" t="n"/>
+      <c r="BO45" s="277" t="n"/>
+      <c r="BP45" s="277" t="n"/>
+      <c r="BQ45" s="277" t="n"/>
+      <c r="BR45" s="277" t="n"/>
+      <c r="BS45" s="277" t="n"/>
+      <c r="BT45" s="277" t="n"/>
+      <c r="BU45" s="277" t="n"/>
+      <c r="BV45" s="277" t="n"/>
+      <c r="BW45" s="277" t="n"/>
+      <c r="BX45" s="277" t="n"/>
+      <c r="BY45" s="277" t="n"/>
+      <c r="BZ45" s="277" t="n"/>
+      <c r="CA45" s="277" t="n"/>
+      <c r="CB45" s="277" t="n"/>
+      <c r="CC45" s="277" t="n"/>
+      <c r="CD45" s="280" t="n"/>
     </row>
     <row r="46" ht="3" customHeight="1">
       <c r="A46" s="686" t="n"/>
@@ -11766,92 +11626,92 @@
       <c r="CD46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="679" t="inlineStr">
+      <c r="A47" s="787" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-311_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="27" t="n"/>
-      <c r="J47" s="27" t="n"/>
-      <c r="K47" s="27" t="n"/>
-      <c r="L47" s="27" t="n"/>
-      <c r="M47" s="27" t="n"/>
-      <c r="N47" s="27" t="n"/>
-      <c r="O47" s="27" t="n"/>
-      <c r="P47" s="27" t="n"/>
-      <c r="Q47" s="27" t="n"/>
-      <c r="R47" s="27" t="n"/>
-      <c r="S47" s="27" t="n"/>
-      <c r="T47" s="27" t="n"/>
-      <c r="U47" s="27" t="n"/>
-      <c r="V47" s="27" t="n"/>
-      <c r="W47" s="27" t="n"/>
-      <c r="X47" s="27" t="n"/>
-      <c r="Y47" s="27" t="n"/>
-      <c r="Z47" s="27" t="n"/>
-      <c r="AA47" s="27" t="n"/>
-      <c r="AB47" s="27" t="n"/>
-      <c r="AC47" s="27" t="n"/>
-      <c r="AD47" s="27" t="n"/>
-      <c r="AE47" s="27" t="n"/>
-      <c r="AF47" s="27" t="n"/>
-      <c r="AG47" s="27" t="n"/>
-      <c r="AH47" s="27" t="n"/>
-      <c r="AI47" s="27" t="n"/>
-      <c r="AJ47" s="27" t="n"/>
-      <c r="AK47" s="27" t="n"/>
-      <c r="AL47" s="27" t="n"/>
-      <c r="AM47" s="27" t="n"/>
-      <c r="AN47" s="27" t="n"/>
-      <c r="AO47" s="27" t="n"/>
-      <c r="AP47" s="27" t="n"/>
-      <c r="AQ47" s="27" t="n"/>
-      <c r="AR47" s="27" t="n"/>
-      <c r="AS47" s="27" t="n"/>
-      <c r="AT47" s="27" t="n"/>
-      <c r="AU47" s="27" t="n"/>
-      <c r="AV47" s="27" t="n"/>
-      <c r="AW47" s="27" t="n"/>
-      <c r="AX47" s="27" t="n"/>
-      <c r="AY47" s="27" t="n"/>
-      <c r="AZ47" s="27" t="n"/>
-      <c r="BA47" s="27" t="n"/>
-      <c r="BB47" s="27" t="n"/>
-      <c r="BC47" s="27" t="n"/>
-      <c r="BD47" s="27" t="n"/>
-      <c r="BE47" s="27" t="n"/>
-      <c r="BF47" s="27" t="n"/>
-      <c r="BG47" s="27" t="n"/>
-      <c r="BH47" s="27" t="n"/>
-      <c r="BI47" s="27" t="n"/>
-      <c r="BJ47" s="27" t="n"/>
-      <c r="BK47" s="27" t="n"/>
-      <c r="BL47" s="27" t="n"/>
-      <c r="BM47" s="27" t="n"/>
-      <c r="BN47" s="27" t="n"/>
-      <c r="BO47" s="27" t="n"/>
-      <c r="BP47" s="27" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
-      <c r="BR47" s="27" t="n"/>
-      <c r="BS47" s="27" t="n"/>
-      <c r="BT47" s="27" t="n"/>
-      <c r="BU47" s="27" t="n"/>
-      <c r="BV47" s="27" t="n"/>
-      <c r="BW47" s="27" t="n"/>
-      <c r="BX47" s="27" t="n"/>
-      <c r="BY47" s="27" t="n"/>
-      <c r="BZ47" s="27" t="n"/>
-      <c r="CA47" s="27" t="n"/>
-      <c r="CB47" s="27" t="n"/>
-      <c r="CC47" s="27" t="n"/>
-      <c r="CD47" s="28" t="n"/>
+      <c r="B47" s="289" t="n"/>
+      <c r="C47" s="289" t="n"/>
+      <c r="D47" s="289" t="n"/>
+      <c r="E47" s="289" t="n"/>
+      <c r="F47" s="289" t="n"/>
+      <c r="G47" s="289" t="n"/>
+      <c r="H47" s="289" t="n"/>
+      <c r="I47" s="289" t="n"/>
+      <c r="J47" s="289" t="n"/>
+      <c r="K47" s="289" t="n"/>
+      <c r="L47" s="289" t="n"/>
+      <c r="M47" s="289" t="n"/>
+      <c r="N47" s="289" t="n"/>
+      <c r="O47" s="289" t="n"/>
+      <c r="P47" s="289" t="n"/>
+      <c r="Q47" s="289" t="n"/>
+      <c r="R47" s="289" t="n"/>
+      <c r="S47" s="289" t="n"/>
+      <c r="T47" s="289" t="n"/>
+      <c r="U47" s="289" t="n"/>
+      <c r="V47" s="289" t="n"/>
+      <c r="W47" s="289" t="n"/>
+      <c r="X47" s="289" t="n"/>
+      <c r="Y47" s="289" t="n"/>
+      <c r="Z47" s="289" t="n"/>
+      <c r="AA47" s="289" t="n"/>
+      <c r="AB47" s="289" t="n"/>
+      <c r="AC47" s="289" t="n"/>
+      <c r="AD47" s="289" t="n"/>
+      <c r="AE47" s="289" t="n"/>
+      <c r="AF47" s="289" t="n"/>
+      <c r="AG47" s="289" t="n"/>
+      <c r="AH47" s="289" t="n"/>
+      <c r="AI47" s="289" t="n"/>
+      <c r="AJ47" s="289" t="n"/>
+      <c r="AK47" s="289" t="n"/>
+      <c r="AL47" s="289" t="n"/>
+      <c r="AM47" s="289" t="n"/>
+      <c r="AN47" s="289" t="n"/>
+      <c r="AO47" s="289" t="n"/>
+      <c r="AP47" s="289" t="n"/>
+      <c r="AQ47" s="289" t="n"/>
+      <c r="AR47" s="289" t="n"/>
+      <c r="AS47" s="289" t="n"/>
+      <c r="AT47" s="289" t="n"/>
+      <c r="AU47" s="289" t="n"/>
+      <c r="AV47" s="289" t="n"/>
+      <c r="AW47" s="289" t="n"/>
+      <c r="AX47" s="289" t="n"/>
+      <c r="AY47" s="289" t="n"/>
+      <c r="AZ47" s="289" t="n"/>
+      <c r="BA47" s="289" t="n"/>
+      <c r="BB47" s="289" t="n"/>
+      <c r="BC47" s="289" t="n"/>
+      <c r="BD47" s="289" t="n"/>
+      <c r="BE47" s="289" t="n"/>
+      <c r="BF47" s="289" t="n"/>
+      <c r="BG47" s="289" t="n"/>
+      <c r="BH47" s="289" t="n"/>
+      <c r="BI47" s="289" t="n"/>
+      <c r="BJ47" s="289" t="n"/>
+      <c r="BK47" s="289" t="n"/>
+      <c r="BL47" s="289" t="n"/>
+      <c r="BM47" s="289" t="n"/>
+      <c r="BN47" s="289" t="n"/>
+      <c r="BO47" s="289" t="n"/>
+      <c r="BP47" s="289" t="n"/>
+      <c r="BQ47" s="289" t="n"/>
+      <c r="BR47" s="289" t="n"/>
+      <c r="BS47" s="289" t="n"/>
+      <c r="BT47" s="289" t="n"/>
+      <c r="BU47" s="289" t="n"/>
+      <c r="BV47" s="289" t="n"/>
+      <c r="BW47" s="289" t="n"/>
+      <c r="BX47" s="289" t="n"/>
+      <c r="BY47" s="289" t="n"/>
+      <c r="BZ47" s="289" t="n"/>
+      <c r="CA47" s="289" t="n"/>
+      <c r="CB47" s="289" t="n"/>
+      <c r="CC47" s="289" t="n"/>
+      <c r="CD47" s="290" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -12262,7 +12122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -12898,7 +12758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -13665,18 +13525,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="345" t="n"/>
-      <c r="B1" s="53" t="n"/>
+      <c r="A1" s="399" t="n"/>
+      <c r="B1" s="325" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>CHARACTERISTIC RESULTS</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="268" t="n"/>
       <c r="I1" s="716" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -13719,14 +13579,9 @@
       <c r="AN1" s="719" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="326" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="I2" s="720" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -13769,14 +13624,9 @@
       <c r="AN2" s="723" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="326" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="I3" s="720" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -13819,18 +13669,13 @@
       <c r="AN3" s="723" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="326" t="n"/>
       <c r="C4" s="724" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
       <c r="I4" s="725" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -13869,18 +13714,18 @@
       <c r="AN4" s="723" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="727" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
+      <c r="H5" s="283" t="n"/>
       <c r="I5" s="728" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -13966,15 +13811,15 @@
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="289" t="n"/>
+      <c r="J7" s="289" t="n"/>
       <c r="K7" s="733" t="n"/>
       <c r="L7" s="733" t="n"/>
       <c r="M7" s="733" t="n"/>
@@ -14007,32 +13852,32 @@
       <c r="AN7" s="734" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="735" t="inlineStr">
+      <c r="A8" s="769" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="736" t="inlineStr">
+      <c r="B8" s="272" t="n"/>
+      <c r="C8" s="816" t="inlineStr">
         <is>
           <t>FRM-311 · FAI REPORT</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="737" t="inlineStr">
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="272" t="n"/>
+      <c r="F8" s="770" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="736" t="inlineStr">
+      <c r="G8" s="272" t="n"/>
+      <c r="H8" s="816" t="inlineStr">
         <is>
           <t>CHAR_RESULTS</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="6" t="n"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="272" t="n"/>
       <c r="K8" s="738" t="n"/>
       <c r="L8" s="738" t="n"/>
       <c r="M8" s="738" t="n"/>
@@ -14065,28 +13910,28 @@
       <c r="AN8" s="739" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="740" t="inlineStr">
+      <c r="A9" s="771" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="741" t="inlineStr">
+      <c r="B9" s="278" t="n"/>
+      <c r="C9" s="817" t="inlineStr">
         <is>
           <t>Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="742" t="inlineStr">
+      <c r="D9" s="277" t="n"/>
+      <c r="E9" s="278" t="n"/>
+      <c r="F9" s="772" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="741" t="inlineStr"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="13" t="n"/>
+      <c r="G9" s="278" t="n"/>
+      <c r="H9" s="817" t="inlineStr"/>
+      <c r="I9" s="277" t="n"/>
+      <c r="J9" s="278" t="n"/>
       <c r="K9" s="743" t="n"/>
       <c r="L9" s="743" t="n"/>
       <c r="M9" s="743" t="n"/>
@@ -14119,28 +13964,28 @@
       <c r="AN9" s="744" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="740" t="inlineStr">
+      <c r="A10" s="771" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="741" t="inlineStr">
+      <c r="B10" s="278" t="n"/>
+      <c r="C10" s="817" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="742" t="inlineStr">
+      <c r="D10" s="277" t="n"/>
+      <c r="E10" s="278" t="n"/>
+      <c r="F10" s="772" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="741" t="inlineStr"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="13" t="n"/>
+      <c r="G10" s="278" t="n"/>
+      <c r="H10" s="817" t="inlineStr"/>
+      <c r="I10" s="277" t="n"/>
+      <c r="J10" s="278" t="n"/>
       <c r="K10" s="743" t="n"/>
       <c r="L10" s="743" t="n"/>
       <c r="M10" s="743" t="n"/>
@@ -14173,32 +14018,32 @@
       <c r="AN10" s="744" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="740" t="inlineStr">
+      <c r="A11" s="771" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="741" t="inlineStr">
+      <c r="B11" s="278" t="n"/>
+      <c r="C11" s="817" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="742" t="inlineStr">
+      <c r="D11" s="277" t="n"/>
+      <c r="E11" s="278" t="n"/>
+      <c r="F11" s="772" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="741" t="inlineStr">
+      <c r="G11" s="278" t="n"/>
+      <c r="H11" s="817" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="13" t="n"/>
+      <c r="I11" s="277" t="n"/>
+      <c r="J11" s="278" t="n"/>
       <c r="K11" s="745" t="n"/>
       <c r="L11" s="745" t="n"/>
       <c r="M11" s="745" t="n"/>
@@ -14231,32 +14076,32 @@
       <c r="AN11" s="746" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="747" t="inlineStr">
+      <c r="A12" s="773" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="748" t="inlineStr">
+      <c r="B12" s="285" t="n"/>
+      <c r="C12" s="818" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="749" t="inlineStr">
+      <c r="D12" s="283" t="n"/>
+      <c r="E12" s="285" t="n"/>
+      <c r="F12" s="774" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="748" t="inlineStr">
+      <c r="G12" s="285" t="n"/>
+      <c r="H12" s="818" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="22" t="n"/>
+      <c r="I12" s="283" t="n"/>
+      <c r="J12" s="285" t="n"/>
       <c r="K12" s="750" t="n"/>
       <c r="L12" s="750" t="n"/>
       <c r="M12" s="750" t="n"/>
@@ -14336,15 +14181,15 @@
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
+      <c r="I14" s="289" t="n"/>
+      <c r="J14" s="289" t="n"/>
       <c r="K14" s="733" t="n"/>
       <c r="L14" s="733" t="n"/>
       <c r="M14" s="733" t="n"/>
@@ -14382,15 +14227,15 @@
           <t>Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="27" t="n"/>
+      <c r="B15" s="289" t="n"/>
+      <c r="C15" s="289" t="n"/>
+      <c r="D15" s="289" t="n"/>
+      <c r="E15" s="289" t="n"/>
+      <c r="F15" s="289" t="n"/>
+      <c r="G15" s="289" t="n"/>
+      <c r="H15" s="289" t="n"/>
+      <c r="I15" s="289" t="n"/>
+      <c r="J15" s="289" t="n"/>
       <c r="K15" s="733" t="n"/>
       <c r="L15" s="733" t="n"/>
       <c r="M15" s="733" t="n"/>
@@ -15362,15 +15207,15 @@
           <t>NOTICE  —  Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="27" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="27" t="n"/>
-      <c r="H36" s="27" t="n"/>
-      <c r="I36" s="27" t="n"/>
-      <c r="J36" s="27" t="n"/>
+      <c r="B36" s="289" t="n"/>
+      <c r="C36" s="289" t="n"/>
+      <c r="D36" s="289" t="n"/>
+      <c r="E36" s="289" t="n"/>
+      <c r="F36" s="289" t="n"/>
+      <c r="G36" s="289" t="n"/>
+      <c r="H36" s="289" t="n"/>
+      <c r="I36" s="289" t="n"/>
+      <c r="J36" s="289" t="n"/>
       <c r="K36" s="733" t="n"/>
       <c r="L36" s="733" t="n"/>
       <c r="M36" s="733" t="n"/>
@@ -15684,16 +15529,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="345" t="n"/>
-      <c r="B1" s="53" t="n"/>
+      <c r="A1" s="399" t="n"/>
+      <c r="B1" s="325" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>MATERIAL / SPECIAL PROCESS CERTIFICATION MATRIX</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
       <c r="G1" s="757" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -15738,12 +15583,9 @@
       <c r="AN1" s="719" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="326" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="G2" s="759" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -15788,12 +15630,9 @@
       <c r="AN2" s="723" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="326" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="G3" s="759" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -15838,16 +15677,13 @@
       <c r="AN3" s="723" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="326" t="n"/>
       <c r="C4" s="724" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
       <c r="G4" s="759" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -15888,16 +15724,16 @@
       <c r="AN4" s="723" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="727" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
       <c r="G5" s="761" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -15985,13 +15821,13 @@
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
       <c r="I7" s="733" t="n"/>
       <c r="J7" s="733" t="n"/>
       <c r="K7" s="733" t="n"/>
@@ -16026,30 +15862,30 @@
       <c r="AN7" s="734" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="735" t="inlineStr">
+      <c r="A8" s="769" t="inlineStr">
         <is>
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="736" t="inlineStr">
+      <c r="B8" s="272" t="n"/>
+      <c r="C8" s="816" t="inlineStr">
         <is>
           <t>FRM-311 · FAI REPORT</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="737" t="inlineStr">
+      <c r="D8" s="272" t="n"/>
+      <c r="E8" s="770" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="736" t="inlineStr">
+      <c r="F8" s="272" t="n"/>
+      <c r="G8" s="816" t="inlineStr">
         <is>
           <t>MATL_PROC</t>
         </is>
       </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="H8" s="272" t="n"/>
       <c r="I8" s="738" t="n"/>
       <c r="J8" s="738" t="n"/>
       <c r="K8" s="738" t="n"/>
@@ -16084,26 +15920,26 @@
       <c r="AN8" s="739" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="740" t="inlineStr">
+      <c r="A9" s="771" t="inlineStr">
         <is>
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="741" t="inlineStr">
+      <c r="B9" s="278" t="n"/>
+      <c r="C9" s="817" t="inlineStr">
         <is>
           <t>Material, special-process and supporting certification linkage for the FAI package.</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="742" t="inlineStr">
+      <c r="D9" s="278" t="n"/>
+      <c r="E9" s="772" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="741" t="inlineStr"/>
-      <c r="H9" s="13" t="n"/>
+      <c r="F9" s="278" t="n"/>
+      <c r="G9" s="817" t="inlineStr"/>
+      <c r="H9" s="278" t="n"/>
       <c r="I9" s="743" t="n"/>
       <c r="J9" s="743" t="n"/>
       <c r="K9" s="743" t="n"/>
@@ -16138,26 +15974,26 @@
       <c r="AN9" s="744" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="740" t="inlineStr">
+      <c r="A10" s="771" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="741" t="inlineStr">
+      <c r="B10" s="278" t="n"/>
+      <c r="C10" s="817" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="742" t="inlineStr">
+      <c r="D10" s="278" t="n"/>
+      <c r="E10" s="772" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="741" t="inlineStr"/>
-      <c r="H10" s="13" t="n"/>
+      <c r="F10" s="278" t="n"/>
+      <c r="G10" s="817" t="inlineStr"/>
+      <c r="H10" s="278" t="n"/>
       <c r="I10" s="743" t="n"/>
       <c r="J10" s="743" t="n"/>
       <c r="K10" s="743" t="n"/>
@@ -16192,30 +16028,30 @@
       <c r="AN10" s="744" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="740" t="inlineStr">
+      <c r="A11" s="771" t="inlineStr">
         <is>
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="741" t="inlineStr">
+      <c r="B11" s="278" t="n"/>
+      <c r="C11" s="817" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="742" t="inlineStr">
+      <c r="D11" s="278" t="n"/>
+      <c r="E11" s="772" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="741" t="inlineStr">
+      <c r="F11" s="278" t="n"/>
+      <c r="G11" s="817" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="H11" s="13" t="n"/>
+      <c r="H11" s="278" t="n"/>
       <c r="I11" s="745" t="n"/>
       <c r="J11" s="745" t="n"/>
       <c r="K11" s="745" t="n"/>
@@ -16250,30 +16086,30 @@
       <c r="AN11" s="746" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="747" t="inlineStr">
+      <c r="A12" s="773" t="inlineStr">
         <is>
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="748" t="inlineStr">
+      <c r="B12" s="285" t="n"/>
+      <c r="C12" s="818" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="749" t="inlineStr">
+      <c r="D12" s="285" t="n"/>
+      <c r="E12" s="774" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="748" t="inlineStr">
+      <c r="F12" s="285" t="n"/>
+      <c r="G12" s="818" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="H12" s="22" t="n"/>
+      <c r="H12" s="285" t="n"/>
       <c r="I12" s="750" t="n"/>
       <c r="J12" s="750" t="n"/>
       <c r="K12" s="750" t="n"/>
@@ -16355,13 +16191,13 @@
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
       <c r="I14" s="733" t="n"/>
       <c r="J14" s="733" t="n"/>
       <c r="K14" s="733" t="n"/>
@@ -16401,13 +16237,13 @@
           <t>Material, special-process and supporting certification linkage for the FAI package.</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
+      <c r="B15" s="289" t="n"/>
+      <c r="C15" s="289" t="n"/>
+      <c r="D15" s="289" t="n"/>
+      <c r="E15" s="289" t="n"/>
+      <c r="F15" s="289" t="n"/>
+      <c r="G15" s="289" t="n"/>
+      <c r="H15" s="289" t="n"/>
       <c r="I15" s="733" t="n"/>
       <c r="J15" s="733" t="n"/>
       <c r="K15" s="733" t="n"/>
@@ -17013,13 +16849,13 @@
           <t>NOTICE  —  Material, special-process and supporting certification linkage for the FAI package.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
-      <c r="H28" s="27" t="n"/>
+      <c r="B28" s="289" t="n"/>
+      <c r="C28" s="289" t="n"/>
+      <c r="D28" s="289" t="n"/>
+      <c r="E28" s="289" t="n"/>
+      <c r="F28" s="289" t="n"/>
+      <c r="G28" s="289" t="n"/>
+      <c r="H28" s="289" t="n"/>
       <c r="I28" s="733" t="n"/>
       <c r="J28" s="733" t="n"/>
       <c r="K28" s="733" t="n"/>
@@ -17337,15 +17173,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="345" t="n"/>
-      <c r="B1" s="53" t="n"/>
+      <c r="A1" s="399" t="n"/>
+      <c r="B1" s="325" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
           <t>REVALIDATION TRIGGER LOG</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
       <c r="F1" s="757" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -17391,11 +17227,9 @@
       <c r="AN1" s="719" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="54" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="326" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="F2" s="759" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -17441,11 +17275,9 @@
       <c r="AN2" s="723" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="326" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="F3" s="759" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -17491,15 +17323,13 @@
       <c r="AN3" s="723" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="326" t="n"/>
       <c r="C4" s="724" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
       <c r="F4" s="759" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -17541,15 +17371,15 @@
       <c r="AN4" s="723" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="727" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
       <c r="F5" s="761" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -17638,12 +17468,12 @@
           <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
       <c r="H7" s="733" t="n"/>
       <c r="I7" s="733" t="n"/>
       <c r="J7" s="733" t="n"/>
@@ -17684,24 +17514,24 @@
           <t>Parent Form</t>
         </is>
       </c>
-      <c r="B8" s="736" t="inlineStr">
+      <c r="B8" s="816" t="inlineStr">
         <is>
           <t>FRM-311 · FAI REPORT</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="272" t="n"/>
       <c r="E8" s="770" t="inlineStr">
         <is>
           <t>Support Tab</t>
         </is>
       </c>
-      <c r="F8" s="736" t="inlineStr">
+      <c r="F8" s="816" t="inlineStr">
         <is>
           <t>REVALIDATION</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="272" t="n"/>
       <c r="H8" s="738" t="n"/>
       <c r="I8" s="738" t="n"/>
       <c r="J8" s="738" t="n"/>
@@ -17742,20 +17572,20 @@
           <t>Tab Purpose</t>
         </is>
       </c>
-      <c r="B9" s="741" t="inlineStr">
+      <c r="B9" s="817" t="inlineStr">
         <is>
           <t>Use for revalidation triggers, scope and follow-up approval actions.</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="13" t="n"/>
+      <c r="C9" s="277" t="n"/>
+      <c r="D9" s="278" t="n"/>
       <c r="E9" s="772" t="inlineStr">
         <is>
           <t>Working Owner</t>
         </is>
       </c>
-      <c r="F9" s="741" t="inlineStr"/>
-      <c r="G9" s="13" t="n"/>
+      <c r="F9" s="817" t="inlineStr"/>
+      <c r="G9" s="278" t="n"/>
       <c r="H9" s="743" t="n"/>
       <c r="I9" s="743" t="n"/>
       <c r="J9" s="743" t="n"/>
@@ -17796,20 +17626,20 @@
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B10" s="741" t="inlineStr">
+      <c r="B10" s="817" t="inlineStr">
         <is>
           <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="13" t="n"/>
+      <c r="C10" s="277" t="n"/>
+      <c r="D10" s="278" t="n"/>
       <c r="E10" s="772" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="F10" s="741" t="inlineStr"/>
-      <c r="G10" s="13" t="n"/>
+      <c r="F10" s="817" t="inlineStr"/>
+      <c r="G10" s="278" t="n"/>
       <c r="H10" s="743" t="n"/>
       <c r="I10" s="743" t="n"/>
       <c r="J10" s="743" t="n"/>
@@ -17850,24 +17680,24 @@
           <t>Update Trigger</t>
         </is>
       </c>
-      <c r="B11" s="741" t="inlineStr">
+      <c r="B11" s="817" t="inlineStr">
         <is>
           <t>Update when the linked review, evidence or follow-up status changes.</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="13" t="n"/>
+      <c r="C11" s="277" t="n"/>
+      <c r="D11" s="278" t="n"/>
       <c r="E11" s="772" t="inlineStr">
         <is>
           <t>Data Structure</t>
         </is>
       </c>
-      <c r="F11" s="741" t="inlineStr">
+      <c r="F11" s="817" t="inlineStr">
         <is>
           <t>Structured Excel Table with filters and print-title rows.</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n"/>
+      <c r="G11" s="278" t="n"/>
       <c r="H11" s="745" t="n"/>
       <c r="I11" s="745" t="n"/>
       <c r="J11" s="745" t="n"/>
@@ -17908,24 +17738,24 @@
           <t>Retention Rule</t>
         </is>
       </c>
-      <c r="B12" s="748" t="inlineStr">
+      <c r="B12" s="818" t="inlineStr">
         <is>
           <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="22" t="n"/>
+      <c r="C12" s="283" t="n"/>
+      <c r="D12" s="285" t="n"/>
       <c r="E12" s="774" t="inlineStr">
         <is>
           <t>Controlled Status</t>
         </is>
       </c>
-      <c r="F12" s="748" t="inlineStr">
+      <c r="F12" s="818" t="inlineStr">
         <is>
           <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n"/>
+      <c r="G12" s="285" t="n"/>
       <c r="H12" s="750" t="n"/>
       <c r="I12" s="750" t="n"/>
       <c r="J12" s="750" t="n"/>
@@ -18008,12 +17838,12 @@
           <t>2.  WORKING TABLE / DETAIL LINES</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
       <c r="H14" s="733" t="n"/>
       <c r="I14" s="733" t="n"/>
       <c r="J14" s="733" t="n"/>
@@ -18054,12 +17884,12 @@
           <t>Use for revalidation triggers, scope and follow-up approval actions.</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
+      <c r="B15" s="289" t="n"/>
+      <c r="C15" s="289" t="n"/>
+      <c r="D15" s="289" t="n"/>
+      <c r="E15" s="289" t="n"/>
+      <c r="F15" s="289" t="n"/>
+      <c r="G15" s="289" t="n"/>
       <c r="H15" s="733" t="n"/>
       <c r="I15" s="733" t="n"/>
       <c r="J15" s="733" t="n"/>
@@ -18662,12 +18492,12 @@
           <t>NOTICE  —  Use for revalidation triggers, scope and follow-up approval actions.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
+      <c r="B28" s="289" t="n"/>
+      <c r="C28" s="289" t="n"/>
+      <c r="D28" s="289" t="n"/>
+      <c r="E28" s="289" t="n"/>
+      <c r="F28" s="289" t="n"/>
+      <c r="G28" s="289" t="n"/>
       <c r="H28" s="733" t="n"/>
       <c r="I28" s="733" t="n"/>
       <c r="J28" s="733" t="n"/>
@@ -18940,7 +18770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -6,9 +6,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-311_FAI" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAR_RESULTS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATL_PROC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVALIDATION" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAR_RESULTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATL_PROC" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVALIDATION" sheetId="6" state="veryHidden" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="7" state="veryHidden" r:id="rId7"/>
   </sheets>
   <definedNames>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -33,12 +33,575 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
+  </si>
+  <si>
+    <t>1.  FAI HEADER</t>
+  </si>
+  <si>
+    <t>2.  CHARACTERISTIC RESULTS SECTION</t>
+  </si>
+  <si>
+    <t>2.  WORKING TABLE / DETAIL LINES</t>
+  </si>
+  <si>
+    <t>3.  REVALIDATION TRIGGER SECTION</t>
+  </si>
+  <si>
+    <t>4.  DISPOSITION AND APPROVAL SECTION WITH LINKED NCR / CONCESSION IF APPLICABLE.</t>
+  </si>
+  <si>
+    <t>5.  REVIEW / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$17)+1</t>
+  </si>
+  <si>
+    <t>ABN</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Abnormal results and concessions are linked.</t>
+  </si>
+  <si>
+    <t>Action Owner</t>
+  </si>
+  <si>
+    <t>Any discrepancy has hold or concession logic.</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>BAS</t>
+  </si>
+  <si>
+    <t>Balloon / Method Rev.</t>
+  </si>
+  <si>
+    <t>Balloon No.</t>
+  </si>
+  <si>
+    <t>Balloon or requirement linkage is unique.</t>
+  </si>
+  <si>
+    <t>CELL-TURN-01</t>
+  </si>
+  <si>
+    <t>CHARACTERISTIC RESULTS</t>
+  </si>
+  <si>
+    <t>CHAR_RESULTS</t>
+  </si>
+  <si>
+    <t>CHR</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CMM-001</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>Cat.</t>
+  </si>
+  <si>
+    <t>Certificate / Evidence Ref</t>
+  </si>
+  <si>
+    <t>Certifications or special-process evidence are linked.</t>
+  </si>
+  <si>
+    <t>Characteristic / Requirement</t>
+  </si>
+  <si>
+    <t>Characteristic list is complete and traceable.</t>
+  </si>
+  <si>
+    <t>Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.</t>
+  </si>
+  <si>
+    <t>Commercial Owner</t>
+  </si>
+  <si>
+    <t>Control Item / Check</t>
+  </si>
+  <si>
+    <t>Controlled Status</t>
+  </si>
+  <si>
+    <t>Data Structure</t>
+  </si>
+  <si>
+    <t>Disposition</t>
+  </si>
+  <si>
+    <t>Disposition authority is explicit.</t>
+  </si>
+  <si>
+    <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
+  </si>
+  <si>
+    <t>Document / Record</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>EVD</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Engineering Lead</t>
+  </si>
+  <si>
+    <t>Epicor://Job/JOB-240001</t>
+  </si>
+  <si>
+    <t>Escalation if Not Released</t>
+  </si>
+  <si>
+    <t>Evidence / Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Evidence Folder</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Evidence package and result log are complete.</t>
+  </si>
+  <si>
+    <t>FAI Owner</t>
+  </si>
+  <si>
+    <t>FAI REPORT</t>
+  </si>
+  <si>
+    <t>FAI Status</t>
+  </si>
+  <si>
+    <t>FAI Trigger / Scope</t>
+  </si>
+  <si>
+    <t>FAI Type / Scope</t>
+  </si>
+  <si>
+    <t>FAI is performed against the correct released package.</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FIN-01</t>
+  </si>
+  <si>
+    <t>FRM-311</t>
+  </si>
+  <si>
+    <t>FRM-311 · FAI REPORT</t>
+  </si>
+  <si>
+    <t>Final FAI release or hold matches authority matrix.</t>
+  </si>
+  <si>
+    <t>First-article sample identity is unique.</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>Future change conditions are explicit.</t>
+  </si>
+  <si>
+    <t>GAG</t>
+  </si>
+  <si>
+    <t>GAGE-001</t>
+  </si>
+  <si>
+    <t>GAGE-002</t>
+  </si>
+  <si>
+    <t>GRIND-01</t>
+  </si>
+  <si>
+    <t>Gage / Program Ref.</t>
+  </si>
+  <si>
+    <t>Gages and measuring resources are verified.</t>
+  </si>
+  <si>
+    <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>Inspection program / method is aligned.</t>
+  </si>
+  <si>
+    <t>Issue / Condition</t>
+  </si>
+  <si>
+    <t>JOB-240001</t>
+  </si>
+  <si>
+    <t>JOB-240002</t>
+  </si>
+  <si>
+    <t>JOB-240003</t>
+  </si>
+  <si>
+    <t>JOB-240004</t>
+  </si>
+  <si>
+    <t>Job / WO</t>
+  </si>
+  <si>
+    <t>M365://dossier/JOB-240001</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>MATERIAL / SPECIAL PROCESS CERTIFICATION MATRIX</t>
+  </si>
+  <si>
+    <t>MATL_PROC</t>
+  </si>
+  <si>
+    <t>MIC-025</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Machine / Cell</t>
+  </si>
+  <si>
+    <t>Maintenance Lead</t>
+  </si>
+  <si>
+    <t>Material / Process Item</t>
+  </si>
+  <si>
+    <t>Material and process evidence are available.</t>
+  </si>
+  <si>
+    <t>Material, special-process and supporting certification linkage for the FAI package.</t>
+  </si>
+  <si>
+    <t>Measurement resources are current and suitable.</t>
+  </si>
+  <si>
+    <t>Method / Gage</t>
+  </si>
+  <si>
+    <t>Method / program rev matches the baseline.</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NOTICE  —  Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
+  </si>
+  <si>
+    <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-311_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
+  </si>
+  <si>
+    <t>NOTICE  —  Material, special-process and supporting certification linkage for the FAI package.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
+  </si>
+  <si>
+    <t>NOTICE  —  Use for revalidation triggers, scope and follow-up approval actions.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
+  </si>
+  <si>
+    <t>Name  /  Signature  /  Date</t>
+  </si>
+  <si>
+    <t>Next Step</t>
+  </si>
+  <si>
+    <t>Nominal / Tol</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PN-1001 / Rev.A</t>
+  </si>
+  <si>
+    <t>PN-1002 / Rev.B</t>
+  </si>
+  <si>
+    <t>PN-1003 / Rev.C</t>
+  </si>
+  <si>
+    <t>PN-1004 / Rev.D</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>Parent Form</t>
+  </si>
+  <si>
+    <t>Part No. / Revision</t>
+  </si>
+  <si>
+    <t>Planning Lead</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Production Supervisor</t>
+  </si>
+  <si>
+    <t>QA / Engineering</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>QA Manager</t>
+  </si>
+  <si>
+    <t>Quality Management System  ·  Controlled Document</t>
+  </si>
+  <si>
+    <t>REF_EVIDENCE_LINK</t>
+  </si>
+  <si>
+    <t>REF_GAGE_MASTER</t>
+  </si>
+  <si>
+    <t>REF_JOB_WO_MASTER</t>
+  </si>
+  <si>
+    <t>REF_LINKS</t>
+  </si>
+  <si>
+    <t>REF_MACHINE_WC_MASTER</t>
+  </si>
+  <si>
+    <t>REF_OWNER_PERSON_MASTER</t>
+  </si>
+  <si>
+    <t>REF_PART_REV_MASTER</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>REL</t>
+  </si>
+  <si>
+    <t>REV</t>
+  </si>
+  <si>
+    <t>REVALIDATION</t>
+  </si>
+  <si>
+    <t>REVALIDATION TRIGGER LOG</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Ref Type</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Reference Epicor / M365 / controlled documents only.</t>
+  </si>
+  <si>
+    <t>Released baseline and revision are current.</t>
+  </si>
+  <si>
+    <t>Required Action</t>
+  </si>
+  <si>
+    <t>Required Revalidation</t>
+  </si>
+  <si>
+    <t>Requirement / Source</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Result records are uniquely recoverable.</t>
+  </si>
+  <si>
+    <t>Retention Rule</t>
+  </si>
+  <si>
+    <t>Revalidation trigger is assessed.</t>
+  </si>
+  <si>
+    <t>Review Date</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Reviewed by</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SP://evidence/FRM-202/001</t>
+  </si>
+  <si>
+    <t>SP://evidence/FRM-306/002</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>Sample / First Article ID</t>
+  </si>
+  <si>
+    <t>Sample / lot traceability is maintained.</t>
+  </si>
+  <si>
+    <t>Setup Technician</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Structured Excel Table with filters and print-title rows.</t>
+  </si>
+  <si>
+    <t>Support Tab</t>
+  </si>
+  <si>
+    <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
+  </si>
+  <si>
+    <t>System of Record</t>
+  </si>
+  <si>
+    <t>TIER 1</t>
+  </si>
+  <si>
+    <t>TIER 2</t>
+  </si>
+  <si>
+    <t>TIER 3</t>
+  </si>
+  <si>
+    <t>TRC</t>
+  </si>
+  <si>
+    <t>Tab Purpose</t>
+  </si>
+  <si>
+    <t>Top Abnormality / Revalidation Need</t>
+  </si>
+  <si>
+    <t>Trigger / Change</t>
+  </si>
+  <si>
+    <t>Unique Ref</t>
+  </si>
+  <si>
+    <t>Update Trigger</t>
+  </si>
+  <si>
+    <t>Update when the linked review, evidence or follow-up status changes.</t>
+  </si>
+  <si>
+    <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
+  </si>
+  <si>
+    <t>Use for revalidation triggers, scope and follow-up approval actions.</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VAL_DECISION_GATE_CORE</t>
+  </si>
+  <si>
+    <t>VAL_ESCALATION_LEVEL</t>
+  </si>
+  <si>
+    <t>VAL_RESULT_CORE</t>
+  </si>
+  <si>
+    <t>VAL_STATUS_CORE</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>Verified by</t>
+  </si>
+  <si>
+    <t>WAR ROOM</t>
+  </si>
+  <si>
+    <t>WC-3AX-01</t>
+  </si>
+  <si>
+    <t>WC-5AX-02</t>
+  </si>
+  <si>
+    <t>Working Owner</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="95">
+  <fonts count="96">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -577,8 +1140,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="63">
+  <fills count="64">
     <fill>
       <patternFill/>
     </fill>
@@ -890,8 +1458,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="386">
+  <borders count="389">
     <border>
       <left/>
       <right/>
@@ -5072,11 +5645,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="819">
+  <cellXfs count="822">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7123,6 +7730,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="63" borderId="386" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="63" borderId="387" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="63" borderId="388" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11625,93 +12241,93 @@
       <c r="CC46" s="10" t="n"/>
       <c r="CD46" s="10" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="787" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="819" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-311_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="289" t="n"/>
-      <c r="C47" s="289" t="n"/>
-      <c r="D47" s="289" t="n"/>
-      <c r="E47" s="289" t="n"/>
-      <c r="F47" s="289" t="n"/>
-      <c r="G47" s="289" t="n"/>
-      <c r="H47" s="289" t="n"/>
-      <c r="I47" s="289" t="n"/>
-      <c r="J47" s="289" t="n"/>
-      <c r="K47" s="289" t="n"/>
-      <c r="L47" s="289" t="n"/>
-      <c r="M47" s="289" t="n"/>
-      <c r="N47" s="289" t="n"/>
-      <c r="O47" s="289" t="n"/>
-      <c r="P47" s="289" t="n"/>
-      <c r="Q47" s="289" t="n"/>
-      <c r="R47" s="289" t="n"/>
-      <c r="S47" s="289" t="n"/>
-      <c r="T47" s="289" t="n"/>
-      <c r="U47" s="289" t="n"/>
-      <c r="V47" s="289" t="n"/>
-      <c r="W47" s="289" t="n"/>
-      <c r="X47" s="289" t="n"/>
-      <c r="Y47" s="289" t="n"/>
-      <c r="Z47" s="289" t="n"/>
-      <c r="AA47" s="289" t="n"/>
-      <c r="AB47" s="289" t="n"/>
-      <c r="AC47" s="289" t="n"/>
-      <c r="AD47" s="289" t="n"/>
-      <c r="AE47" s="289" t="n"/>
-      <c r="AF47" s="289" t="n"/>
-      <c r="AG47" s="289" t="n"/>
-      <c r="AH47" s="289" t="n"/>
-      <c r="AI47" s="289" t="n"/>
-      <c r="AJ47" s="289" t="n"/>
-      <c r="AK47" s="289" t="n"/>
-      <c r="AL47" s="289" t="n"/>
-      <c r="AM47" s="289" t="n"/>
-      <c r="AN47" s="289" t="n"/>
-      <c r="AO47" s="289" t="n"/>
-      <c r="AP47" s="289" t="n"/>
-      <c r="AQ47" s="289" t="n"/>
-      <c r="AR47" s="289" t="n"/>
-      <c r="AS47" s="289" t="n"/>
-      <c r="AT47" s="289" t="n"/>
-      <c r="AU47" s="289" t="n"/>
-      <c r="AV47" s="289" t="n"/>
-      <c r="AW47" s="289" t="n"/>
-      <c r="AX47" s="289" t="n"/>
-      <c r="AY47" s="289" t="n"/>
-      <c r="AZ47" s="289" t="n"/>
-      <c r="BA47" s="289" t="n"/>
-      <c r="BB47" s="289" t="n"/>
-      <c r="BC47" s="289" t="n"/>
-      <c r="BD47" s="289" t="n"/>
-      <c r="BE47" s="289" t="n"/>
-      <c r="BF47" s="289" t="n"/>
-      <c r="BG47" s="289" t="n"/>
-      <c r="BH47" s="289" t="n"/>
-      <c r="BI47" s="289" t="n"/>
-      <c r="BJ47" s="289" t="n"/>
-      <c r="BK47" s="289" t="n"/>
-      <c r="BL47" s="289" t="n"/>
-      <c r="BM47" s="289" t="n"/>
-      <c r="BN47" s="289" t="n"/>
-      <c r="BO47" s="289" t="n"/>
-      <c r="BP47" s="289" t="n"/>
-      <c r="BQ47" s="289" t="n"/>
-      <c r="BR47" s="289" t="n"/>
-      <c r="BS47" s="289" t="n"/>
-      <c r="BT47" s="289" t="n"/>
-      <c r="BU47" s="289" t="n"/>
-      <c r="BV47" s="289" t="n"/>
-      <c r="BW47" s="289" t="n"/>
-      <c r="BX47" s="289" t="n"/>
-      <c r="BY47" s="289" t="n"/>
-      <c r="BZ47" s="289" t="n"/>
-      <c r="CA47" s="289" t="n"/>
-      <c r="CB47" s="289" t="n"/>
-      <c r="CC47" s="289" t="n"/>
-      <c r="CD47" s="290" t="n"/>
+      <c r="B47" s="820" t="n"/>
+      <c r="C47" s="820" t="n"/>
+      <c r="D47" s="820" t="n"/>
+      <c r="E47" s="820" t="n"/>
+      <c r="F47" s="820" t="n"/>
+      <c r="G47" s="820" t="n"/>
+      <c r="H47" s="820" t="n"/>
+      <c r="I47" s="820" t="n"/>
+      <c r="J47" s="820" t="n"/>
+      <c r="K47" s="820" t="n"/>
+      <c r="L47" s="820" t="n"/>
+      <c r="M47" s="820" t="n"/>
+      <c r="N47" s="820" t="n"/>
+      <c r="O47" s="820" t="n"/>
+      <c r="P47" s="820" t="n"/>
+      <c r="Q47" s="820" t="n"/>
+      <c r="R47" s="820" t="n"/>
+      <c r="S47" s="820" t="n"/>
+      <c r="T47" s="820" t="n"/>
+      <c r="U47" s="820" t="n"/>
+      <c r="V47" s="820" t="n"/>
+      <c r="W47" s="820" t="n"/>
+      <c r="X47" s="820" t="n"/>
+      <c r="Y47" s="820" t="n"/>
+      <c r="Z47" s="820" t="n"/>
+      <c r="AA47" s="820" t="n"/>
+      <c r="AB47" s="820" t="n"/>
+      <c r="AC47" s="820" t="n"/>
+      <c r="AD47" s="820" t="n"/>
+      <c r="AE47" s="820" t="n"/>
+      <c r="AF47" s="820" t="n"/>
+      <c r="AG47" s="820" t="n"/>
+      <c r="AH47" s="820" t="n"/>
+      <c r="AI47" s="820" t="n"/>
+      <c r="AJ47" s="820" t="n"/>
+      <c r="AK47" s="820" t="n"/>
+      <c r="AL47" s="820" t="n"/>
+      <c r="AM47" s="820" t="n"/>
+      <c r="AN47" s="820" t="n"/>
+      <c r="AO47" s="820" t="n"/>
+      <c r="AP47" s="820" t="n"/>
+      <c r="AQ47" s="820" t="n"/>
+      <c r="AR47" s="820" t="n"/>
+      <c r="AS47" s="820" t="n"/>
+      <c r="AT47" s="820" t="n"/>
+      <c r="AU47" s="820" t="n"/>
+      <c r="AV47" s="820" t="n"/>
+      <c r="AW47" s="820" t="n"/>
+      <c r="AX47" s="820" t="n"/>
+      <c r="AY47" s="820" t="n"/>
+      <c r="AZ47" s="820" t="n"/>
+      <c r="BA47" s="820" t="n"/>
+      <c r="BB47" s="820" t="n"/>
+      <c r="BC47" s="820" t="n"/>
+      <c r="BD47" s="820" t="n"/>
+      <c r="BE47" s="820" t="n"/>
+      <c r="BF47" s="820" t="n"/>
+      <c r="BG47" s="820" t="n"/>
+      <c r="BH47" s="820" t="n"/>
+      <c r="BI47" s="820" t="n"/>
+      <c r="BJ47" s="820" t="n"/>
+      <c r="BK47" s="820" t="n"/>
+      <c r="BL47" s="820" t="n"/>
+      <c r="BM47" s="820" t="n"/>
+      <c r="BN47" s="820" t="n"/>
+      <c r="BO47" s="820" t="n"/>
+      <c r="BP47" s="820" t="n"/>
+      <c r="BQ47" s="820" t="n"/>
+      <c r="BR47" s="820" t="n"/>
+      <c r="BS47" s="820" t="n"/>
+      <c r="BT47" s="820" t="n"/>
+      <c r="BU47" s="820" t="n"/>
+      <c r="BV47" s="820" t="n"/>
+      <c r="BW47" s="820" t="n"/>
+      <c r="BX47" s="820" t="n"/>
+      <c r="BY47" s="820" t="n"/>
+      <c r="BZ47" s="820" t="n"/>
+      <c r="CA47" s="820" t="n"/>
+      <c r="CB47" s="820" t="n"/>
+      <c r="CC47" s="820" t="n"/>
+      <c r="CD47" s="821" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -111,6 +111,9 @@
     <t>CLOSED</t>
   </si>
   <si>
+    <t>CMM Program / Rev</t>
+  </si>
+  <si>
     <t>CMM-001</t>
   </si>
   <si>
@@ -150,6 +153,9 @@
     <t>Data Structure</t>
   </si>
   <si>
+    <t>Delta / Partial FAIR? Y/N</t>
+  </si>
+  <si>
     <t>Disposition</t>
   </si>
   <si>
@@ -177,13 +183,7 @@
     <t>Epicor://Job/JOB-240001</t>
   </si>
   <si>
-    <t>Escalation if Not Released</t>
-  </si>
-  <si>
     <t>Evidence / Acceptance Criteria</t>
-  </si>
-  <si>
-    <t>Evidence Folder</t>
   </si>
   <si>
     <t>Evidence Ref</t>
@@ -1464,7 +1464,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="389">
+  <borders count="394">
     <border>
       <left/>
       <right/>
@@ -5679,11 +5679,69 @@
         <color rgb="00F9A825"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="822">
+  <cellXfs count="827">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7740,6 +7798,17 @@
     <xf numFmtId="0" fontId="95" fillId="63" borderId="388" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="90" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="63" borderId="389" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -9078,9 +9147,9 @@
       <c r="CD10" s="280" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="790" t="inlineStr">
-        <is>
-          <t>Evidence Folder</t>
+      <c r="A11" s="822" t="inlineStr">
+        <is>
+          <t>CMM Program / Rev</t>
         </is>
       </c>
       <c r="B11" s="277" t="n"/>
@@ -9710,9 +9779,9 @@
       <c r="CD17" s="280" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="792" t="inlineStr">
-        <is>
-          <t>Escalation if Not Released</t>
+      <c r="A18" s="823" t="inlineStr">
+        <is>
+          <t>Delta / Partial FAIR? Y/N</t>
         </is>
       </c>
       <c r="B18" s="283" t="n"/>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -33,575 +33,12 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-  </si>
-  <si>
-    <t>1.  FAI HEADER</t>
-  </si>
-  <si>
-    <t>2.  CHARACTERISTIC RESULTS SECTION</t>
-  </si>
-  <si>
-    <t>2.  WORKING TABLE / DETAIL LINES</t>
-  </si>
-  <si>
-    <t>3.  REVALIDATION TRIGGER SECTION</t>
-  </si>
-  <si>
-    <t>4.  DISPOSITION AND APPROVAL SECTION WITH LINKED NCR / CONCESSION IF APPLICABLE.</t>
-  </si>
-  <si>
-    <t>5.  REVIEW / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$17)+1</t>
-  </si>
-  <si>
-    <t>ABN</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Abnormal results and concessions are linked.</t>
-  </si>
-  <si>
-    <t>Action Owner</t>
-  </si>
-  <si>
-    <t>Any discrepancy has hold or concession logic.</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>BAS</t>
-  </si>
-  <si>
-    <t>Balloon / Method Rev.</t>
-  </si>
-  <si>
-    <t>Balloon No.</t>
-  </si>
-  <si>
-    <t>Balloon or requirement linkage is unique.</t>
-  </si>
-  <si>
-    <t>CELL-TURN-01</t>
-  </si>
-  <si>
-    <t>CHARACTERISTIC RESULTS</t>
-  </si>
-  <si>
-    <t>CHAR_RESULTS</t>
-  </si>
-  <si>
-    <t>CHR</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CMM Program / Rev</t>
-  </si>
-  <si>
-    <t>CMM-001</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>Cat.</t>
-  </si>
-  <si>
-    <t>Certificate / Evidence Ref</t>
-  </si>
-  <si>
-    <t>Certifications or special-process evidence are linked.</t>
-  </si>
-  <si>
-    <t>Characteristic / Requirement</t>
-  </si>
-  <si>
-    <t>Characteristic list is complete and traceable.</t>
-  </si>
-  <si>
-    <t>Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.</t>
-  </si>
-  <si>
-    <t>Commercial Owner</t>
-  </si>
-  <si>
-    <t>Control Item / Check</t>
-  </si>
-  <si>
-    <t>Controlled Status</t>
-  </si>
-  <si>
-    <t>Data Structure</t>
-  </si>
-  <si>
-    <t>Delta / Partial FAIR? Y/N</t>
-  </si>
-  <si>
-    <t>Disposition</t>
-  </si>
-  <si>
-    <t>Disposition authority is explicit.</t>
-  </si>
-  <si>
-    <t>Do not delete historical lines once evidence has been recorded or reviewed.</t>
-  </si>
-  <si>
-    <t>Document / Record</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>EVD</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Engineering Lead</t>
-  </si>
-  <si>
-    <t>Epicor://Job/JOB-240001</t>
-  </si>
-  <si>
-    <t>Evidence / Acceptance Criteria</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Evidence package and result log are complete.</t>
-  </si>
-  <si>
-    <t>FAI Owner</t>
-  </si>
-  <si>
-    <t>FAI REPORT</t>
-  </si>
-  <si>
-    <t>FAI Status</t>
-  </si>
-  <si>
-    <t>FAI Trigger / Scope</t>
-  </si>
-  <si>
-    <t>FAI Type / Scope</t>
-  </si>
-  <si>
-    <t>FAI is performed against the correct released package.</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FIN-01</t>
-  </si>
-  <si>
-    <t>FRM-311</t>
-  </si>
-  <si>
-    <t>FRM-311 · FAI REPORT</t>
-  </si>
-  <si>
-    <t>Final FAI release or hold matches authority matrix.</t>
-  </si>
-  <si>
-    <t>First-article sample identity is unique.</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>Future change conditions are explicit.</t>
-  </si>
-  <si>
-    <t>GAG</t>
-  </si>
-  <si>
-    <t>GAGE-001</t>
-  </si>
-  <si>
-    <t>GAGE-002</t>
-  </si>
-  <si>
-    <t>GRIND-01</t>
-  </si>
-  <si>
-    <t>Gage / Program Ref.</t>
-  </si>
-  <si>
-    <t>Gages and measuring resources are verified.</t>
-  </si>
-  <si>
-    <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>Inspection program / method is aligned.</t>
-  </si>
-  <si>
-    <t>Issue / Condition</t>
-  </si>
-  <si>
-    <t>JOB-240001</t>
-  </si>
-  <si>
-    <t>JOB-240002</t>
-  </si>
-  <si>
-    <t>JOB-240003</t>
-  </si>
-  <si>
-    <t>JOB-240004</t>
-  </si>
-  <si>
-    <t>Job / WO</t>
-  </si>
-  <si>
-    <t>M365://dossier/JOB-240001</t>
-  </si>
-  <si>
-    <t>MAT</t>
-  </si>
-  <si>
-    <t>MATERIAL / SPECIAL PROCESS CERTIFICATION MATRIX</t>
-  </si>
-  <si>
-    <t>MATL_PROC</t>
-  </si>
-  <si>
-    <t>MIC-025</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Machine / Cell</t>
-  </si>
-  <si>
-    <t>Maintenance Lead</t>
-  </si>
-  <si>
-    <t>Material / Process Item</t>
-  </si>
-  <si>
-    <t>Material and process evidence are available.</t>
-  </si>
-  <si>
-    <t>Material, special-process and supporting certification linkage for the FAI package.</t>
-  </si>
-  <si>
-    <t>Measurement resources are current and suitable.</t>
-  </si>
-  <si>
-    <t>Method / Gage</t>
-  </si>
-  <si>
-    <t>Method / program rev matches the baseline.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NOTICE  —  Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
-  </si>
-  <si>
-    <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-311_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
-  </si>
-  <si>
-    <t>NOTICE  —  Material, special-process and supporting certification linkage for the FAI package.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
-  </si>
-  <si>
-    <t>NOTICE  —  Use for revalidation triggers, scope and follow-up approval actions.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
-  </si>
-  <si>
-    <t>Name  /  Signature  /  Date</t>
-  </si>
-  <si>
-    <t>Next Step</t>
-  </si>
-  <si>
-    <t>Nominal / Tol</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PN-1001 / Rev.A</t>
-  </si>
-  <si>
-    <t>PN-1002 / Rev.B</t>
-  </si>
-  <si>
-    <t>PN-1003 / Rev.C</t>
-  </si>
-  <si>
-    <t>PN-1004 / Rev.D</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>Parent Form</t>
-  </si>
-  <si>
-    <t>Part No. / Revision</t>
-  </si>
-  <si>
-    <t>Planning Lead</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Production Supervisor</t>
-  </si>
-  <si>
-    <t>QA / Engineering</t>
-  </si>
-  <si>
-    <t>QA Engineer</t>
-  </si>
-  <si>
-    <t>QA Manager</t>
-  </si>
-  <si>
-    <t>Quality Management System  ·  Controlled Document</t>
-  </si>
-  <si>
-    <t>REF_EVIDENCE_LINK</t>
-  </si>
-  <si>
-    <t>REF_GAGE_MASTER</t>
-  </si>
-  <si>
-    <t>REF_JOB_WO_MASTER</t>
-  </si>
-  <si>
-    <t>REF_LINKS</t>
-  </si>
-  <si>
-    <t>REF_MACHINE_WC_MASTER</t>
-  </si>
-  <si>
-    <t>REF_OWNER_PERSON_MASTER</t>
-  </si>
-  <si>
-    <t>REF_PART_REV_MASTER</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>REV</t>
-  </si>
-  <si>
-    <t>REVALIDATION</t>
-  </si>
-  <si>
-    <t>REVALIDATION TRIGGER LOG</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Ref Type</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Reference Epicor / M365 / controlled documents only.</t>
-  </si>
-  <si>
-    <t>Released baseline and revision are current.</t>
-  </si>
-  <si>
-    <t>Required Action</t>
-  </si>
-  <si>
-    <t>Required Revalidation</t>
-  </si>
-  <si>
-    <t>Requirement / Source</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Result records are uniquely recoverable.</t>
-  </si>
-  <si>
-    <t>Retention Rule</t>
-  </si>
-  <si>
-    <t>Revalidation trigger is assessed.</t>
-  </si>
-  <si>
-    <t>Review Date</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SP://evidence/FRM-202/001</t>
-  </si>
-  <si>
-    <t>SP://evidence/FRM-306/002</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>Sample / First Article ID</t>
-  </si>
-  <si>
-    <t>Sample / lot traceability is maintained.</t>
-  </si>
-  <si>
-    <t>Setup Technician</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Structured Excel Table with filters and print-title rows.</t>
-  </si>
-  <si>
-    <t>Support Tab</t>
-  </si>
-  <si>
-    <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
-  </si>
-  <si>
-    <t>System of Record</t>
-  </si>
-  <si>
-    <t>TIER 1</t>
-  </si>
-  <si>
-    <t>TIER 2</t>
-  </si>
-  <si>
-    <t>TIER 3</t>
-  </si>
-  <si>
-    <t>TRC</t>
-  </si>
-  <si>
-    <t>Tab Purpose</t>
-  </si>
-  <si>
-    <t>Top Abnormality / Revalidation Need</t>
-  </si>
-  <si>
-    <t>Trigger / Change</t>
-  </si>
-  <si>
-    <t>Unique Ref</t>
-  </si>
-  <si>
-    <t>Update Trigger</t>
-  </si>
-  <si>
-    <t>Update when the linked review, evidence or follow-up status changes.</t>
-  </si>
-  <si>
-    <t>Use controlled parent-form references, _IMPORT lists and approved evidence sources only.</t>
-  </si>
-  <si>
-    <t>Use for revalidation triggers, scope and follow-up approval actions.</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VAL_DECISION_GATE_CORE</t>
-  </si>
-  <si>
-    <t>VAL_ESCALATION_LEVEL</t>
-  </si>
-  <si>
-    <t>VAL_RESULT_CORE</t>
-  </si>
-  <si>
-    <t>VAL_STATUS_CORE</t>
-  </si>
-  <si>
-    <t>VOID</t>
-  </si>
-  <si>
-    <t>Verified by</t>
-  </si>
-  <si>
-    <t>WAR ROOM</t>
-  </si>
-  <si>
-    <t>WC-3AX-01</t>
-  </si>
-  <si>
-    <t>WC-5AX-02</t>
-  </si>
-  <si>
-    <t>Working Owner</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="96">
+  <fonts count="97">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1145,6 +582,9 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="64">
     <fill>
@@ -1464,7 +904,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="394">
+  <borders count="395">
     <border>
       <left/>
       <right/>
@@ -5737,11 +5177,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="827">
+  <cellXfs count="847">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7809,6 +7259,40 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="90" fillId="59" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="59" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="58" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -12807,7 +12291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -12852,401 +12336,822 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="414" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="B1" s="414" t="inlineStr">
-        <is>
-          <t>VAL_ESCALATION_LEVEL</t>
-        </is>
-      </c>
-      <c r="C1" s="414" t="inlineStr">
-        <is>
-          <t>VAL_RESULT_CORE</t>
-        </is>
-      </c>
-      <c r="D1" s="414" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="E1" s="414" t="n"/>
-      <c r="F1" s="414" t="n"/>
-      <c r="G1" s="414" t="n"/>
-      <c r="H1" s="414" t="n"/>
-      <c r="I1" s="414" t="n"/>
-      <c r="J1" s="414" t="n"/>
-      <c r="K1" s="414" t="n"/>
-      <c r="L1" s="414" t="n"/>
-      <c r="M1" s="414" t="n"/>
-      <c r="N1" s="414" t="n"/>
-      <c r="O1" s="414" t="n"/>
-      <c r="P1" s="414" t="n"/>
-      <c r="Q1" s="414" t="n"/>
-      <c r="R1" s="414" t="n"/>
-      <c r="S1" s="414" t="n"/>
-      <c r="T1" s="414" t="n"/>
-      <c r="U1" s="414" t="n"/>
-      <c r="V1" s="414" t="n"/>
-      <c r="W1" s="414" t="n"/>
-      <c r="X1" s="414" t="n"/>
-      <c r="Y1" s="414" t="n"/>
-      <c r="Z1" s="414" t="n"/>
-      <c r="AA1" s="414" t="n"/>
-      <c r="AB1" s="414" t="n"/>
-      <c r="AC1" s="414" t="n"/>
-      <c r="AD1" s="414" t="n"/>
-      <c r="AE1" s="414" t="n"/>
-      <c r="AF1" s="414" t="n"/>
-      <c r="AG1" s="414" t="n"/>
-      <c r="AH1" s="414" t="n"/>
-      <c r="AI1" s="414" t="n"/>
-      <c r="AJ1" s="414" t="n"/>
-      <c r="AK1" s="414" t="n"/>
-      <c r="AL1" s="414" t="n"/>
-      <c r="AM1" s="414" t="n"/>
-      <c r="AN1" s="414" t="n"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="827" t="n"/>
+      <c r="B1" s="828" t="n"/>
+      <c r="C1" s="828" t="n"/>
+      <c r="D1" s="828" t="n"/>
+      <c r="E1" s="828" t="n"/>
+      <c r="F1" s="828" t="n"/>
+      <c r="G1" s="828" t="n"/>
+      <c r="H1" s="829" t="n"/>
+      <c r="I1" s="830" t="inlineStr">
+        <is>
+          <t>FAI REPORT</t>
+        </is>
+      </c>
+      <c r="J1" s="828" t="n"/>
+      <c r="K1" s="828" t="n"/>
+      <c r="L1" s="828" t="n"/>
+      <c r="M1" s="828" t="n"/>
+      <c r="N1" s="828" t="n"/>
+      <c r="O1" s="828" t="n"/>
+      <c r="P1" s="828" t="n"/>
+      <c r="Q1" s="828" t="n"/>
+      <c r="R1" s="828" t="n"/>
+      <c r="S1" s="828" t="n"/>
+      <c r="T1" s="828" t="n"/>
+      <c r="U1" s="828" t="n"/>
+      <c r="V1" s="828" t="n"/>
+      <c r="W1" s="828" t="n"/>
+      <c r="X1" s="828" t="n"/>
+      <c r="Y1" s="828" t="n"/>
+      <c r="Z1" s="828" t="n"/>
+      <c r="AA1" s="828" t="n"/>
+      <c r="AB1" s="828" t="n"/>
+      <c r="AC1" s="828" t="n"/>
+      <c r="AD1" s="829" t="n"/>
+      <c r="AE1" s="518" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="828" t="n"/>
+      <c r="AG1" s="828" t="n"/>
+      <c r="AH1" s="831" t="n"/>
+      <c r="AI1" s="521" t="inlineStr">
+        <is>
+          <t>FRM-311</t>
+        </is>
+      </c>
+      <c r="AJ1" s="828" t="n"/>
+      <c r="AK1" s="828" t="n"/>
+      <c r="AL1" s="828" t="n"/>
+      <c r="AM1" s="828" t="n"/>
+      <c r="AN1" s="829" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="414" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="B2" s="414" t="inlineStr">
-        <is>
-          <t>TIER 1</t>
-        </is>
-      </c>
-      <c r="C2" s="414" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D2" s="414" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E2" s="414" t="n"/>
-      <c r="F2" s="414" t="n"/>
-      <c r="G2" s="414" t="n"/>
-      <c r="H2" s="414" t="n"/>
-      <c r="I2" s="414" t="n"/>
-      <c r="J2" s="414" t="n"/>
-      <c r="K2" s="414" t="n"/>
-      <c r="L2" s="414" t="n"/>
-      <c r="M2" s="414" t="n"/>
-      <c r="N2" s="414" t="n"/>
-      <c r="O2" s="414" t="n"/>
-      <c r="P2" s="414" t="n"/>
-      <c r="Q2" s="414" t="n"/>
-      <c r="R2" s="414" t="n"/>
-      <c r="S2" s="414" t="n"/>
-      <c r="T2" s="414" t="n"/>
-      <c r="U2" s="414" t="n"/>
-      <c r="V2" s="414" t="n"/>
-      <c r="W2" s="414" t="n"/>
-      <c r="X2" s="414" t="n"/>
-      <c r="Y2" s="414" t="n"/>
-      <c r="Z2" s="414" t="n"/>
-      <c r="AA2" s="414" t="n"/>
-      <c r="AB2" s="414" t="n"/>
-      <c r="AC2" s="414" t="n"/>
-      <c r="AD2" s="414" t="n"/>
-      <c r="AE2" s="414" t="n"/>
-      <c r="AF2" s="414" t="n"/>
-      <c r="AG2" s="414" t="n"/>
-      <c r="AH2" s="414" t="n"/>
-      <c r="AI2" s="414" t="n"/>
-      <c r="AJ2" s="414" t="n"/>
-      <c r="AK2" s="414" t="n"/>
-      <c r="AL2" s="414" t="n"/>
-      <c r="AM2" s="414" t="n"/>
-      <c r="AN2" s="414" t="n"/>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="832" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="833" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="833" t="n"/>
+      <c r="AE2" s="834" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="835" t="n"/>
+      <c r="AI2" s="836" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="833" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="414" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="B3" s="414" t="inlineStr">
-        <is>
-          <t>TIER 2</t>
-        </is>
-      </c>
-      <c r="C3" s="414" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="D3" s="414" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="E3" s="414" t="n"/>
-      <c r="F3" s="414" t="n"/>
-      <c r="G3" s="414" t="n"/>
-      <c r="H3" s="414" t="n"/>
-      <c r="I3" s="414" t="n"/>
-      <c r="J3" s="414" t="n"/>
-      <c r="K3" s="414" t="n"/>
-      <c r="L3" s="414" t="n"/>
-      <c r="M3" s="414" t="n"/>
-      <c r="N3" s="414" t="n"/>
-      <c r="O3" s="414" t="n"/>
-      <c r="P3" s="414" t="n"/>
-      <c r="Q3" s="414" t="n"/>
-      <c r="R3" s="414" t="n"/>
-      <c r="S3" s="414" t="n"/>
-      <c r="T3" s="414" t="n"/>
-      <c r="U3" s="414" t="n"/>
-      <c r="V3" s="414" t="n"/>
-      <c r="W3" s="414" t="n"/>
-      <c r="X3" s="414" t="n"/>
-      <c r="Y3" s="414" t="n"/>
-      <c r="Z3" s="414" t="n"/>
-      <c r="AA3" s="414" t="n"/>
-      <c r="AB3" s="414" t="n"/>
-      <c r="AC3" s="414" t="n"/>
-      <c r="AD3" s="414" t="n"/>
-      <c r="AE3" s="414" t="n"/>
-      <c r="AF3" s="414" t="n"/>
-      <c r="AG3" s="414" t="n"/>
-      <c r="AH3" s="414" t="n"/>
-      <c r="AI3" s="414" t="n"/>
-      <c r="AJ3" s="414" t="n"/>
-      <c r="AK3" s="414" t="n"/>
-      <c r="AL3" s="414" t="n"/>
-      <c r="AM3" s="414" t="n"/>
-      <c r="AN3" s="414" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="832" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="833" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="833" t="n"/>
+      <c r="AE3" s="834" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="835" t="n"/>
+      <c r="AI3" s="836" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="833" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="414" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B4" s="414" t="inlineStr">
-        <is>
-          <t>TIER 3</t>
-        </is>
-      </c>
-      <c r="C4" s="414" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D4" s="414" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="E4" s="414" t="n"/>
-      <c r="F4" s="414" t="n"/>
-      <c r="G4" s="414" t="n"/>
-      <c r="H4" s="414" t="n"/>
-      <c r="I4" s="414" t="n"/>
-      <c r="J4" s="414" t="n"/>
-      <c r="K4" s="414" t="n"/>
-      <c r="L4" s="414" t="n"/>
-      <c r="M4" s="414" t="n"/>
-      <c r="N4" s="414" t="n"/>
-      <c r="O4" s="414" t="n"/>
-      <c r="P4" s="414" t="n"/>
-      <c r="Q4" s="414" t="n"/>
-      <c r="R4" s="414" t="n"/>
-      <c r="S4" s="414" t="n"/>
-      <c r="T4" s="414" t="n"/>
-      <c r="U4" s="414" t="n"/>
-      <c r="V4" s="414" t="n"/>
-      <c r="W4" s="414" t="n"/>
-      <c r="X4" s="414" t="n"/>
-      <c r="Y4" s="414" t="n"/>
-      <c r="Z4" s="414" t="n"/>
-      <c r="AA4" s="414" t="n"/>
-      <c r="AB4" s="414" t="n"/>
-      <c r="AC4" s="414" t="n"/>
-      <c r="AD4" s="414" t="n"/>
-      <c r="AE4" s="414" t="n"/>
-      <c r="AF4" s="414" t="n"/>
-      <c r="AG4" s="414" t="n"/>
-      <c r="AH4" s="414" t="n"/>
-      <c r="AI4" s="414" t="n"/>
-      <c r="AJ4" s="414" t="n"/>
-      <c r="AK4" s="414" t="n"/>
-      <c r="AL4" s="414" t="n"/>
-      <c r="AM4" s="414" t="n"/>
-      <c r="AN4" s="414" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="832" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="833" t="n"/>
+      <c r="I4" s="837" t="inlineStr">
+        <is>
+          <t>Quality Management System  ·  Controlled Document</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="833" t="n"/>
+      <c r="AE4" s="834" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="835" t="n"/>
+      <c r="AI4" s="836" t="inlineStr">
+        <is>
+          <t>QA / Engineering</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="833" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="414" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="B5" s="414" t="inlineStr">
-        <is>
-          <t>WAR ROOM</t>
-        </is>
-      </c>
-      <c r="C5" s="414" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D5" s="414" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="E5" s="414" t="n"/>
-      <c r="F5" s="414" t="n"/>
-      <c r="G5" s="414" t="n"/>
-      <c r="H5" s="414" t="n"/>
-      <c r="I5" s="414" t="n"/>
-      <c r="J5" s="414" t="n"/>
-      <c r="K5" s="414" t="n"/>
-      <c r="L5" s="414" t="n"/>
-      <c r="M5" s="414" t="n"/>
-      <c r="N5" s="414" t="n"/>
-      <c r="O5" s="414" t="n"/>
-      <c r="P5" s="414" t="n"/>
-      <c r="Q5" s="414" t="n"/>
-      <c r="R5" s="414" t="n"/>
-      <c r="S5" s="414" t="n"/>
-      <c r="T5" s="414" t="n"/>
-      <c r="U5" s="414" t="n"/>
-      <c r="V5" s="414" t="n"/>
-      <c r="W5" s="414" t="n"/>
-      <c r="X5" s="414" t="n"/>
-      <c r="Y5" s="414" t="n"/>
-      <c r="Z5" s="414" t="n"/>
-      <c r="AA5" s="414" t="n"/>
-      <c r="AB5" s="414" t="n"/>
-      <c r="AC5" s="414" t="n"/>
-      <c r="AD5" s="414" t="n"/>
-      <c r="AE5" s="414" t="n"/>
-      <c r="AF5" s="414" t="n"/>
-      <c r="AG5" s="414" t="n"/>
-      <c r="AH5" s="414" t="n"/>
-      <c r="AI5" s="414" t="n"/>
-      <c r="AJ5" s="414" t="n"/>
-      <c r="AK5" s="414" t="n"/>
-      <c r="AL5" s="414" t="n"/>
-      <c r="AM5" s="414" t="n"/>
-      <c r="AN5" s="414" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="838" t="n"/>
+      <c r="B5" s="839" t="n"/>
+      <c r="C5" s="839" t="n"/>
+      <c r="D5" s="839" t="n"/>
+      <c r="E5" s="839" t="n"/>
+      <c r="F5" s="839" t="n"/>
+      <c r="G5" s="839" t="n"/>
+      <c r="H5" s="840" t="n"/>
+      <c r="I5" s="841" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="839" t="n"/>
+      <c r="K5" s="839" t="n"/>
+      <c r="L5" s="839" t="n"/>
+      <c r="M5" s="839" t="n"/>
+      <c r="N5" s="839" t="n"/>
+      <c r="O5" s="839" t="n"/>
+      <c r="P5" s="839" t="n"/>
+      <c r="Q5" s="839" t="n"/>
+      <c r="R5" s="839" t="n"/>
+      <c r="S5" s="839" t="n"/>
+      <c r="T5" s="839" t="n"/>
+      <c r="U5" s="839" t="n"/>
+      <c r="V5" s="839" t="n"/>
+      <c r="W5" s="839" t="n"/>
+      <c r="X5" s="839" t="n"/>
+      <c r="Y5" s="839" t="n"/>
+      <c r="Z5" s="839" t="n"/>
+      <c r="AA5" s="839" t="n"/>
+      <c r="AB5" s="839" t="n"/>
+      <c r="AC5" s="839" t="n"/>
+      <c r="AD5" s="840" t="n"/>
+      <c r="AE5" s="842" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="839" t="n"/>
+      <c r="AG5" s="839" t="n"/>
+      <c r="AH5" s="843" t="n"/>
+      <c r="AI5" s="844" t="inlineStr">
+        <is>
+          <t>QA Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="839" t="n"/>
+      <c r="AK5" s="839" t="n"/>
+      <c r="AL5" s="839" t="n"/>
+      <c r="AM5" s="839" t="n"/>
+      <c r="AN5" s="840" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="414" t="n"/>
-      <c r="B6" s="414" t="inlineStr">
-        <is>
-          <t>CUSTOMER</t>
-        </is>
-      </c>
-      <c r="C6" s="414" t="n"/>
-      <c r="D6" s="414" t="inlineStr">
-        <is>
-          <t>SUPERSEDED</t>
-        </is>
-      </c>
-      <c r="E6" s="414" t="n"/>
-      <c r="F6" s="414" t="n"/>
-      <c r="G6" s="414" t="n"/>
-      <c r="H6" s="414" t="n"/>
-      <c r="I6" s="414" t="n"/>
-      <c r="J6" s="414" t="n"/>
-      <c r="K6" s="414" t="n"/>
-      <c r="L6" s="414" t="n"/>
-      <c r="M6" s="414" t="n"/>
-      <c r="N6" s="414" t="n"/>
-      <c r="O6" s="414" t="n"/>
-      <c r="P6" s="414" t="n"/>
-      <c r="Q6" s="414" t="n"/>
-      <c r="R6" s="414" t="n"/>
-      <c r="S6" s="414" t="n"/>
-      <c r="T6" s="414" t="n"/>
-      <c r="U6" s="414" t="n"/>
-      <c r="V6" s="414" t="n"/>
-      <c r="W6" s="414" t="n"/>
-      <c r="X6" s="414" t="n"/>
-      <c r="Y6" s="414" t="n"/>
-      <c r="Z6" s="414" t="n"/>
-      <c r="AA6" s="414" t="n"/>
-      <c r="AB6" s="414" t="n"/>
-      <c r="AC6" s="414" t="n"/>
-      <c r="AD6" s="414" t="n"/>
-      <c r="AE6" s="414" t="n"/>
-      <c r="AF6" s="414" t="n"/>
-      <c r="AG6" s="414" t="n"/>
-      <c r="AH6" s="414" t="n"/>
-      <c r="AI6" s="414" t="n"/>
-      <c r="AJ6" s="414" t="n"/>
-      <c r="AK6" s="414" t="n"/>
-      <c r="AL6" s="414" t="n"/>
-      <c r="AM6" s="414" t="n"/>
-      <c r="AN6" s="414" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="845" t="n"/>
+      <c r="B6" s="845" t="n"/>
+      <c r="C6" s="845" t="n"/>
+      <c r="D6" s="845" t="n"/>
+      <c r="E6" s="845" t="n"/>
+      <c r="F6" s="845" t="n"/>
+      <c r="G6" s="845" t="n"/>
+      <c r="H6" s="845" t="n"/>
+      <c r="I6" s="845" t="n"/>
+      <c r="J6" s="845" t="n"/>
+      <c r="K6" s="845" t="n"/>
+      <c r="L6" s="845" t="n"/>
+      <c r="M6" s="845" t="n"/>
+      <c r="N6" s="845" t="n"/>
+      <c r="O6" s="845" t="n"/>
+      <c r="P6" s="845" t="n"/>
+      <c r="Q6" s="845" t="n"/>
+      <c r="R6" s="845" t="n"/>
+      <c r="S6" s="845" t="n"/>
+      <c r="T6" s="845" t="n"/>
+      <c r="U6" s="845" t="n"/>
+      <c r="V6" s="845" t="n"/>
+      <c r="W6" s="845" t="n"/>
+      <c r="X6" s="845" t="n"/>
+      <c r="Y6" s="845" t="n"/>
+      <c r="Z6" s="845" t="n"/>
+      <c r="AA6" s="845" t="n"/>
+      <c r="AB6" s="845" t="n"/>
+      <c r="AC6" s="845" t="n"/>
+      <c r="AD6" s="845" t="n"/>
+      <c r="AE6" s="845" t="n"/>
+      <c r="AF6" s="845" t="n"/>
+      <c r="AG6" s="845" t="n"/>
+      <c r="AH6" s="845" t="n"/>
+      <c r="AI6" s="845" t="n"/>
+      <c r="AJ6" s="845" t="n"/>
+      <c r="AK6" s="845" t="n"/>
+      <c r="AL6" s="845" t="n"/>
+      <c r="AM6" s="845" t="n"/>
+      <c r="AN6" s="845" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="414" t="n"/>
-      <c r="B7" s="414" t="n"/>
-      <c r="C7" s="414" t="n"/>
+      <c r="A7" s="414" t="inlineStr">
+        <is>
+          <t>VAL_DECISION_GATE_CORE</t>
+        </is>
+      </c>
+      <c r="B7" s="414" t="inlineStr">
+        <is>
+          <t>VAL_ESCALATION_LEVEL</t>
+        </is>
+      </c>
+      <c r="C7" s="414" t="inlineStr">
+        <is>
+          <t>VAL_RESULT_CORE</t>
+        </is>
+      </c>
       <c r="D7" s="414" t="inlineStr">
         <is>
+          <t>VAL_STATUS_CORE</t>
+        </is>
+      </c>
+      <c r="E7" s="846" t="n"/>
+      <c r="F7" s="846" t="n"/>
+      <c r="G7" s="846" t="n"/>
+      <c r="H7" s="846" t="n"/>
+      <c r="I7" s="846" t="n"/>
+      <c r="J7" s="846" t="n"/>
+      <c r="K7" s="846" t="n"/>
+      <c r="L7" s="846" t="n"/>
+      <c r="M7" s="846" t="n"/>
+      <c r="N7" s="846" t="n"/>
+      <c r="O7" s="846" t="n"/>
+      <c r="P7" s="846" t="n"/>
+      <c r="Q7" s="846" t="n"/>
+      <c r="R7" s="846" t="n"/>
+      <c r="S7" s="846" t="n"/>
+      <c r="T7" s="846" t="n"/>
+      <c r="U7" s="846" t="n"/>
+      <c r="V7" s="846" t="n"/>
+      <c r="W7" s="846" t="n"/>
+      <c r="X7" s="846" t="n"/>
+      <c r="Y7" s="846" t="n"/>
+      <c r="Z7" s="846" t="n"/>
+      <c r="AA7" s="846" t="n"/>
+      <c r="AB7" s="846" t="n"/>
+      <c r="AC7" s="846" t="n"/>
+      <c r="AD7" s="846" t="n"/>
+      <c r="AE7" s="846" t="n"/>
+      <c r="AF7" s="846" t="n"/>
+      <c r="AG7" s="846" t="n"/>
+      <c r="AH7" s="846" t="n"/>
+      <c r="AI7" s="846" t="n"/>
+      <c r="AJ7" s="846" t="n"/>
+      <c r="AK7" s="846" t="n"/>
+      <c r="AL7" s="846" t="n"/>
+      <c r="AM7" s="846" t="n"/>
+      <c r="AN7" s="846" t="n"/>
+    </row>
+    <row r="8" hidden="1">
+      <c r="A8" s="414" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="B8" s="414" t="inlineStr">
+        <is>
+          <t>TIER 1</t>
+        </is>
+      </c>
+      <c r="C8" s="414" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" s="414" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E8" s="846" t="n"/>
+      <c r="F8" s="846" t="n"/>
+      <c r="G8" s="846" t="n"/>
+      <c r="H8" s="846" t="n"/>
+      <c r="I8" s="846" t="n"/>
+      <c r="J8" s="846" t="n"/>
+      <c r="K8" s="846" t="n"/>
+      <c r="L8" s="846" t="n"/>
+      <c r="M8" s="846" t="n"/>
+      <c r="N8" s="846" t="n"/>
+      <c r="O8" s="846" t="n"/>
+      <c r="P8" s="846" t="n"/>
+      <c r="Q8" s="846" t="n"/>
+      <c r="R8" s="846" t="n"/>
+      <c r="S8" s="846" t="n"/>
+      <c r="T8" s="846" t="n"/>
+      <c r="U8" s="846" t="n"/>
+      <c r="V8" s="846" t="n"/>
+      <c r="W8" s="846" t="n"/>
+      <c r="X8" s="846" t="n"/>
+      <c r="Y8" s="846" t="n"/>
+      <c r="Z8" s="846" t="n"/>
+      <c r="AA8" s="846" t="n"/>
+      <c r="AB8" s="846" t="n"/>
+      <c r="AC8" s="846" t="n"/>
+      <c r="AD8" s="846" t="n"/>
+      <c r="AE8" s="846" t="n"/>
+      <c r="AF8" s="846" t="n"/>
+      <c r="AG8" s="846" t="n"/>
+      <c r="AH8" s="846" t="n"/>
+      <c r="AI8" s="846" t="n"/>
+      <c r="AJ8" s="846" t="n"/>
+      <c r="AK8" s="846" t="n"/>
+      <c r="AL8" s="846" t="n"/>
+      <c r="AM8" s="846" t="n"/>
+      <c r="AN8" s="846" t="n"/>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="414" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="B9" s="414" t="inlineStr">
+        <is>
+          <t>TIER 2</t>
+        </is>
+      </c>
+      <c r="C9" s="414" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D9" s="414" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="E9" s="846" t="n"/>
+      <c r="F9" s="846" t="n"/>
+      <c r="G9" s="846" t="n"/>
+      <c r="H9" s="846" t="n"/>
+      <c r="I9" s="846" t="n"/>
+      <c r="J9" s="846" t="n"/>
+      <c r="K9" s="846" t="n"/>
+      <c r="L9" s="846" t="n"/>
+      <c r="M9" s="846" t="n"/>
+      <c r="N9" s="846" t="n"/>
+      <c r="O9" s="846" t="n"/>
+      <c r="P9" s="846" t="n"/>
+      <c r="Q9" s="846" t="n"/>
+      <c r="R9" s="846" t="n"/>
+      <c r="S9" s="846" t="n"/>
+      <c r="T9" s="846" t="n"/>
+      <c r="U9" s="846" t="n"/>
+      <c r="V9" s="846" t="n"/>
+      <c r="W9" s="846" t="n"/>
+      <c r="X9" s="846" t="n"/>
+      <c r="Y9" s="846" t="n"/>
+      <c r="Z9" s="846" t="n"/>
+      <c r="AA9" s="846" t="n"/>
+      <c r="AB9" s="846" t="n"/>
+      <c r="AC9" s="846" t="n"/>
+      <c r="AD9" s="846" t="n"/>
+      <c r="AE9" s="846" t="n"/>
+      <c r="AF9" s="846" t="n"/>
+      <c r="AG9" s="846" t="n"/>
+      <c r="AH9" s="846" t="n"/>
+      <c r="AI9" s="846" t="n"/>
+      <c r="AJ9" s="846" t="n"/>
+      <c r="AK9" s="846" t="n"/>
+      <c r="AL9" s="846" t="n"/>
+      <c r="AM9" s="846" t="n"/>
+      <c r="AN9" s="846" t="n"/>
+    </row>
+    <row r="10" hidden="1">
+      <c r="A10" s="414" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B10" s="414" t="inlineStr">
+        <is>
+          <t>TIER 3</t>
+        </is>
+      </c>
+      <c r="C10" s="414" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D10" s="414" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E10" s="846" t="n"/>
+      <c r="F10" s="846" t="n"/>
+      <c r="G10" s="846" t="n"/>
+      <c r="H10" s="846" t="n"/>
+      <c r="I10" s="846" t="n"/>
+      <c r="J10" s="846" t="n"/>
+      <c r="K10" s="846" t="n"/>
+      <c r="L10" s="846" t="n"/>
+      <c r="M10" s="846" t="n"/>
+      <c r="N10" s="846" t="n"/>
+      <c r="O10" s="846" t="n"/>
+      <c r="P10" s="846" t="n"/>
+      <c r="Q10" s="846" t="n"/>
+      <c r="R10" s="846" t="n"/>
+      <c r="S10" s="846" t="n"/>
+      <c r="T10" s="846" t="n"/>
+      <c r="U10" s="846" t="n"/>
+      <c r="V10" s="846" t="n"/>
+      <c r="W10" s="846" t="n"/>
+      <c r="X10" s="846" t="n"/>
+      <c r="Y10" s="846" t="n"/>
+      <c r="Z10" s="846" t="n"/>
+      <c r="AA10" s="846" t="n"/>
+      <c r="AB10" s="846" t="n"/>
+      <c r="AC10" s="846" t="n"/>
+      <c r="AD10" s="846" t="n"/>
+      <c r="AE10" s="846" t="n"/>
+      <c r="AF10" s="846" t="n"/>
+      <c r="AG10" s="846" t="n"/>
+      <c r="AH10" s="846" t="n"/>
+      <c r="AI10" s="846" t="n"/>
+      <c r="AJ10" s="846" t="n"/>
+      <c r="AK10" s="846" t="n"/>
+      <c r="AL10" s="846" t="n"/>
+      <c r="AM10" s="846" t="n"/>
+      <c r="AN10" s="846" t="n"/>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="414" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="B11" s="414" t="inlineStr">
+        <is>
+          <t>WAR ROOM</t>
+        </is>
+      </c>
+      <c r="C11" s="414" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D11" s="414" t="inlineStr">
+        <is>
+          <t>MONITORING</t>
+        </is>
+      </c>
+      <c r="E11" s="846" t="n"/>
+      <c r="F11" s="846" t="n"/>
+      <c r="G11" s="846" t="n"/>
+      <c r="H11" s="846" t="n"/>
+      <c r="I11" s="846" t="n"/>
+      <c r="J11" s="846" t="n"/>
+      <c r="K11" s="846" t="n"/>
+      <c r="L11" s="846" t="n"/>
+      <c r="M11" s="846" t="n"/>
+      <c r="N11" s="846" t="n"/>
+      <c r="O11" s="846" t="n"/>
+      <c r="P11" s="846" t="n"/>
+      <c r="Q11" s="846" t="n"/>
+      <c r="R11" s="846" t="n"/>
+      <c r="S11" s="846" t="n"/>
+      <c r="T11" s="846" t="n"/>
+      <c r="U11" s="846" t="n"/>
+      <c r="V11" s="846" t="n"/>
+      <c r="W11" s="846" t="n"/>
+      <c r="X11" s="846" t="n"/>
+      <c r="Y11" s="846" t="n"/>
+      <c r="Z11" s="846" t="n"/>
+      <c r="AA11" s="846" t="n"/>
+      <c r="AB11" s="846" t="n"/>
+      <c r="AC11" s="846" t="n"/>
+      <c r="AD11" s="846" t="n"/>
+      <c r="AE11" s="846" t="n"/>
+      <c r="AF11" s="846" t="n"/>
+      <c r="AG11" s="846" t="n"/>
+      <c r="AH11" s="846" t="n"/>
+      <c r="AI11" s="846" t="n"/>
+      <c r="AJ11" s="846" t="n"/>
+      <c r="AK11" s="846" t="n"/>
+      <c r="AL11" s="846" t="n"/>
+      <c r="AM11" s="846" t="n"/>
+      <c r="AN11" s="846" t="n"/>
+    </row>
+    <row r="12" hidden="1">
+      <c r="A12" s="846" t="n"/>
+      <c r="B12" s="414" t="inlineStr">
+        <is>
+          <t>CUSTOMER</t>
+        </is>
+      </c>
+      <c r="C12" s="846" t="n"/>
+      <c r="D12" s="414" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="E12" s="846" t="n"/>
+      <c r="F12" s="846" t="n"/>
+      <c r="G12" s="846" t="n"/>
+      <c r="H12" s="846" t="n"/>
+      <c r="I12" s="846" t="n"/>
+      <c r="J12" s="846" t="n"/>
+      <c r="K12" s="846" t="n"/>
+      <c r="L12" s="846" t="n"/>
+      <c r="M12" s="846" t="n"/>
+      <c r="N12" s="846" t="n"/>
+      <c r="O12" s="846" t="n"/>
+      <c r="P12" s="846" t="n"/>
+      <c r="Q12" s="846" t="n"/>
+      <c r="R12" s="846" t="n"/>
+      <c r="S12" s="846" t="n"/>
+      <c r="T12" s="846" t="n"/>
+      <c r="U12" s="846" t="n"/>
+      <c r="V12" s="846" t="n"/>
+      <c r="W12" s="846" t="n"/>
+      <c r="X12" s="846" t="n"/>
+      <c r="Y12" s="846" t="n"/>
+      <c r="Z12" s="846" t="n"/>
+      <c r="AA12" s="846" t="n"/>
+      <c r="AB12" s="846" t="n"/>
+      <c r="AC12" s="846" t="n"/>
+      <c r="AD12" s="846" t="n"/>
+      <c r="AE12" s="846" t="n"/>
+      <c r="AF12" s="846" t="n"/>
+      <c r="AG12" s="846" t="n"/>
+      <c r="AH12" s="846" t="n"/>
+      <c r="AI12" s="846" t="n"/>
+      <c r="AJ12" s="846" t="n"/>
+      <c r="AK12" s="846" t="n"/>
+      <c r="AL12" s="846" t="n"/>
+      <c r="AM12" s="846" t="n"/>
+      <c r="AN12" s="846" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="846" t="n"/>
+      <c r="B13" s="846" t="n"/>
+      <c r="C13" s="846" t="n"/>
+      <c r="D13" s="414" t="inlineStr">
+        <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="E7" s="414" t="n"/>
-      <c r="F7" s="414" t="n"/>
-      <c r="G7" s="414" t="n"/>
-      <c r="H7" s="414" t="n"/>
-      <c r="I7" s="414" t="n"/>
-      <c r="J7" s="414" t="n"/>
-      <c r="K7" s="414" t="n"/>
-      <c r="L7" s="414" t="n"/>
-      <c r="M7" s="414" t="n"/>
-      <c r="N7" s="414" t="n"/>
-      <c r="O7" s="414" t="n"/>
-      <c r="P7" s="414" t="n"/>
-      <c r="Q7" s="414" t="n"/>
-      <c r="R7" s="414" t="n"/>
-      <c r="S7" s="414" t="n"/>
-      <c r="T7" s="414" t="n"/>
-      <c r="U7" s="414" t="n"/>
-      <c r="V7" s="414" t="n"/>
-      <c r="W7" s="414" t="n"/>
-      <c r="X7" s="414" t="n"/>
-      <c r="Y7" s="414" t="n"/>
-      <c r="Z7" s="414" t="n"/>
-      <c r="AA7" s="414" t="n"/>
-      <c r="AB7" s="414" t="n"/>
-      <c r="AC7" s="414" t="n"/>
-      <c r="AD7" s="414" t="n"/>
-      <c r="AE7" s="414" t="n"/>
-      <c r="AF7" s="414" t="n"/>
-      <c r="AG7" s="414" t="n"/>
-      <c r="AH7" s="414" t="n"/>
-      <c r="AI7" s="414" t="n"/>
-      <c r="AJ7" s="414" t="n"/>
-      <c r="AK7" s="414" t="n"/>
-      <c r="AL7" s="414" t="n"/>
-      <c r="AM7" s="414" t="n"/>
-      <c r="AN7" s="414" t="n"/>
+      <c r="E13" s="846" t="n"/>
+      <c r="F13" s="846" t="n"/>
+      <c r="G13" s="846" t="n"/>
+      <c r="H13" s="846" t="n"/>
+      <c r="I13" s="846" t="n"/>
+      <c r="J13" s="846" t="n"/>
+      <c r="K13" s="846" t="n"/>
+      <c r="L13" s="846" t="n"/>
+      <c r="M13" s="846" t="n"/>
+      <c r="N13" s="846" t="n"/>
+      <c r="O13" s="846" t="n"/>
+      <c r="P13" s="846" t="n"/>
+      <c r="Q13" s="846" t="n"/>
+      <c r="R13" s="846" t="n"/>
+      <c r="S13" s="846" t="n"/>
+      <c r="T13" s="846" t="n"/>
+      <c r="U13" s="846" t="n"/>
+      <c r="V13" s="846" t="n"/>
+      <c r="W13" s="846" t="n"/>
+      <c r="X13" s="846" t="n"/>
+      <c r="Y13" s="846" t="n"/>
+      <c r="Z13" s="846" t="n"/>
+      <c r="AA13" s="846" t="n"/>
+      <c r="AB13" s="846" t="n"/>
+      <c r="AC13" s="846" t="n"/>
+      <c r="AD13" s="846" t="n"/>
+      <c r="AE13" s="846" t="n"/>
+      <c r="AF13" s="846" t="n"/>
+      <c r="AG13" s="846" t="n"/>
+      <c r="AH13" s="846" t="n"/>
+      <c r="AI13" s="846" t="n"/>
+      <c r="AJ13" s="846" t="n"/>
+      <c r="AK13" s="846" t="n"/>
+      <c r="AL13" s="846" t="n"/>
+      <c r="AM13" s="846" t="n"/>
+      <c r="AN13" s="846" t="n"/>
     </row>
-    <row r="8" hidden="1"/>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
+    <row r="14" hidden="1">
+      <c r="A14" s="846" t="n"/>
+      <c r="B14" s="846" t="n"/>
+      <c r="C14" s="846" t="n"/>
+      <c r="D14" s="846" t="n"/>
+      <c r="E14" s="846" t="n"/>
+      <c r="F14" s="846" t="n"/>
+      <c r="G14" s="846" t="n"/>
+      <c r="H14" s="846" t="n"/>
+      <c r="I14" s="846" t="n"/>
+      <c r="J14" s="846" t="n"/>
+      <c r="K14" s="846" t="n"/>
+      <c r="L14" s="846" t="n"/>
+      <c r="M14" s="846" t="n"/>
+      <c r="N14" s="846" t="n"/>
+      <c r="O14" s="846" t="n"/>
+      <c r="P14" s="846" t="n"/>
+      <c r="Q14" s="846" t="n"/>
+      <c r="R14" s="846" t="n"/>
+      <c r="S14" s="846" t="n"/>
+      <c r="T14" s="846" t="n"/>
+      <c r="U14" s="846" t="n"/>
+      <c r="V14" s="846" t="n"/>
+      <c r="W14" s="846" t="n"/>
+      <c r="X14" s="846" t="n"/>
+      <c r="Y14" s="846" t="n"/>
+      <c r="Z14" s="846" t="n"/>
+      <c r="AA14" s="846" t="n"/>
+      <c r="AB14" s="846" t="n"/>
+      <c r="AC14" s="846" t="n"/>
+      <c r="AD14" s="846" t="n"/>
+      <c r="AE14" s="846" t="n"/>
+      <c r="AF14" s="846" t="n"/>
+      <c r="AG14" s="846" t="n"/>
+      <c r="AH14" s="846" t="n"/>
+      <c r="AI14" s="846" t="n"/>
+      <c r="AJ14" s="846" t="n"/>
+      <c r="AK14" s="846" t="n"/>
+      <c r="AL14" s="846" t="n"/>
+      <c r="AM14" s="846" t="n"/>
+      <c r="AN14" s="846" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="846" t="n"/>
+      <c r="B15" s="846" t="n"/>
+      <c r="C15" s="846" t="n"/>
+      <c r="D15" s="846" t="n"/>
+      <c r="E15" s="846" t="n"/>
+      <c r="F15" s="846" t="n"/>
+      <c r="G15" s="846" t="n"/>
+      <c r="H15" s="846" t="n"/>
+      <c r="I15" s="846" t="n"/>
+      <c r="J15" s="846" t="n"/>
+      <c r="K15" s="846" t="n"/>
+      <c r="L15" s="846" t="n"/>
+      <c r="M15" s="846" t="n"/>
+      <c r="N15" s="846" t="n"/>
+      <c r="O15" s="846" t="n"/>
+      <c r="P15" s="846" t="n"/>
+      <c r="Q15" s="846" t="n"/>
+      <c r="R15" s="846" t="n"/>
+      <c r="S15" s="846" t="n"/>
+      <c r="T15" s="846" t="n"/>
+      <c r="U15" s="846" t="n"/>
+      <c r="V15" s="846" t="n"/>
+      <c r="W15" s="846" t="n"/>
+      <c r="X15" s="846" t="n"/>
+      <c r="Y15" s="846" t="n"/>
+      <c r="Z15" s="846" t="n"/>
+      <c r="AA15" s="846" t="n"/>
+      <c r="AB15" s="846" t="n"/>
+      <c r="AC15" s="846" t="n"/>
+      <c r="AD15" s="846" t="n"/>
+      <c r="AE15" s="846" t="n"/>
+      <c r="AF15" s="846" t="n"/>
+      <c r="AG15" s="846" t="n"/>
+      <c r="AH15" s="846" t="n"/>
+      <c r="AI15" s="846" t="n"/>
+      <c r="AJ15" s="846" t="n"/>
+      <c r="AK15" s="846" t="n"/>
+      <c r="AL15" s="846" t="n"/>
+      <c r="AM15" s="846" t="n"/>
+      <c r="AN15" s="846" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="846" t="n"/>
+      <c r="B16" s="846" t="n"/>
+      <c r="C16" s="846" t="n"/>
+      <c r="D16" s="846" t="n"/>
+      <c r="E16" s="846" t="n"/>
+      <c r="F16" s="846" t="n"/>
+      <c r="G16" s="846" t="n"/>
+      <c r="H16" s="846" t="n"/>
+      <c r="I16" s="846" t="n"/>
+      <c r="J16" s="846" t="n"/>
+      <c r="K16" s="846" t="n"/>
+      <c r="L16" s="846" t="n"/>
+      <c r="M16" s="846" t="n"/>
+      <c r="N16" s="846" t="n"/>
+      <c r="O16" s="846" t="n"/>
+      <c r="P16" s="846" t="n"/>
+      <c r="Q16" s="846" t="n"/>
+      <c r="R16" s="846" t="n"/>
+      <c r="S16" s="846" t="n"/>
+      <c r="T16" s="846" t="n"/>
+      <c r="U16" s="846" t="n"/>
+      <c r="V16" s="846" t="n"/>
+      <c r="W16" s="846" t="n"/>
+      <c r="X16" s="846" t="n"/>
+      <c r="Y16" s="846" t="n"/>
+      <c r="Z16" s="846" t="n"/>
+      <c r="AA16" s="846" t="n"/>
+      <c r="AB16" s="846" t="n"/>
+      <c r="AC16" s="846" t="n"/>
+      <c r="AD16" s="846" t="n"/>
+      <c r="AE16" s="846" t="n"/>
+      <c r="AF16" s="846" t="n"/>
+      <c r="AG16" s="846" t="n"/>
+      <c r="AH16" s="846" t="n"/>
+      <c r="AI16" s="846" t="n"/>
+      <c r="AJ16" s="846" t="n"/>
+      <c r="AK16" s="846" t="n"/>
+      <c r="AL16" s="846" t="n"/>
+      <c r="AM16" s="846" t="n"/>
+      <c r="AN16" s="846" t="n"/>
+    </row>
     <row r="17" hidden="1"/>
     <row r="18" hidden="1"/>
     <row r="19" hidden="1"/>
@@ -13432,6 +13337,22 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -13443,7 +13364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -13488,487 +13409,908 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="604" t="inlineStr">
-        <is>
-          <t>REF_EVIDENCE_LINK</t>
-        </is>
-      </c>
-      <c r="B1" s="554" t="inlineStr">
-        <is>
-          <t>REF_GAGE_MASTER</t>
-        </is>
-      </c>
-      <c r="C1" s="554" t="inlineStr">
-        <is>
-          <t>REF_JOB_WO_MASTER</t>
-        </is>
-      </c>
-      <c r="D1" s="554" t="inlineStr">
-        <is>
-          <t>REF_MACHINE_WC_MASTER</t>
-        </is>
-      </c>
-      <c r="E1" s="554" t="inlineStr">
-        <is>
-          <t>REF_OWNER_PERSON_MASTER</t>
-        </is>
-      </c>
-      <c r="F1" s="554" t="inlineStr">
-        <is>
-          <t>REF_PART_REV_MASTER</t>
-        </is>
-      </c>
-      <c r="G1" s="554" t="n"/>
-      <c r="H1" s="554" t="n"/>
-      <c r="I1" s="554" t="n"/>
-      <c r="J1" s="554" t="n"/>
-      <c r="K1" s="554" t="n"/>
-      <c r="L1" s="554" t="n"/>
-      <c r="M1" s="554" t="n"/>
-      <c r="N1" s="554" t="n"/>
-      <c r="O1" s="554" t="n"/>
-      <c r="P1" s="554" t="n"/>
-      <c r="Q1" s="554" t="n"/>
-      <c r="R1" s="554" t="n"/>
-      <c r="S1" s="554" t="n"/>
-      <c r="T1" s="554" t="n"/>
-      <c r="U1" s="554" t="n"/>
-      <c r="V1" s="554" t="n"/>
-      <c r="W1" s="554" t="n"/>
-      <c r="X1" s="554" t="n"/>
-      <c r="Y1" s="554" t="n"/>
-      <c r="Z1" s="554" t="n"/>
-      <c r="AA1" s="554" t="n"/>
-      <c r="AB1" s="554" t="n"/>
-      <c r="AC1" s="554" t="n"/>
-      <c r="AD1" s="554" t="n"/>
-      <c r="AE1" s="554" t="n"/>
-      <c r="AF1" s="554" t="n"/>
-      <c r="AG1" s="554" t="n"/>
-      <c r="AH1" s="554" t="n"/>
-      <c r="AI1" s="554" t="n"/>
-      <c r="AJ1" s="554" t="n"/>
-      <c r="AK1" s="554" t="n"/>
-      <c r="AL1" s="554" t="n"/>
-      <c r="AM1" s="554" t="n"/>
-      <c r="AN1" s="557" t="n"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="827" t="n"/>
+      <c r="B1" s="828" t="n"/>
+      <c r="C1" s="828" t="n"/>
+      <c r="D1" s="828" t="n"/>
+      <c r="E1" s="828" t="n"/>
+      <c r="F1" s="828" t="n"/>
+      <c r="G1" s="828" t="n"/>
+      <c r="H1" s="829" t="n"/>
+      <c r="I1" s="830" t="inlineStr">
+        <is>
+          <t>FAI REPORT</t>
+        </is>
+      </c>
+      <c r="J1" s="828" t="n"/>
+      <c r="K1" s="828" t="n"/>
+      <c r="L1" s="828" t="n"/>
+      <c r="M1" s="828" t="n"/>
+      <c r="N1" s="828" t="n"/>
+      <c r="O1" s="828" t="n"/>
+      <c r="P1" s="828" t="n"/>
+      <c r="Q1" s="828" t="n"/>
+      <c r="R1" s="828" t="n"/>
+      <c r="S1" s="828" t="n"/>
+      <c r="T1" s="828" t="n"/>
+      <c r="U1" s="828" t="n"/>
+      <c r="V1" s="828" t="n"/>
+      <c r="W1" s="828" t="n"/>
+      <c r="X1" s="828" t="n"/>
+      <c r="Y1" s="828" t="n"/>
+      <c r="Z1" s="828" t="n"/>
+      <c r="AA1" s="828" t="n"/>
+      <c r="AB1" s="828" t="n"/>
+      <c r="AC1" s="828" t="n"/>
+      <c r="AD1" s="829" t="n"/>
+      <c r="AE1" s="518" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="828" t="n"/>
+      <c r="AG1" s="828" t="n"/>
+      <c r="AH1" s="831" t="n"/>
+      <c r="AI1" s="521" t="inlineStr">
+        <is>
+          <t>FRM-311</t>
+        </is>
+      </c>
+      <c r="AJ1" s="828" t="n"/>
+      <c r="AK1" s="828" t="n"/>
+      <c r="AL1" s="828" t="n"/>
+      <c r="AM1" s="828" t="n"/>
+      <c r="AN1" s="829" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="600" t="inlineStr">
-        <is>
-          <t>M365://dossier/JOB-240001</t>
-        </is>
-      </c>
-      <c r="B2" s="410" t="inlineStr">
-        <is>
-          <t>GAGE-001</t>
-        </is>
-      </c>
-      <c r="C2" s="410" t="inlineStr">
-        <is>
-          <t>JOB-240001</t>
-        </is>
-      </c>
-      <c r="D2" s="410" t="inlineStr">
-        <is>
-          <t>WC-3AX-01</t>
-        </is>
-      </c>
-      <c r="E2" s="410" t="inlineStr">
-        <is>
-          <t>Planning Lead</t>
-        </is>
-      </c>
-      <c r="F2" s="410" t="inlineStr">
-        <is>
-          <t>PN-1001 / Rev.A</t>
-        </is>
-      </c>
-      <c r="G2" s="410" t="n"/>
-      <c r="H2" s="410" t="n"/>
-      <c r="I2" s="410" t="n"/>
-      <c r="J2" s="410" t="n"/>
-      <c r="K2" s="410" t="n"/>
-      <c r="L2" s="410" t="n"/>
-      <c r="M2" s="410" t="n"/>
-      <c r="N2" s="410" t="n"/>
-      <c r="O2" s="410" t="n"/>
-      <c r="P2" s="410" t="n"/>
-      <c r="Q2" s="410" t="n"/>
-      <c r="R2" s="410" t="n"/>
-      <c r="S2" s="410" t="n"/>
-      <c r="T2" s="410" t="n"/>
-      <c r="U2" s="410" t="n"/>
-      <c r="V2" s="410" t="n"/>
-      <c r="W2" s="410" t="n"/>
-      <c r="X2" s="410" t="n"/>
-      <c r="Y2" s="410" t="n"/>
-      <c r="Z2" s="410" t="n"/>
-      <c r="AA2" s="410" t="n"/>
-      <c r="AB2" s="410" t="n"/>
-      <c r="AC2" s="410" t="n"/>
-      <c r="AD2" s="410" t="n"/>
-      <c r="AE2" s="410" t="n"/>
-      <c r="AF2" s="410" t="n"/>
-      <c r="AG2" s="410" t="n"/>
-      <c r="AH2" s="410" t="n"/>
-      <c r="AI2" s="410" t="n"/>
-      <c r="AJ2" s="410" t="n"/>
-      <c r="AK2" s="410" t="n"/>
-      <c r="AL2" s="410" t="n"/>
-      <c r="AM2" s="410" t="n"/>
-      <c r="AN2" s="561" t="n"/>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="832" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="833" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="833" t="n"/>
+      <c r="AE2" s="834" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="835" t="n"/>
+      <c r="AI2" s="836" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="833" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="600" t="inlineStr">
-        <is>
-          <t>SP://evidence/FRM-202/001</t>
-        </is>
-      </c>
-      <c r="B3" s="410" t="inlineStr">
-        <is>
-          <t>GAGE-002</t>
-        </is>
-      </c>
-      <c r="C3" s="410" t="inlineStr">
-        <is>
-          <t>JOB-240002</t>
-        </is>
-      </c>
-      <c r="D3" s="410" t="inlineStr">
-        <is>
-          <t>WC-5AX-02</t>
-        </is>
-      </c>
-      <c r="E3" s="410" t="inlineStr">
-        <is>
-          <t>Production Supervisor</t>
-        </is>
-      </c>
-      <c r="F3" s="410" t="inlineStr">
-        <is>
-          <t>PN-1002 / Rev.B</t>
-        </is>
-      </c>
-      <c r="G3" s="410" t="n"/>
-      <c r="H3" s="410" t="n"/>
-      <c r="I3" s="410" t="n"/>
-      <c r="J3" s="410" t="n"/>
-      <c r="K3" s="410" t="n"/>
-      <c r="L3" s="410" t="n"/>
-      <c r="M3" s="410" t="n"/>
-      <c r="N3" s="410" t="n"/>
-      <c r="O3" s="410" t="n"/>
-      <c r="P3" s="410" t="n"/>
-      <c r="Q3" s="410" t="n"/>
-      <c r="R3" s="410" t="n"/>
-      <c r="S3" s="410" t="n"/>
-      <c r="T3" s="410" t="n"/>
-      <c r="U3" s="410" t="n"/>
-      <c r="V3" s="410" t="n"/>
-      <c r="W3" s="410" t="n"/>
-      <c r="X3" s="410" t="n"/>
-      <c r="Y3" s="410" t="n"/>
-      <c r="Z3" s="410" t="n"/>
-      <c r="AA3" s="410" t="n"/>
-      <c r="AB3" s="410" t="n"/>
-      <c r="AC3" s="410" t="n"/>
-      <c r="AD3" s="410" t="n"/>
-      <c r="AE3" s="410" t="n"/>
-      <c r="AF3" s="410" t="n"/>
-      <c r="AG3" s="410" t="n"/>
-      <c r="AH3" s="410" t="n"/>
-      <c r="AI3" s="410" t="n"/>
-      <c r="AJ3" s="410" t="n"/>
-      <c r="AK3" s="410" t="n"/>
-      <c r="AL3" s="410" t="n"/>
-      <c r="AM3" s="410" t="n"/>
-      <c r="AN3" s="561" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="832" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="833" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="833" t="n"/>
+      <c r="AE3" s="834" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="835" t="n"/>
+      <c r="AI3" s="836" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="833" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="600" t="inlineStr">
-        <is>
-          <t>SP://evidence/FRM-306/002</t>
-        </is>
-      </c>
-      <c r="B4" s="410" t="inlineStr">
-        <is>
-          <t>CMM-001</t>
-        </is>
-      </c>
-      <c r="C4" s="410" t="inlineStr">
-        <is>
-          <t>JOB-240003</t>
-        </is>
-      </c>
-      <c r="D4" s="410" t="inlineStr">
-        <is>
-          <t>CELL-TURN-01</t>
-        </is>
-      </c>
-      <c r="E4" s="410" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="F4" s="410" t="inlineStr">
-        <is>
-          <t>PN-1003 / Rev.C</t>
-        </is>
-      </c>
-      <c r="G4" s="410" t="n"/>
-      <c r="H4" s="410" t="n"/>
-      <c r="I4" s="410" t="n"/>
-      <c r="J4" s="410" t="n"/>
-      <c r="K4" s="410" t="n"/>
-      <c r="L4" s="410" t="n"/>
-      <c r="M4" s="410" t="n"/>
-      <c r="N4" s="410" t="n"/>
-      <c r="O4" s="410" t="n"/>
-      <c r="P4" s="410" t="n"/>
-      <c r="Q4" s="410" t="n"/>
-      <c r="R4" s="410" t="n"/>
-      <c r="S4" s="410" t="n"/>
-      <c r="T4" s="410" t="n"/>
-      <c r="U4" s="410" t="n"/>
-      <c r="V4" s="410" t="n"/>
-      <c r="W4" s="410" t="n"/>
-      <c r="X4" s="410" t="n"/>
-      <c r="Y4" s="410" t="n"/>
-      <c r="Z4" s="410" t="n"/>
-      <c r="AA4" s="410" t="n"/>
-      <c r="AB4" s="410" t="n"/>
-      <c r="AC4" s="410" t="n"/>
-      <c r="AD4" s="410" t="n"/>
-      <c r="AE4" s="410" t="n"/>
-      <c r="AF4" s="410" t="n"/>
-      <c r="AG4" s="410" t="n"/>
-      <c r="AH4" s="410" t="n"/>
-      <c r="AI4" s="410" t="n"/>
-      <c r="AJ4" s="410" t="n"/>
-      <c r="AK4" s="410" t="n"/>
-      <c r="AL4" s="410" t="n"/>
-      <c r="AM4" s="410" t="n"/>
-      <c r="AN4" s="561" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="832" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="833" t="n"/>
+      <c r="I4" s="837" t="inlineStr">
+        <is>
+          <t>Quality Management System  ·  Controlled Document</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="833" t="n"/>
+      <c r="AE4" s="834" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="835" t="n"/>
+      <c r="AI4" s="836" t="inlineStr">
+        <is>
+          <t>QA / Engineering</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="833" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="600" t="inlineStr">
-        <is>
-          <t>Epicor://Job/JOB-240001</t>
-        </is>
-      </c>
-      <c r="B5" s="410" t="inlineStr">
-        <is>
-          <t>MIC-025</t>
-        </is>
-      </c>
-      <c r="C5" s="410" t="inlineStr">
-        <is>
-          <t>JOB-240004</t>
-        </is>
-      </c>
-      <c r="D5" s="410" t="inlineStr">
-        <is>
-          <t>FIN-01</t>
-        </is>
-      </c>
-      <c r="E5" s="410" t="inlineStr">
-        <is>
-          <t>Engineering Lead</t>
-        </is>
-      </c>
-      <c r="F5" s="410" t="inlineStr">
-        <is>
-          <t>PN-1004 / Rev.D</t>
-        </is>
-      </c>
-      <c r="G5" s="410" t="n"/>
-      <c r="H5" s="410" t="n"/>
-      <c r="I5" s="410" t="n"/>
-      <c r="J5" s="410" t="n"/>
-      <c r="K5" s="410" t="n"/>
-      <c r="L5" s="410" t="n"/>
-      <c r="M5" s="410" t="n"/>
-      <c r="N5" s="410" t="n"/>
-      <c r="O5" s="410" t="n"/>
-      <c r="P5" s="410" t="n"/>
-      <c r="Q5" s="410" t="n"/>
-      <c r="R5" s="410" t="n"/>
-      <c r="S5" s="410" t="n"/>
-      <c r="T5" s="410" t="n"/>
-      <c r="U5" s="410" t="n"/>
-      <c r="V5" s="410" t="n"/>
-      <c r="W5" s="410" t="n"/>
-      <c r="X5" s="410" t="n"/>
-      <c r="Y5" s="410" t="n"/>
-      <c r="Z5" s="410" t="n"/>
-      <c r="AA5" s="410" t="n"/>
-      <c r="AB5" s="410" t="n"/>
-      <c r="AC5" s="410" t="n"/>
-      <c r="AD5" s="410" t="n"/>
-      <c r="AE5" s="410" t="n"/>
-      <c r="AF5" s="410" t="n"/>
-      <c r="AG5" s="410" t="n"/>
-      <c r="AH5" s="410" t="n"/>
-      <c r="AI5" s="410" t="n"/>
-      <c r="AJ5" s="410" t="n"/>
-      <c r="AK5" s="410" t="n"/>
-      <c r="AL5" s="410" t="n"/>
-      <c r="AM5" s="410" t="n"/>
-      <c r="AN5" s="561" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="838" t="n"/>
+      <c r="B5" s="839" t="n"/>
+      <c r="C5" s="839" t="n"/>
+      <c r="D5" s="839" t="n"/>
+      <c r="E5" s="839" t="n"/>
+      <c r="F5" s="839" t="n"/>
+      <c r="G5" s="839" t="n"/>
+      <c r="H5" s="840" t="n"/>
+      <c r="I5" s="841" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="839" t="n"/>
+      <c r="K5" s="839" t="n"/>
+      <c r="L5" s="839" t="n"/>
+      <c r="M5" s="839" t="n"/>
+      <c r="N5" s="839" t="n"/>
+      <c r="O5" s="839" t="n"/>
+      <c r="P5" s="839" t="n"/>
+      <c r="Q5" s="839" t="n"/>
+      <c r="R5" s="839" t="n"/>
+      <c r="S5" s="839" t="n"/>
+      <c r="T5" s="839" t="n"/>
+      <c r="U5" s="839" t="n"/>
+      <c r="V5" s="839" t="n"/>
+      <c r="W5" s="839" t="n"/>
+      <c r="X5" s="839" t="n"/>
+      <c r="Y5" s="839" t="n"/>
+      <c r="Z5" s="839" t="n"/>
+      <c r="AA5" s="839" t="n"/>
+      <c r="AB5" s="839" t="n"/>
+      <c r="AC5" s="839" t="n"/>
+      <c r="AD5" s="840" t="n"/>
+      <c r="AE5" s="842" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="839" t="n"/>
+      <c r="AG5" s="839" t="n"/>
+      <c r="AH5" s="843" t="n"/>
+      <c r="AI5" s="844" t="inlineStr">
+        <is>
+          <t>QA Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="839" t="n"/>
+      <c r="AK5" s="839" t="n"/>
+      <c r="AL5" s="839" t="n"/>
+      <c r="AM5" s="839" t="n"/>
+      <c r="AN5" s="840" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="600" t="n"/>
-      <c r="B6" s="410" t="n"/>
-      <c r="C6" s="410" t="n"/>
-      <c r="D6" s="410" t="inlineStr">
-        <is>
-          <t>GRIND-01</t>
-        </is>
-      </c>
-      <c r="E6" s="410" t="inlineStr">
-        <is>
-          <t>Setup Technician</t>
-        </is>
-      </c>
-      <c r="F6" s="410" t="n"/>
-      <c r="G6" s="410" t="n"/>
-      <c r="H6" s="410" t="n"/>
-      <c r="I6" s="410" t="n"/>
-      <c r="J6" s="410" t="n"/>
-      <c r="K6" s="410" t="n"/>
-      <c r="L6" s="410" t="n"/>
-      <c r="M6" s="410" t="n"/>
-      <c r="N6" s="410" t="n"/>
-      <c r="O6" s="410" t="n"/>
-      <c r="P6" s="410" t="n"/>
-      <c r="Q6" s="410" t="n"/>
-      <c r="R6" s="410" t="n"/>
-      <c r="S6" s="410" t="n"/>
-      <c r="T6" s="410" t="n"/>
-      <c r="U6" s="410" t="n"/>
-      <c r="V6" s="410" t="n"/>
-      <c r="W6" s="410" t="n"/>
-      <c r="X6" s="410" t="n"/>
-      <c r="Y6" s="410" t="n"/>
-      <c r="Z6" s="410" t="n"/>
-      <c r="AA6" s="410" t="n"/>
-      <c r="AB6" s="410" t="n"/>
-      <c r="AC6" s="410" t="n"/>
-      <c r="AD6" s="410" t="n"/>
-      <c r="AE6" s="410" t="n"/>
-      <c r="AF6" s="410" t="n"/>
-      <c r="AG6" s="410" t="n"/>
-      <c r="AH6" s="410" t="n"/>
-      <c r="AI6" s="410" t="n"/>
-      <c r="AJ6" s="410" t="n"/>
-      <c r="AK6" s="410" t="n"/>
-      <c r="AL6" s="410" t="n"/>
-      <c r="AM6" s="410" t="n"/>
-      <c r="AN6" s="561" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="845" t="n"/>
+      <c r="B6" s="845" t="n"/>
+      <c r="C6" s="845" t="n"/>
+      <c r="D6" s="845" t="n"/>
+      <c r="E6" s="845" t="n"/>
+      <c r="F6" s="845" t="n"/>
+      <c r="G6" s="845" t="n"/>
+      <c r="H6" s="845" t="n"/>
+      <c r="I6" s="845" t="n"/>
+      <c r="J6" s="845" t="n"/>
+      <c r="K6" s="845" t="n"/>
+      <c r="L6" s="845" t="n"/>
+      <c r="M6" s="845" t="n"/>
+      <c r="N6" s="845" t="n"/>
+      <c r="O6" s="845" t="n"/>
+      <c r="P6" s="845" t="n"/>
+      <c r="Q6" s="845" t="n"/>
+      <c r="R6" s="845" t="n"/>
+      <c r="S6" s="845" t="n"/>
+      <c r="T6" s="845" t="n"/>
+      <c r="U6" s="845" t="n"/>
+      <c r="V6" s="845" t="n"/>
+      <c r="W6" s="845" t="n"/>
+      <c r="X6" s="845" t="n"/>
+      <c r="Y6" s="845" t="n"/>
+      <c r="Z6" s="845" t="n"/>
+      <c r="AA6" s="845" t="n"/>
+      <c r="AB6" s="845" t="n"/>
+      <c r="AC6" s="845" t="n"/>
+      <c r="AD6" s="845" t="n"/>
+      <c r="AE6" s="845" t="n"/>
+      <c r="AF6" s="845" t="n"/>
+      <c r="AG6" s="845" t="n"/>
+      <c r="AH6" s="845" t="n"/>
+      <c r="AI6" s="845" t="n"/>
+      <c r="AJ6" s="845" t="n"/>
+      <c r="AK6" s="845" t="n"/>
+      <c r="AL6" s="845" t="n"/>
+      <c r="AM6" s="845" t="n"/>
+      <c r="AN6" s="845" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="600" t="n"/>
-      <c r="B7" s="410" t="n"/>
-      <c r="C7" s="410" t="n"/>
-      <c r="D7" s="410" t="n"/>
-      <c r="E7" s="410" t="inlineStr">
-        <is>
-          <t>Maintenance Lead</t>
-        </is>
-      </c>
-      <c r="F7" s="410" t="n"/>
-      <c r="G7" s="410" t="n"/>
-      <c r="H7" s="410" t="n"/>
-      <c r="I7" s="410" t="n"/>
-      <c r="J7" s="410" t="n"/>
-      <c r="K7" s="410" t="n"/>
-      <c r="L7" s="410" t="n"/>
-      <c r="M7" s="410" t="n"/>
-      <c r="N7" s="410" t="n"/>
-      <c r="O7" s="410" t="n"/>
-      <c r="P7" s="410" t="n"/>
-      <c r="Q7" s="410" t="n"/>
-      <c r="R7" s="410" t="n"/>
-      <c r="S7" s="410" t="n"/>
-      <c r="T7" s="410" t="n"/>
-      <c r="U7" s="410" t="n"/>
-      <c r="V7" s="410" t="n"/>
-      <c r="W7" s="410" t="n"/>
-      <c r="X7" s="410" t="n"/>
-      <c r="Y7" s="410" t="n"/>
-      <c r="Z7" s="410" t="n"/>
-      <c r="AA7" s="410" t="n"/>
-      <c r="AB7" s="410" t="n"/>
-      <c r="AC7" s="410" t="n"/>
-      <c r="AD7" s="410" t="n"/>
-      <c r="AE7" s="410" t="n"/>
-      <c r="AF7" s="410" t="n"/>
-      <c r="AG7" s="410" t="n"/>
-      <c r="AH7" s="410" t="n"/>
-      <c r="AI7" s="410" t="n"/>
-      <c r="AJ7" s="410" t="n"/>
-      <c r="AK7" s="410" t="n"/>
-      <c r="AL7" s="410" t="n"/>
-      <c r="AM7" s="410" t="n"/>
-      <c r="AN7" s="561" t="n"/>
+      <c r="A7" s="604" t="inlineStr">
+        <is>
+          <t>REF_EVIDENCE_LINK</t>
+        </is>
+      </c>
+      <c r="B7" s="554" t="inlineStr">
+        <is>
+          <t>REF_GAGE_MASTER</t>
+        </is>
+      </c>
+      <c r="C7" s="554" t="inlineStr">
+        <is>
+          <t>REF_JOB_WO_MASTER</t>
+        </is>
+      </c>
+      <c r="D7" s="554" t="inlineStr">
+        <is>
+          <t>REF_MACHINE_WC_MASTER</t>
+        </is>
+      </c>
+      <c r="E7" s="554" t="inlineStr">
+        <is>
+          <t>REF_OWNER_PERSON_MASTER</t>
+        </is>
+      </c>
+      <c r="F7" s="554" t="inlineStr">
+        <is>
+          <t>REF_PART_REV_MASTER</t>
+        </is>
+      </c>
+      <c r="G7" s="846" t="n"/>
+      <c r="H7" s="846" t="n"/>
+      <c r="I7" s="846" t="n"/>
+      <c r="J7" s="846" t="n"/>
+      <c r="K7" s="846" t="n"/>
+      <c r="L7" s="846" t="n"/>
+      <c r="M7" s="846" t="n"/>
+      <c r="N7" s="846" t="n"/>
+      <c r="O7" s="846" t="n"/>
+      <c r="P7" s="846" t="n"/>
+      <c r="Q7" s="846" t="n"/>
+      <c r="R7" s="846" t="n"/>
+      <c r="S7" s="846" t="n"/>
+      <c r="T7" s="846" t="n"/>
+      <c r="U7" s="846" t="n"/>
+      <c r="V7" s="846" t="n"/>
+      <c r="W7" s="846" t="n"/>
+      <c r="X7" s="846" t="n"/>
+      <c r="Y7" s="846" t="n"/>
+      <c r="Z7" s="846" t="n"/>
+      <c r="AA7" s="846" t="n"/>
+      <c r="AB7" s="846" t="n"/>
+      <c r="AC7" s="846" t="n"/>
+      <c r="AD7" s="846" t="n"/>
+      <c r="AE7" s="846" t="n"/>
+      <c r="AF7" s="846" t="n"/>
+      <c r="AG7" s="846" t="n"/>
+      <c r="AH7" s="846" t="n"/>
+      <c r="AI7" s="846" t="n"/>
+      <c r="AJ7" s="846" t="n"/>
+      <c r="AK7" s="846" t="n"/>
+      <c r="AL7" s="846" t="n"/>
+      <c r="AM7" s="846" t="n"/>
+      <c r="AN7" s="846" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="605" t="n"/>
-      <c r="B8" s="606" t="n"/>
-      <c r="C8" s="606" t="n"/>
-      <c r="D8" s="606" t="n"/>
-      <c r="E8" s="606" t="inlineStr">
+      <c r="A8" s="600" t="inlineStr">
+        <is>
+          <t>M365://dossier/JOB-240001</t>
+        </is>
+      </c>
+      <c r="B8" s="410" t="inlineStr">
+        <is>
+          <t>GAGE-001</t>
+        </is>
+      </c>
+      <c r="C8" s="410" t="inlineStr">
+        <is>
+          <t>JOB-240001</t>
+        </is>
+      </c>
+      <c r="D8" s="410" t="inlineStr">
+        <is>
+          <t>WC-3AX-01</t>
+        </is>
+      </c>
+      <c r="E8" s="410" t="inlineStr">
+        <is>
+          <t>Planning Lead</t>
+        </is>
+      </c>
+      <c r="F8" s="410" t="inlineStr">
+        <is>
+          <t>PN-1001 / Rev.A</t>
+        </is>
+      </c>
+      <c r="G8" s="846" t="n"/>
+      <c r="H8" s="846" t="n"/>
+      <c r="I8" s="846" t="n"/>
+      <c r="J8" s="846" t="n"/>
+      <c r="K8" s="846" t="n"/>
+      <c r="L8" s="846" t="n"/>
+      <c r="M8" s="846" t="n"/>
+      <c r="N8" s="846" t="n"/>
+      <c r="O8" s="846" t="n"/>
+      <c r="P8" s="846" t="n"/>
+      <c r="Q8" s="846" t="n"/>
+      <c r="R8" s="846" t="n"/>
+      <c r="S8" s="846" t="n"/>
+      <c r="T8" s="846" t="n"/>
+      <c r="U8" s="846" t="n"/>
+      <c r="V8" s="846" t="n"/>
+      <c r="W8" s="846" t="n"/>
+      <c r="X8" s="846" t="n"/>
+      <c r="Y8" s="846" t="n"/>
+      <c r="Z8" s="846" t="n"/>
+      <c r="AA8" s="846" t="n"/>
+      <c r="AB8" s="846" t="n"/>
+      <c r="AC8" s="846" t="n"/>
+      <c r="AD8" s="846" t="n"/>
+      <c r="AE8" s="846" t="n"/>
+      <c r="AF8" s="846" t="n"/>
+      <c r="AG8" s="846" t="n"/>
+      <c r="AH8" s="846" t="n"/>
+      <c r="AI8" s="846" t="n"/>
+      <c r="AJ8" s="846" t="n"/>
+      <c r="AK8" s="846" t="n"/>
+      <c r="AL8" s="846" t="n"/>
+      <c r="AM8" s="846" t="n"/>
+      <c r="AN8" s="846" t="n"/>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="600" t="inlineStr">
+        <is>
+          <t>SP://evidence/FRM-202/001</t>
+        </is>
+      </c>
+      <c r="B9" s="410" t="inlineStr">
+        <is>
+          <t>GAGE-002</t>
+        </is>
+      </c>
+      <c r="C9" s="410" t="inlineStr">
+        <is>
+          <t>JOB-240002</t>
+        </is>
+      </c>
+      <c r="D9" s="410" t="inlineStr">
+        <is>
+          <t>WC-5AX-02</t>
+        </is>
+      </c>
+      <c r="E9" s="410" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+      <c r="F9" s="410" t="inlineStr">
+        <is>
+          <t>PN-1002 / Rev.B</t>
+        </is>
+      </c>
+      <c r="G9" s="846" t="n"/>
+      <c r="H9" s="846" t="n"/>
+      <c r="I9" s="846" t="n"/>
+      <c r="J9" s="846" t="n"/>
+      <c r="K9" s="846" t="n"/>
+      <c r="L9" s="846" t="n"/>
+      <c r="M9" s="846" t="n"/>
+      <c r="N9" s="846" t="n"/>
+      <c r="O9" s="846" t="n"/>
+      <c r="P9" s="846" t="n"/>
+      <c r="Q9" s="846" t="n"/>
+      <c r="R9" s="846" t="n"/>
+      <c r="S9" s="846" t="n"/>
+      <c r="T9" s="846" t="n"/>
+      <c r="U9" s="846" t="n"/>
+      <c r="V9" s="846" t="n"/>
+      <c r="W9" s="846" t="n"/>
+      <c r="X9" s="846" t="n"/>
+      <c r="Y9" s="846" t="n"/>
+      <c r="Z9" s="846" t="n"/>
+      <c r="AA9" s="846" t="n"/>
+      <c r="AB9" s="846" t="n"/>
+      <c r="AC9" s="846" t="n"/>
+      <c r="AD9" s="846" t="n"/>
+      <c r="AE9" s="846" t="n"/>
+      <c r="AF9" s="846" t="n"/>
+      <c r="AG9" s="846" t="n"/>
+      <c r="AH9" s="846" t="n"/>
+      <c r="AI9" s="846" t="n"/>
+      <c r="AJ9" s="846" t="n"/>
+      <c r="AK9" s="846" t="n"/>
+      <c r="AL9" s="846" t="n"/>
+      <c r="AM9" s="846" t="n"/>
+      <c r="AN9" s="846" t="n"/>
+    </row>
+    <row r="10" hidden="1">
+      <c r="A10" s="600" t="inlineStr">
+        <is>
+          <t>SP://evidence/FRM-306/002</t>
+        </is>
+      </c>
+      <c r="B10" s="410" t="inlineStr">
+        <is>
+          <t>CMM-001</t>
+        </is>
+      </c>
+      <c r="C10" s="410" t="inlineStr">
+        <is>
+          <t>JOB-240003</t>
+        </is>
+      </c>
+      <c r="D10" s="410" t="inlineStr">
+        <is>
+          <t>CELL-TURN-01</t>
+        </is>
+      </c>
+      <c r="E10" s="410" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="F10" s="410" t="inlineStr">
+        <is>
+          <t>PN-1003 / Rev.C</t>
+        </is>
+      </c>
+      <c r="G10" s="846" t="n"/>
+      <c r="H10" s="846" t="n"/>
+      <c r="I10" s="846" t="n"/>
+      <c r="J10" s="846" t="n"/>
+      <c r="K10" s="846" t="n"/>
+      <c r="L10" s="846" t="n"/>
+      <c r="M10" s="846" t="n"/>
+      <c r="N10" s="846" t="n"/>
+      <c r="O10" s="846" t="n"/>
+      <c r="P10" s="846" t="n"/>
+      <c r="Q10" s="846" t="n"/>
+      <c r="R10" s="846" t="n"/>
+      <c r="S10" s="846" t="n"/>
+      <c r="T10" s="846" t="n"/>
+      <c r="U10" s="846" t="n"/>
+      <c r="V10" s="846" t="n"/>
+      <c r="W10" s="846" t="n"/>
+      <c r="X10" s="846" t="n"/>
+      <c r="Y10" s="846" t="n"/>
+      <c r="Z10" s="846" t="n"/>
+      <c r="AA10" s="846" t="n"/>
+      <c r="AB10" s="846" t="n"/>
+      <c r="AC10" s="846" t="n"/>
+      <c r="AD10" s="846" t="n"/>
+      <c r="AE10" s="846" t="n"/>
+      <c r="AF10" s="846" t="n"/>
+      <c r="AG10" s="846" t="n"/>
+      <c r="AH10" s="846" t="n"/>
+      <c r="AI10" s="846" t="n"/>
+      <c r="AJ10" s="846" t="n"/>
+      <c r="AK10" s="846" t="n"/>
+      <c r="AL10" s="846" t="n"/>
+      <c r="AM10" s="846" t="n"/>
+      <c r="AN10" s="846" t="n"/>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="600" t="inlineStr">
+        <is>
+          <t>Epicor://Job/JOB-240001</t>
+        </is>
+      </c>
+      <c r="B11" s="410" t="inlineStr">
+        <is>
+          <t>MIC-025</t>
+        </is>
+      </c>
+      <c r="C11" s="410" t="inlineStr">
+        <is>
+          <t>JOB-240004</t>
+        </is>
+      </c>
+      <c r="D11" s="410" t="inlineStr">
+        <is>
+          <t>FIN-01</t>
+        </is>
+      </c>
+      <c r="E11" s="410" t="inlineStr">
+        <is>
+          <t>Engineering Lead</t>
+        </is>
+      </c>
+      <c r="F11" s="410" t="inlineStr">
+        <is>
+          <t>PN-1004 / Rev.D</t>
+        </is>
+      </c>
+      <c r="G11" s="846" t="n"/>
+      <c r="H11" s="846" t="n"/>
+      <c r="I11" s="846" t="n"/>
+      <c r="J11" s="846" t="n"/>
+      <c r="K11" s="846" t="n"/>
+      <c r="L11" s="846" t="n"/>
+      <c r="M11" s="846" t="n"/>
+      <c r="N11" s="846" t="n"/>
+      <c r="O11" s="846" t="n"/>
+      <c r="P11" s="846" t="n"/>
+      <c r="Q11" s="846" t="n"/>
+      <c r="R11" s="846" t="n"/>
+      <c r="S11" s="846" t="n"/>
+      <c r="T11" s="846" t="n"/>
+      <c r="U11" s="846" t="n"/>
+      <c r="V11" s="846" t="n"/>
+      <c r="W11" s="846" t="n"/>
+      <c r="X11" s="846" t="n"/>
+      <c r="Y11" s="846" t="n"/>
+      <c r="Z11" s="846" t="n"/>
+      <c r="AA11" s="846" t="n"/>
+      <c r="AB11" s="846" t="n"/>
+      <c r="AC11" s="846" t="n"/>
+      <c r="AD11" s="846" t="n"/>
+      <c r="AE11" s="846" t="n"/>
+      <c r="AF11" s="846" t="n"/>
+      <c r="AG11" s="846" t="n"/>
+      <c r="AH11" s="846" t="n"/>
+      <c r="AI11" s="846" t="n"/>
+      <c r="AJ11" s="846" t="n"/>
+      <c r="AK11" s="846" t="n"/>
+      <c r="AL11" s="846" t="n"/>
+      <c r="AM11" s="846" t="n"/>
+      <c r="AN11" s="846" t="n"/>
+    </row>
+    <row r="12" hidden="1">
+      <c r="A12" s="846" t="n"/>
+      <c r="B12" s="846" t="n"/>
+      <c r="C12" s="846" t="n"/>
+      <c r="D12" s="410" t="inlineStr">
+        <is>
+          <t>GRIND-01</t>
+        </is>
+      </c>
+      <c r="E12" s="410" t="inlineStr">
+        <is>
+          <t>Setup Technician</t>
+        </is>
+      </c>
+      <c r="F12" s="846" t="n"/>
+      <c r="G12" s="846" t="n"/>
+      <c r="H12" s="846" t="n"/>
+      <c r="I12" s="846" t="n"/>
+      <c r="J12" s="846" t="n"/>
+      <c r="K12" s="846" t="n"/>
+      <c r="L12" s="846" t="n"/>
+      <c r="M12" s="846" t="n"/>
+      <c r="N12" s="846" t="n"/>
+      <c r="O12" s="846" t="n"/>
+      <c r="P12" s="846" t="n"/>
+      <c r="Q12" s="846" t="n"/>
+      <c r="R12" s="846" t="n"/>
+      <c r="S12" s="846" t="n"/>
+      <c r="T12" s="846" t="n"/>
+      <c r="U12" s="846" t="n"/>
+      <c r="V12" s="846" t="n"/>
+      <c r="W12" s="846" t="n"/>
+      <c r="X12" s="846" t="n"/>
+      <c r="Y12" s="846" t="n"/>
+      <c r="Z12" s="846" t="n"/>
+      <c r="AA12" s="846" t="n"/>
+      <c r="AB12" s="846" t="n"/>
+      <c r="AC12" s="846" t="n"/>
+      <c r="AD12" s="846" t="n"/>
+      <c r="AE12" s="846" t="n"/>
+      <c r="AF12" s="846" t="n"/>
+      <c r="AG12" s="846" t="n"/>
+      <c r="AH12" s="846" t="n"/>
+      <c r="AI12" s="846" t="n"/>
+      <c r="AJ12" s="846" t="n"/>
+      <c r="AK12" s="846" t="n"/>
+      <c r="AL12" s="846" t="n"/>
+      <c r="AM12" s="846" t="n"/>
+      <c r="AN12" s="846" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="846" t="n"/>
+      <c r="B13" s="846" t="n"/>
+      <c r="C13" s="846" t="n"/>
+      <c r="D13" s="846" t="n"/>
+      <c r="E13" s="410" t="inlineStr">
+        <is>
+          <t>Maintenance Lead</t>
+        </is>
+      </c>
+      <c r="F13" s="846" t="n"/>
+      <c r="G13" s="846" t="n"/>
+      <c r="H13" s="846" t="n"/>
+      <c r="I13" s="846" t="n"/>
+      <c r="J13" s="846" t="n"/>
+      <c r="K13" s="846" t="n"/>
+      <c r="L13" s="846" t="n"/>
+      <c r="M13" s="846" t="n"/>
+      <c r="N13" s="846" t="n"/>
+      <c r="O13" s="846" t="n"/>
+      <c r="P13" s="846" t="n"/>
+      <c r="Q13" s="846" t="n"/>
+      <c r="R13" s="846" t="n"/>
+      <c r="S13" s="846" t="n"/>
+      <c r="T13" s="846" t="n"/>
+      <c r="U13" s="846" t="n"/>
+      <c r="V13" s="846" t="n"/>
+      <c r="W13" s="846" t="n"/>
+      <c r="X13" s="846" t="n"/>
+      <c r="Y13" s="846" t="n"/>
+      <c r="Z13" s="846" t="n"/>
+      <c r="AA13" s="846" t="n"/>
+      <c r="AB13" s="846" t="n"/>
+      <c r="AC13" s="846" t="n"/>
+      <c r="AD13" s="846" t="n"/>
+      <c r="AE13" s="846" t="n"/>
+      <c r="AF13" s="846" t="n"/>
+      <c r="AG13" s="846" t="n"/>
+      <c r="AH13" s="846" t="n"/>
+      <c r="AI13" s="846" t="n"/>
+      <c r="AJ13" s="846" t="n"/>
+      <c r="AK13" s="846" t="n"/>
+      <c r="AL13" s="846" t="n"/>
+      <c r="AM13" s="846" t="n"/>
+      <c r="AN13" s="846" t="n"/>
+    </row>
+    <row r="14" hidden="1">
+      <c r="A14" s="846" t="n"/>
+      <c r="B14" s="846" t="n"/>
+      <c r="C14" s="846" t="n"/>
+      <c r="D14" s="846" t="n"/>
+      <c r="E14" s="606" t="inlineStr">
         <is>
           <t>Commercial Owner</t>
         </is>
       </c>
-      <c r="F8" s="606" t="n"/>
-      <c r="G8" s="606" t="n"/>
-      <c r="H8" s="606" t="n"/>
-      <c r="I8" s="606" t="n"/>
-      <c r="J8" s="606" t="n"/>
-      <c r="K8" s="606" t="n"/>
-      <c r="L8" s="606" t="n"/>
-      <c r="M8" s="606" t="n"/>
-      <c r="N8" s="606" t="n"/>
-      <c r="O8" s="606" t="n"/>
-      <c r="P8" s="606" t="n"/>
-      <c r="Q8" s="606" t="n"/>
-      <c r="R8" s="606" t="n"/>
-      <c r="S8" s="606" t="n"/>
-      <c r="T8" s="606" t="n"/>
-      <c r="U8" s="606" t="n"/>
-      <c r="V8" s="606" t="n"/>
-      <c r="W8" s="606" t="n"/>
-      <c r="X8" s="606" t="n"/>
-      <c r="Y8" s="606" t="n"/>
-      <c r="Z8" s="606" t="n"/>
-      <c r="AA8" s="606" t="n"/>
-      <c r="AB8" s="606" t="n"/>
-      <c r="AC8" s="606" t="n"/>
-      <c r="AD8" s="606" t="n"/>
-      <c r="AE8" s="606" t="n"/>
-      <c r="AF8" s="606" t="n"/>
-      <c r="AG8" s="606" t="n"/>
-      <c r="AH8" s="606" t="n"/>
-      <c r="AI8" s="606" t="n"/>
-      <c r="AJ8" s="606" t="n"/>
-      <c r="AK8" s="606" t="n"/>
-      <c r="AL8" s="606" t="n"/>
-      <c r="AM8" s="606" t="n"/>
-      <c r="AN8" s="607" t="n"/>
+      <c r="F14" s="846" t="n"/>
+      <c r="G14" s="846" t="n"/>
+      <c r="H14" s="846" t="n"/>
+      <c r="I14" s="846" t="n"/>
+      <c r="J14" s="846" t="n"/>
+      <c r="K14" s="846" t="n"/>
+      <c r="L14" s="846" t="n"/>
+      <c r="M14" s="846" t="n"/>
+      <c r="N14" s="846" t="n"/>
+      <c r="O14" s="846" t="n"/>
+      <c r="P14" s="846" t="n"/>
+      <c r="Q14" s="846" t="n"/>
+      <c r="R14" s="846" t="n"/>
+      <c r="S14" s="846" t="n"/>
+      <c r="T14" s="846" t="n"/>
+      <c r="U14" s="846" t="n"/>
+      <c r="V14" s="846" t="n"/>
+      <c r="W14" s="846" t="n"/>
+      <c r="X14" s="846" t="n"/>
+      <c r="Y14" s="846" t="n"/>
+      <c r="Z14" s="846" t="n"/>
+      <c r="AA14" s="846" t="n"/>
+      <c r="AB14" s="846" t="n"/>
+      <c r="AC14" s="846" t="n"/>
+      <c r="AD14" s="846" t="n"/>
+      <c r="AE14" s="846" t="n"/>
+      <c r="AF14" s="846" t="n"/>
+      <c r="AG14" s="846" t="n"/>
+      <c r="AH14" s="846" t="n"/>
+      <c r="AI14" s="846" t="n"/>
+      <c r="AJ14" s="846" t="n"/>
+      <c r="AK14" s="846" t="n"/>
+      <c r="AL14" s="846" t="n"/>
+      <c r="AM14" s="846" t="n"/>
+      <c r="AN14" s="846" t="n"/>
     </row>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
+    <row r="15" hidden="1">
+      <c r="A15" s="846" t="n"/>
+      <c r="B15" s="846" t="n"/>
+      <c r="C15" s="846" t="n"/>
+      <c r="D15" s="846" t="n"/>
+      <c r="E15" s="846" t="n"/>
+      <c r="F15" s="846" t="n"/>
+      <c r="G15" s="846" t="n"/>
+      <c r="H15" s="846" t="n"/>
+      <c r="I15" s="846" t="n"/>
+      <c r="J15" s="846" t="n"/>
+      <c r="K15" s="846" t="n"/>
+      <c r="L15" s="846" t="n"/>
+      <c r="M15" s="846" t="n"/>
+      <c r="N15" s="846" t="n"/>
+      <c r="O15" s="846" t="n"/>
+      <c r="P15" s="846" t="n"/>
+      <c r="Q15" s="846" t="n"/>
+      <c r="R15" s="846" t="n"/>
+      <c r="S15" s="846" t="n"/>
+      <c r="T15" s="846" t="n"/>
+      <c r="U15" s="846" t="n"/>
+      <c r="V15" s="846" t="n"/>
+      <c r="W15" s="846" t="n"/>
+      <c r="X15" s="846" t="n"/>
+      <c r="Y15" s="846" t="n"/>
+      <c r="Z15" s="846" t="n"/>
+      <c r="AA15" s="846" t="n"/>
+      <c r="AB15" s="846" t="n"/>
+      <c r="AC15" s="846" t="n"/>
+      <c r="AD15" s="846" t="n"/>
+      <c r="AE15" s="846" t="n"/>
+      <c r="AF15" s="846" t="n"/>
+      <c r="AG15" s="846" t="n"/>
+      <c r="AH15" s="846" t="n"/>
+      <c r="AI15" s="846" t="n"/>
+      <c r="AJ15" s="846" t="n"/>
+      <c r="AK15" s="846" t="n"/>
+      <c r="AL15" s="846" t="n"/>
+      <c r="AM15" s="846" t="n"/>
+      <c r="AN15" s="846" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="846" t="n"/>
+      <c r="B16" s="846" t="n"/>
+      <c r="C16" s="846" t="n"/>
+      <c r="D16" s="846" t="n"/>
+      <c r="E16" s="846" t="n"/>
+      <c r="F16" s="846" t="n"/>
+      <c r="G16" s="846" t="n"/>
+      <c r="H16" s="846" t="n"/>
+      <c r="I16" s="846" t="n"/>
+      <c r="J16" s="846" t="n"/>
+      <c r="K16" s="846" t="n"/>
+      <c r="L16" s="846" t="n"/>
+      <c r="M16" s="846" t="n"/>
+      <c r="N16" s="846" t="n"/>
+      <c r="O16" s="846" t="n"/>
+      <c r="P16" s="846" t="n"/>
+      <c r="Q16" s="846" t="n"/>
+      <c r="R16" s="846" t="n"/>
+      <c r="S16" s="846" t="n"/>
+      <c r="T16" s="846" t="n"/>
+      <c r="U16" s="846" t="n"/>
+      <c r="V16" s="846" t="n"/>
+      <c r="W16" s="846" t="n"/>
+      <c r="X16" s="846" t="n"/>
+      <c r="Y16" s="846" t="n"/>
+      <c r="Z16" s="846" t="n"/>
+      <c r="AA16" s="846" t="n"/>
+      <c r="AB16" s="846" t="n"/>
+      <c r="AC16" s="846" t="n"/>
+      <c r="AD16" s="846" t="n"/>
+      <c r="AE16" s="846" t="n"/>
+      <c r="AF16" s="846" t="n"/>
+      <c r="AG16" s="846" t="n"/>
+      <c r="AH16" s="846" t="n"/>
+      <c r="AI16" s="846" t="n"/>
+      <c r="AJ16" s="846" t="n"/>
+      <c r="AK16" s="846" t="n"/>
+      <c r="AL16" s="846" t="n"/>
+      <c r="AM16" s="846" t="n"/>
+      <c r="AN16" s="846" t="n"/>
+    </row>
+    <row r="17" hidden="1">
+      <c r="A17" s="846" t="n"/>
+      <c r="B17" s="846" t="n"/>
+      <c r="C17" s="846" t="n"/>
+      <c r="D17" s="846" t="n"/>
+      <c r="E17" s="846" t="n"/>
+      <c r="F17" s="846" t="n"/>
+      <c r="G17" s="846" t="n"/>
+      <c r="H17" s="846" t="n"/>
+      <c r="I17" s="846" t="n"/>
+      <c r="J17" s="846" t="n"/>
+      <c r="K17" s="846" t="n"/>
+      <c r="L17" s="846" t="n"/>
+      <c r="M17" s="846" t="n"/>
+      <c r="N17" s="846" t="n"/>
+      <c r="O17" s="846" t="n"/>
+      <c r="P17" s="846" t="n"/>
+      <c r="Q17" s="846" t="n"/>
+      <c r="R17" s="846" t="n"/>
+      <c r="S17" s="846" t="n"/>
+      <c r="T17" s="846" t="n"/>
+      <c r="U17" s="846" t="n"/>
+      <c r="V17" s="846" t="n"/>
+      <c r="W17" s="846" t="n"/>
+      <c r="X17" s="846" t="n"/>
+      <c r="Y17" s="846" t="n"/>
+      <c r="Z17" s="846" t="n"/>
+      <c r="AA17" s="846" t="n"/>
+      <c r="AB17" s="846" t="n"/>
+      <c r="AC17" s="846" t="n"/>
+      <c r="AD17" s="846" t="n"/>
+      <c r="AE17" s="846" t="n"/>
+      <c r="AF17" s="846" t="n"/>
+      <c r="AG17" s="846" t="n"/>
+      <c r="AH17" s="846" t="n"/>
+      <c r="AI17" s="846" t="n"/>
+      <c r="AJ17" s="846" t="n"/>
+      <c r="AK17" s="846" t="n"/>
+      <c r="AL17" s="846" t="n"/>
+      <c r="AM17" s="846" t="n"/>
+      <c r="AN17" s="846" t="n"/>
+    </row>
     <row r="18" hidden="1"/>
     <row r="19" hidden="1"/>
     <row r="20" hidden="1"/>
@@ -14153,6 +14495,22 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -15886,51 +16244,51 @@
       <c r="AM35" s="750" t="n"/>
       <c r="AN35" s="751" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="679" t="inlineStr">
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="819" t="inlineStr">
         <is>
           <t>NOTICE  —  Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B36" s="289" t="n"/>
-      <c r="C36" s="289" t="n"/>
-      <c r="D36" s="289" t="n"/>
-      <c r="E36" s="289" t="n"/>
-      <c r="F36" s="289" t="n"/>
-      <c r="G36" s="289" t="n"/>
-      <c r="H36" s="289" t="n"/>
-      <c r="I36" s="289" t="n"/>
-      <c r="J36" s="289" t="n"/>
-      <c r="K36" s="733" t="n"/>
-      <c r="L36" s="733" t="n"/>
-      <c r="M36" s="733" t="n"/>
-      <c r="N36" s="733" t="n"/>
-      <c r="O36" s="733" t="n"/>
-      <c r="P36" s="733" t="n"/>
-      <c r="Q36" s="733" t="n"/>
-      <c r="R36" s="733" t="n"/>
-      <c r="S36" s="733" t="n"/>
-      <c r="T36" s="733" t="n"/>
-      <c r="U36" s="733" t="n"/>
-      <c r="V36" s="733" t="n"/>
-      <c r="W36" s="733" t="n"/>
-      <c r="X36" s="733" t="n"/>
-      <c r="Y36" s="733" t="n"/>
-      <c r="Z36" s="733" t="n"/>
-      <c r="AA36" s="733" t="n"/>
-      <c r="AB36" s="733" t="n"/>
-      <c r="AC36" s="733" t="n"/>
-      <c r="AD36" s="733" t="n"/>
-      <c r="AE36" s="733" t="n"/>
-      <c r="AF36" s="733" t="n"/>
-      <c r="AG36" s="733" t="n"/>
-      <c r="AH36" s="733" t="n"/>
-      <c r="AI36" s="733" t="n"/>
-      <c r="AJ36" s="733" t="n"/>
-      <c r="AK36" s="733" t="n"/>
-      <c r="AL36" s="733" t="n"/>
-      <c r="AM36" s="733" t="n"/>
-      <c r="AN36" s="734" t="n"/>
+      <c r="B36" s="820" t="n"/>
+      <c r="C36" s="820" t="n"/>
+      <c r="D36" s="820" t="n"/>
+      <c r="E36" s="820" t="n"/>
+      <c r="F36" s="820" t="n"/>
+      <c r="G36" s="820" t="n"/>
+      <c r="H36" s="820" t="n"/>
+      <c r="I36" s="820" t="n"/>
+      <c r="J36" s="820" t="n"/>
+      <c r="K36" s="820" t="n"/>
+      <c r="L36" s="820" t="n"/>
+      <c r="M36" s="820" t="n"/>
+      <c r="N36" s="820" t="n"/>
+      <c r="O36" s="820" t="n"/>
+      <c r="P36" s="820" t="n"/>
+      <c r="Q36" s="820" t="n"/>
+      <c r="R36" s="820" t="n"/>
+      <c r="S36" s="820" t="n"/>
+      <c r="T36" s="820" t="n"/>
+      <c r="U36" s="820" t="n"/>
+      <c r="V36" s="820" t="n"/>
+      <c r="W36" s="820" t="n"/>
+      <c r="X36" s="820" t="n"/>
+      <c r="Y36" s="820" t="n"/>
+      <c r="Z36" s="820" t="n"/>
+      <c r="AA36" s="820" t="n"/>
+      <c r="AB36" s="820" t="n"/>
+      <c r="AC36" s="820" t="n"/>
+      <c r="AD36" s="820" t="n"/>
+      <c r="AE36" s="820" t="n"/>
+      <c r="AF36" s="820" t="n"/>
+      <c r="AG36" s="820" t="n"/>
+      <c r="AH36" s="820" t="n"/>
+      <c r="AI36" s="820" t="n"/>
+      <c r="AJ36" s="820" t="n"/>
+      <c r="AK36" s="820" t="n"/>
+      <c r="AL36" s="820" t="n"/>
+      <c r="AM36" s="820" t="n"/>
+      <c r="AN36" s="821" t="n"/>
     </row>
     <row r="37" hidden="1" outlineLevel="1"/>
     <row r="38" hidden="1" outlineLevel="1"/>
@@ -17528,51 +17886,51 @@
       <c r="AM27" s="750" t="n"/>
       <c r="AN27" s="751" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="679" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="819" t="inlineStr">
         <is>
           <t>NOTICE  —  Material, special-process and supporting certification linkage for the FAI package.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="289" t="n"/>
-      <c r="C28" s="289" t="n"/>
-      <c r="D28" s="289" t="n"/>
-      <c r="E28" s="289" t="n"/>
-      <c r="F28" s="289" t="n"/>
-      <c r="G28" s="289" t="n"/>
-      <c r="H28" s="289" t="n"/>
-      <c r="I28" s="733" t="n"/>
-      <c r="J28" s="733" t="n"/>
-      <c r="K28" s="733" t="n"/>
-      <c r="L28" s="733" t="n"/>
-      <c r="M28" s="733" t="n"/>
-      <c r="N28" s="733" t="n"/>
-      <c r="O28" s="733" t="n"/>
-      <c r="P28" s="733" t="n"/>
-      <c r="Q28" s="733" t="n"/>
-      <c r="R28" s="733" t="n"/>
-      <c r="S28" s="733" t="n"/>
-      <c r="T28" s="733" t="n"/>
-      <c r="U28" s="733" t="n"/>
-      <c r="V28" s="733" t="n"/>
-      <c r="W28" s="733" t="n"/>
-      <c r="X28" s="733" t="n"/>
-      <c r="Y28" s="733" t="n"/>
-      <c r="Z28" s="733" t="n"/>
-      <c r="AA28" s="733" t="n"/>
-      <c r="AB28" s="733" t="n"/>
-      <c r="AC28" s="733" t="n"/>
-      <c r="AD28" s="733" t="n"/>
-      <c r="AE28" s="733" t="n"/>
-      <c r="AF28" s="733" t="n"/>
-      <c r="AG28" s="733" t="n"/>
-      <c r="AH28" s="733" t="n"/>
-      <c r="AI28" s="733" t="n"/>
-      <c r="AJ28" s="733" t="n"/>
-      <c r="AK28" s="733" t="n"/>
-      <c r="AL28" s="733" t="n"/>
-      <c r="AM28" s="733" t="n"/>
-      <c r="AN28" s="734" t="n"/>
+      <c r="B28" s="820" t="n"/>
+      <c r="C28" s="820" t="n"/>
+      <c r="D28" s="820" t="n"/>
+      <c r="E28" s="820" t="n"/>
+      <c r="F28" s="820" t="n"/>
+      <c r="G28" s="820" t="n"/>
+      <c r="H28" s="820" t="n"/>
+      <c r="I28" s="820" t="n"/>
+      <c r="J28" s="820" t="n"/>
+      <c r="K28" s="820" t="n"/>
+      <c r="L28" s="820" t="n"/>
+      <c r="M28" s="820" t="n"/>
+      <c r="N28" s="820" t="n"/>
+      <c r="O28" s="820" t="n"/>
+      <c r="P28" s="820" t="n"/>
+      <c r="Q28" s="820" t="n"/>
+      <c r="R28" s="820" t="n"/>
+      <c r="S28" s="820" t="n"/>
+      <c r="T28" s="820" t="n"/>
+      <c r="U28" s="820" t="n"/>
+      <c r="V28" s="820" t="n"/>
+      <c r="W28" s="820" t="n"/>
+      <c r="X28" s="820" t="n"/>
+      <c r="Y28" s="820" t="n"/>
+      <c r="Z28" s="820" t="n"/>
+      <c r="AA28" s="820" t="n"/>
+      <c r="AB28" s="820" t="n"/>
+      <c r="AC28" s="820" t="n"/>
+      <c r="AD28" s="820" t="n"/>
+      <c r="AE28" s="820" t="n"/>
+      <c r="AF28" s="820" t="n"/>
+      <c r="AG28" s="820" t="n"/>
+      <c r="AH28" s="820" t="n"/>
+      <c r="AI28" s="820" t="n"/>
+      <c r="AJ28" s="820" t="n"/>
+      <c r="AK28" s="820" t="n"/>
+      <c r="AL28" s="820" t="n"/>
+      <c r="AM28" s="820" t="n"/>
+      <c r="AN28" s="821" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -19171,51 +19529,51 @@
       <c r="AM27" s="750" t="n"/>
       <c r="AN27" s="751" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="679" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="819" t="inlineStr">
         <is>
           <t>NOTICE  —  Use for revalidation triggers, scope and follow-up approval actions.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="289" t="n"/>
-      <c r="C28" s="289" t="n"/>
-      <c r="D28" s="289" t="n"/>
-      <c r="E28" s="289" t="n"/>
-      <c r="F28" s="289" t="n"/>
-      <c r="G28" s="289" t="n"/>
-      <c r="H28" s="733" t="n"/>
-      <c r="I28" s="733" t="n"/>
-      <c r="J28" s="733" t="n"/>
-      <c r="K28" s="733" t="n"/>
-      <c r="L28" s="733" t="n"/>
-      <c r="M28" s="733" t="n"/>
-      <c r="N28" s="733" t="n"/>
-      <c r="O28" s="733" t="n"/>
-      <c r="P28" s="733" t="n"/>
-      <c r="Q28" s="733" t="n"/>
-      <c r="R28" s="733" t="n"/>
-      <c r="S28" s="733" t="n"/>
-      <c r="T28" s="733" t="n"/>
-      <c r="U28" s="733" t="n"/>
-      <c r="V28" s="733" t="n"/>
-      <c r="W28" s="733" t="n"/>
-      <c r="X28" s="733" t="n"/>
-      <c r="Y28" s="733" t="n"/>
-      <c r="Z28" s="733" t="n"/>
-      <c r="AA28" s="733" t="n"/>
-      <c r="AB28" s="733" t="n"/>
-      <c r="AC28" s="733" t="n"/>
-      <c r="AD28" s="733" t="n"/>
-      <c r="AE28" s="733" t="n"/>
-      <c r="AF28" s="733" t="n"/>
-      <c r="AG28" s="733" t="n"/>
-      <c r="AH28" s="733" t="n"/>
-      <c r="AI28" s="733" t="n"/>
-      <c r="AJ28" s="733" t="n"/>
-      <c r="AK28" s="733" t="n"/>
-      <c r="AL28" s="733" t="n"/>
-      <c r="AM28" s="733" t="n"/>
-      <c r="AN28" s="734" t="n"/>
+      <c r="B28" s="820" t="n"/>
+      <c r="C28" s="820" t="n"/>
+      <c r="D28" s="820" t="n"/>
+      <c r="E28" s="820" t="n"/>
+      <c r="F28" s="820" t="n"/>
+      <c r="G28" s="820" t="n"/>
+      <c r="H28" s="820" t="n"/>
+      <c r="I28" s="820" t="n"/>
+      <c r="J28" s="820" t="n"/>
+      <c r="K28" s="820" t="n"/>
+      <c r="L28" s="820" t="n"/>
+      <c r="M28" s="820" t="n"/>
+      <c r="N28" s="820" t="n"/>
+      <c r="O28" s="820" t="n"/>
+      <c r="P28" s="820" t="n"/>
+      <c r="Q28" s="820" t="n"/>
+      <c r="R28" s="820" t="n"/>
+      <c r="S28" s="820" t="n"/>
+      <c r="T28" s="820" t="n"/>
+      <c r="U28" s="820" t="n"/>
+      <c r="V28" s="820" t="n"/>
+      <c r="W28" s="820" t="n"/>
+      <c r="X28" s="820" t="n"/>
+      <c r="Y28" s="820" t="n"/>
+      <c r="Z28" s="820" t="n"/>
+      <c r="AA28" s="820" t="n"/>
+      <c r="AB28" s="820" t="n"/>
+      <c r="AC28" s="820" t="n"/>
+      <c r="AD28" s="820" t="n"/>
+      <c r="AE28" s="820" t="n"/>
+      <c r="AF28" s="820" t="n"/>
+      <c r="AG28" s="820" t="n"/>
+      <c r="AH28" s="820" t="n"/>
+      <c r="AI28" s="820" t="n"/>
+      <c r="AJ28" s="820" t="n"/>
+      <c r="AK28" s="820" t="n"/>
+      <c r="AL28" s="820" t="n"/>
+      <c r="AM28" s="820" t="n"/>
+      <c r="AN28" s="821" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -19455,7 +19813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -19501,506 +19859,927 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="648" t="inlineStr">
-        <is>
-          <t>REF_LINKS</t>
-        </is>
-      </c>
-      <c r="B1" s="775" t="n"/>
-      <c r="C1" s="775" t="n"/>
-      <c r="D1" s="775" t="n"/>
-      <c r="E1" s="775" t="n"/>
-      <c r="F1" s="775" t="n"/>
-      <c r="G1" s="775" t="n"/>
-      <c r="H1" s="643" t="n"/>
-      <c r="I1" s="514" t="n"/>
-      <c r="J1" s="515" t="n"/>
-      <c r="K1" s="515" t="n"/>
-      <c r="L1" s="515" t="n"/>
-      <c r="M1" s="515" t="n"/>
-      <c r="N1" s="515" t="n"/>
-      <c r="O1" s="515" t="n"/>
-      <c r="P1" s="515" t="n"/>
-      <c r="Q1" s="515" t="n"/>
-      <c r="R1" s="515" t="n"/>
-      <c r="S1" s="515" t="n"/>
-      <c r="T1" s="515" t="n"/>
-      <c r="U1" s="515" t="n"/>
-      <c r="V1" s="515" t="n"/>
-      <c r="W1" s="515" t="n"/>
-      <c r="X1" s="515" t="n"/>
-      <c r="Y1" s="515" t="n"/>
-      <c r="Z1" s="515" t="n"/>
-      <c r="AA1" s="515" t="n"/>
-      <c r="AB1" s="515" t="n"/>
-      <c r="AC1" s="515" t="n"/>
-      <c r="AD1" s="516" t="n"/>
-      <c r="AE1" s="517" t="n"/>
-      <c r="AF1" s="518" t="n"/>
-      <c r="AG1" s="518" t="n"/>
-      <c r="AH1" s="519" t="n"/>
-      <c r="AI1" s="520" t="n"/>
-      <c r="AJ1" s="521" t="n"/>
-      <c r="AK1" s="521" t="n"/>
-      <c r="AL1" s="521" t="n"/>
-      <c r="AM1" s="521" t="n"/>
-      <c r="AN1" s="522" t="n"/>
+      <c r="A1" s="827" t="n"/>
+      <c r="B1" s="828" t="n"/>
+      <c r="C1" s="828" t="n"/>
+      <c r="D1" s="828" t="n"/>
+      <c r="E1" s="828" t="n"/>
+      <c r="F1" s="828" t="n"/>
+      <c r="G1" s="828" t="n"/>
+      <c r="H1" s="829" t="n"/>
+      <c r="I1" s="830" t="inlineStr">
+        <is>
+          <t>FAI REPORT</t>
+        </is>
+      </c>
+      <c r="J1" s="828" t="n"/>
+      <c r="K1" s="828" t="n"/>
+      <c r="L1" s="828" t="n"/>
+      <c r="M1" s="828" t="n"/>
+      <c r="N1" s="828" t="n"/>
+      <c r="O1" s="828" t="n"/>
+      <c r="P1" s="828" t="n"/>
+      <c r="Q1" s="828" t="n"/>
+      <c r="R1" s="828" t="n"/>
+      <c r="S1" s="828" t="n"/>
+      <c r="T1" s="828" t="n"/>
+      <c r="U1" s="828" t="n"/>
+      <c r="V1" s="828" t="n"/>
+      <c r="W1" s="828" t="n"/>
+      <c r="X1" s="828" t="n"/>
+      <c r="Y1" s="828" t="n"/>
+      <c r="Z1" s="828" t="n"/>
+      <c r="AA1" s="828" t="n"/>
+      <c r="AB1" s="828" t="n"/>
+      <c r="AC1" s="828" t="n"/>
+      <c r="AD1" s="829" t="n"/>
+      <c r="AE1" s="518" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="828" t="n"/>
+      <c r="AG1" s="828" t="n"/>
+      <c r="AH1" s="831" t="n"/>
+      <c r="AI1" s="521" t="inlineStr">
+        <is>
+          <t>FRM-311</t>
+        </is>
+      </c>
+      <c r="AJ1" s="828" t="n"/>
+      <c r="AK1" s="828" t="n"/>
+      <c r="AL1" s="828" t="n"/>
+      <c r="AM1" s="828" t="n"/>
+      <c r="AN1" s="829" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="649" t="inlineStr">
-        <is>
-          <t>Reference Epicor / M365 / controlled documents only.</t>
-        </is>
-      </c>
-      <c r="H2" s="645" t="n"/>
-      <c r="I2" s="525" t="n"/>
-      <c r="J2" s="526" t="n"/>
-      <c r="K2" s="526" t="n"/>
-      <c r="L2" s="526" t="n"/>
-      <c r="M2" s="526" t="n"/>
-      <c r="N2" s="526" t="n"/>
-      <c r="O2" s="526" t="n"/>
-      <c r="P2" s="526" t="n"/>
-      <c r="Q2" s="526" t="n"/>
-      <c r="R2" s="526" t="n"/>
-      <c r="S2" s="526" t="n"/>
-      <c r="T2" s="526" t="n"/>
-      <c r="U2" s="526" t="n"/>
-      <c r="V2" s="526" t="n"/>
-      <c r="W2" s="526" t="n"/>
-      <c r="X2" s="526" t="n"/>
-      <c r="Y2" s="526" t="n"/>
-      <c r="Z2" s="526" t="n"/>
-      <c r="AA2" s="526" t="n"/>
-      <c r="AB2" s="526" t="n"/>
-      <c r="AC2" s="526" t="n"/>
-      <c r="AD2" s="527" t="n"/>
-      <c r="AE2" s="528" t="n"/>
-      <c r="AF2" s="529" t="n"/>
-      <c r="AG2" s="529" t="n"/>
-      <c r="AH2" s="530" t="n"/>
-      <c r="AI2" s="531" t="n"/>
-      <c r="AJ2" s="532" t="n"/>
-      <c r="AK2" s="532" t="n"/>
-      <c r="AL2" s="532" t="n"/>
-      <c r="AM2" s="532" t="n"/>
-      <c r="AN2" s="533" t="n"/>
+      <c r="A2" s="832" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="833" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="833" t="n"/>
+      <c r="AE2" s="834" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="835" t="n"/>
+      <c r="AI2" s="836" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="833" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="650" t="inlineStr">
-        <is>
-          <t>Ref Type</t>
-        </is>
-      </c>
-      <c r="B3" s="651" t="inlineStr">
-        <is>
-          <t>Document / Record</t>
-        </is>
-      </c>
-      <c r="C3" s="651" t="inlineStr">
-        <is>
-          <t>System of Record</t>
-        </is>
-      </c>
-      <c r="D3" s="651" t="inlineStr">
-        <is>
-          <t>Unique Ref</t>
-        </is>
-      </c>
-      <c r="E3" s="651" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F3" s="651" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G3" s="651" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="H3" s="645" t="n"/>
-      <c r="I3" s="525" t="n"/>
-      <c r="J3" s="526" t="n"/>
-      <c r="K3" s="526" t="n"/>
-      <c r="L3" s="526" t="n"/>
-      <c r="M3" s="526" t="n"/>
-      <c r="N3" s="526" t="n"/>
-      <c r="O3" s="526" t="n"/>
-      <c r="P3" s="526" t="n"/>
-      <c r="Q3" s="526" t="n"/>
-      <c r="R3" s="526" t="n"/>
-      <c r="S3" s="526" t="n"/>
-      <c r="T3" s="526" t="n"/>
-      <c r="U3" s="526" t="n"/>
-      <c r="V3" s="526" t="n"/>
-      <c r="W3" s="526" t="n"/>
-      <c r="X3" s="526" t="n"/>
-      <c r="Y3" s="526" t="n"/>
-      <c r="Z3" s="526" t="n"/>
-      <c r="AA3" s="526" t="n"/>
-      <c r="AB3" s="526" t="n"/>
-      <c r="AC3" s="526" t="n"/>
-      <c r="AD3" s="527" t="n"/>
-      <c r="AE3" s="528" t="n"/>
-      <c r="AF3" s="529" t="n"/>
-      <c r="AG3" s="529" t="n"/>
-      <c r="AH3" s="530" t="n"/>
-      <c r="AI3" s="531" t="n"/>
-      <c r="AJ3" s="532" t="n"/>
-      <c r="AK3" s="532" t="n"/>
-      <c r="AL3" s="532" t="n"/>
-      <c r="AM3" s="532" t="n"/>
-      <c r="AN3" s="533" t="n"/>
+      <c r="A3" s="832" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="833" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="833" t="n"/>
+      <c r="AE3" s="834" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="835" t="n"/>
+      <c r="AI3" s="836" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="833" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="652" t="n"/>
-      <c r="B4" s="653" t="n"/>
-      <c r="C4" s="653" t="n"/>
-      <c r="D4" s="653" t="n"/>
-      <c r="E4" s="653" t="n"/>
-      <c r="F4" s="653" t="n"/>
-      <c r="G4" s="653" t="n"/>
-      <c r="H4" s="645" t="n"/>
-      <c r="I4" s="534" t="n"/>
-      <c r="J4" s="535" t="n"/>
-      <c r="K4" s="535" t="n"/>
-      <c r="L4" s="535" t="n"/>
-      <c r="M4" s="535" t="n"/>
-      <c r="N4" s="535" t="n"/>
-      <c r="O4" s="535" t="n"/>
-      <c r="P4" s="535" t="n"/>
-      <c r="Q4" s="535" t="n"/>
-      <c r="R4" s="535" t="n"/>
-      <c r="S4" s="535" t="n"/>
-      <c r="T4" s="535" t="n"/>
-      <c r="U4" s="535" t="n"/>
-      <c r="V4" s="535" t="n"/>
-      <c r="W4" s="535" t="n"/>
-      <c r="X4" s="535" t="n"/>
-      <c r="Y4" s="535" t="n"/>
-      <c r="Z4" s="535" t="n"/>
-      <c r="AA4" s="535" t="n"/>
-      <c r="AB4" s="535" t="n"/>
-      <c r="AC4" s="535" t="n"/>
-      <c r="AD4" s="536" t="n"/>
-      <c r="AE4" s="528" t="n"/>
-      <c r="AF4" s="529" t="n"/>
-      <c r="AG4" s="529" t="n"/>
-      <c r="AH4" s="530" t="n"/>
-      <c r="AI4" s="531" t="n"/>
-      <c r="AJ4" s="532" t="n"/>
-      <c r="AK4" s="532" t="n"/>
-      <c r="AL4" s="532" t="n"/>
-      <c r="AM4" s="532" t="n"/>
-      <c r="AN4" s="533" t="n"/>
+      <c r="A4" s="832" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="833" t="n"/>
+      <c r="I4" s="837" t="inlineStr">
+        <is>
+          <t>Quality Management System  ·  Controlled Document</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="833" t="n"/>
+      <c r="AE4" s="834" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="835" t="n"/>
+      <c r="AI4" s="836" t="inlineStr">
+        <is>
+          <t>QA / Engineering</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="833" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="654" t="n"/>
-      <c r="B5" s="655" t="n"/>
-      <c r="C5" s="655" t="n"/>
-      <c r="D5" s="655" t="n"/>
-      <c r="E5" s="655" t="n"/>
-      <c r="F5" s="655" t="n"/>
-      <c r="G5" s="655" t="n"/>
-      <c r="H5" s="647" t="n"/>
-      <c r="I5" s="540" t="n"/>
-      <c r="J5" s="541" t="n"/>
-      <c r="K5" s="541" t="n"/>
-      <c r="L5" s="541" t="n"/>
-      <c r="M5" s="541" t="n"/>
-      <c r="N5" s="541" t="n"/>
-      <c r="O5" s="541" t="n"/>
-      <c r="P5" s="541" t="n"/>
-      <c r="Q5" s="541" t="n"/>
-      <c r="R5" s="541" t="n"/>
-      <c r="S5" s="541" t="n"/>
-      <c r="T5" s="541" t="n"/>
-      <c r="U5" s="541" t="n"/>
-      <c r="V5" s="541" t="n"/>
-      <c r="W5" s="541" t="n"/>
-      <c r="X5" s="541" t="n"/>
-      <c r="Y5" s="541" t="n"/>
-      <c r="Z5" s="541" t="n"/>
-      <c r="AA5" s="541" t="n"/>
-      <c r="AB5" s="541" t="n"/>
-      <c r="AC5" s="541" t="n"/>
-      <c r="AD5" s="542" t="n"/>
-      <c r="AE5" s="543" t="n"/>
-      <c r="AF5" s="544" t="n"/>
-      <c r="AG5" s="544" t="n"/>
-      <c r="AH5" s="545" t="n"/>
-      <c r="AI5" s="546" t="n"/>
-      <c r="AJ5" s="547" t="n"/>
-      <c r="AK5" s="547" t="n"/>
-      <c r="AL5" s="547" t="n"/>
-      <c r="AM5" s="547" t="n"/>
-      <c r="AN5" s="548" t="n"/>
+      <c r="A5" s="838" t="n"/>
+      <c r="B5" s="839" t="n"/>
+      <c r="C5" s="839" t="n"/>
+      <c r="D5" s="839" t="n"/>
+      <c r="E5" s="839" t="n"/>
+      <c r="F5" s="839" t="n"/>
+      <c r="G5" s="839" t="n"/>
+      <c r="H5" s="840" t="n"/>
+      <c r="I5" s="841" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="839" t="n"/>
+      <c r="K5" s="839" t="n"/>
+      <c r="L5" s="839" t="n"/>
+      <c r="M5" s="839" t="n"/>
+      <c r="N5" s="839" t="n"/>
+      <c r="O5" s="839" t="n"/>
+      <c r="P5" s="839" t="n"/>
+      <c r="Q5" s="839" t="n"/>
+      <c r="R5" s="839" t="n"/>
+      <c r="S5" s="839" t="n"/>
+      <c r="T5" s="839" t="n"/>
+      <c r="U5" s="839" t="n"/>
+      <c r="V5" s="839" t="n"/>
+      <c r="W5" s="839" t="n"/>
+      <c r="X5" s="839" t="n"/>
+      <c r="Y5" s="839" t="n"/>
+      <c r="Z5" s="839" t="n"/>
+      <c r="AA5" s="839" t="n"/>
+      <c r="AB5" s="839" t="n"/>
+      <c r="AC5" s="839" t="n"/>
+      <c r="AD5" s="840" t="n"/>
+      <c r="AE5" s="842" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="839" t="n"/>
+      <c r="AG5" s="839" t="n"/>
+      <c r="AH5" s="843" t="n"/>
+      <c r="AI5" s="844" t="inlineStr">
+        <is>
+          <t>QA Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="839" t="n"/>
+      <c r="AK5" s="839" t="n"/>
+      <c r="AL5" s="839" t="n"/>
+      <c r="AM5" s="839" t="n"/>
+      <c r="AN5" s="840" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="656" t="n"/>
-      <c r="B6" s="657" t="n"/>
-      <c r="C6" s="657" t="n"/>
-      <c r="D6" s="657" t="n"/>
-      <c r="E6" s="657" t="n"/>
-      <c r="F6" s="657" t="n"/>
-      <c r="G6" s="657" t="n"/>
-      <c r="H6" s="554" t="n"/>
-      <c r="I6" s="554" t="n"/>
-      <c r="J6" s="554" t="n"/>
-      <c r="K6" s="554" t="n"/>
-      <c r="L6" s="554" t="n"/>
-      <c r="M6" s="554" t="n"/>
-      <c r="N6" s="554" t="n"/>
-      <c r="O6" s="554" t="n"/>
-      <c r="P6" s="554" t="n"/>
-      <c r="Q6" s="554" t="n"/>
-      <c r="R6" s="554" t="n"/>
-      <c r="S6" s="554" t="n"/>
-      <c r="T6" s="554" t="n"/>
-      <c r="U6" s="554" t="n"/>
-      <c r="V6" s="554" t="n"/>
-      <c r="W6" s="554" t="n"/>
-      <c r="X6" s="554" t="n"/>
-      <c r="Y6" s="554" t="n"/>
-      <c r="Z6" s="554" t="n"/>
-      <c r="AA6" s="554" t="n"/>
-      <c r="AB6" s="554" t="n"/>
-      <c r="AC6" s="554" t="n"/>
-      <c r="AD6" s="554" t="n"/>
-      <c r="AE6" s="554" t="n"/>
-      <c r="AF6" s="554" t="n"/>
-      <c r="AG6" s="554" t="n"/>
-      <c r="AH6" s="554" t="n"/>
-      <c r="AI6" s="554" t="n"/>
-      <c r="AJ6" s="554" t="n"/>
-      <c r="AK6" s="554" t="n"/>
-      <c r="AL6" s="554" t="n"/>
-      <c r="AM6" s="554" t="n"/>
-      <c r="AN6" s="557" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="845" t="n"/>
+      <c r="B6" s="845" t="n"/>
+      <c r="C6" s="845" t="n"/>
+      <c r="D6" s="845" t="n"/>
+      <c r="E6" s="845" t="n"/>
+      <c r="F6" s="845" t="n"/>
+      <c r="G6" s="845" t="n"/>
+      <c r="H6" s="845" t="n"/>
+      <c r="I6" s="845" t="n"/>
+      <c r="J6" s="845" t="n"/>
+      <c r="K6" s="845" t="n"/>
+      <c r="L6" s="845" t="n"/>
+      <c r="M6" s="845" t="n"/>
+      <c r="N6" s="845" t="n"/>
+      <c r="O6" s="845" t="n"/>
+      <c r="P6" s="845" t="n"/>
+      <c r="Q6" s="845" t="n"/>
+      <c r="R6" s="845" t="n"/>
+      <c r="S6" s="845" t="n"/>
+      <c r="T6" s="845" t="n"/>
+      <c r="U6" s="845" t="n"/>
+      <c r="V6" s="845" t="n"/>
+      <c r="W6" s="845" t="n"/>
+      <c r="X6" s="845" t="n"/>
+      <c r="Y6" s="845" t="n"/>
+      <c r="Z6" s="845" t="n"/>
+      <c r="AA6" s="845" t="n"/>
+      <c r="AB6" s="845" t="n"/>
+      <c r="AC6" s="845" t="n"/>
+      <c r="AD6" s="845" t="n"/>
+      <c r="AE6" s="845" t="n"/>
+      <c r="AF6" s="845" t="n"/>
+      <c r="AG6" s="845" t="n"/>
+      <c r="AH6" s="845" t="n"/>
+      <c r="AI6" s="845" t="n"/>
+      <c r="AJ6" s="845" t="n"/>
+      <c r="AK6" s="845" t="n"/>
+      <c r="AL6" s="845" t="n"/>
+      <c r="AM6" s="845" t="n"/>
+      <c r="AN6" s="845" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="658" t="n"/>
-      <c r="B7" s="659" t="n"/>
-      <c r="C7" s="659" t="n"/>
-      <c r="D7" s="659" t="n"/>
-      <c r="E7" s="659" t="n"/>
-      <c r="F7" s="659" t="n"/>
-      <c r="G7" s="659" t="n"/>
-      <c r="H7" s="410" t="n"/>
-      <c r="I7" s="410" t="n"/>
-      <c r="J7" s="410" t="n"/>
-      <c r="K7" s="410" t="n"/>
-      <c r="L7" s="410" t="n"/>
-      <c r="M7" s="410" t="n"/>
-      <c r="N7" s="410" t="n"/>
-      <c r="O7" s="410" t="n"/>
-      <c r="P7" s="410" t="n"/>
-      <c r="Q7" s="410" t="n"/>
-      <c r="R7" s="410" t="n"/>
-      <c r="S7" s="410" t="n"/>
-      <c r="T7" s="410" t="n"/>
-      <c r="U7" s="410" t="n"/>
-      <c r="V7" s="410" t="n"/>
-      <c r="W7" s="410" t="n"/>
-      <c r="X7" s="410" t="n"/>
-      <c r="Y7" s="410" t="n"/>
-      <c r="Z7" s="410" t="n"/>
-      <c r="AA7" s="410" t="n"/>
-      <c r="AB7" s="410" t="n"/>
-      <c r="AC7" s="410" t="n"/>
-      <c r="AD7" s="410" t="n"/>
-      <c r="AE7" s="410" t="n"/>
-      <c r="AF7" s="410" t="n"/>
-      <c r="AG7" s="410" t="n"/>
-      <c r="AH7" s="410" t="n"/>
-      <c r="AI7" s="410" t="n"/>
-      <c r="AJ7" s="410" t="n"/>
-      <c r="AK7" s="410" t="n"/>
-      <c r="AL7" s="410" t="n"/>
-      <c r="AM7" s="410" t="n"/>
-      <c r="AN7" s="561" t="n"/>
+      <c r="A7" s="648" t="inlineStr">
+        <is>
+          <t>REF_LINKS</t>
+        </is>
+      </c>
+      <c r="B7" s="775" t="n"/>
+      <c r="C7" s="775" t="n"/>
+      <c r="D7" s="775" t="n"/>
+      <c r="E7" s="775" t="n"/>
+      <c r="F7" s="775" t="n"/>
+      <c r="G7" s="775" t="n"/>
+      <c r="H7" s="846" t="n"/>
+      <c r="I7" s="846" t="n"/>
+      <c r="J7" s="846" t="n"/>
+      <c r="K7" s="846" t="n"/>
+      <c r="L7" s="846" t="n"/>
+      <c r="M7" s="846" t="n"/>
+      <c r="N7" s="846" t="n"/>
+      <c r="O7" s="846" t="n"/>
+      <c r="P7" s="846" t="n"/>
+      <c r="Q7" s="846" t="n"/>
+      <c r="R7" s="846" t="n"/>
+      <c r="S7" s="846" t="n"/>
+      <c r="T7" s="846" t="n"/>
+      <c r="U7" s="846" t="n"/>
+      <c r="V7" s="846" t="n"/>
+      <c r="W7" s="846" t="n"/>
+      <c r="X7" s="846" t="n"/>
+      <c r="Y7" s="846" t="n"/>
+      <c r="Z7" s="846" t="n"/>
+      <c r="AA7" s="846" t="n"/>
+      <c r="AB7" s="846" t="n"/>
+      <c r="AC7" s="846" t="n"/>
+      <c r="AD7" s="846" t="n"/>
+      <c r="AE7" s="846" t="n"/>
+      <c r="AF7" s="846" t="n"/>
+      <c r="AG7" s="846" t="n"/>
+      <c r="AH7" s="846" t="n"/>
+      <c r="AI7" s="846" t="n"/>
+      <c r="AJ7" s="846" t="n"/>
+      <c r="AK7" s="846" t="n"/>
+      <c r="AL7" s="846" t="n"/>
+      <c r="AM7" s="846" t="n"/>
+      <c r="AN7" s="846" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="658" t="n"/>
-      <c r="B8" s="659" t="n"/>
-      <c r="C8" s="659" t="n"/>
-      <c r="D8" s="659" t="n"/>
-      <c r="E8" s="659" t="n"/>
-      <c r="F8" s="659" t="n"/>
-      <c r="G8" s="659" t="n"/>
-      <c r="H8" s="425" t="n"/>
-      <c r="I8" s="425" t="n"/>
-      <c r="J8" s="425" t="n"/>
-      <c r="K8" s="425" t="n"/>
-      <c r="L8" s="425" t="n"/>
-      <c r="M8" s="425" t="n"/>
-      <c r="N8" s="425" t="n"/>
-      <c r="O8" s="425" t="n"/>
-      <c r="P8" s="425" t="n"/>
-      <c r="Q8" s="425" t="n"/>
-      <c r="R8" s="425" t="n"/>
-      <c r="S8" s="425" t="n"/>
-      <c r="T8" s="425" t="n"/>
-      <c r="U8" s="425" t="n"/>
-      <c r="V8" s="425" t="n"/>
-      <c r="W8" s="425" t="n"/>
-      <c r="X8" s="425" t="n"/>
-      <c r="Y8" s="425" t="n"/>
-      <c r="Z8" s="425" t="n"/>
-      <c r="AA8" s="425" t="n"/>
-      <c r="AB8" s="425" t="n"/>
-      <c r="AC8" s="425" t="n"/>
-      <c r="AD8" s="425" t="n"/>
-      <c r="AE8" s="425" t="n"/>
-      <c r="AF8" s="425" t="n"/>
-      <c r="AG8" s="425" t="n"/>
-      <c r="AH8" s="425" t="n"/>
-      <c r="AI8" s="425" t="n"/>
-      <c r="AJ8" s="425" t="n"/>
-      <c r="AK8" s="425" t="n"/>
-      <c r="AL8" s="425" t="n"/>
-      <c r="AM8" s="425" t="n"/>
-      <c r="AN8" s="623" t="n"/>
+      <c r="A8" s="649" t="inlineStr">
+        <is>
+          <t>Reference Epicor / M365 / controlled documents only.</t>
+        </is>
+      </c>
+      <c r="H8" s="846" t="n"/>
+      <c r="I8" s="846" t="n"/>
+      <c r="J8" s="846" t="n"/>
+      <c r="K8" s="846" t="n"/>
+      <c r="L8" s="846" t="n"/>
+      <c r="M8" s="846" t="n"/>
+      <c r="N8" s="846" t="n"/>
+      <c r="O8" s="846" t="n"/>
+      <c r="P8" s="846" t="n"/>
+      <c r="Q8" s="846" t="n"/>
+      <c r="R8" s="846" t="n"/>
+      <c r="S8" s="846" t="n"/>
+      <c r="T8" s="846" t="n"/>
+      <c r="U8" s="846" t="n"/>
+      <c r="V8" s="846" t="n"/>
+      <c r="W8" s="846" t="n"/>
+      <c r="X8" s="846" t="n"/>
+      <c r="Y8" s="846" t="n"/>
+      <c r="Z8" s="846" t="n"/>
+      <c r="AA8" s="846" t="n"/>
+      <c r="AB8" s="846" t="n"/>
+      <c r="AC8" s="846" t="n"/>
+      <c r="AD8" s="846" t="n"/>
+      <c r="AE8" s="846" t="n"/>
+      <c r="AF8" s="846" t="n"/>
+      <c r="AG8" s="846" t="n"/>
+      <c r="AH8" s="846" t="n"/>
+      <c r="AI8" s="846" t="n"/>
+      <c r="AJ8" s="846" t="n"/>
+      <c r="AK8" s="846" t="n"/>
+      <c r="AL8" s="846" t="n"/>
+      <c r="AM8" s="846" t="n"/>
+      <c r="AN8" s="846" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="658" t="n"/>
-      <c r="B9" s="659" t="n"/>
-      <c r="C9" s="659" t="n"/>
-      <c r="D9" s="659" t="n"/>
-      <c r="E9" s="659" t="n"/>
-      <c r="F9" s="659" t="n"/>
-      <c r="G9" s="659" t="n"/>
-      <c r="H9" s="425" t="n"/>
-      <c r="I9" s="425" t="n"/>
-      <c r="J9" s="425" t="n"/>
-      <c r="K9" s="425" t="n"/>
-      <c r="L9" s="425" t="n"/>
-      <c r="M9" s="425" t="n"/>
-      <c r="N9" s="425" t="n"/>
-      <c r="O9" s="425" t="n"/>
-      <c r="P9" s="425" t="n"/>
-      <c r="Q9" s="425" t="n"/>
-      <c r="R9" s="425" t="n"/>
-      <c r="S9" s="425" t="n"/>
-      <c r="T9" s="425" t="n"/>
-      <c r="U9" s="425" t="n"/>
-      <c r="V9" s="425" t="n"/>
-      <c r="W9" s="425" t="n"/>
-      <c r="X9" s="425" t="n"/>
-      <c r="Y9" s="425" t="n"/>
-      <c r="Z9" s="425" t="n"/>
-      <c r="AA9" s="425" t="n"/>
-      <c r="AB9" s="425" t="n"/>
-      <c r="AC9" s="425" t="n"/>
-      <c r="AD9" s="425" t="n"/>
-      <c r="AE9" s="425" t="n"/>
-      <c r="AF9" s="425" t="n"/>
-      <c r="AG9" s="425" t="n"/>
-      <c r="AH9" s="425" t="n"/>
-      <c r="AI9" s="425" t="n"/>
-      <c r="AJ9" s="425" t="n"/>
-      <c r="AK9" s="425" t="n"/>
-      <c r="AL9" s="425" t="n"/>
-      <c r="AM9" s="425" t="n"/>
-      <c r="AN9" s="623" t="n"/>
+      <c r="A9" s="650" t="inlineStr">
+        <is>
+          <t>Ref Type</t>
+        </is>
+      </c>
+      <c r="B9" s="651" t="inlineStr">
+        <is>
+          <t>Document / Record</t>
+        </is>
+      </c>
+      <c r="C9" s="651" t="inlineStr">
+        <is>
+          <t>System of Record</t>
+        </is>
+      </c>
+      <c r="D9" s="651" t="inlineStr">
+        <is>
+          <t>Unique Ref</t>
+        </is>
+      </c>
+      <c r="E9" s="651" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F9" s="651" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G9" s="651" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="H9" s="846" t="n"/>
+      <c r="I9" s="846" t="n"/>
+      <c r="J9" s="846" t="n"/>
+      <c r="K9" s="846" t="n"/>
+      <c r="L9" s="846" t="n"/>
+      <c r="M9" s="846" t="n"/>
+      <c r="N9" s="846" t="n"/>
+      <c r="O9" s="846" t="n"/>
+      <c r="P9" s="846" t="n"/>
+      <c r="Q9" s="846" t="n"/>
+      <c r="R9" s="846" t="n"/>
+      <c r="S9" s="846" t="n"/>
+      <c r="T9" s="846" t="n"/>
+      <c r="U9" s="846" t="n"/>
+      <c r="V9" s="846" t="n"/>
+      <c r="W9" s="846" t="n"/>
+      <c r="X9" s="846" t="n"/>
+      <c r="Y9" s="846" t="n"/>
+      <c r="Z9" s="846" t="n"/>
+      <c r="AA9" s="846" t="n"/>
+      <c r="AB9" s="846" t="n"/>
+      <c r="AC9" s="846" t="n"/>
+      <c r="AD9" s="846" t="n"/>
+      <c r="AE9" s="846" t="n"/>
+      <c r="AF9" s="846" t="n"/>
+      <c r="AG9" s="846" t="n"/>
+      <c r="AH9" s="846" t="n"/>
+      <c r="AI9" s="846" t="n"/>
+      <c r="AJ9" s="846" t="n"/>
+      <c r="AK9" s="846" t="n"/>
+      <c r="AL9" s="846" t="n"/>
+      <c r="AM9" s="846" t="n"/>
+      <c r="AN9" s="846" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="658" t="n"/>
-      <c r="B10" s="659" t="n"/>
-      <c r="C10" s="659" t="n"/>
-      <c r="D10" s="659" t="n"/>
-      <c r="E10" s="659" t="n"/>
-      <c r="F10" s="659" t="n"/>
-      <c r="G10" s="659" t="n"/>
-      <c r="H10" s="425" t="n"/>
-      <c r="I10" s="425" t="n"/>
-      <c r="J10" s="425" t="n"/>
-      <c r="K10" s="425" t="n"/>
-      <c r="L10" s="425" t="n"/>
-      <c r="M10" s="425" t="n"/>
-      <c r="N10" s="425" t="n"/>
-      <c r="O10" s="425" t="n"/>
-      <c r="P10" s="425" t="n"/>
-      <c r="Q10" s="425" t="n"/>
-      <c r="R10" s="425" t="n"/>
-      <c r="S10" s="425" t="n"/>
-      <c r="T10" s="425" t="n"/>
-      <c r="U10" s="425" t="n"/>
-      <c r="V10" s="425" t="n"/>
-      <c r="W10" s="425" t="n"/>
-      <c r="X10" s="425" t="n"/>
-      <c r="Y10" s="425" t="n"/>
-      <c r="Z10" s="425" t="n"/>
-      <c r="AA10" s="425" t="n"/>
-      <c r="AB10" s="425" t="n"/>
-      <c r="AC10" s="425" t="n"/>
-      <c r="AD10" s="425" t="n"/>
-      <c r="AE10" s="425" t="n"/>
-      <c r="AF10" s="425" t="n"/>
-      <c r="AG10" s="425" t="n"/>
-      <c r="AH10" s="425" t="n"/>
-      <c r="AI10" s="425" t="n"/>
-      <c r="AJ10" s="425" t="n"/>
-      <c r="AK10" s="425" t="n"/>
-      <c r="AL10" s="425" t="n"/>
-      <c r="AM10" s="425" t="n"/>
-      <c r="AN10" s="623" t="n"/>
+      <c r="A10" s="846" t="n"/>
+      <c r="B10" s="846" t="n"/>
+      <c r="C10" s="846" t="n"/>
+      <c r="D10" s="846" t="n"/>
+      <c r="E10" s="846" t="n"/>
+      <c r="F10" s="846" t="n"/>
+      <c r="G10" s="846" t="n"/>
+      <c r="H10" s="846" t="n"/>
+      <c r="I10" s="846" t="n"/>
+      <c r="J10" s="846" t="n"/>
+      <c r="K10" s="846" t="n"/>
+      <c r="L10" s="846" t="n"/>
+      <c r="M10" s="846" t="n"/>
+      <c r="N10" s="846" t="n"/>
+      <c r="O10" s="846" t="n"/>
+      <c r="P10" s="846" t="n"/>
+      <c r="Q10" s="846" t="n"/>
+      <c r="R10" s="846" t="n"/>
+      <c r="S10" s="846" t="n"/>
+      <c r="T10" s="846" t="n"/>
+      <c r="U10" s="846" t="n"/>
+      <c r="V10" s="846" t="n"/>
+      <c r="W10" s="846" t="n"/>
+      <c r="X10" s="846" t="n"/>
+      <c r="Y10" s="846" t="n"/>
+      <c r="Z10" s="846" t="n"/>
+      <c r="AA10" s="846" t="n"/>
+      <c r="AB10" s="846" t="n"/>
+      <c r="AC10" s="846" t="n"/>
+      <c r="AD10" s="846" t="n"/>
+      <c r="AE10" s="846" t="n"/>
+      <c r="AF10" s="846" t="n"/>
+      <c r="AG10" s="846" t="n"/>
+      <c r="AH10" s="846" t="n"/>
+      <c r="AI10" s="846" t="n"/>
+      <c r="AJ10" s="846" t="n"/>
+      <c r="AK10" s="846" t="n"/>
+      <c r="AL10" s="846" t="n"/>
+      <c r="AM10" s="846" t="n"/>
+      <c r="AN10" s="846" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="660" t="n"/>
-      <c r="B11" s="661" t="n"/>
-      <c r="C11" s="661" t="n"/>
-      <c r="D11" s="661" t="n"/>
-      <c r="E11" s="661" t="n"/>
-      <c r="F11" s="661" t="n"/>
-      <c r="G11" s="661" t="n"/>
-      <c r="H11" s="606" t="n"/>
-      <c r="I11" s="606" t="n"/>
-      <c r="J11" s="606" t="n"/>
-      <c r="K11" s="606" t="n"/>
-      <c r="L11" s="606" t="n"/>
-      <c r="M11" s="606" t="n"/>
-      <c r="N11" s="606" t="n"/>
-      <c r="O11" s="606" t="n"/>
-      <c r="P11" s="606" t="n"/>
-      <c r="Q11" s="606" t="n"/>
-      <c r="R11" s="606" t="n"/>
-      <c r="S11" s="606" t="n"/>
-      <c r="T11" s="606" t="n"/>
-      <c r="U11" s="606" t="n"/>
-      <c r="V11" s="606" t="n"/>
-      <c r="W11" s="606" t="n"/>
-      <c r="X11" s="606" t="n"/>
-      <c r="Y11" s="606" t="n"/>
-      <c r="Z11" s="606" t="n"/>
-      <c r="AA11" s="606" t="n"/>
-      <c r="AB11" s="606" t="n"/>
-      <c r="AC11" s="606" t="n"/>
-      <c r="AD11" s="606" t="n"/>
-      <c r="AE11" s="606" t="n"/>
-      <c r="AF11" s="606" t="n"/>
-      <c r="AG11" s="606" t="n"/>
-      <c r="AH11" s="606" t="n"/>
-      <c r="AI11" s="606" t="n"/>
-      <c r="AJ11" s="606" t="n"/>
-      <c r="AK11" s="606" t="n"/>
-      <c r="AL11" s="606" t="n"/>
-      <c r="AM11" s="606" t="n"/>
-      <c r="AN11" s="607" t="n"/>
+      <c r="A11" s="846" t="n"/>
+      <c r="B11" s="846" t="n"/>
+      <c r="C11" s="846" t="n"/>
+      <c r="D11" s="846" t="n"/>
+      <c r="E11" s="846" t="n"/>
+      <c r="F11" s="846" t="n"/>
+      <c r="G11" s="846" t="n"/>
+      <c r="H11" s="846" t="n"/>
+      <c r="I11" s="846" t="n"/>
+      <c r="J11" s="846" t="n"/>
+      <c r="K11" s="846" t="n"/>
+      <c r="L11" s="846" t="n"/>
+      <c r="M11" s="846" t="n"/>
+      <c r="N11" s="846" t="n"/>
+      <c r="O11" s="846" t="n"/>
+      <c r="P11" s="846" t="n"/>
+      <c r="Q11" s="846" t="n"/>
+      <c r="R11" s="846" t="n"/>
+      <c r="S11" s="846" t="n"/>
+      <c r="T11" s="846" t="n"/>
+      <c r="U11" s="846" t="n"/>
+      <c r="V11" s="846" t="n"/>
+      <c r="W11" s="846" t="n"/>
+      <c r="X11" s="846" t="n"/>
+      <c r="Y11" s="846" t="n"/>
+      <c r="Z11" s="846" t="n"/>
+      <c r="AA11" s="846" t="n"/>
+      <c r="AB11" s="846" t="n"/>
+      <c r="AC11" s="846" t="n"/>
+      <c r="AD11" s="846" t="n"/>
+      <c r="AE11" s="846" t="n"/>
+      <c r="AF11" s="846" t="n"/>
+      <c r="AG11" s="846" t="n"/>
+      <c r="AH11" s="846" t="n"/>
+      <c r="AI11" s="846" t="n"/>
+      <c r="AJ11" s="846" t="n"/>
+      <c r="AK11" s="846" t="n"/>
+      <c r="AL11" s="846" t="n"/>
+      <c r="AM11" s="846" t="n"/>
+      <c r="AN11" s="846" t="n"/>
     </row>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
-    <row r="18" hidden="1"/>
-    <row r="19" hidden="1"/>
-    <row r="20" hidden="1"/>
+    <row r="12" hidden="1">
+      <c r="A12" s="846" t="n"/>
+      <c r="B12" s="846" t="n"/>
+      <c r="C12" s="846" t="n"/>
+      <c r="D12" s="846" t="n"/>
+      <c r="E12" s="846" t="n"/>
+      <c r="F12" s="846" t="n"/>
+      <c r="G12" s="846" t="n"/>
+      <c r="H12" s="846" t="n"/>
+      <c r="I12" s="846" t="n"/>
+      <c r="J12" s="846" t="n"/>
+      <c r="K12" s="846" t="n"/>
+      <c r="L12" s="846" t="n"/>
+      <c r="M12" s="846" t="n"/>
+      <c r="N12" s="846" t="n"/>
+      <c r="O12" s="846" t="n"/>
+      <c r="P12" s="846" t="n"/>
+      <c r="Q12" s="846" t="n"/>
+      <c r="R12" s="846" t="n"/>
+      <c r="S12" s="846" t="n"/>
+      <c r="T12" s="846" t="n"/>
+      <c r="U12" s="846" t="n"/>
+      <c r="V12" s="846" t="n"/>
+      <c r="W12" s="846" t="n"/>
+      <c r="X12" s="846" t="n"/>
+      <c r="Y12" s="846" t="n"/>
+      <c r="Z12" s="846" t="n"/>
+      <c r="AA12" s="846" t="n"/>
+      <c r="AB12" s="846" t="n"/>
+      <c r="AC12" s="846" t="n"/>
+      <c r="AD12" s="846" t="n"/>
+      <c r="AE12" s="846" t="n"/>
+      <c r="AF12" s="846" t="n"/>
+      <c r="AG12" s="846" t="n"/>
+      <c r="AH12" s="846" t="n"/>
+      <c r="AI12" s="846" t="n"/>
+      <c r="AJ12" s="846" t="n"/>
+      <c r="AK12" s="846" t="n"/>
+      <c r="AL12" s="846" t="n"/>
+      <c r="AM12" s="846" t="n"/>
+      <c r="AN12" s="846" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="846" t="n"/>
+      <c r="B13" s="846" t="n"/>
+      <c r="C13" s="846" t="n"/>
+      <c r="D13" s="846" t="n"/>
+      <c r="E13" s="846" t="n"/>
+      <c r="F13" s="846" t="n"/>
+      <c r="G13" s="846" t="n"/>
+      <c r="H13" s="846" t="n"/>
+      <c r="I13" s="846" t="n"/>
+      <c r="J13" s="846" t="n"/>
+      <c r="K13" s="846" t="n"/>
+      <c r="L13" s="846" t="n"/>
+      <c r="M13" s="846" t="n"/>
+      <c r="N13" s="846" t="n"/>
+      <c r="O13" s="846" t="n"/>
+      <c r="P13" s="846" t="n"/>
+      <c r="Q13" s="846" t="n"/>
+      <c r="R13" s="846" t="n"/>
+      <c r="S13" s="846" t="n"/>
+      <c r="T13" s="846" t="n"/>
+      <c r="U13" s="846" t="n"/>
+      <c r="V13" s="846" t="n"/>
+      <c r="W13" s="846" t="n"/>
+      <c r="X13" s="846" t="n"/>
+      <c r="Y13" s="846" t="n"/>
+      <c r="Z13" s="846" t="n"/>
+      <c r="AA13" s="846" t="n"/>
+      <c r="AB13" s="846" t="n"/>
+      <c r="AC13" s="846" t="n"/>
+      <c r="AD13" s="846" t="n"/>
+      <c r="AE13" s="846" t="n"/>
+      <c r="AF13" s="846" t="n"/>
+      <c r="AG13" s="846" t="n"/>
+      <c r="AH13" s="846" t="n"/>
+      <c r="AI13" s="846" t="n"/>
+      <c r="AJ13" s="846" t="n"/>
+      <c r="AK13" s="846" t="n"/>
+      <c r="AL13" s="846" t="n"/>
+      <c r="AM13" s="846" t="n"/>
+      <c r="AN13" s="846" t="n"/>
+    </row>
+    <row r="14" hidden="1">
+      <c r="A14" s="846" t="n"/>
+      <c r="B14" s="846" t="n"/>
+      <c r="C14" s="846" t="n"/>
+      <c r="D14" s="846" t="n"/>
+      <c r="E14" s="846" t="n"/>
+      <c r="F14" s="846" t="n"/>
+      <c r="G14" s="846" t="n"/>
+      <c r="H14" s="846" t="n"/>
+      <c r="I14" s="846" t="n"/>
+      <c r="J14" s="846" t="n"/>
+      <c r="K14" s="846" t="n"/>
+      <c r="L14" s="846" t="n"/>
+      <c r="M14" s="846" t="n"/>
+      <c r="N14" s="846" t="n"/>
+      <c r="O14" s="846" t="n"/>
+      <c r="P14" s="846" t="n"/>
+      <c r="Q14" s="846" t="n"/>
+      <c r="R14" s="846" t="n"/>
+      <c r="S14" s="846" t="n"/>
+      <c r="T14" s="846" t="n"/>
+      <c r="U14" s="846" t="n"/>
+      <c r="V14" s="846" t="n"/>
+      <c r="W14" s="846" t="n"/>
+      <c r="X14" s="846" t="n"/>
+      <c r="Y14" s="846" t="n"/>
+      <c r="Z14" s="846" t="n"/>
+      <c r="AA14" s="846" t="n"/>
+      <c r="AB14" s="846" t="n"/>
+      <c r="AC14" s="846" t="n"/>
+      <c r="AD14" s="846" t="n"/>
+      <c r="AE14" s="846" t="n"/>
+      <c r="AF14" s="846" t="n"/>
+      <c r="AG14" s="846" t="n"/>
+      <c r="AH14" s="846" t="n"/>
+      <c r="AI14" s="846" t="n"/>
+      <c r="AJ14" s="846" t="n"/>
+      <c r="AK14" s="846" t="n"/>
+      <c r="AL14" s="846" t="n"/>
+      <c r="AM14" s="846" t="n"/>
+      <c r="AN14" s="846" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="846" t="n"/>
+      <c r="B15" s="846" t="n"/>
+      <c r="C15" s="846" t="n"/>
+      <c r="D15" s="846" t="n"/>
+      <c r="E15" s="846" t="n"/>
+      <c r="F15" s="846" t="n"/>
+      <c r="G15" s="846" t="n"/>
+      <c r="H15" s="846" t="n"/>
+      <c r="I15" s="846" t="n"/>
+      <c r="J15" s="846" t="n"/>
+      <c r="K15" s="846" t="n"/>
+      <c r="L15" s="846" t="n"/>
+      <c r="M15" s="846" t="n"/>
+      <c r="N15" s="846" t="n"/>
+      <c r="O15" s="846" t="n"/>
+      <c r="P15" s="846" t="n"/>
+      <c r="Q15" s="846" t="n"/>
+      <c r="R15" s="846" t="n"/>
+      <c r="S15" s="846" t="n"/>
+      <c r="T15" s="846" t="n"/>
+      <c r="U15" s="846" t="n"/>
+      <c r="V15" s="846" t="n"/>
+      <c r="W15" s="846" t="n"/>
+      <c r="X15" s="846" t="n"/>
+      <c r="Y15" s="846" t="n"/>
+      <c r="Z15" s="846" t="n"/>
+      <c r="AA15" s="846" t="n"/>
+      <c r="AB15" s="846" t="n"/>
+      <c r="AC15" s="846" t="n"/>
+      <c r="AD15" s="846" t="n"/>
+      <c r="AE15" s="846" t="n"/>
+      <c r="AF15" s="846" t="n"/>
+      <c r="AG15" s="846" t="n"/>
+      <c r="AH15" s="846" t="n"/>
+      <c r="AI15" s="846" t="n"/>
+      <c r="AJ15" s="846" t="n"/>
+      <c r="AK15" s="846" t="n"/>
+      <c r="AL15" s="846" t="n"/>
+      <c r="AM15" s="846" t="n"/>
+      <c r="AN15" s="846" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="846" t="n"/>
+      <c r="B16" s="846" t="n"/>
+      <c r="C16" s="846" t="n"/>
+      <c r="D16" s="846" t="n"/>
+      <c r="E16" s="846" t="n"/>
+      <c r="F16" s="846" t="n"/>
+      <c r="G16" s="846" t="n"/>
+      <c r="H16" s="846" t="n"/>
+      <c r="I16" s="846" t="n"/>
+      <c r="J16" s="846" t="n"/>
+      <c r="K16" s="846" t="n"/>
+      <c r="L16" s="846" t="n"/>
+      <c r="M16" s="846" t="n"/>
+      <c r="N16" s="846" t="n"/>
+      <c r="O16" s="846" t="n"/>
+      <c r="P16" s="846" t="n"/>
+      <c r="Q16" s="846" t="n"/>
+      <c r="R16" s="846" t="n"/>
+      <c r="S16" s="846" t="n"/>
+      <c r="T16" s="846" t="n"/>
+      <c r="U16" s="846" t="n"/>
+      <c r="V16" s="846" t="n"/>
+      <c r="W16" s="846" t="n"/>
+      <c r="X16" s="846" t="n"/>
+      <c r="Y16" s="846" t="n"/>
+      <c r="Z16" s="846" t="n"/>
+      <c r="AA16" s="846" t="n"/>
+      <c r="AB16" s="846" t="n"/>
+      <c r="AC16" s="846" t="n"/>
+      <c r="AD16" s="846" t="n"/>
+      <c r="AE16" s="846" t="n"/>
+      <c r="AF16" s="846" t="n"/>
+      <c r="AG16" s="846" t="n"/>
+      <c r="AH16" s="846" t="n"/>
+      <c r="AI16" s="846" t="n"/>
+      <c r="AJ16" s="846" t="n"/>
+      <c r="AK16" s="846" t="n"/>
+      <c r="AL16" s="846" t="n"/>
+      <c r="AM16" s="846" t="n"/>
+      <c r="AN16" s="846" t="n"/>
+    </row>
+    <row r="17" hidden="1">
+      <c r="A17" s="846" t="n"/>
+      <c r="B17" s="846" t="n"/>
+      <c r="C17" s="846" t="n"/>
+      <c r="D17" s="846" t="n"/>
+      <c r="E17" s="846" t="n"/>
+      <c r="F17" s="846" t="n"/>
+      <c r="G17" s="846" t="n"/>
+      <c r="H17" s="846" t="n"/>
+      <c r="I17" s="846" t="n"/>
+      <c r="J17" s="846" t="n"/>
+      <c r="K17" s="846" t="n"/>
+      <c r="L17" s="846" t="n"/>
+      <c r="M17" s="846" t="n"/>
+      <c r="N17" s="846" t="n"/>
+      <c r="O17" s="846" t="n"/>
+      <c r="P17" s="846" t="n"/>
+      <c r="Q17" s="846" t="n"/>
+      <c r="R17" s="846" t="n"/>
+      <c r="S17" s="846" t="n"/>
+      <c r="T17" s="846" t="n"/>
+      <c r="U17" s="846" t="n"/>
+      <c r="V17" s="846" t="n"/>
+      <c r="W17" s="846" t="n"/>
+      <c r="X17" s="846" t="n"/>
+      <c r="Y17" s="846" t="n"/>
+      <c r="Z17" s="846" t="n"/>
+      <c r="AA17" s="846" t="n"/>
+      <c r="AB17" s="846" t="n"/>
+      <c r="AC17" s="846" t="n"/>
+      <c r="AD17" s="846" t="n"/>
+      <c r="AE17" s="846" t="n"/>
+      <c r="AF17" s="846" t="n"/>
+      <c r="AG17" s="846" t="n"/>
+      <c r="AH17" s="846" t="n"/>
+      <c r="AI17" s="846" t="n"/>
+      <c r="AJ17" s="846" t="n"/>
+      <c r="AK17" s="846" t="n"/>
+      <c r="AL17" s="846" t="n"/>
+      <c r="AM17" s="846" t="n"/>
+      <c r="AN17" s="846" t="n"/>
+    </row>
+    <row r="18" hidden="1">
+      <c r="A18" s="846" t="n"/>
+      <c r="B18" s="846" t="n"/>
+      <c r="C18" s="846" t="n"/>
+      <c r="D18" s="846" t="n"/>
+      <c r="E18" s="846" t="n"/>
+      <c r="F18" s="846" t="n"/>
+      <c r="G18" s="846" t="n"/>
+      <c r="H18" s="846" t="n"/>
+      <c r="I18" s="846" t="n"/>
+      <c r="J18" s="846" t="n"/>
+      <c r="K18" s="846" t="n"/>
+      <c r="L18" s="846" t="n"/>
+      <c r="M18" s="846" t="n"/>
+      <c r="N18" s="846" t="n"/>
+      <c r="O18" s="846" t="n"/>
+      <c r="P18" s="846" t="n"/>
+      <c r="Q18" s="846" t="n"/>
+      <c r="R18" s="846" t="n"/>
+      <c r="S18" s="846" t="n"/>
+      <c r="T18" s="846" t="n"/>
+      <c r="U18" s="846" t="n"/>
+      <c r="V18" s="846" t="n"/>
+      <c r="W18" s="846" t="n"/>
+      <c r="X18" s="846" t="n"/>
+      <c r="Y18" s="846" t="n"/>
+      <c r="Z18" s="846" t="n"/>
+      <c r="AA18" s="846" t="n"/>
+      <c r="AB18" s="846" t="n"/>
+      <c r="AC18" s="846" t="n"/>
+      <c r="AD18" s="846" t="n"/>
+      <c r="AE18" s="846" t="n"/>
+      <c r="AF18" s="846" t="n"/>
+      <c r="AG18" s="846" t="n"/>
+      <c r="AH18" s="846" t="n"/>
+      <c r="AI18" s="846" t="n"/>
+      <c r="AJ18" s="846" t="n"/>
+      <c r="AK18" s="846" t="n"/>
+      <c r="AL18" s="846" t="n"/>
+      <c r="AM18" s="846" t="n"/>
+      <c r="AN18" s="846" t="n"/>
+    </row>
+    <row r="19" hidden="1">
+      <c r="A19" s="846" t="n"/>
+      <c r="B19" s="846" t="n"/>
+      <c r="C19" s="846" t="n"/>
+      <c r="D19" s="846" t="n"/>
+      <c r="E19" s="846" t="n"/>
+      <c r="F19" s="846" t="n"/>
+      <c r="G19" s="846" t="n"/>
+      <c r="H19" s="846" t="n"/>
+      <c r="I19" s="846" t="n"/>
+      <c r="J19" s="846" t="n"/>
+      <c r="K19" s="846" t="n"/>
+      <c r="L19" s="846" t="n"/>
+      <c r="M19" s="846" t="n"/>
+      <c r="N19" s="846" t="n"/>
+      <c r="O19" s="846" t="n"/>
+      <c r="P19" s="846" t="n"/>
+      <c r="Q19" s="846" t="n"/>
+      <c r="R19" s="846" t="n"/>
+      <c r="S19" s="846" t="n"/>
+      <c r="T19" s="846" t="n"/>
+      <c r="U19" s="846" t="n"/>
+      <c r="V19" s="846" t="n"/>
+      <c r="W19" s="846" t="n"/>
+      <c r="X19" s="846" t="n"/>
+      <c r="Y19" s="846" t="n"/>
+      <c r="Z19" s="846" t="n"/>
+      <c r="AA19" s="846" t="n"/>
+      <c r="AB19" s="846" t="n"/>
+      <c r="AC19" s="846" t="n"/>
+      <c r="AD19" s="846" t="n"/>
+      <c r="AE19" s="846" t="n"/>
+      <c r="AF19" s="846" t="n"/>
+      <c r="AG19" s="846" t="n"/>
+      <c r="AH19" s="846" t="n"/>
+      <c r="AI19" s="846" t="n"/>
+      <c r="AJ19" s="846" t="n"/>
+      <c r="AK19" s="846" t="n"/>
+      <c r="AL19" s="846" t="n"/>
+      <c r="AM19" s="846" t="n"/>
+      <c r="AN19" s="846" t="n"/>
+    </row>
+    <row r="20" hidden="1">
+      <c r="A20" s="846" t="n"/>
+      <c r="B20" s="846" t="n"/>
+      <c r="C20" s="846" t="n"/>
+      <c r="D20" s="846" t="n"/>
+      <c r="E20" s="846" t="n"/>
+      <c r="F20" s="846" t="n"/>
+      <c r="G20" s="846" t="n"/>
+      <c r="H20" s="846" t="n"/>
+      <c r="I20" s="846" t="n"/>
+      <c r="J20" s="846" t="n"/>
+      <c r="K20" s="846" t="n"/>
+      <c r="L20" s="846" t="n"/>
+      <c r="M20" s="846" t="n"/>
+      <c r="N20" s="846" t="n"/>
+      <c r="O20" s="846" t="n"/>
+      <c r="P20" s="846" t="n"/>
+      <c r="Q20" s="846" t="n"/>
+      <c r="R20" s="846" t="n"/>
+      <c r="S20" s="846" t="n"/>
+      <c r="T20" s="846" t="n"/>
+      <c r="U20" s="846" t="n"/>
+      <c r="V20" s="846" t="n"/>
+      <c r="W20" s="846" t="n"/>
+      <c r="X20" s="846" t="n"/>
+      <c r="Y20" s="846" t="n"/>
+      <c r="Z20" s="846" t="n"/>
+      <c r="AA20" s="846" t="n"/>
+      <c r="AB20" s="846" t="n"/>
+      <c r="AC20" s="846" t="n"/>
+      <c r="AD20" s="846" t="n"/>
+      <c r="AE20" s="846" t="n"/>
+      <c r="AF20" s="846" t="n"/>
+      <c r="AG20" s="846" t="n"/>
+      <c r="AH20" s="846" t="n"/>
+      <c r="AI20" s="846" t="n"/>
+      <c r="AJ20" s="846" t="n"/>
+      <c r="AK20" s="846" t="n"/>
+      <c r="AL20" s="846" t="n"/>
+      <c r="AM20" s="846" t="n"/>
+      <c r="AN20" s="846" t="n"/>
+    </row>
     <row r="21" hidden="1"/>
     <row r="22" hidden="1"/>
     <row r="23" hidden="1"/>
@@ -20182,9 +20961,23 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="A4:A11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled drop-down values only." prompt="Select REF_EVIDENCE_LINK" type="list">

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -904,7 +904,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="395">
+  <borders count="399">
     <border>
       <left/>
       <right/>
@@ -5187,11 +5187,56 @@
         <color rgb="002C9CD7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="847">
+  <cellXfs count="912">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7293,6 +7338,161 @@
     </xf>
     <xf numFmtId="0" fontId="96" fillId="58" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="344" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="372" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="396" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="397" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="398" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="398" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -7393,11 +7593,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>622620</colOff>
-      <row>0</row>
-      <rowOff>238275</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1652040" cy="476550"/>
+    <ext cx="2257425" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7411,9 +7611,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7426,11 +7623,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7444,9 +7641,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7459,11 +7653,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7477,9 +7671,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7492,11 +7683,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7510,9 +7701,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7529,7 +7717,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7543,9 +7731,66 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -7802,92 +8047,92 @@
   <dimension ref="A1:CD47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.329999923706055" customWidth="1" min="1" max="1"/>
-    <col width="2.329999923706055" customWidth="1" min="2" max="2"/>
-    <col width="2.329999923706055" customWidth="1" min="3" max="3"/>
-    <col width="2.329999923706055" customWidth="1" min="4" max="4"/>
-    <col width="2.329999923706055" customWidth="1" min="5" max="5"/>
-    <col width="2.329999923706055" customWidth="1" min="6" max="6"/>
-    <col width="2.329999923706055" customWidth="1" min="7" max="7"/>
-    <col width="2.329999923706055" customWidth="1" min="8" max="8"/>
-    <col width="2.329999923706055" customWidth="1" min="9" max="9"/>
-    <col width="2.329999923706055" customWidth="1" min="10" max="10"/>
-    <col width="2.329999923706055" customWidth="1" min="11" max="11"/>
-    <col width="2.329999923706055" customWidth="1" min="12" max="12"/>
-    <col width="2.329999923706055" customWidth="1" min="13" max="13"/>
-    <col width="2.329999923706055" customWidth="1" min="14" max="14"/>
-    <col width="2.329999923706055" customWidth="1" min="15" max="15"/>
-    <col width="2.329999923706055" customWidth="1" min="16" max="16"/>
-    <col width="2.329999923706055" customWidth="1" min="17" max="17"/>
-    <col width="2.329999923706055" customWidth="1" min="18" max="18"/>
-    <col width="2.329999923706055" customWidth="1" min="19" max="19"/>
-    <col width="2.329999923706055" customWidth="1" min="20" max="20"/>
-    <col width="2.329999923706055" customWidth="1" min="21" max="21"/>
-    <col width="2.329999923706055" customWidth="1" min="22" max="22"/>
-    <col width="2.329999923706055" customWidth="1" min="23" max="23"/>
-    <col width="2.329999923706055" customWidth="1" min="24" max="24"/>
-    <col width="2.329999923706055" customWidth="1" min="25" max="25"/>
-    <col width="2.329999923706055" customWidth="1" min="26" max="26"/>
-    <col width="2.329999923706055" customWidth="1" min="27" max="27"/>
-    <col width="2.329999923706055" customWidth="1" min="28" max="28"/>
-    <col width="2.329999923706055" customWidth="1" min="29" max="29"/>
-    <col width="2.329999923706055" customWidth="1" min="30" max="30"/>
-    <col width="2.329999923706055" customWidth="1" min="31" max="31"/>
-    <col width="2.329999923706055" customWidth="1" min="32" max="32"/>
-    <col width="2.329999923706055" customWidth="1" min="33" max="33"/>
-    <col width="2.329999923706055" customWidth="1" min="34" max="34"/>
-    <col width="2.329999923706055" customWidth="1" min="35" max="35"/>
-    <col width="2.329999923706055" customWidth="1" min="36" max="36"/>
-    <col width="2.329999923706055" customWidth="1" min="37" max="37"/>
-    <col width="2.329999923706055" customWidth="1" min="38" max="38"/>
-    <col width="2.329999923706055" customWidth="1" min="39" max="39"/>
-    <col width="2.329999923706055" customWidth="1" min="40" max="40"/>
-    <col width="2.329999923706055" customWidth="1" min="41" max="41"/>
-    <col width="2.329999923706055" customWidth="1" min="42" max="42"/>
-    <col width="2.329999923706055" customWidth="1" min="43" max="43"/>
-    <col width="2.329999923706055" customWidth="1" min="44" max="44"/>
-    <col width="2.329999923706055" customWidth="1" min="45" max="45"/>
-    <col width="2.329999923706055" customWidth="1" min="46" max="46"/>
-    <col width="2.329999923706055" customWidth="1" min="47" max="47"/>
-    <col width="2.329999923706055" customWidth="1" min="48" max="48"/>
-    <col width="2.329999923706055" customWidth="1" min="49" max="49"/>
-    <col width="2.329999923706055" customWidth="1" min="50" max="50"/>
-    <col width="2.329999923706055" customWidth="1" min="51" max="51"/>
-    <col width="2.329999923706055" customWidth="1" min="52" max="52"/>
-    <col width="2.329999923706055" customWidth="1" min="53" max="53"/>
-    <col width="2.329999923706055" customWidth="1" min="54" max="54"/>
-    <col width="2.329999923706055" customWidth="1" min="55" max="55"/>
-    <col width="2.329999923706055" customWidth="1" min="56" max="56"/>
-    <col width="2.329999923706055" customWidth="1" min="57" max="57"/>
-    <col width="2.329999923706055" customWidth="1" min="58" max="58"/>
-    <col width="2.329999923706055" customWidth="1" min="59" max="59"/>
-    <col width="2.329999923706055" customWidth="1" min="60" max="60"/>
-    <col width="2.329999923706055" customWidth="1" min="61" max="61"/>
-    <col width="2.329999923706055" customWidth="1" min="62" max="62"/>
-    <col width="2.329999923706055" customWidth="1" min="63" max="63"/>
-    <col width="2.329999923706055" customWidth="1" min="64" max="64"/>
-    <col width="2.329999923706055" customWidth="1" min="65" max="65"/>
-    <col width="2.329999923706055" customWidth="1" min="66" max="66"/>
-    <col width="2.329999923706055" customWidth="1" min="67" max="67"/>
-    <col width="2.329999923706055" customWidth="1" min="68" max="68"/>
-    <col width="2.329999923706055" customWidth="1" min="69" max="69"/>
-    <col width="2.329999923706055" customWidth="1" min="70" max="70"/>
-    <col width="2.329999923706055" customWidth="1" min="71" max="71"/>
-    <col width="2.329999923706055" customWidth="1" min="72" max="72"/>
-    <col width="2.329999923706055" customWidth="1" min="73" max="73"/>
-    <col width="2.329999923706055" customWidth="1" min="74" max="74"/>
-    <col width="2.329999923706055" customWidth="1" min="75" max="75"/>
-    <col width="2.329999923706055" customWidth="1" min="76" max="76"/>
-    <col width="2.329999923706055" customWidth="1" min="77" max="77"/>
-    <col width="2.329999923706055" customWidth="1" min="78" max="78"/>
-    <col width="2.329999923706055" customWidth="1" min="79" max="79"/>
-    <col width="2.329999923706055" customWidth="1" min="80" max="80"/>
-    <col width="2.329999923706055" customWidth="1" min="81" max="81"/>
-    <col width="2.329999923706055" customWidth="1" min="82" max="82"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
+    <col width="2.33" customWidth="1" min="41" max="41"/>
+    <col width="2.33" customWidth="1" min="42" max="42"/>
+    <col width="2.33" customWidth="1" min="43" max="43"/>
+    <col width="2.33" customWidth="1" min="44" max="44"/>
+    <col width="2.33" customWidth="1" min="45" max="45"/>
+    <col width="2.33" customWidth="1" min="46" max="46"/>
+    <col width="2.33" customWidth="1" min="47" max="47"/>
+    <col width="2.33" customWidth="1" min="48" max="48"/>
+    <col width="2.33" customWidth="1" min="49" max="49"/>
+    <col width="2.33" customWidth="1" min="50" max="50"/>
+    <col width="2.33" customWidth="1" min="51" max="51"/>
+    <col width="2.33" customWidth="1" min="52" max="52"/>
+    <col width="2.33" customWidth="1" min="53" max="53"/>
+    <col width="2.33" customWidth="1" min="54" max="54"/>
+    <col width="2.33" customWidth="1" min="55" max="55"/>
+    <col width="2.33" customWidth="1" min="56" max="56"/>
+    <col width="2.33" customWidth="1" min="57" max="57"/>
+    <col width="2.33" customWidth="1" min="58" max="58"/>
+    <col width="2.33" customWidth="1" min="59" max="59"/>
+    <col width="2.33" customWidth="1" min="60" max="60"/>
+    <col width="2.33" customWidth="1" min="61" max="61"/>
+    <col width="2.33" customWidth="1" min="62" max="62"/>
+    <col width="2.33" customWidth="1" min="63" max="63"/>
+    <col width="2.33" customWidth="1" min="64" max="64"/>
+    <col width="2.33" customWidth="1" min="65" max="65"/>
+    <col width="2.33" customWidth="1" min="66" max="66"/>
+    <col width="2.33" customWidth="1" min="67" max="67"/>
+    <col width="2.33" customWidth="1" min="68" max="68"/>
+    <col width="2.33" customWidth="1" min="69" max="69"/>
+    <col width="2.33" customWidth="1" min="70" max="70"/>
+    <col width="2.33" customWidth="1" min="71" max="71"/>
+    <col width="2.33" customWidth="1" min="72" max="72"/>
+    <col width="2.33" customWidth="1" min="73" max="73"/>
+    <col width="2.33" customWidth="1" min="74" max="74"/>
+    <col width="2.33" customWidth="1" min="75" max="75"/>
+    <col width="2.33" customWidth="1" min="76" max="76"/>
+    <col width="2.33" customWidth="1" min="77" max="77"/>
+    <col width="2.33" customWidth="1" min="78" max="78"/>
+    <col width="2.33" customWidth="1" min="79" max="79"/>
+    <col width="2.33" customWidth="1" min="80" max="80"/>
+    <col width="2.33" customWidth="1" min="81" max="81"/>
+    <col width="2.33" customWidth="1" min="82" max="82"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="83" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="776" t="n"/>
       <c r="B1" s="268" t="n"/>
       <c r="C1" s="268" t="n"/>
@@ -7904,7 +8149,7 @@
       <c r="N1" s="268" t="n"/>
       <c r="O1" s="268" t="n"/>
       <c r="P1" s="325" t="n"/>
-      <c r="Q1" s="663" t="inlineStr">
+      <c r="Q1" s="910" t="inlineStr">
         <is>
           <t>FAI REPORT</t>
         </is>
@@ -7953,7 +8198,7 @@
       <c r="BG1" s="268" t="n"/>
       <c r="BH1" s="268" t="n"/>
       <c r="BI1" s="268" t="n"/>
-      <c r="BJ1" s="268" t="n"/>
+      <c r="BJ1" s="325" t="n"/>
       <c r="BK1" s="777" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -7984,375 +8229,548 @@
       <c r="CD1" s="325" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="P2" s="326" t="n"/>
-      <c r="Q2" s="275" t="n"/>
-      <c r="BK2" s="779" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="847" t="n"/>
+      <c r="C2" s="847" t="n"/>
+      <c r="D2" s="847" t="n"/>
+      <c r="E2" s="847" t="n"/>
+      <c r="F2" s="847" t="n"/>
+      <c r="G2" s="847" t="n"/>
+      <c r="H2" s="847" t="n"/>
+      <c r="I2" s="847" t="n"/>
+      <c r="J2" s="847" t="n"/>
+      <c r="K2" s="847" t="n"/>
+      <c r="L2" s="847" t="n"/>
+      <c r="M2" s="847" t="n"/>
+      <c r="N2" s="847" t="n"/>
+      <c r="O2" s="847" t="n"/>
+      <c r="P2" s="848" t="n"/>
+      <c r="Q2" s="847" t="n"/>
+      <c r="R2" s="847" t="n"/>
+      <c r="S2" s="847" t="n"/>
+      <c r="T2" s="847" t="n"/>
+      <c r="U2" s="847" t="n"/>
+      <c r="V2" s="847" t="n"/>
+      <c r="W2" s="847" t="n"/>
+      <c r="X2" s="847" t="n"/>
+      <c r="Y2" s="847" t="n"/>
+      <c r="Z2" s="847" t="n"/>
+      <c r="AA2" s="847" t="n"/>
+      <c r="AB2" s="847" t="n"/>
+      <c r="AC2" s="847" t="n"/>
+      <c r="AD2" s="847" t="n"/>
+      <c r="AE2" s="847" t="n"/>
+      <c r="AF2" s="847" t="n"/>
+      <c r="AG2" s="847" t="n"/>
+      <c r="AH2" s="847" t="n"/>
+      <c r="AI2" s="847" t="n"/>
+      <c r="AJ2" s="847" t="n"/>
+      <c r="AK2" s="847" t="n"/>
+      <c r="AL2" s="847" t="n"/>
+      <c r="AM2" s="847" t="n"/>
+      <c r="AN2" s="847" t="n"/>
+      <c r="AO2" s="847" t="n"/>
+      <c r="AP2" s="847" t="n"/>
+      <c r="AQ2" s="847" t="n"/>
+      <c r="AR2" s="847" t="n"/>
+      <c r="AS2" s="847" t="n"/>
+      <c r="AT2" s="847" t="n"/>
+      <c r="AU2" s="847" t="n"/>
+      <c r="AV2" s="847" t="n"/>
+      <c r="AW2" s="847" t="n"/>
+      <c r="AX2" s="847" t="n"/>
+      <c r="AY2" s="847" t="n"/>
+      <c r="AZ2" s="847" t="n"/>
+      <c r="BA2" s="847" t="n"/>
+      <c r="BB2" s="847" t="n"/>
+      <c r="BC2" s="847" t="n"/>
+      <c r="BD2" s="847" t="n"/>
+      <c r="BE2" s="847" t="n"/>
+      <c r="BF2" s="847" t="n"/>
+      <c r="BG2" s="847" t="n"/>
+      <c r="BH2" s="847" t="n"/>
+      <c r="BI2" s="847" t="n"/>
+      <c r="BJ2" s="848" t="n"/>
+      <c r="BK2" s="849" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="BL2" s="780" t="n"/>
-      <c r="BM2" s="780" t="n"/>
-      <c r="BN2" s="780" t="n"/>
-      <c r="BO2" s="780" t="n"/>
-      <c r="BP2" s="780" t="n"/>
-      <c r="BQ2" s="780" t="n"/>
-      <c r="BR2" s="781" t="n"/>
-      <c r="BS2" s="723" t="inlineStr">
+      <c r="BL2" s="850" t="n"/>
+      <c r="BM2" s="850" t="n"/>
+      <c r="BN2" s="850" t="n"/>
+      <c r="BO2" s="850" t="n"/>
+      <c r="BP2" s="850" t="n"/>
+      <c r="BQ2" s="850" t="n"/>
+      <c r="BR2" s="851" t="n"/>
+      <c r="BS2" s="852" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="BT2" s="780" t="n"/>
-      <c r="BU2" s="780" t="n"/>
-      <c r="BV2" s="780" t="n"/>
-      <c r="BW2" s="780" t="n"/>
-      <c r="BX2" s="780" t="n"/>
-      <c r="BY2" s="780" t="n"/>
-      <c r="BZ2" s="780" t="n"/>
-      <c r="CA2" s="780" t="n"/>
-      <c r="CB2" s="780" t="n"/>
-      <c r="CC2" s="780" t="n"/>
-      <c r="CD2" s="782" t="n"/>
+      <c r="BT2" s="853" t="n"/>
+      <c r="BU2" s="853" t="n"/>
+      <c r="BV2" s="853" t="n"/>
+      <c r="BW2" s="853" t="n"/>
+      <c r="BX2" s="853" t="n"/>
+      <c r="BY2" s="853" t="n"/>
+      <c r="BZ2" s="853" t="n"/>
+      <c r="CA2" s="853" t="n"/>
+      <c r="CB2" s="853" t="n"/>
+      <c r="CC2" s="853" t="n"/>
+      <c r="CD2" s="854" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="P3" s="326" t="n"/>
-      <c r="Q3" s="275" t="n"/>
-      <c r="BK3" s="779" t="inlineStr">
+      <c r="A3" s="855" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="856" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="25" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="25" t="n"/>
+      <c r="AH3" s="25" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="25" t="n"/>
+      <c r="AL3" s="25" t="n"/>
+      <c r="AM3" s="25" t="n"/>
+      <c r="AN3" s="25" t="n"/>
+      <c r="AO3" s="25" t="n"/>
+      <c r="AP3" s="25" t="n"/>
+      <c r="AQ3" s="25" t="n"/>
+      <c r="AR3" s="25" t="n"/>
+      <c r="AS3" s="25" t="n"/>
+      <c r="AT3" s="25" t="n"/>
+      <c r="AU3" s="25" t="n"/>
+      <c r="AV3" s="25" t="n"/>
+      <c r="AW3" s="25" t="n"/>
+      <c r="AX3" s="25" t="n"/>
+      <c r="AY3" s="25" t="n"/>
+      <c r="AZ3" s="25" t="n"/>
+      <c r="BA3" s="25" t="n"/>
+      <c r="BB3" s="25" t="n"/>
+      <c r="BC3" s="25" t="n"/>
+      <c r="BD3" s="25" t="n"/>
+      <c r="BE3" s="25" t="n"/>
+      <c r="BF3" s="25" t="n"/>
+      <c r="BG3" s="25" t="n"/>
+      <c r="BH3" s="25" t="n"/>
+      <c r="BI3" s="25" t="n"/>
+      <c r="BJ3" s="856" t="n"/>
+      <c r="BK3" s="857" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="BL3" s="780" t="n"/>
-      <c r="BM3" s="780" t="n"/>
-      <c r="BN3" s="780" t="n"/>
-      <c r="BO3" s="780" t="n"/>
-      <c r="BP3" s="780" t="n"/>
-      <c r="BQ3" s="780" t="n"/>
-      <c r="BR3" s="781" t="n"/>
-      <c r="BS3" s="723" t="inlineStr">
+      <c r="BL3" s="858" t="n"/>
+      <c r="BM3" s="858" t="n"/>
+      <c r="BN3" s="858" t="n"/>
+      <c r="BO3" s="858" t="n"/>
+      <c r="BP3" s="858" t="n"/>
+      <c r="BQ3" s="858" t="n"/>
+      <c r="BR3" s="859" t="n"/>
+      <c r="BS3" s="741" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="BT3" s="780" t="n"/>
-      <c r="BU3" s="780" t="n"/>
-      <c r="BV3" s="780" t="n"/>
-      <c r="BW3" s="780" t="n"/>
-      <c r="BX3" s="780" t="n"/>
-      <c r="BY3" s="780" t="n"/>
-      <c r="BZ3" s="780" t="n"/>
-      <c r="CA3" s="780" t="n"/>
-      <c r="CB3" s="780" t="n"/>
-      <c r="CC3" s="780" t="n"/>
-      <c r="CD3" s="782" t="n"/>
+      <c r="BT3" s="860" t="n"/>
+      <c r="BU3" s="860" t="n"/>
+      <c r="BV3" s="860" t="n"/>
+      <c r="BW3" s="860" t="n"/>
+      <c r="BX3" s="860" t="n"/>
+      <c r="BY3" s="860" t="n"/>
+      <c r="BZ3" s="860" t="n"/>
+      <c r="CA3" s="860" t="n"/>
+      <c r="CB3" s="860" t="n"/>
+      <c r="CC3" s="860" t="n"/>
+      <c r="CD3" s="861" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="P4" s="326" t="n"/>
-      <c r="Q4" s="672" t="inlineStr">
+      <c r="A4" s="855" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="856" t="n"/>
+      <c r="Q4" s="354" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="BK4" s="779" t="inlineStr">
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="25" t="n"/>
+      <c r="AE4" s="25" t="n"/>
+      <c r="AF4" s="25" t="n"/>
+      <c r="AG4" s="25" t="n"/>
+      <c r="AH4" s="25" t="n"/>
+      <c r="AI4" s="25" t="n"/>
+      <c r="AJ4" s="25" t="n"/>
+      <c r="AK4" s="25" t="n"/>
+      <c r="AL4" s="25" t="n"/>
+      <c r="AM4" s="25" t="n"/>
+      <c r="AN4" s="25" t="n"/>
+      <c r="AO4" s="25" t="n"/>
+      <c r="AP4" s="25" t="n"/>
+      <c r="AQ4" s="25" t="n"/>
+      <c r="AR4" s="25" t="n"/>
+      <c r="AS4" s="25" t="n"/>
+      <c r="AT4" s="25" t="n"/>
+      <c r="AU4" s="25" t="n"/>
+      <c r="AV4" s="25" t="n"/>
+      <c r="AW4" s="25" t="n"/>
+      <c r="AX4" s="25" t="n"/>
+      <c r="AY4" s="25" t="n"/>
+      <c r="AZ4" s="25" t="n"/>
+      <c r="BA4" s="25" t="n"/>
+      <c r="BB4" s="25" t="n"/>
+      <c r="BC4" s="25" t="n"/>
+      <c r="BD4" s="25" t="n"/>
+      <c r="BE4" s="25" t="n"/>
+      <c r="BF4" s="25" t="n"/>
+      <c r="BG4" s="25" t="n"/>
+      <c r="BH4" s="25" t="n"/>
+      <c r="BI4" s="25" t="n"/>
+      <c r="BJ4" s="856" t="n"/>
+      <c r="BK4" s="857" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="BL4" s="780" t="n"/>
-      <c r="BM4" s="780" t="n"/>
-      <c r="BN4" s="780" t="n"/>
-      <c r="BO4" s="780" t="n"/>
-      <c r="BP4" s="780" t="n"/>
-      <c r="BQ4" s="780" t="n"/>
-      <c r="BR4" s="781" t="n"/>
-      <c r="BS4" s="723" t="inlineStr">
+      <c r="BL4" s="858" t="n"/>
+      <c r="BM4" s="858" t="n"/>
+      <c r="BN4" s="858" t="n"/>
+      <c r="BO4" s="858" t="n"/>
+      <c r="BP4" s="858" t="n"/>
+      <c r="BQ4" s="858" t="n"/>
+      <c r="BR4" s="859" t="n"/>
+      <c r="BS4" s="741" t="inlineStr">
         <is>
           <t>QA / Engineering</t>
         </is>
       </c>
-      <c r="BT4" s="780" t="n"/>
-      <c r="BU4" s="780" t="n"/>
-      <c r="BV4" s="780" t="n"/>
-      <c r="BW4" s="780" t="n"/>
-      <c r="BX4" s="780" t="n"/>
-      <c r="BY4" s="780" t="n"/>
-      <c r="BZ4" s="780" t="n"/>
-      <c r="CA4" s="780" t="n"/>
-      <c r="CB4" s="780" t="n"/>
-      <c r="CC4" s="780" t="n"/>
-      <c r="CD4" s="782" t="n"/>
+      <c r="BT4" s="860" t="n"/>
+      <c r="BU4" s="860" t="n"/>
+      <c r="BV4" s="860" t="n"/>
+      <c r="BW4" s="860" t="n"/>
+      <c r="BX4" s="860" t="n"/>
+      <c r="BY4" s="860" t="n"/>
+      <c r="BZ4" s="860" t="n"/>
+      <c r="CA4" s="860" t="n"/>
+      <c r="CB4" s="860" t="n"/>
+      <c r="CC4" s="860" t="n"/>
+      <c r="CD4" s="861" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="283" t="n"/>
-      <c r="C5" s="283" t="n"/>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="283" t="n"/>
-      <c r="I5" s="283" t="n"/>
-      <c r="J5" s="283" t="n"/>
-      <c r="K5" s="283" t="n"/>
-      <c r="L5" s="283" t="n"/>
-      <c r="M5" s="283" t="n"/>
-      <c r="N5" s="283" t="n"/>
-      <c r="O5" s="283" t="n"/>
-      <c r="P5" s="287" t="n"/>
-      <c r="Q5" s="20" t="inlineStr">
+      <c r="A5" s="855" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="856" t="n"/>
+      <c r="Q5" s="610" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="R5" s="283" t="n"/>
-      <c r="S5" s="283" t="n"/>
-      <c r="T5" s="283" t="n"/>
-      <c r="U5" s="283" t="n"/>
-      <c r="V5" s="283" t="n"/>
-      <c r="W5" s="283" t="n"/>
-      <c r="X5" s="283" t="n"/>
-      <c r="Y5" s="283" t="n"/>
-      <c r="Z5" s="283" t="n"/>
-      <c r="AA5" s="283" t="n"/>
-      <c r="AB5" s="283" t="n"/>
-      <c r="AC5" s="283" t="n"/>
-      <c r="AD5" s="283" t="n"/>
-      <c r="AE5" s="283" t="n"/>
-      <c r="AF5" s="283" t="n"/>
-      <c r="AG5" s="283" t="n"/>
-      <c r="AH5" s="283" t="n"/>
-      <c r="AI5" s="283" t="n"/>
-      <c r="AJ5" s="283" t="n"/>
-      <c r="AK5" s="283" t="n"/>
-      <c r="AL5" s="283" t="n"/>
-      <c r="AM5" s="283" t="n"/>
-      <c r="AN5" s="283" t="n"/>
-      <c r="AO5" s="283" t="n"/>
-      <c r="AP5" s="283" t="n"/>
-      <c r="AQ5" s="283" t="n"/>
-      <c r="AR5" s="283" t="n"/>
-      <c r="AS5" s="283" t="n"/>
-      <c r="AT5" s="283" t="n"/>
-      <c r="AU5" s="283" t="n"/>
-      <c r="AV5" s="283" t="n"/>
-      <c r="AW5" s="283" t="n"/>
-      <c r="AX5" s="283" t="n"/>
-      <c r="AY5" s="283" t="n"/>
-      <c r="AZ5" s="283" t="n"/>
-      <c r="BA5" s="283" t="n"/>
-      <c r="BB5" s="283" t="n"/>
-      <c r="BC5" s="283" t="n"/>
-      <c r="BD5" s="283" t="n"/>
-      <c r="BE5" s="283" t="n"/>
-      <c r="BF5" s="283" t="n"/>
-      <c r="BG5" s="283" t="n"/>
-      <c r="BH5" s="283" t="n"/>
-      <c r="BI5" s="283" t="n"/>
-      <c r="BJ5" s="283" t="n"/>
-      <c r="BK5" s="783" t="inlineStr">
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="25" t="n"/>
+      <c r="AE5" s="25" t="n"/>
+      <c r="AF5" s="25" t="n"/>
+      <c r="AG5" s="25" t="n"/>
+      <c r="AH5" s="25" t="n"/>
+      <c r="AI5" s="25" t="n"/>
+      <c r="AJ5" s="25" t="n"/>
+      <c r="AK5" s="25" t="n"/>
+      <c r="AL5" s="25" t="n"/>
+      <c r="AM5" s="25" t="n"/>
+      <c r="AN5" s="25" t="n"/>
+      <c r="AO5" s="25" t="n"/>
+      <c r="AP5" s="25" t="n"/>
+      <c r="AQ5" s="25" t="n"/>
+      <c r="AR5" s="25" t="n"/>
+      <c r="AS5" s="25" t="n"/>
+      <c r="AT5" s="25" t="n"/>
+      <c r="AU5" s="25" t="n"/>
+      <c r="AV5" s="25" t="n"/>
+      <c r="AW5" s="25" t="n"/>
+      <c r="AX5" s="25" t="n"/>
+      <c r="AY5" s="25" t="n"/>
+      <c r="AZ5" s="25" t="n"/>
+      <c r="BA5" s="25" t="n"/>
+      <c r="BB5" s="25" t="n"/>
+      <c r="BC5" s="25" t="n"/>
+      <c r="BD5" s="25" t="n"/>
+      <c r="BE5" s="25" t="n"/>
+      <c r="BF5" s="25" t="n"/>
+      <c r="BG5" s="25" t="n"/>
+      <c r="BH5" s="25" t="n"/>
+      <c r="BI5" s="25" t="n"/>
+      <c r="BJ5" s="856" t="n"/>
+      <c r="BK5" s="857" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="BL5" s="784" t="n"/>
-      <c r="BM5" s="784" t="n"/>
-      <c r="BN5" s="784" t="n"/>
-      <c r="BO5" s="784" t="n"/>
-      <c r="BP5" s="784" t="n"/>
-      <c r="BQ5" s="784" t="n"/>
-      <c r="BR5" s="785" t="n"/>
-      <c r="BS5" s="731" t="inlineStr">
+      <c r="BL5" s="858" t="n"/>
+      <c r="BM5" s="858" t="n"/>
+      <c r="BN5" s="858" t="n"/>
+      <c r="BO5" s="858" t="n"/>
+      <c r="BP5" s="858" t="n"/>
+      <c r="BQ5" s="858" t="n"/>
+      <c r="BR5" s="859" t="n"/>
+      <c r="BS5" s="741" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="BT5" s="784" t="n"/>
-      <c r="BU5" s="784" t="n"/>
-      <c r="BV5" s="784" t="n"/>
-      <c r="BW5" s="784" t="n"/>
-      <c r="BX5" s="784" t="n"/>
-      <c r="BY5" s="784" t="n"/>
-      <c r="BZ5" s="784" t="n"/>
-      <c r="CA5" s="784" t="n"/>
-      <c r="CB5" s="784" t="n"/>
-      <c r="CC5" s="784" t="n"/>
-      <c r="CD5" s="786" t="n"/>
+      <c r="BT5" s="860" t="n"/>
+      <c r="BU5" s="860" t="n"/>
+      <c r="BV5" s="860" t="n"/>
+      <c r="BW5" s="860" t="n"/>
+      <c r="BX5" s="860" t="n"/>
+      <c r="BY5" s="860" t="n"/>
+      <c r="BZ5" s="860" t="n"/>
+      <c r="CA5" s="860" t="n"/>
+      <c r="CB5" s="860" t="n"/>
+      <c r="CC5" s="860" t="n"/>
+      <c r="CD5" s="861" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="678" t="n"/>
-      <c r="B6" s="678" t="n"/>
-      <c r="C6" s="678" t="n"/>
-      <c r="D6" s="678" t="n"/>
-      <c r="E6" s="678" t="n"/>
-      <c r="F6" s="678" t="n"/>
-      <c r="G6" s="678" t="n"/>
-      <c r="H6" s="678" t="n"/>
-      <c r="I6" s="678" t="n"/>
-      <c r="J6" s="678" t="n"/>
-      <c r="K6" s="678" t="n"/>
-      <c r="L6" s="678" t="n"/>
-      <c r="M6" s="678" t="n"/>
-      <c r="N6" s="678" t="n"/>
-      <c r="O6" s="678" t="n"/>
-      <c r="P6" s="678" t="n"/>
-      <c r="Q6" s="678" t="n"/>
-      <c r="R6" s="678" t="n"/>
-      <c r="S6" s="678" t="n"/>
-      <c r="T6" s="678" t="n"/>
-      <c r="U6" s="678" t="n"/>
-      <c r="V6" s="678" t="n"/>
-      <c r="W6" s="678" t="n"/>
-      <c r="X6" s="678" t="n"/>
-      <c r="Y6" s="678" t="n"/>
-      <c r="Z6" s="678" t="n"/>
-      <c r="AA6" s="678" t="n"/>
-      <c r="AB6" s="678" t="n"/>
-      <c r="AC6" s="678" t="n"/>
-      <c r="AD6" s="678" t="n"/>
-      <c r="AE6" s="678" t="n"/>
-      <c r="AF6" s="678" t="n"/>
-      <c r="AG6" s="678" t="n"/>
-      <c r="AH6" s="678" t="n"/>
-      <c r="AI6" s="678" t="n"/>
-      <c r="AJ6" s="678" t="n"/>
-      <c r="AK6" s="678" t="n"/>
-      <c r="AL6" s="678" t="n"/>
-      <c r="AM6" s="678" t="n"/>
-      <c r="AN6" s="678" t="n"/>
-      <c r="AO6" s="678" t="n"/>
-      <c r="AP6" s="678" t="n"/>
-      <c r="AQ6" s="678" t="n"/>
-      <c r="AR6" s="678" t="n"/>
-      <c r="AS6" s="678" t="n"/>
-      <c r="AT6" s="678" t="n"/>
-      <c r="AU6" s="678" t="n"/>
-      <c r="AV6" s="678" t="n"/>
-      <c r="AW6" s="678" t="n"/>
-      <c r="AX6" s="678" t="n"/>
-      <c r="AY6" s="678" t="n"/>
-      <c r="AZ6" s="678" t="n"/>
-      <c r="BA6" s="678" t="n"/>
-      <c r="BB6" s="678" t="n"/>
-      <c r="BC6" s="678" t="n"/>
-      <c r="BD6" s="678" t="n"/>
-      <c r="BE6" s="678" t="n"/>
-      <c r="BF6" s="678" t="n"/>
-      <c r="BG6" s="678" t="n"/>
-      <c r="BH6" s="678" t="n"/>
-      <c r="BI6" s="678" t="n"/>
-      <c r="BJ6" s="678" t="n"/>
-      <c r="BK6" s="678" t="n"/>
-      <c r="BL6" s="678" t="n"/>
-      <c r="BM6" s="678" t="n"/>
-      <c r="BN6" s="678" t="n"/>
-      <c r="BO6" s="678" t="n"/>
-      <c r="BP6" s="678" t="n"/>
-      <c r="BQ6" s="678" t="n"/>
-      <c r="BR6" s="678" t="n"/>
-      <c r="BS6" s="678" t="n"/>
-      <c r="BT6" s="678" t="n"/>
-      <c r="BU6" s="678" t="n"/>
-      <c r="BV6" s="678" t="n"/>
-      <c r="BW6" s="678" t="n"/>
-      <c r="BX6" s="678" t="n"/>
-      <c r="BY6" s="678" t="n"/>
-      <c r="BZ6" s="678" t="n"/>
-      <c r="CA6" s="678" t="n"/>
-      <c r="CB6" s="678" t="n"/>
-      <c r="CC6" s="678" t="n"/>
-      <c r="CD6" s="678" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="862" t="n"/>
+      <c r="B6" s="863" t="n"/>
+      <c r="C6" s="863" t="n"/>
+      <c r="D6" s="863" t="n"/>
+      <c r="E6" s="863" t="n"/>
+      <c r="F6" s="863" t="n"/>
+      <c r="G6" s="863" t="n"/>
+      <c r="H6" s="863" t="n"/>
+      <c r="I6" s="863" t="n"/>
+      <c r="J6" s="863" t="n"/>
+      <c r="K6" s="863" t="n"/>
+      <c r="L6" s="863" t="n"/>
+      <c r="M6" s="863" t="n"/>
+      <c r="N6" s="863" t="n"/>
+      <c r="O6" s="863" t="n"/>
+      <c r="P6" s="864" t="n"/>
+      <c r="Q6" s="863" t="n"/>
+      <c r="R6" s="863" t="n"/>
+      <c r="S6" s="863" t="n"/>
+      <c r="T6" s="863" t="n"/>
+      <c r="U6" s="863" t="n"/>
+      <c r="V6" s="863" t="n"/>
+      <c r="W6" s="863" t="n"/>
+      <c r="X6" s="863" t="n"/>
+      <c r="Y6" s="863" t="n"/>
+      <c r="Z6" s="863" t="n"/>
+      <c r="AA6" s="863" t="n"/>
+      <c r="AB6" s="863" t="n"/>
+      <c r="AC6" s="863" t="n"/>
+      <c r="AD6" s="863" t="n"/>
+      <c r="AE6" s="863" t="n"/>
+      <c r="AF6" s="863" t="n"/>
+      <c r="AG6" s="863" t="n"/>
+      <c r="AH6" s="863" t="n"/>
+      <c r="AI6" s="863" t="n"/>
+      <c r="AJ6" s="863" t="n"/>
+      <c r="AK6" s="863" t="n"/>
+      <c r="AL6" s="863" t="n"/>
+      <c r="AM6" s="863" t="n"/>
+      <c r="AN6" s="863" t="n"/>
+      <c r="AO6" s="863" t="n"/>
+      <c r="AP6" s="863" t="n"/>
+      <c r="AQ6" s="863" t="n"/>
+      <c r="AR6" s="863" t="n"/>
+      <c r="AS6" s="863" t="n"/>
+      <c r="AT6" s="863" t="n"/>
+      <c r="AU6" s="863" t="n"/>
+      <c r="AV6" s="863" t="n"/>
+      <c r="AW6" s="863" t="n"/>
+      <c r="AX6" s="863" t="n"/>
+      <c r="AY6" s="863" t="n"/>
+      <c r="AZ6" s="863" t="n"/>
+      <c r="BA6" s="863" t="n"/>
+      <c r="BB6" s="863" t="n"/>
+      <c r="BC6" s="863" t="n"/>
+      <c r="BD6" s="863" t="n"/>
+      <c r="BE6" s="863" t="n"/>
+      <c r="BF6" s="863" t="n"/>
+      <c r="BG6" s="863" t="n"/>
+      <c r="BH6" s="863" t="n"/>
+      <c r="BI6" s="863" t="n"/>
+      <c r="BJ6" s="864" t="n"/>
+      <c r="BK6" s="865" t="n"/>
+      <c r="BL6" s="865" t="n"/>
+      <c r="BM6" s="865" t="n"/>
+      <c r="BN6" s="865" t="n"/>
+      <c r="BO6" s="865" t="n"/>
+      <c r="BP6" s="865" t="n"/>
+      <c r="BQ6" s="865" t="n"/>
+      <c r="BR6" s="866" t="n"/>
+      <c r="BS6" s="867" t="n"/>
+      <c r="BT6" s="867" t="n"/>
+      <c r="BU6" s="867" t="n"/>
+      <c r="BV6" s="867" t="n"/>
+      <c r="BW6" s="867" t="n"/>
+      <c r="BX6" s="867" t="n"/>
+      <c r="BY6" s="867" t="n"/>
+      <c r="BZ6" s="867" t="n"/>
+      <c r="CA6" s="867" t="n"/>
+      <c r="CB6" s="867" t="n"/>
+      <c r="CC6" s="867" t="n"/>
+      <c r="CD6" s="868" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="787" t="inlineStr">
-        <is>
-          <t>1.  FAI HEADER</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="289" t="n"/>
-      <c r="K7" s="289" t="n"/>
-      <c r="L7" s="289" t="n"/>
-      <c r="M7" s="289" t="n"/>
-      <c r="N7" s="289" t="n"/>
-      <c r="O7" s="289" t="n"/>
-      <c r="P7" s="289" t="n"/>
-      <c r="Q7" s="289" t="n"/>
-      <c r="R7" s="289" t="n"/>
-      <c r="S7" s="289" t="n"/>
-      <c r="T7" s="289" t="n"/>
-      <c r="U7" s="289" t="n"/>
-      <c r="V7" s="289" t="n"/>
-      <c r="W7" s="289" t="n"/>
-      <c r="X7" s="289" t="n"/>
-      <c r="Y7" s="289" t="n"/>
-      <c r="Z7" s="289" t="n"/>
-      <c r="AA7" s="289" t="n"/>
-      <c r="AB7" s="289" t="n"/>
-      <c r="AC7" s="289" t="n"/>
-      <c r="AD7" s="289" t="n"/>
-      <c r="AE7" s="289" t="n"/>
-      <c r="AF7" s="289" t="n"/>
-      <c r="AG7" s="289" t="n"/>
-      <c r="AH7" s="289" t="n"/>
-      <c r="AI7" s="289" t="n"/>
-      <c r="AJ7" s="289" t="n"/>
-      <c r="AK7" s="289" t="n"/>
-      <c r="AL7" s="289" t="n"/>
-      <c r="AM7" s="289" t="n"/>
-      <c r="AN7" s="289" t="n"/>
-      <c r="AO7" s="289" t="n"/>
-      <c r="AP7" s="289" t="n"/>
-      <c r="AQ7" s="289" t="n"/>
-      <c r="AR7" s="289" t="n"/>
-      <c r="AS7" s="289" t="n"/>
-      <c r="AT7" s="289" t="n"/>
-      <c r="AU7" s="289" t="n"/>
-      <c r="AV7" s="289" t="n"/>
-      <c r="AW7" s="289" t="n"/>
-      <c r="AX7" s="289" t="n"/>
-      <c r="AY7" s="289" t="n"/>
-      <c r="AZ7" s="289" t="n"/>
-      <c r="BA7" s="289" t="n"/>
-      <c r="BB7" s="289" t="n"/>
-      <c r="BC7" s="289" t="n"/>
-      <c r="BD7" s="289" t="n"/>
-      <c r="BE7" s="289" t="n"/>
-      <c r="BF7" s="289" t="n"/>
-      <c r="BG7" s="289" t="n"/>
-      <c r="BH7" s="289" t="n"/>
-      <c r="BI7" s="289" t="n"/>
-      <c r="BJ7" s="289" t="n"/>
-      <c r="BK7" s="289" t="n"/>
-      <c r="BL7" s="289" t="n"/>
-      <c r="BM7" s="289" t="n"/>
-      <c r="BN7" s="289" t="n"/>
-      <c r="BO7" s="289" t="n"/>
-      <c r="BP7" s="289" t="n"/>
-      <c r="BQ7" s="289" t="n"/>
-      <c r="BR7" s="289" t="n"/>
-      <c r="BS7" s="289" t="n"/>
-      <c r="BT7" s="289" t="n"/>
-      <c r="BU7" s="289" t="n"/>
-      <c r="BV7" s="289" t="n"/>
-      <c r="BW7" s="289" t="n"/>
-      <c r="BX7" s="289" t="n"/>
-      <c r="BY7" s="289" t="n"/>
-      <c r="BZ7" s="289" t="n"/>
-      <c r="CA7" s="289" t="n"/>
-      <c r="CB7" s="289" t="n"/>
-      <c r="CC7" s="289" t="n"/>
-      <c r="CD7" s="290" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="869" t="n"/>
+      <c r="B7" s="870" t="n"/>
+      <c r="C7" s="870" t="n"/>
+      <c r="D7" s="870" t="n"/>
+      <c r="E7" s="870" t="n"/>
+      <c r="F7" s="870" t="n"/>
+      <c r="G7" s="870" t="n"/>
+      <c r="H7" s="870" t="n"/>
+      <c r="I7" s="870" t="n"/>
+      <c r="J7" s="870" t="n"/>
+      <c r="K7" s="870" t="n"/>
+      <c r="L7" s="870" t="n"/>
+      <c r="M7" s="870" t="n"/>
+      <c r="N7" s="870" t="n"/>
+      <c r="O7" s="870" t="n"/>
+      <c r="P7" s="870" t="n"/>
+      <c r="Q7" s="870" t="n"/>
+      <c r="R7" s="870" t="n"/>
+      <c r="S7" s="870" t="n"/>
+      <c r="T7" s="870" t="n"/>
+      <c r="U7" s="870" t="n"/>
+      <c r="V7" s="870" t="n"/>
+      <c r="W7" s="870" t="n"/>
+      <c r="X7" s="870" t="n"/>
+      <c r="Y7" s="870" t="n"/>
+      <c r="Z7" s="870" t="n"/>
+      <c r="AA7" s="870" t="n"/>
+      <c r="AB7" s="870" t="n"/>
+      <c r="AC7" s="870" t="n"/>
+      <c r="AD7" s="870" t="n"/>
+      <c r="AE7" s="870" t="n"/>
+      <c r="AF7" s="870" t="n"/>
+      <c r="AG7" s="870" t="n"/>
+      <c r="AH7" s="870" t="n"/>
+      <c r="AI7" s="870" t="n"/>
+      <c r="AJ7" s="870" t="n"/>
+      <c r="AK7" s="870" t="n"/>
+      <c r="AL7" s="870" t="n"/>
+      <c r="AM7" s="870" t="n"/>
+      <c r="AN7" s="870" t="n"/>
+      <c r="AO7" s="870" t="n"/>
+      <c r="AP7" s="870" t="n"/>
+      <c r="AQ7" s="870" t="n"/>
+      <c r="AR7" s="870" t="n"/>
+      <c r="AS7" s="870" t="n"/>
+      <c r="AT7" s="870" t="n"/>
+      <c r="AU7" s="870" t="n"/>
+      <c r="AV7" s="870" t="n"/>
+      <c r="AW7" s="870" t="n"/>
+      <c r="AX7" s="870" t="n"/>
+      <c r="AY7" s="870" t="n"/>
+      <c r="AZ7" s="870" t="n"/>
+      <c r="BA7" s="870" t="n"/>
+      <c r="BB7" s="870" t="n"/>
+      <c r="BC7" s="870" t="n"/>
+      <c r="BD7" s="870" t="n"/>
+      <c r="BE7" s="870" t="n"/>
+      <c r="BF7" s="870" t="n"/>
+      <c r="BG7" s="870" t="n"/>
+      <c r="BH7" s="870" t="n"/>
+      <c r="BI7" s="870" t="n"/>
+      <c r="BJ7" s="870" t="n"/>
+      <c r="BK7" s="870" t="n"/>
+      <c r="BL7" s="870" t="n"/>
+      <c r="BM7" s="870" t="n"/>
+      <c r="BN7" s="870" t="n"/>
+      <c r="BO7" s="870" t="n"/>
+      <c r="BP7" s="870" t="n"/>
+      <c r="BQ7" s="870" t="n"/>
+      <c r="BR7" s="870" t="n"/>
+      <c r="BS7" s="870" t="n"/>
+      <c r="BT7" s="870" t="n"/>
+      <c r="BU7" s="870" t="n"/>
+      <c r="BV7" s="870" t="n"/>
+      <c r="BW7" s="870" t="n"/>
+      <c r="BX7" s="870" t="n"/>
+      <c r="BY7" s="870" t="n"/>
+      <c r="BZ7" s="870" t="n"/>
+      <c r="CA7" s="870" t="n"/>
+      <c r="CB7" s="870" t="n"/>
+      <c r="CC7" s="870" t="n"/>
+      <c r="CD7" s="870" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="788" t="inlineStr">
@@ -8631,7 +9049,7 @@
       <c r="CD10" s="280" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="822" t="inlineStr">
+      <c r="A11" s="790" t="inlineStr">
         <is>
           <t>CMM Program / Rev</t>
         </is>
@@ -8816,87 +9234,87 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="686" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n"/>
-      <c r="M13" s="10" t="n"/>
-      <c r="N13" s="10" t="n"/>
-      <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n"/>
-      <c r="T13" s="10" t="n"/>
-      <c r="U13" s="10" t="n"/>
-      <c r="V13" s="10" t="n"/>
-      <c r="W13" s="10" t="n"/>
-      <c r="X13" s="10" t="n"/>
-      <c r="Y13" s="10" t="n"/>
-      <c r="Z13" s="10" t="n"/>
-      <c r="AA13" s="10" t="n"/>
-      <c r="AB13" s="10" t="n"/>
-      <c r="AC13" s="10" t="n"/>
-      <c r="AD13" s="10" t="n"/>
-      <c r="AE13" s="10" t="n"/>
-      <c r="AF13" s="10" t="n"/>
-      <c r="AG13" s="10" t="n"/>
-      <c r="AH13" s="10" t="n"/>
-      <c r="AI13" s="10" t="n"/>
-      <c r="AJ13" s="10" t="n"/>
-      <c r="AK13" s="10" t="n"/>
-      <c r="AL13" s="10" t="n"/>
-      <c r="AM13" s="10" t="n"/>
-      <c r="AN13" s="10" t="n"/>
-      <c r="AO13" s="10" t="n"/>
-      <c r="AP13" s="10" t="n"/>
-      <c r="AQ13" s="10" t="n"/>
-      <c r="AR13" s="10" t="n"/>
-      <c r="AS13" s="10" t="n"/>
-      <c r="AT13" s="10" t="n"/>
-      <c r="AU13" s="10" t="n"/>
-      <c r="AV13" s="10" t="n"/>
-      <c r="AW13" s="10" t="n"/>
-      <c r="AX13" s="10" t="n"/>
-      <c r="AY13" s="10" t="n"/>
-      <c r="AZ13" s="10" t="n"/>
-      <c r="BA13" s="10" t="n"/>
-      <c r="BB13" s="10" t="n"/>
-      <c r="BC13" s="10" t="n"/>
-      <c r="BD13" s="10" t="n"/>
-      <c r="BE13" s="10" t="n"/>
-      <c r="BF13" s="10" t="n"/>
-      <c r="BG13" s="10" t="n"/>
-      <c r="BH13" s="10" t="n"/>
-      <c r="BI13" s="10" t="n"/>
-      <c r="BJ13" s="10" t="n"/>
-      <c r="BK13" s="10" t="n"/>
-      <c r="BL13" s="10" t="n"/>
-      <c r="BM13" s="10" t="n"/>
-      <c r="BN13" s="10" t="n"/>
-      <c r="BO13" s="10" t="n"/>
-      <c r="BP13" s="10" t="n"/>
-      <c r="BQ13" s="10" t="n"/>
-      <c r="BR13" s="10" t="n"/>
-      <c r="BS13" s="10" t="n"/>
-      <c r="BT13" s="10" t="n"/>
-      <c r="BU13" s="10" t="n"/>
-      <c r="BV13" s="10" t="n"/>
-      <c r="BW13" s="10" t="n"/>
-      <c r="BX13" s="10" t="n"/>
-      <c r="BY13" s="10" t="n"/>
-      <c r="BZ13" s="10" t="n"/>
-      <c r="CA13" s="10" t="n"/>
-      <c r="CB13" s="10" t="n"/>
-      <c r="CC13" s="10" t="n"/>
-      <c r="CD13" s="10" t="n"/>
+      <c r="B13" s="686" t="n"/>
+      <c r="C13" s="686" t="n"/>
+      <c r="D13" s="686" t="n"/>
+      <c r="E13" s="686" t="n"/>
+      <c r="F13" s="686" t="n"/>
+      <c r="G13" s="686" t="n"/>
+      <c r="H13" s="686" t="n"/>
+      <c r="I13" s="686" t="n"/>
+      <c r="J13" s="686" t="n"/>
+      <c r="K13" s="686" t="n"/>
+      <c r="L13" s="686" t="n"/>
+      <c r="M13" s="686" t="n"/>
+      <c r="N13" s="686" t="n"/>
+      <c r="O13" s="686" t="n"/>
+      <c r="P13" s="686" t="n"/>
+      <c r="Q13" s="686" t="n"/>
+      <c r="R13" s="686" t="n"/>
+      <c r="S13" s="686" t="n"/>
+      <c r="T13" s="686" t="n"/>
+      <c r="U13" s="686" t="n"/>
+      <c r="V13" s="686" t="n"/>
+      <c r="W13" s="686" t="n"/>
+      <c r="X13" s="686" t="n"/>
+      <c r="Y13" s="686" t="n"/>
+      <c r="Z13" s="686" t="n"/>
+      <c r="AA13" s="686" t="n"/>
+      <c r="AB13" s="686" t="n"/>
+      <c r="AC13" s="686" t="n"/>
+      <c r="AD13" s="686" t="n"/>
+      <c r="AE13" s="686" t="n"/>
+      <c r="AF13" s="686" t="n"/>
+      <c r="AG13" s="686" t="n"/>
+      <c r="AH13" s="686" t="n"/>
+      <c r="AI13" s="686" t="n"/>
+      <c r="AJ13" s="686" t="n"/>
+      <c r="AK13" s="686" t="n"/>
+      <c r="AL13" s="686" t="n"/>
+      <c r="AM13" s="686" t="n"/>
+      <c r="AN13" s="686" t="n"/>
+      <c r="AO13" s="686" t="n"/>
+      <c r="AP13" s="686" t="n"/>
+      <c r="AQ13" s="686" t="n"/>
+      <c r="AR13" s="686" t="n"/>
+      <c r="AS13" s="686" t="n"/>
+      <c r="AT13" s="686" t="n"/>
+      <c r="AU13" s="686" t="n"/>
+      <c r="AV13" s="686" t="n"/>
+      <c r="AW13" s="686" t="n"/>
+      <c r="AX13" s="686" t="n"/>
+      <c r="AY13" s="686" t="n"/>
+      <c r="AZ13" s="686" t="n"/>
+      <c r="BA13" s="686" t="n"/>
+      <c r="BB13" s="686" t="n"/>
+      <c r="BC13" s="686" t="n"/>
+      <c r="BD13" s="686" t="n"/>
+      <c r="BE13" s="686" t="n"/>
+      <c r="BF13" s="686" t="n"/>
+      <c r="BG13" s="686" t="n"/>
+      <c r="BH13" s="686" t="n"/>
+      <c r="BI13" s="686" t="n"/>
+      <c r="BJ13" s="686" t="n"/>
+      <c r="BK13" s="686" t="n"/>
+      <c r="BL13" s="686" t="n"/>
+      <c r="BM13" s="686" t="n"/>
+      <c r="BN13" s="686" t="n"/>
+      <c r="BO13" s="686" t="n"/>
+      <c r="BP13" s="686" t="n"/>
+      <c r="BQ13" s="686" t="n"/>
+      <c r="BR13" s="686" t="n"/>
+      <c r="BS13" s="686" t="n"/>
+      <c r="BT13" s="686" t="n"/>
+      <c r="BU13" s="686" t="n"/>
+      <c r="BV13" s="686" t="n"/>
+      <c r="BW13" s="686" t="n"/>
+      <c r="BX13" s="686" t="n"/>
+      <c r="BY13" s="686" t="n"/>
+      <c r="BZ13" s="686" t="n"/>
+      <c r="CA13" s="686" t="n"/>
+      <c r="CB13" s="686" t="n"/>
+      <c r="CC13" s="686" t="n"/>
+      <c r="CD13" s="686" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="787" t="inlineStr">
@@ -9263,7 +9681,7 @@
       <c r="CD17" s="280" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="823" t="inlineStr">
+      <c r="A18" s="792" t="inlineStr">
         <is>
           <t>Delta / Partial FAIR? Y/N</t>
         </is>
@@ -9356,87 +9774,87 @@
     </row>
     <row r="19" ht="3" customHeight="1">
       <c r="A19" s="686" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="10" t="n"/>
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="n"/>
-      <c r="AA19" s="10" t="n"/>
-      <c r="AB19" s="10" t="n"/>
-      <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="10" t="n"/>
-      <c r="AE19" s="10" t="n"/>
-      <c r="AF19" s="10" t="n"/>
-      <c r="AG19" s="10" t="n"/>
-      <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="10" t="n"/>
-      <c r="AJ19" s="10" t="n"/>
-      <c r="AK19" s="10" t="n"/>
-      <c r="AL19" s="10" t="n"/>
-      <c r="AM19" s="10" t="n"/>
-      <c r="AN19" s="10" t="n"/>
-      <c r="AO19" s="10" t="n"/>
-      <c r="AP19" s="10" t="n"/>
-      <c r="AQ19" s="10" t="n"/>
-      <c r="AR19" s="10" t="n"/>
-      <c r="AS19" s="10" t="n"/>
-      <c r="AT19" s="10" t="n"/>
-      <c r="AU19" s="10" t="n"/>
-      <c r="AV19" s="10" t="n"/>
-      <c r="AW19" s="10" t="n"/>
-      <c r="AX19" s="10" t="n"/>
-      <c r="AY19" s="10" t="n"/>
-      <c r="AZ19" s="10" t="n"/>
-      <c r="BA19" s="10" t="n"/>
-      <c r="BB19" s="10" t="n"/>
-      <c r="BC19" s="10" t="n"/>
-      <c r="BD19" s="10" t="n"/>
-      <c r="BE19" s="10" t="n"/>
-      <c r="BF19" s="10" t="n"/>
-      <c r="BG19" s="10" t="n"/>
-      <c r="BH19" s="10" t="n"/>
-      <c r="BI19" s="10" t="n"/>
-      <c r="BJ19" s="10" t="n"/>
-      <c r="BK19" s="10" t="n"/>
-      <c r="BL19" s="10" t="n"/>
-      <c r="BM19" s="10" t="n"/>
-      <c r="BN19" s="10" t="n"/>
-      <c r="BO19" s="10" t="n"/>
-      <c r="BP19" s="10" t="n"/>
-      <c r="BQ19" s="10" t="n"/>
-      <c r="BR19" s="10" t="n"/>
-      <c r="BS19" s="10" t="n"/>
-      <c r="BT19" s="10" t="n"/>
-      <c r="BU19" s="10" t="n"/>
-      <c r="BV19" s="10" t="n"/>
-      <c r="BW19" s="10" t="n"/>
-      <c r="BX19" s="10" t="n"/>
-      <c r="BY19" s="10" t="n"/>
-      <c r="BZ19" s="10" t="n"/>
-      <c r="CA19" s="10" t="n"/>
-      <c r="CB19" s="10" t="n"/>
-      <c r="CC19" s="10" t="n"/>
-      <c r="CD19" s="10" t="n"/>
+      <c r="B19" s="686" t="n"/>
+      <c r="C19" s="686" t="n"/>
+      <c r="D19" s="686" t="n"/>
+      <c r="E19" s="686" t="n"/>
+      <c r="F19" s="686" t="n"/>
+      <c r="G19" s="686" t="n"/>
+      <c r="H19" s="686" t="n"/>
+      <c r="I19" s="686" t="n"/>
+      <c r="J19" s="686" t="n"/>
+      <c r="K19" s="686" t="n"/>
+      <c r="L19" s="686" t="n"/>
+      <c r="M19" s="686" t="n"/>
+      <c r="N19" s="686" t="n"/>
+      <c r="O19" s="686" t="n"/>
+      <c r="P19" s="686" t="n"/>
+      <c r="Q19" s="686" t="n"/>
+      <c r="R19" s="686" t="n"/>
+      <c r="S19" s="686" t="n"/>
+      <c r="T19" s="686" t="n"/>
+      <c r="U19" s="686" t="n"/>
+      <c r="V19" s="686" t="n"/>
+      <c r="W19" s="686" t="n"/>
+      <c r="X19" s="686" t="n"/>
+      <c r="Y19" s="686" t="n"/>
+      <c r="Z19" s="686" t="n"/>
+      <c r="AA19" s="686" t="n"/>
+      <c r="AB19" s="686" t="n"/>
+      <c r="AC19" s="686" t="n"/>
+      <c r="AD19" s="686" t="n"/>
+      <c r="AE19" s="686" t="n"/>
+      <c r="AF19" s="686" t="n"/>
+      <c r="AG19" s="686" t="n"/>
+      <c r="AH19" s="686" t="n"/>
+      <c r="AI19" s="686" t="n"/>
+      <c r="AJ19" s="686" t="n"/>
+      <c r="AK19" s="686" t="n"/>
+      <c r="AL19" s="686" t="n"/>
+      <c r="AM19" s="686" t="n"/>
+      <c r="AN19" s="686" t="n"/>
+      <c r="AO19" s="686" t="n"/>
+      <c r="AP19" s="686" t="n"/>
+      <c r="AQ19" s="686" t="n"/>
+      <c r="AR19" s="686" t="n"/>
+      <c r="AS19" s="686" t="n"/>
+      <c r="AT19" s="686" t="n"/>
+      <c r="AU19" s="686" t="n"/>
+      <c r="AV19" s="686" t="n"/>
+      <c r="AW19" s="686" t="n"/>
+      <c r="AX19" s="686" t="n"/>
+      <c r="AY19" s="686" t="n"/>
+      <c r="AZ19" s="686" t="n"/>
+      <c r="BA19" s="686" t="n"/>
+      <c r="BB19" s="686" t="n"/>
+      <c r="BC19" s="686" t="n"/>
+      <c r="BD19" s="686" t="n"/>
+      <c r="BE19" s="686" t="n"/>
+      <c r="BF19" s="686" t="n"/>
+      <c r="BG19" s="686" t="n"/>
+      <c r="BH19" s="686" t="n"/>
+      <c r="BI19" s="686" t="n"/>
+      <c r="BJ19" s="686" t="n"/>
+      <c r="BK19" s="686" t="n"/>
+      <c r="BL19" s="686" t="n"/>
+      <c r="BM19" s="686" t="n"/>
+      <c r="BN19" s="686" t="n"/>
+      <c r="BO19" s="686" t="n"/>
+      <c r="BP19" s="686" t="n"/>
+      <c r="BQ19" s="686" t="n"/>
+      <c r="BR19" s="686" t="n"/>
+      <c r="BS19" s="686" t="n"/>
+      <c r="BT19" s="686" t="n"/>
+      <c r="BU19" s="686" t="n"/>
+      <c r="BV19" s="686" t="n"/>
+      <c r="BW19" s="686" t="n"/>
+      <c r="BX19" s="686" t="n"/>
+      <c r="BY19" s="686" t="n"/>
+      <c r="BZ19" s="686" t="n"/>
+      <c r="CA19" s="686" t="n"/>
+      <c r="CB19" s="686" t="n"/>
+      <c r="CC19" s="686" t="n"/>
+      <c r="CD19" s="686" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="787" t="inlineStr">
@@ -10620,87 +11038,87 @@
     </row>
     <row r="32" ht="3" customHeight="1">
       <c r="A32" s="686" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="10" t="n"/>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="10" t="n"/>
-      <c r="Q32" s="10" t="n"/>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="10" t="n"/>
-      <c r="T32" s="10" t="n"/>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="10" t="n"/>
-      <c r="Y32" s="10" t="n"/>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="10" t="n"/>
-      <c r="AF32" s="10" t="n"/>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="10" t="n"/>
-      <c r="AL32" s="10" t="n"/>
-      <c r="AM32" s="10" t="n"/>
-      <c r="AN32" s="10" t="n"/>
-      <c r="AO32" s="10" t="n"/>
-      <c r="AP32" s="10" t="n"/>
-      <c r="AQ32" s="10" t="n"/>
-      <c r="AR32" s="10" t="n"/>
-      <c r="AS32" s="10" t="n"/>
-      <c r="AT32" s="10" t="n"/>
-      <c r="AU32" s="10" t="n"/>
-      <c r="AV32" s="10" t="n"/>
-      <c r="AW32" s="10" t="n"/>
-      <c r="AX32" s="10" t="n"/>
-      <c r="AY32" s="10" t="n"/>
-      <c r="AZ32" s="10" t="n"/>
-      <c r="BA32" s="10" t="n"/>
-      <c r="BB32" s="10" t="n"/>
-      <c r="BC32" s="10" t="n"/>
-      <c r="BD32" s="10" t="n"/>
-      <c r="BE32" s="10" t="n"/>
-      <c r="BF32" s="10" t="n"/>
-      <c r="BG32" s="10" t="n"/>
-      <c r="BH32" s="10" t="n"/>
-      <c r="BI32" s="10" t="n"/>
-      <c r="BJ32" s="10" t="n"/>
-      <c r="BK32" s="10" t="n"/>
-      <c r="BL32" s="10" t="n"/>
-      <c r="BM32" s="10" t="n"/>
-      <c r="BN32" s="10" t="n"/>
-      <c r="BO32" s="10" t="n"/>
-      <c r="BP32" s="10" t="n"/>
-      <c r="BQ32" s="10" t="n"/>
-      <c r="BR32" s="10" t="n"/>
-      <c r="BS32" s="10" t="n"/>
-      <c r="BT32" s="10" t="n"/>
-      <c r="BU32" s="10" t="n"/>
-      <c r="BV32" s="10" t="n"/>
-      <c r="BW32" s="10" t="n"/>
-      <c r="BX32" s="10" t="n"/>
-      <c r="BY32" s="10" t="n"/>
-      <c r="BZ32" s="10" t="n"/>
-      <c r="CA32" s="10" t="n"/>
-      <c r="CB32" s="10" t="n"/>
-      <c r="CC32" s="10" t="n"/>
-      <c r="CD32" s="10" t="n"/>
+      <c r="B32" s="686" t="n"/>
+      <c r="C32" s="686" t="n"/>
+      <c r="D32" s="686" t="n"/>
+      <c r="E32" s="686" t="n"/>
+      <c r="F32" s="686" t="n"/>
+      <c r="G32" s="686" t="n"/>
+      <c r="H32" s="686" t="n"/>
+      <c r="I32" s="686" t="n"/>
+      <c r="J32" s="686" t="n"/>
+      <c r="K32" s="686" t="n"/>
+      <c r="L32" s="686" t="n"/>
+      <c r="M32" s="686" t="n"/>
+      <c r="N32" s="686" t="n"/>
+      <c r="O32" s="686" t="n"/>
+      <c r="P32" s="686" t="n"/>
+      <c r="Q32" s="686" t="n"/>
+      <c r="R32" s="686" t="n"/>
+      <c r="S32" s="686" t="n"/>
+      <c r="T32" s="686" t="n"/>
+      <c r="U32" s="686" t="n"/>
+      <c r="V32" s="686" t="n"/>
+      <c r="W32" s="686" t="n"/>
+      <c r="X32" s="686" t="n"/>
+      <c r="Y32" s="686" t="n"/>
+      <c r="Z32" s="686" t="n"/>
+      <c r="AA32" s="686" t="n"/>
+      <c r="AB32" s="686" t="n"/>
+      <c r="AC32" s="686" t="n"/>
+      <c r="AD32" s="686" t="n"/>
+      <c r="AE32" s="686" t="n"/>
+      <c r="AF32" s="686" t="n"/>
+      <c r="AG32" s="686" t="n"/>
+      <c r="AH32" s="686" t="n"/>
+      <c r="AI32" s="686" t="n"/>
+      <c r="AJ32" s="686" t="n"/>
+      <c r="AK32" s="686" t="n"/>
+      <c r="AL32" s="686" t="n"/>
+      <c r="AM32" s="686" t="n"/>
+      <c r="AN32" s="686" t="n"/>
+      <c r="AO32" s="686" t="n"/>
+      <c r="AP32" s="686" t="n"/>
+      <c r="AQ32" s="686" t="n"/>
+      <c r="AR32" s="686" t="n"/>
+      <c r="AS32" s="686" t="n"/>
+      <c r="AT32" s="686" t="n"/>
+      <c r="AU32" s="686" t="n"/>
+      <c r="AV32" s="686" t="n"/>
+      <c r="AW32" s="686" t="n"/>
+      <c r="AX32" s="686" t="n"/>
+      <c r="AY32" s="686" t="n"/>
+      <c r="AZ32" s="686" t="n"/>
+      <c r="BA32" s="686" t="n"/>
+      <c r="BB32" s="686" t="n"/>
+      <c r="BC32" s="686" t="n"/>
+      <c r="BD32" s="686" t="n"/>
+      <c r="BE32" s="686" t="n"/>
+      <c r="BF32" s="686" t="n"/>
+      <c r="BG32" s="686" t="n"/>
+      <c r="BH32" s="686" t="n"/>
+      <c r="BI32" s="686" t="n"/>
+      <c r="BJ32" s="686" t="n"/>
+      <c r="BK32" s="686" t="n"/>
+      <c r="BL32" s="686" t="n"/>
+      <c r="BM32" s="686" t="n"/>
+      <c r="BN32" s="686" t="n"/>
+      <c r="BO32" s="686" t="n"/>
+      <c r="BP32" s="686" t="n"/>
+      <c r="BQ32" s="686" t="n"/>
+      <c r="BR32" s="686" t="n"/>
+      <c r="BS32" s="686" t="n"/>
+      <c r="BT32" s="686" t="n"/>
+      <c r="BU32" s="686" t="n"/>
+      <c r="BV32" s="686" t="n"/>
+      <c r="BW32" s="686" t="n"/>
+      <c r="BX32" s="686" t="n"/>
+      <c r="BY32" s="686" t="n"/>
+      <c r="BZ32" s="686" t="n"/>
+      <c r="CA32" s="686" t="n"/>
+      <c r="CB32" s="686" t="n"/>
+      <c r="CC32" s="686" t="n"/>
+      <c r="CD32" s="686" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="787" t="inlineStr">
@@ -11334,87 +11752,87 @@
     </row>
     <row r="40" ht="3" customHeight="1">
       <c r="A40" s="686" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="10" t="n"/>
-      <c r="AL40" s="10" t="n"/>
-      <c r="AM40" s="10" t="n"/>
-      <c r="AN40" s="10" t="n"/>
-      <c r="AO40" s="10" t="n"/>
-      <c r="AP40" s="10" t="n"/>
-      <c r="AQ40" s="10" t="n"/>
-      <c r="AR40" s="10" t="n"/>
-      <c r="AS40" s="10" t="n"/>
-      <c r="AT40" s="10" t="n"/>
-      <c r="AU40" s="10" t="n"/>
-      <c r="AV40" s="10" t="n"/>
-      <c r="AW40" s="10" t="n"/>
-      <c r="AX40" s="10" t="n"/>
-      <c r="AY40" s="10" t="n"/>
-      <c r="AZ40" s="10" t="n"/>
-      <c r="BA40" s="10" t="n"/>
-      <c r="BB40" s="10" t="n"/>
-      <c r="BC40" s="10" t="n"/>
-      <c r="BD40" s="10" t="n"/>
-      <c r="BE40" s="10" t="n"/>
-      <c r="BF40" s="10" t="n"/>
-      <c r="BG40" s="10" t="n"/>
-      <c r="BH40" s="10" t="n"/>
-      <c r="BI40" s="10" t="n"/>
-      <c r="BJ40" s="10" t="n"/>
-      <c r="BK40" s="10" t="n"/>
-      <c r="BL40" s="10" t="n"/>
-      <c r="BM40" s="10" t="n"/>
-      <c r="BN40" s="10" t="n"/>
-      <c r="BO40" s="10" t="n"/>
-      <c r="BP40" s="10" t="n"/>
-      <c r="BQ40" s="10" t="n"/>
-      <c r="BR40" s="10" t="n"/>
-      <c r="BS40" s="10" t="n"/>
-      <c r="BT40" s="10" t="n"/>
-      <c r="BU40" s="10" t="n"/>
-      <c r="BV40" s="10" t="n"/>
-      <c r="BW40" s="10" t="n"/>
-      <c r="BX40" s="10" t="n"/>
-      <c r="BY40" s="10" t="n"/>
-      <c r="BZ40" s="10" t="n"/>
-      <c r="CA40" s="10" t="n"/>
-      <c r="CB40" s="10" t="n"/>
-      <c r="CC40" s="10" t="n"/>
-      <c r="CD40" s="10" t="n"/>
+      <c r="B40" s="686" t="n"/>
+      <c r="C40" s="686" t="n"/>
+      <c r="D40" s="686" t="n"/>
+      <c r="E40" s="686" t="n"/>
+      <c r="F40" s="686" t="n"/>
+      <c r="G40" s="686" t="n"/>
+      <c r="H40" s="686" t="n"/>
+      <c r="I40" s="686" t="n"/>
+      <c r="J40" s="686" t="n"/>
+      <c r="K40" s="686" t="n"/>
+      <c r="L40" s="686" t="n"/>
+      <c r="M40" s="686" t="n"/>
+      <c r="N40" s="686" t="n"/>
+      <c r="O40" s="686" t="n"/>
+      <c r="P40" s="686" t="n"/>
+      <c r="Q40" s="686" t="n"/>
+      <c r="R40" s="686" t="n"/>
+      <c r="S40" s="686" t="n"/>
+      <c r="T40" s="686" t="n"/>
+      <c r="U40" s="686" t="n"/>
+      <c r="V40" s="686" t="n"/>
+      <c r="W40" s="686" t="n"/>
+      <c r="X40" s="686" t="n"/>
+      <c r="Y40" s="686" t="n"/>
+      <c r="Z40" s="686" t="n"/>
+      <c r="AA40" s="686" t="n"/>
+      <c r="AB40" s="686" t="n"/>
+      <c r="AC40" s="686" t="n"/>
+      <c r="AD40" s="686" t="n"/>
+      <c r="AE40" s="686" t="n"/>
+      <c r="AF40" s="686" t="n"/>
+      <c r="AG40" s="686" t="n"/>
+      <c r="AH40" s="686" t="n"/>
+      <c r="AI40" s="686" t="n"/>
+      <c r="AJ40" s="686" t="n"/>
+      <c r="AK40" s="686" t="n"/>
+      <c r="AL40" s="686" t="n"/>
+      <c r="AM40" s="686" t="n"/>
+      <c r="AN40" s="686" t="n"/>
+      <c r="AO40" s="686" t="n"/>
+      <c r="AP40" s="686" t="n"/>
+      <c r="AQ40" s="686" t="n"/>
+      <c r="AR40" s="686" t="n"/>
+      <c r="AS40" s="686" t="n"/>
+      <c r="AT40" s="686" t="n"/>
+      <c r="AU40" s="686" t="n"/>
+      <c r="AV40" s="686" t="n"/>
+      <c r="AW40" s="686" t="n"/>
+      <c r="AX40" s="686" t="n"/>
+      <c r="AY40" s="686" t="n"/>
+      <c r="AZ40" s="686" t="n"/>
+      <c r="BA40" s="686" t="n"/>
+      <c r="BB40" s="686" t="n"/>
+      <c r="BC40" s="686" t="n"/>
+      <c r="BD40" s="686" t="n"/>
+      <c r="BE40" s="686" t="n"/>
+      <c r="BF40" s="686" t="n"/>
+      <c r="BG40" s="686" t="n"/>
+      <c r="BH40" s="686" t="n"/>
+      <c r="BI40" s="686" t="n"/>
+      <c r="BJ40" s="686" t="n"/>
+      <c r="BK40" s="686" t="n"/>
+      <c r="BL40" s="686" t="n"/>
+      <c r="BM40" s="686" t="n"/>
+      <c r="BN40" s="686" t="n"/>
+      <c r="BO40" s="686" t="n"/>
+      <c r="BP40" s="686" t="n"/>
+      <c r="BQ40" s="686" t="n"/>
+      <c r="BR40" s="686" t="n"/>
+      <c r="BS40" s="686" t="n"/>
+      <c r="BT40" s="686" t="n"/>
+      <c r="BU40" s="686" t="n"/>
+      <c r="BV40" s="686" t="n"/>
+      <c r="BW40" s="686" t="n"/>
+      <c r="BX40" s="686" t="n"/>
+      <c r="BY40" s="686" t="n"/>
+      <c r="BZ40" s="686" t="n"/>
+      <c r="CA40" s="686" t="n"/>
+      <c r="CB40" s="686" t="n"/>
+      <c r="CC40" s="686" t="n"/>
+      <c r="CD40" s="686" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="787" t="inlineStr">
@@ -11712,175 +12130,175 @@
     </row>
     <row r="46" ht="3" customHeight="1">
       <c r="A46" s="686" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="10" t="n"/>
-      <c r="AL46" s="10" t="n"/>
-      <c r="AM46" s="10" t="n"/>
-      <c r="AN46" s="10" t="n"/>
-      <c r="AO46" s="10" t="n"/>
-      <c r="AP46" s="10" t="n"/>
-      <c r="AQ46" s="10" t="n"/>
-      <c r="AR46" s="10" t="n"/>
-      <c r="AS46" s="10" t="n"/>
-      <c r="AT46" s="10" t="n"/>
-      <c r="AU46" s="10" t="n"/>
-      <c r="AV46" s="10" t="n"/>
-      <c r="AW46" s="10" t="n"/>
-      <c r="AX46" s="10" t="n"/>
-      <c r="AY46" s="10" t="n"/>
-      <c r="AZ46" s="10" t="n"/>
-      <c r="BA46" s="10" t="n"/>
-      <c r="BB46" s="10" t="n"/>
-      <c r="BC46" s="10" t="n"/>
-      <c r="BD46" s="10" t="n"/>
-      <c r="BE46" s="10" t="n"/>
-      <c r="BF46" s="10" t="n"/>
-      <c r="BG46" s="10" t="n"/>
-      <c r="BH46" s="10" t="n"/>
-      <c r="BI46" s="10" t="n"/>
-      <c r="BJ46" s="10" t="n"/>
-      <c r="BK46" s="10" t="n"/>
-      <c r="BL46" s="10" t="n"/>
-      <c r="BM46" s="10" t="n"/>
-      <c r="BN46" s="10" t="n"/>
-      <c r="BO46" s="10" t="n"/>
-      <c r="BP46" s="10" t="n"/>
-      <c r="BQ46" s="10" t="n"/>
-      <c r="BR46" s="10" t="n"/>
-      <c r="BS46" s="10" t="n"/>
-      <c r="BT46" s="10" t="n"/>
-      <c r="BU46" s="10" t="n"/>
-      <c r="BV46" s="10" t="n"/>
-      <c r="BW46" s="10" t="n"/>
-      <c r="BX46" s="10" t="n"/>
-      <c r="BY46" s="10" t="n"/>
-      <c r="BZ46" s="10" t="n"/>
-      <c r="CA46" s="10" t="n"/>
-      <c r="CB46" s="10" t="n"/>
-      <c r="CC46" s="10" t="n"/>
-      <c r="CD46" s="10" t="n"/>
+      <c r="B46" s="686" t="n"/>
+      <c r="C46" s="686" t="n"/>
+      <c r="D46" s="686" t="n"/>
+      <c r="E46" s="686" t="n"/>
+      <c r="F46" s="686" t="n"/>
+      <c r="G46" s="686" t="n"/>
+      <c r="H46" s="686" t="n"/>
+      <c r="I46" s="686" t="n"/>
+      <c r="J46" s="686" t="n"/>
+      <c r="K46" s="686" t="n"/>
+      <c r="L46" s="686" t="n"/>
+      <c r="M46" s="686" t="n"/>
+      <c r="N46" s="686" t="n"/>
+      <c r="O46" s="686" t="n"/>
+      <c r="P46" s="686" t="n"/>
+      <c r="Q46" s="686" t="n"/>
+      <c r="R46" s="686" t="n"/>
+      <c r="S46" s="686" t="n"/>
+      <c r="T46" s="686" t="n"/>
+      <c r="U46" s="686" t="n"/>
+      <c r="V46" s="686" t="n"/>
+      <c r="W46" s="686" t="n"/>
+      <c r="X46" s="686" t="n"/>
+      <c r="Y46" s="686" t="n"/>
+      <c r="Z46" s="686" t="n"/>
+      <c r="AA46" s="686" t="n"/>
+      <c r="AB46" s="686" t="n"/>
+      <c r="AC46" s="686" t="n"/>
+      <c r="AD46" s="686" t="n"/>
+      <c r="AE46" s="686" t="n"/>
+      <c r="AF46" s="686" t="n"/>
+      <c r="AG46" s="686" t="n"/>
+      <c r="AH46" s="686" t="n"/>
+      <c r="AI46" s="686" t="n"/>
+      <c r="AJ46" s="686" t="n"/>
+      <c r="AK46" s="686" t="n"/>
+      <c r="AL46" s="686" t="n"/>
+      <c r="AM46" s="686" t="n"/>
+      <c r="AN46" s="686" t="n"/>
+      <c r="AO46" s="686" t="n"/>
+      <c r="AP46" s="686" t="n"/>
+      <c r="AQ46" s="686" t="n"/>
+      <c r="AR46" s="686" t="n"/>
+      <c r="AS46" s="686" t="n"/>
+      <c r="AT46" s="686" t="n"/>
+      <c r="AU46" s="686" t="n"/>
+      <c r="AV46" s="686" t="n"/>
+      <c r="AW46" s="686" t="n"/>
+      <c r="AX46" s="686" t="n"/>
+      <c r="AY46" s="686" t="n"/>
+      <c r="AZ46" s="686" t="n"/>
+      <c r="BA46" s="686" t="n"/>
+      <c r="BB46" s="686" t="n"/>
+      <c r="BC46" s="686" t="n"/>
+      <c r="BD46" s="686" t="n"/>
+      <c r="BE46" s="686" t="n"/>
+      <c r="BF46" s="686" t="n"/>
+      <c r="BG46" s="686" t="n"/>
+      <c r="BH46" s="686" t="n"/>
+      <c r="BI46" s="686" t="n"/>
+      <c r="BJ46" s="686" t="n"/>
+      <c r="BK46" s="686" t="n"/>
+      <c r="BL46" s="686" t="n"/>
+      <c r="BM46" s="686" t="n"/>
+      <c r="BN46" s="686" t="n"/>
+      <c r="BO46" s="686" t="n"/>
+      <c r="BP46" s="686" t="n"/>
+      <c r="BQ46" s="686" t="n"/>
+      <c r="BR46" s="686" t="n"/>
+      <c r="BS46" s="686" t="n"/>
+      <c r="BT46" s="686" t="n"/>
+      <c r="BU46" s="686" t="n"/>
+      <c r="BV46" s="686" t="n"/>
+      <c r="BW46" s="686" t="n"/>
+      <c r="BX46" s="686" t="n"/>
+      <c r="BY46" s="686" t="n"/>
+      <c r="BZ46" s="686" t="n"/>
+      <c r="CA46" s="686" t="n"/>
+      <c r="CB46" s="686" t="n"/>
+      <c r="CC46" s="686" t="n"/>
+      <c r="CD46" s="686" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="819" t="inlineStr">
+      <c r="A47" s="382" t="inlineStr">
         <is>
           <t>NOTICE  —  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-311_[RECORDID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="820" t="n"/>
-      <c r="C47" s="820" t="n"/>
-      <c r="D47" s="820" t="n"/>
-      <c r="E47" s="820" t="n"/>
-      <c r="F47" s="820" t="n"/>
-      <c r="G47" s="820" t="n"/>
-      <c r="H47" s="820" t="n"/>
-      <c r="I47" s="820" t="n"/>
-      <c r="J47" s="820" t="n"/>
-      <c r="K47" s="820" t="n"/>
-      <c r="L47" s="820" t="n"/>
-      <c r="M47" s="820" t="n"/>
-      <c r="N47" s="820" t="n"/>
-      <c r="O47" s="820" t="n"/>
-      <c r="P47" s="820" t="n"/>
-      <c r="Q47" s="820" t="n"/>
-      <c r="R47" s="820" t="n"/>
-      <c r="S47" s="820" t="n"/>
-      <c r="T47" s="820" t="n"/>
-      <c r="U47" s="820" t="n"/>
-      <c r="V47" s="820" t="n"/>
-      <c r="W47" s="820" t="n"/>
-      <c r="X47" s="820" t="n"/>
-      <c r="Y47" s="820" t="n"/>
-      <c r="Z47" s="820" t="n"/>
-      <c r="AA47" s="820" t="n"/>
-      <c r="AB47" s="820" t="n"/>
-      <c r="AC47" s="820" t="n"/>
-      <c r="AD47" s="820" t="n"/>
-      <c r="AE47" s="820" t="n"/>
-      <c r="AF47" s="820" t="n"/>
-      <c r="AG47" s="820" t="n"/>
-      <c r="AH47" s="820" t="n"/>
-      <c r="AI47" s="820" t="n"/>
-      <c r="AJ47" s="820" t="n"/>
-      <c r="AK47" s="820" t="n"/>
-      <c r="AL47" s="820" t="n"/>
-      <c r="AM47" s="820" t="n"/>
-      <c r="AN47" s="820" t="n"/>
-      <c r="AO47" s="820" t="n"/>
-      <c r="AP47" s="820" t="n"/>
-      <c r="AQ47" s="820" t="n"/>
-      <c r="AR47" s="820" t="n"/>
-      <c r="AS47" s="820" t="n"/>
-      <c r="AT47" s="820" t="n"/>
-      <c r="AU47" s="820" t="n"/>
-      <c r="AV47" s="820" t="n"/>
-      <c r="AW47" s="820" t="n"/>
-      <c r="AX47" s="820" t="n"/>
-      <c r="AY47" s="820" t="n"/>
-      <c r="AZ47" s="820" t="n"/>
-      <c r="BA47" s="820" t="n"/>
-      <c r="BB47" s="820" t="n"/>
-      <c r="BC47" s="820" t="n"/>
-      <c r="BD47" s="820" t="n"/>
-      <c r="BE47" s="820" t="n"/>
-      <c r="BF47" s="820" t="n"/>
-      <c r="BG47" s="820" t="n"/>
-      <c r="BH47" s="820" t="n"/>
-      <c r="BI47" s="820" t="n"/>
-      <c r="BJ47" s="820" t="n"/>
-      <c r="BK47" s="820" t="n"/>
-      <c r="BL47" s="820" t="n"/>
-      <c r="BM47" s="820" t="n"/>
-      <c r="BN47" s="820" t="n"/>
-      <c r="BO47" s="820" t="n"/>
-      <c r="BP47" s="820" t="n"/>
-      <c r="BQ47" s="820" t="n"/>
-      <c r="BR47" s="820" t="n"/>
-      <c r="BS47" s="820" t="n"/>
-      <c r="BT47" s="820" t="n"/>
-      <c r="BU47" s="820" t="n"/>
-      <c r="BV47" s="820" t="n"/>
-      <c r="BW47" s="820" t="n"/>
-      <c r="BX47" s="820" t="n"/>
-      <c r="BY47" s="820" t="n"/>
-      <c r="BZ47" s="820" t="n"/>
-      <c r="CA47" s="820" t="n"/>
-      <c r="CB47" s="820" t="n"/>
-      <c r="CC47" s="820" t="n"/>
-      <c r="CD47" s="821" t="n"/>
+      <c r="B47" s="383" t="n"/>
+      <c r="C47" s="383" t="n"/>
+      <c r="D47" s="383" t="n"/>
+      <c r="E47" s="383" t="n"/>
+      <c r="F47" s="383" t="n"/>
+      <c r="G47" s="383" t="n"/>
+      <c r="H47" s="383" t="n"/>
+      <c r="I47" s="383" t="n"/>
+      <c r="J47" s="383" t="n"/>
+      <c r="K47" s="383" t="n"/>
+      <c r="L47" s="383" t="n"/>
+      <c r="M47" s="383" t="n"/>
+      <c r="N47" s="383" t="n"/>
+      <c r="O47" s="383" t="n"/>
+      <c r="P47" s="383" t="n"/>
+      <c r="Q47" s="383" t="n"/>
+      <c r="R47" s="383" t="n"/>
+      <c r="S47" s="383" t="n"/>
+      <c r="T47" s="383" t="n"/>
+      <c r="U47" s="383" t="n"/>
+      <c r="V47" s="383" t="n"/>
+      <c r="W47" s="383" t="n"/>
+      <c r="X47" s="383" t="n"/>
+      <c r="Y47" s="383" t="n"/>
+      <c r="Z47" s="383" t="n"/>
+      <c r="AA47" s="383" t="n"/>
+      <c r="AB47" s="383" t="n"/>
+      <c r="AC47" s="383" t="n"/>
+      <c r="AD47" s="383" t="n"/>
+      <c r="AE47" s="383" t="n"/>
+      <c r="AF47" s="383" t="n"/>
+      <c r="AG47" s="383" t="n"/>
+      <c r="AH47" s="383" t="n"/>
+      <c r="AI47" s="383" t="n"/>
+      <c r="AJ47" s="383" t="n"/>
+      <c r="AK47" s="383" t="n"/>
+      <c r="AL47" s="383" t="n"/>
+      <c r="AM47" s="383" t="n"/>
+      <c r="AN47" s="383" t="n"/>
+      <c r="AO47" s="383" t="n"/>
+      <c r="AP47" s="383" t="n"/>
+      <c r="AQ47" s="383" t="n"/>
+      <c r="AR47" s="383" t="n"/>
+      <c r="AS47" s="383" t="n"/>
+      <c r="AT47" s="383" t="n"/>
+      <c r="AU47" s="383" t="n"/>
+      <c r="AV47" s="383" t="n"/>
+      <c r="AW47" s="383" t="n"/>
+      <c r="AX47" s="383" t="n"/>
+      <c r="AY47" s="383" t="n"/>
+      <c r="AZ47" s="383" t="n"/>
+      <c r="BA47" s="383" t="n"/>
+      <c r="BB47" s="383" t="n"/>
+      <c r="BC47" s="383" t="n"/>
+      <c r="BD47" s="383" t="n"/>
+      <c r="BE47" s="383" t="n"/>
+      <c r="BF47" s="383" t="n"/>
+      <c r="BG47" s="383" t="n"/>
+      <c r="BH47" s="383" t="n"/>
+      <c r="BI47" s="383" t="n"/>
+      <c r="BJ47" s="383" t="n"/>
+      <c r="BK47" s="383" t="n"/>
+      <c r="BL47" s="383" t="n"/>
+      <c r="BM47" s="383" t="n"/>
+      <c r="BN47" s="383" t="n"/>
+      <c r="BO47" s="383" t="n"/>
+      <c r="BP47" s="383" t="n"/>
+      <c r="BQ47" s="383" t="n"/>
+      <c r="BR47" s="383" t="n"/>
+      <c r="BS47" s="383" t="n"/>
+      <c r="BT47" s="383" t="n"/>
+      <c r="BU47" s="383" t="n"/>
+      <c r="BV47" s="383" t="n"/>
+      <c r="BW47" s="383" t="n"/>
+      <c r="BX47" s="383" t="n"/>
+      <c r="BY47" s="383" t="n"/>
+      <c r="BZ47" s="383" t="n"/>
+      <c r="CA47" s="383" t="n"/>
+      <c r="CB47" s="383" t="n"/>
+      <c r="CC47" s="383" t="n"/>
+      <c r="CD47" s="384" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -12336,367 +12754,351 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="827" t="n"/>
-      <c r="B1" s="828" t="n"/>
-      <c r="C1" s="828" t="n"/>
-      <c r="D1" s="828" t="n"/>
-      <c r="E1" s="828" t="n"/>
-      <c r="F1" s="828" t="n"/>
-      <c r="G1" s="828" t="n"/>
-      <c r="H1" s="829" t="n"/>
-      <c r="I1" s="830" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="871" t="n"/>
+      <c r="B1" s="775" t="n"/>
+      <c r="C1" s="775" t="n"/>
+      <c r="D1" s="775" t="n"/>
+      <c r="E1" s="775" t="n"/>
+      <c r="F1" s="775" t="n"/>
+      <c r="G1" s="775" t="n"/>
+      <c r="H1" s="872" t="n"/>
+      <c r="I1" s="873" t="inlineStr">
         <is>
           <t>FAI REPORT</t>
         </is>
       </c>
-      <c r="J1" s="828" t="n"/>
-      <c r="K1" s="828" t="n"/>
-      <c r="L1" s="828" t="n"/>
-      <c r="M1" s="828" t="n"/>
-      <c r="N1" s="828" t="n"/>
-      <c r="O1" s="828" t="n"/>
-      <c r="P1" s="828" t="n"/>
-      <c r="Q1" s="828" t="n"/>
-      <c r="R1" s="828" t="n"/>
-      <c r="S1" s="828" t="n"/>
-      <c r="T1" s="828" t="n"/>
-      <c r="U1" s="828" t="n"/>
-      <c r="V1" s="828" t="n"/>
-      <c r="W1" s="828" t="n"/>
-      <c r="X1" s="828" t="n"/>
-      <c r="Y1" s="828" t="n"/>
-      <c r="Z1" s="828" t="n"/>
-      <c r="AA1" s="828" t="n"/>
-      <c r="AB1" s="828" t="n"/>
-      <c r="AC1" s="828" t="n"/>
-      <c r="AD1" s="829" t="n"/>
-      <c r="AE1" s="518" t="inlineStr">
+      <c r="J1" s="775" t="n"/>
+      <c r="K1" s="775" t="n"/>
+      <c r="L1" s="775" t="n"/>
+      <c r="M1" s="775" t="n"/>
+      <c r="N1" s="775" t="n"/>
+      <c r="O1" s="775" t="n"/>
+      <c r="P1" s="775" t="n"/>
+      <c r="Q1" s="775" t="n"/>
+      <c r="R1" s="775" t="n"/>
+      <c r="S1" s="775" t="n"/>
+      <c r="T1" s="775" t="n"/>
+      <c r="U1" s="775" t="n"/>
+      <c r="V1" s="775" t="n"/>
+      <c r="W1" s="775" t="n"/>
+      <c r="X1" s="775" t="n"/>
+      <c r="Y1" s="775" t="n"/>
+      <c r="Z1" s="775" t="n"/>
+      <c r="AA1" s="775" t="n"/>
+      <c r="AB1" s="775" t="n"/>
+      <c r="AC1" s="775" t="n"/>
+      <c r="AD1" s="872" t="n"/>
+      <c r="AE1" s="519" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="828" t="n"/>
-      <c r="AG1" s="828" t="n"/>
-      <c r="AH1" s="831" t="n"/>
-      <c r="AI1" s="521" t="inlineStr">
+      <c r="AF1" s="775" t="n"/>
+      <c r="AG1" s="775" t="n"/>
+      <c r="AH1" s="874" t="n"/>
+      <c r="AI1" s="522" t="inlineStr">
         <is>
           <t>FRM-311</t>
         </is>
       </c>
-      <c r="AJ1" s="828" t="n"/>
-      <c r="AK1" s="828" t="n"/>
-      <c r="AL1" s="828" t="n"/>
-      <c r="AM1" s="828" t="n"/>
-      <c r="AN1" s="829" t="n"/>
+      <c r="AJ1" s="775" t="n"/>
+      <c r="AK1" s="775" t="n"/>
+      <c r="AL1" s="775" t="n"/>
+      <c r="AM1" s="775" t="n"/>
+      <c r="AN1" s="872" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="832" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="833" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="833" t="n"/>
-      <c r="AE2" s="834" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="847" t="n"/>
+      <c r="C2" s="847" t="n"/>
+      <c r="D2" s="847" t="n"/>
+      <c r="E2" s="847" t="n"/>
+      <c r="F2" s="847" t="n"/>
+      <c r="G2" s="847" t="n"/>
+      <c r="H2" s="848" t="n"/>
+      <c r="I2" s="847" t="n"/>
+      <c r="J2" s="847" t="n"/>
+      <c r="K2" s="847" t="n"/>
+      <c r="L2" s="847" t="n"/>
+      <c r="M2" s="847" t="n"/>
+      <c r="N2" s="847" t="n"/>
+      <c r="O2" s="847" t="n"/>
+      <c r="P2" s="847" t="n"/>
+      <c r="Q2" s="847" t="n"/>
+      <c r="R2" s="847" t="n"/>
+      <c r="S2" s="847" t="n"/>
+      <c r="T2" s="847" t="n"/>
+      <c r="U2" s="847" t="n"/>
+      <c r="V2" s="847" t="n"/>
+      <c r="W2" s="847" t="n"/>
+      <c r="X2" s="847" t="n"/>
+      <c r="Y2" s="847" t="n"/>
+      <c r="Z2" s="847" t="n"/>
+      <c r="AA2" s="847" t="n"/>
+      <c r="AB2" s="847" t="n"/>
+      <c r="AC2" s="847" t="n"/>
+      <c r="AD2" s="848" t="n"/>
+      <c r="AE2" s="849" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="835" t="n"/>
-      <c r="AI2" s="836" t="inlineStr">
+      <c r="AF2" s="850" t="n"/>
+      <c r="AG2" s="850" t="n"/>
+      <c r="AH2" s="851" t="n"/>
+      <c r="AI2" s="852" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="833" t="n"/>
+      <c r="AJ2" s="853" t="n"/>
+      <c r="AK2" s="853" t="n"/>
+      <c r="AL2" s="853" t="n"/>
+      <c r="AM2" s="853" t="n"/>
+      <c r="AN2" s="854" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="832" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="833" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="833" t="n"/>
-      <c r="AE3" s="834" t="inlineStr">
+      <c r="A3" s="855" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="856" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="856" t="n"/>
+      <c r="AE3" s="857" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="835" t="n"/>
-      <c r="AI3" s="836" t="inlineStr">
+      <c r="AF3" s="858" t="n"/>
+      <c r="AG3" s="858" t="n"/>
+      <c r="AH3" s="859" t="n"/>
+      <c r="AI3" s="741" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="833" t="n"/>
+      <c r="AJ3" s="860" t="n"/>
+      <c r="AK3" s="860" t="n"/>
+      <c r="AL3" s="860" t="n"/>
+      <c r="AM3" s="860" t="n"/>
+      <c r="AN3" s="861" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="832" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="833" t="n"/>
-      <c r="I4" s="837" t="inlineStr">
+      <c r="A4" s="855" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="856" t="n"/>
+      <c r="I4" s="354" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="833" t="n"/>
-      <c r="AE4" s="834" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="856" t="n"/>
+      <c r="AE4" s="857" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="835" t="n"/>
-      <c r="AI4" s="836" t="inlineStr">
+      <c r="AF4" s="858" t="n"/>
+      <c r="AG4" s="858" t="n"/>
+      <c r="AH4" s="859" t="n"/>
+      <c r="AI4" s="741" t="inlineStr">
         <is>
           <t>QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="833" t="n"/>
+      <c r="AJ4" s="860" t="n"/>
+      <c r="AK4" s="860" t="n"/>
+      <c r="AL4" s="860" t="n"/>
+      <c r="AM4" s="860" t="n"/>
+      <c r="AN4" s="861" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="838" t="n"/>
-      <c r="B5" s="839" t="n"/>
-      <c r="C5" s="839" t="n"/>
-      <c r="D5" s="839" t="n"/>
-      <c r="E5" s="839" t="n"/>
-      <c r="F5" s="839" t="n"/>
-      <c r="G5" s="839" t="n"/>
-      <c r="H5" s="840" t="n"/>
-      <c r="I5" s="841" t="inlineStr">
+      <c r="A5" s="855" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="856" t="n"/>
+      <c r="I5" s="610" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="839" t="n"/>
-      <c r="K5" s="839" t="n"/>
-      <c r="L5" s="839" t="n"/>
-      <c r="M5" s="839" t="n"/>
-      <c r="N5" s="839" t="n"/>
-      <c r="O5" s="839" t="n"/>
-      <c r="P5" s="839" t="n"/>
-      <c r="Q5" s="839" t="n"/>
-      <c r="R5" s="839" t="n"/>
-      <c r="S5" s="839" t="n"/>
-      <c r="T5" s="839" t="n"/>
-      <c r="U5" s="839" t="n"/>
-      <c r="V5" s="839" t="n"/>
-      <c r="W5" s="839" t="n"/>
-      <c r="X5" s="839" t="n"/>
-      <c r="Y5" s="839" t="n"/>
-      <c r="Z5" s="839" t="n"/>
-      <c r="AA5" s="839" t="n"/>
-      <c r="AB5" s="839" t="n"/>
-      <c r="AC5" s="839" t="n"/>
-      <c r="AD5" s="840" t="n"/>
-      <c r="AE5" s="842" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="856" t="n"/>
+      <c r="AE5" s="857" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="839" t="n"/>
-      <c r="AG5" s="839" t="n"/>
-      <c r="AH5" s="843" t="n"/>
-      <c r="AI5" s="844" t="inlineStr">
+      <c r="AF5" s="858" t="n"/>
+      <c r="AG5" s="858" t="n"/>
+      <c r="AH5" s="859" t="n"/>
+      <c r="AI5" s="741" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="839" t="n"/>
-      <c r="AK5" s="839" t="n"/>
-      <c r="AL5" s="839" t="n"/>
-      <c r="AM5" s="839" t="n"/>
-      <c r="AN5" s="840" t="n"/>
+      <c r="AJ5" s="860" t="n"/>
+      <c r="AK5" s="860" t="n"/>
+      <c r="AL5" s="860" t="n"/>
+      <c r="AM5" s="860" t="n"/>
+      <c r="AN5" s="861" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="845" t="n"/>
-      <c r="B6" s="845" t="n"/>
-      <c r="C6" s="845" t="n"/>
-      <c r="D6" s="845" t="n"/>
-      <c r="E6" s="845" t="n"/>
-      <c r="F6" s="845" t="n"/>
-      <c r="G6" s="845" t="n"/>
-      <c r="H6" s="845" t="n"/>
-      <c r="I6" s="845" t="n"/>
-      <c r="J6" s="845" t="n"/>
-      <c r="K6" s="845" t="n"/>
-      <c r="L6" s="845" t="n"/>
-      <c r="M6" s="845" t="n"/>
-      <c r="N6" s="845" t="n"/>
-      <c r="O6" s="845" t="n"/>
-      <c r="P6" s="845" t="n"/>
-      <c r="Q6" s="845" t="n"/>
-      <c r="R6" s="845" t="n"/>
-      <c r="S6" s="845" t="n"/>
-      <c r="T6" s="845" t="n"/>
-      <c r="U6" s="845" t="n"/>
-      <c r="V6" s="845" t="n"/>
-      <c r="W6" s="845" t="n"/>
-      <c r="X6" s="845" t="n"/>
-      <c r="Y6" s="845" t="n"/>
-      <c r="Z6" s="845" t="n"/>
-      <c r="AA6" s="845" t="n"/>
-      <c r="AB6" s="845" t="n"/>
-      <c r="AC6" s="845" t="n"/>
-      <c r="AD6" s="845" t="n"/>
-      <c r="AE6" s="845" t="n"/>
-      <c r="AF6" s="845" t="n"/>
-      <c r="AG6" s="845" t="n"/>
-      <c r="AH6" s="845" t="n"/>
-      <c r="AI6" s="845" t="n"/>
-      <c r="AJ6" s="845" t="n"/>
-      <c r="AK6" s="845" t="n"/>
-      <c r="AL6" s="845" t="n"/>
-      <c r="AM6" s="845" t="n"/>
-      <c r="AN6" s="845" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="875" t="n"/>
+      <c r="B6" s="876" t="n"/>
+      <c r="C6" s="876" t="n"/>
+      <c r="D6" s="876" t="n"/>
+      <c r="E6" s="876" t="n"/>
+      <c r="F6" s="876" t="n"/>
+      <c r="G6" s="876" t="n"/>
+      <c r="H6" s="877" t="n"/>
+      <c r="I6" s="876" t="n"/>
+      <c r="J6" s="876" t="n"/>
+      <c r="K6" s="876" t="n"/>
+      <c r="L6" s="876" t="n"/>
+      <c r="M6" s="876" t="n"/>
+      <c r="N6" s="876" t="n"/>
+      <c r="O6" s="876" t="n"/>
+      <c r="P6" s="876" t="n"/>
+      <c r="Q6" s="876" t="n"/>
+      <c r="R6" s="876" t="n"/>
+      <c r="S6" s="876" t="n"/>
+      <c r="T6" s="876" t="n"/>
+      <c r="U6" s="876" t="n"/>
+      <c r="V6" s="876" t="n"/>
+      <c r="W6" s="876" t="n"/>
+      <c r="X6" s="876" t="n"/>
+      <c r="Y6" s="876" t="n"/>
+      <c r="Z6" s="876" t="n"/>
+      <c r="AA6" s="876" t="n"/>
+      <c r="AB6" s="876" t="n"/>
+      <c r="AC6" s="876" t="n"/>
+      <c r="AD6" s="877" t="n"/>
+      <c r="AE6" s="878" t="n"/>
+      <c r="AF6" s="878" t="n"/>
+      <c r="AG6" s="878" t="n"/>
+      <c r="AH6" s="879" t="n"/>
+      <c r="AI6" s="880" t="n"/>
+      <c r="AJ6" s="880" t="n"/>
+      <c r="AK6" s="880" t="n"/>
+      <c r="AL6" s="880" t="n"/>
+      <c r="AM6" s="880" t="n"/>
+      <c r="AN6" s="881" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="414" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="B7" s="414" t="inlineStr">
-        <is>
-          <t>VAL_ESCALATION_LEVEL</t>
-        </is>
-      </c>
-      <c r="C7" s="414" t="inlineStr">
-        <is>
-          <t>VAL_RESULT_CORE</t>
-        </is>
-      </c>
-      <c r="D7" s="414" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="E7" s="846" t="n"/>
-      <c r="F7" s="846" t="n"/>
-      <c r="G7" s="846" t="n"/>
-      <c r="H7" s="846" t="n"/>
-      <c r="I7" s="846" t="n"/>
-      <c r="J7" s="846" t="n"/>
-      <c r="K7" s="846" t="n"/>
-      <c r="L7" s="846" t="n"/>
-      <c r="M7" s="846" t="n"/>
-      <c r="N7" s="846" t="n"/>
-      <c r="O7" s="846" t="n"/>
-      <c r="P7" s="846" t="n"/>
-      <c r="Q7" s="846" t="n"/>
-      <c r="R7" s="846" t="n"/>
-      <c r="S7" s="846" t="n"/>
-      <c r="T7" s="846" t="n"/>
-      <c r="U7" s="846" t="n"/>
-      <c r="V7" s="846" t="n"/>
-      <c r="W7" s="846" t="n"/>
-      <c r="X7" s="846" t="n"/>
-      <c r="Y7" s="846" t="n"/>
-      <c r="Z7" s="846" t="n"/>
-      <c r="AA7" s="846" t="n"/>
-      <c r="AB7" s="846" t="n"/>
-      <c r="AC7" s="846" t="n"/>
-      <c r="AD7" s="846" t="n"/>
-      <c r="AE7" s="846" t="n"/>
-      <c r="AF7" s="846" t="n"/>
-      <c r="AG7" s="846" t="n"/>
-      <c r="AH7" s="846" t="n"/>
-      <c r="AI7" s="846" t="n"/>
-      <c r="AJ7" s="846" t="n"/>
-      <c r="AK7" s="846" t="n"/>
-      <c r="AL7" s="846" t="n"/>
-      <c r="AM7" s="846" t="n"/>
-      <c r="AN7" s="846" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="882" t="n"/>
+      <c r="B7" s="882" t="n"/>
+      <c r="C7" s="882" t="n"/>
+      <c r="D7" s="882" t="n"/>
+      <c r="E7" s="883" t="n"/>
+      <c r="F7" s="883" t="n"/>
+      <c r="G7" s="883" t="n"/>
+      <c r="H7" s="883" t="n"/>
+      <c r="I7" s="883" t="n"/>
+      <c r="J7" s="883" t="n"/>
+      <c r="K7" s="883" t="n"/>
+      <c r="L7" s="883" t="n"/>
+      <c r="M7" s="883" t="n"/>
+      <c r="N7" s="883" t="n"/>
+      <c r="O7" s="883" t="n"/>
+      <c r="P7" s="883" t="n"/>
+      <c r="Q7" s="883" t="n"/>
+      <c r="R7" s="883" t="n"/>
+      <c r="S7" s="883" t="n"/>
+      <c r="T7" s="883" t="n"/>
+      <c r="U7" s="883" t="n"/>
+      <c r="V7" s="883" t="n"/>
+      <c r="W7" s="883" t="n"/>
+      <c r="X7" s="883" t="n"/>
+      <c r="Y7" s="883" t="n"/>
+      <c r="Z7" s="883" t="n"/>
+      <c r="AA7" s="883" t="n"/>
+      <c r="AB7" s="883" t="n"/>
+      <c r="AC7" s="883" t="n"/>
+      <c r="AD7" s="883" t="n"/>
+      <c r="AE7" s="883" t="n"/>
+      <c r="AF7" s="883" t="n"/>
+      <c r="AG7" s="883" t="n"/>
+      <c r="AH7" s="883" t="n"/>
+      <c r="AI7" s="883" t="n"/>
+      <c r="AJ7" s="883" t="n"/>
+      <c r="AK7" s="883" t="n"/>
+      <c r="AL7" s="883" t="n"/>
+      <c r="AM7" s="883" t="n"/>
+      <c r="AN7" s="883" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="414" t="inlineStr">
@@ -13355,6 +13757,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13409,403 +13812,379 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="827" t="n"/>
-      <c r="B1" s="828" t="n"/>
-      <c r="C1" s="828" t="n"/>
-      <c r="D1" s="828" t="n"/>
-      <c r="E1" s="828" t="n"/>
-      <c r="F1" s="828" t="n"/>
-      <c r="G1" s="828" t="n"/>
-      <c r="H1" s="829" t="n"/>
-      <c r="I1" s="830" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="871" t="n"/>
+      <c r="B1" s="775" t="n"/>
+      <c r="C1" s="775" t="n"/>
+      <c r="D1" s="775" t="n"/>
+      <c r="E1" s="775" t="n"/>
+      <c r="F1" s="775" t="n"/>
+      <c r="G1" s="775" t="n"/>
+      <c r="H1" s="872" t="n"/>
+      <c r="I1" s="873" t="inlineStr">
         <is>
           <t>FAI REPORT</t>
         </is>
       </c>
-      <c r="J1" s="828" t="n"/>
-      <c r="K1" s="828" t="n"/>
-      <c r="L1" s="828" t="n"/>
-      <c r="M1" s="828" t="n"/>
-      <c r="N1" s="828" t="n"/>
-      <c r="O1" s="828" t="n"/>
-      <c r="P1" s="828" t="n"/>
-      <c r="Q1" s="828" t="n"/>
-      <c r="R1" s="828" t="n"/>
-      <c r="S1" s="828" t="n"/>
-      <c r="T1" s="828" t="n"/>
-      <c r="U1" s="828" t="n"/>
-      <c r="V1" s="828" t="n"/>
-      <c r="W1" s="828" t="n"/>
-      <c r="X1" s="828" t="n"/>
-      <c r="Y1" s="828" t="n"/>
-      <c r="Z1" s="828" t="n"/>
-      <c r="AA1" s="828" t="n"/>
-      <c r="AB1" s="828" t="n"/>
-      <c r="AC1" s="828" t="n"/>
-      <c r="AD1" s="829" t="n"/>
-      <c r="AE1" s="518" t="inlineStr">
+      <c r="J1" s="775" t="n"/>
+      <c r="K1" s="775" t="n"/>
+      <c r="L1" s="775" t="n"/>
+      <c r="M1" s="775" t="n"/>
+      <c r="N1" s="775" t="n"/>
+      <c r="O1" s="775" t="n"/>
+      <c r="P1" s="775" t="n"/>
+      <c r="Q1" s="775" t="n"/>
+      <c r="R1" s="775" t="n"/>
+      <c r="S1" s="775" t="n"/>
+      <c r="T1" s="775" t="n"/>
+      <c r="U1" s="775" t="n"/>
+      <c r="V1" s="775" t="n"/>
+      <c r="W1" s="775" t="n"/>
+      <c r="X1" s="775" t="n"/>
+      <c r="Y1" s="775" t="n"/>
+      <c r="Z1" s="775" t="n"/>
+      <c r="AA1" s="775" t="n"/>
+      <c r="AB1" s="775" t="n"/>
+      <c r="AC1" s="775" t="n"/>
+      <c r="AD1" s="872" t="n"/>
+      <c r="AE1" s="519" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="828" t="n"/>
-      <c r="AG1" s="828" t="n"/>
-      <c r="AH1" s="831" t="n"/>
-      <c r="AI1" s="521" t="inlineStr">
+      <c r="AF1" s="775" t="n"/>
+      <c r="AG1" s="775" t="n"/>
+      <c r="AH1" s="874" t="n"/>
+      <c r="AI1" s="522" t="inlineStr">
         <is>
           <t>FRM-311</t>
         </is>
       </c>
-      <c r="AJ1" s="828" t="n"/>
-      <c r="AK1" s="828" t="n"/>
-      <c r="AL1" s="828" t="n"/>
-      <c r="AM1" s="828" t="n"/>
-      <c r="AN1" s="829" t="n"/>
+      <c r="AJ1" s="775" t="n"/>
+      <c r="AK1" s="775" t="n"/>
+      <c r="AL1" s="775" t="n"/>
+      <c r="AM1" s="775" t="n"/>
+      <c r="AN1" s="872" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="832" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="833" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="833" t="n"/>
-      <c r="AE2" s="834" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="847" t="n"/>
+      <c r="C2" s="847" t="n"/>
+      <c r="D2" s="847" t="n"/>
+      <c r="E2" s="847" t="n"/>
+      <c r="F2" s="847" t="n"/>
+      <c r="G2" s="847" t="n"/>
+      <c r="H2" s="848" t="n"/>
+      <c r="I2" s="847" t="n"/>
+      <c r="J2" s="847" t="n"/>
+      <c r="K2" s="847" t="n"/>
+      <c r="L2" s="847" t="n"/>
+      <c r="M2" s="847" t="n"/>
+      <c r="N2" s="847" t="n"/>
+      <c r="O2" s="847" t="n"/>
+      <c r="P2" s="847" t="n"/>
+      <c r="Q2" s="847" t="n"/>
+      <c r="R2" s="847" t="n"/>
+      <c r="S2" s="847" t="n"/>
+      <c r="T2" s="847" t="n"/>
+      <c r="U2" s="847" t="n"/>
+      <c r="V2" s="847" t="n"/>
+      <c r="W2" s="847" t="n"/>
+      <c r="X2" s="847" t="n"/>
+      <c r="Y2" s="847" t="n"/>
+      <c r="Z2" s="847" t="n"/>
+      <c r="AA2" s="847" t="n"/>
+      <c r="AB2" s="847" t="n"/>
+      <c r="AC2" s="847" t="n"/>
+      <c r="AD2" s="848" t="n"/>
+      <c r="AE2" s="849" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="835" t="n"/>
-      <c r="AI2" s="836" t="inlineStr">
+      <c r="AF2" s="850" t="n"/>
+      <c r="AG2" s="850" t="n"/>
+      <c r="AH2" s="851" t="n"/>
+      <c r="AI2" s="852" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="833" t="n"/>
+      <c r="AJ2" s="853" t="n"/>
+      <c r="AK2" s="853" t="n"/>
+      <c r="AL2" s="853" t="n"/>
+      <c r="AM2" s="853" t="n"/>
+      <c r="AN2" s="854" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="832" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="833" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="833" t="n"/>
-      <c r="AE3" s="834" t="inlineStr">
+      <c r="A3" s="855" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="856" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="856" t="n"/>
+      <c r="AE3" s="857" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="835" t="n"/>
-      <c r="AI3" s="836" t="inlineStr">
+      <c r="AF3" s="858" t="n"/>
+      <c r="AG3" s="858" t="n"/>
+      <c r="AH3" s="859" t="n"/>
+      <c r="AI3" s="741" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="833" t="n"/>
+      <c r="AJ3" s="860" t="n"/>
+      <c r="AK3" s="860" t="n"/>
+      <c r="AL3" s="860" t="n"/>
+      <c r="AM3" s="860" t="n"/>
+      <c r="AN3" s="861" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="832" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="833" t="n"/>
-      <c r="I4" s="837" t="inlineStr">
+      <c r="A4" s="855" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="856" t="n"/>
+      <c r="I4" s="354" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="833" t="n"/>
-      <c r="AE4" s="834" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="856" t="n"/>
+      <c r="AE4" s="857" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="835" t="n"/>
-      <c r="AI4" s="836" t="inlineStr">
+      <c r="AF4" s="858" t="n"/>
+      <c r="AG4" s="858" t="n"/>
+      <c r="AH4" s="859" t="n"/>
+      <c r="AI4" s="741" t="inlineStr">
         <is>
           <t>QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="833" t="n"/>
+      <c r="AJ4" s="860" t="n"/>
+      <c r="AK4" s="860" t="n"/>
+      <c r="AL4" s="860" t="n"/>
+      <c r="AM4" s="860" t="n"/>
+      <c r="AN4" s="861" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="838" t="n"/>
-      <c r="B5" s="839" t="n"/>
-      <c r="C5" s="839" t="n"/>
-      <c r="D5" s="839" t="n"/>
-      <c r="E5" s="839" t="n"/>
-      <c r="F5" s="839" t="n"/>
-      <c r="G5" s="839" t="n"/>
-      <c r="H5" s="840" t="n"/>
-      <c r="I5" s="841" t="inlineStr">
+      <c r="A5" s="855" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="856" t="n"/>
+      <c r="I5" s="610" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="839" t="n"/>
-      <c r="K5" s="839" t="n"/>
-      <c r="L5" s="839" t="n"/>
-      <c r="M5" s="839" t="n"/>
-      <c r="N5" s="839" t="n"/>
-      <c r="O5" s="839" t="n"/>
-      <c r="P5" s="839" t="n"/>
-      <c r="Q5" s="839" t="n"/>
-      <c r="R5" s="839" t="n"/>
-      <c r="S5" s="839" t="n"/>
-      <c r="T5" s="839" t="n"/>
-      <c r="U5" s="839" t="n"/>
-      <c r="V5" s="839" t="n"/>
-      <c r="W5" s="839" t="n"/>
-      <c r="X5" s="839" t="n"/>
-      <c r="Y5" s="839" t="n"/>
-      <c r="Z5" s="839" t="n"/>
-      <c r="AA5" s="839" t="n"/>
-      <c r="AB5" s="839" t="n"/>
-      <c r="AC5" s="839" t="n"/>
-      <c r="AD5" s="840" t="n"/>
-      <c r="AE5" s="842" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="856" t="n"/>
+      <c r="AE5" s="857" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="839" t="n"/>
-      <c r="AG5" s="839" t="n"/>
-      <c r="AH5" s="843" t="n"/>
-      <c r="AI5" s="844" t="inlineStr">
+      <c r="AF5" s="858" t="n"/>
+      <c r="AG5" s="858" t="n"/>
+      <c r="AH5" s="859" t="n"/>
+      <c r="AI5" s="741" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="839" t="n"/>
-      <c r="AK5" s="839" t="n"/>
-      <c r="AL5" s="839" t="n"/>
-      <c r="AM5" s="839" t="n"/>
-      <c r="AN5" s="840" t="n"/>
+      <c r="AJ5" s="860" t="n"/>
+      <c r="AK5" s="860" t="n"/>
+      <c r="AL5" s="860" t="n"/>
+      <c r="AM5" s="860" t="n"/>
+      <c r="AN5" s="861" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="845" t="n"/>
-      <c r="B6" s="845" t="n"/>
-      <c r="C6" s="845" t="n"/>
-      <c r="D6" s="845" t="n"/>
-      <c r="E6" s="845" t="n"/>
-      <c r="F6" s="845" t="n"/>
-      <c r="G6" s="845" t="n"/>
-      <c r="H6" s="845" t="n"/>
-      <c r="I6" s="845" t="n"/>
-      <c r="J6" s="845" t="n"/>
-      <c r="K6" s="845" t="n"/>
-      <c r="L6" s="845" t="n"/>
-      <c r="M6" s="845" t="n"/>
-      <c r="N6" s="845" t="n"/>
-      <c r="O6" s="845" t="n"/>
-      <c r="P6" s="845" t="n"/>
-      <c r="Q6" s="845" t="n"/>
-      <c r="R6" s="845" t="n"/>
-      <c r="S6" s="845" t="n"/>
-      <c r="T6" s="845" t="n"/>
-      <c r="U6" s="845" t="n"/>
-      <c r="V6" s="845" t="n"/>
-      <c r="W6" s="845" t="n"/>
-      <c r="X6" s="845" t="n"/>
-      <c r="Y6" s="845" t="n"/>
-      <c r="Z6" s="845" t="n"/>
-      <c r="AA6" s="845" t="n"/>
-      <c r="AB6" s="845" t="n"/>
-      <c r="AC6" s="845" t="n"/>
-      <c r="AD6" s="845" t="n"/>
-      <c r="AE6" s="845" t="n"/>
-      <c r="AF6" s="845" t="n"/>
-      <c r="AG6" s="845" t="n"/>
-      <c r="AH6" s="845" t="n"/>
-      <c r="AI6" s="845" t="n"/>
-      <c r="AJ6" s="845" t="n"/>
-      <c r="AK6" s="845" t="n"/>
-      <c r="AL6" s="845" t="n"/>
-      <c r="AM6" s="845" t="n"/>
-      <c r="AN6" s="845" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="875" t="n"/>
+      <c r="B6" s="876" t="n"/>
+      <c r="C6" s="876" t="n"/>
+      <c r="D6" s="876" t="n"/>
+      <c r="E6" s="876" t="n"/>
+      <c r="F6" s="876" t="n"/>
+      <c r="G6" s="876" t="n"/>
+      <c r="H6" s="877" t="n"/>
+      <c r="I6" s="876" t="n"/>
+      <c r="J6" s="876" t="n"/>
+      <c r="K6" s="876" t="n"/>
+      <c r="L6" s="876" t="n"/>
+      <c r="M6" s="876" t="n"/>
+      <c r="N6" s="876" t="n"/>
+      <c r="O6" s="876" t="n"/>
+      <c r="P6" s="876" t="n"/>
+      <c r="Q6" s="876" t="n"/>
+      <c r="R6" s="876" t="n"/>
+      <c r="S6" s="876" t="n"/>
+      <c r="T6" s="876" t="n"/>
+      <c r="U6" s="876" t="n"/>
+      <c r="V6" s="876" t="n"/>
+      <c r="W6" s="876" t="n"/>
+      <c r="X6" s="876" t="n"/>
+      <c r="Y6" s="876" t="n"/>
+      <c r="Z6" s="876" t="n"/>
+      <c r="AA6" s="876" t="n"/>
+      <c r="AB6" s="876" t="n"/>
+      <c r="AC6" s="876" t="n"/>
+      <c r="AD6" s="877" t="n"/>
+      <c r="AE6" s="878" t="n"/>
+      <c r="AF6" s="878" t="n"/>
+      <c r="AG6" s="878" t="n"/>
+      <c r="AH6" s="879" t="n"/>
+      <c r="AI6" s="880" t="n"/>
+      <c r="AJ6" s="880" t="n"/>
+      <c r="AK6" s="880" t="n"/>
+      <c r="AL6" s="880" t="n"/>
+      <c r="AM6" s="880" t="n"/>
+      <c r="AN6" s="881" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="604" t="inlineStr">
-        <is>
-          <t>REF_EVIDENCE_LINK</t>
-        </is>
-      </c>
-      <c r="B7" s="554" t="inlineStr">
-        <is>
-          <t>REF_GAGE_MASTER</t>
-        </is>
-      </c>
-      <c r="C7" s="554" t="inlineStr">
-        <is>
-          <t>REF_JOB_WO_MASTER</t>
-        </is>
-      </c>
-      <c r="D7" s="554" t="inlineStr">
-        <is>
-          <t>REF_MACHINE_WC_MASTER</t>
-        </is>
-      </c>
-      <c r="E7" s="554" t="inlineStr">
-        <is>
-          <t>REF_OWNER_PERSON_MASTER</t>
-        </is>
-      </c>
-      <c r="F7" s="554" t="inlineStr">
-        <is>
-          <t>REF_PART_REV_MASTER</t>
-        </is>
-      </c>
-      <c r="G7" s="846" t="n"/>
-      <c r="H7" s="846" t="n"/>
-      <c r="I7" s="846" t="n"/>
-      <c r="J7" s="846" t="n"/>
-      <c r="K7" s="846" t="n"/>
-      <c r="L7" s="846" t="n"/>
-      <c r="M7" s="846" t="n"/>
-      <c r="N7" s="846" t="n"/>
-      <c r="O7" s="846" t="n"/>
-      <c r="P7" s="846" t="n"/>
-      <c r="Q7" s="846" t="n"/>
-      <c r="R7" s="846" t="n"/>
-      <c r="S7" s="846" t="n"/>
-      <c r="T7" s="846" t="n"/>
-      <c r="U7" s="846" t="n"/>
-      <c r="V7" s="846" t="n"/>
-      <c r="W7" s="846" t="n"/>
-      <c r="X7" s="846" t="n"/>
-      <c r="Y7" s="846" t="n"/>
-      <c r="Z7" s="846" t="n"/>
-      <c r="AA7" s="846" t="n"/>
-      <c r="AB7" s="846" t="n"/>
-      <c r="AC7" s="846" t="n"/>
-      <c r="AD7" s="846" t="n"/>
-      <c r="AE7" s="846" t="n"/>
-      <c r="AF7" s="846" t="n"/>
-      <c r="AG7" s="846" t="n"/>
-      <c r="AH7" s="846" t="n"/>
-      <c r="AI7" s="846" t="n"/>
-      <c r="AJ7" s="846" t="n"/>
-      <c r="AK7" s="846" t="n"/>
-      <c r="AL7" s="846" t="n"/>
-      <c r="AM7" s="846" t="n"/>
-      <c r="AN7" s="846" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="882" t="n"/>
+      <c r="B7" s="882" t="n"/>
+      <c r="C7" s="882" t="n"/>
+      <c r="D7" s="882" t="n"/>
+      <c r="E7" s="882" t="n"/>
+      <c r="F7" s="882" t="n"/>
+      <c r="G7" s="883" t="n"/>
+      <c r="H7" s="883" t="n"/>
+      <c r="I7" s="883" t="n"/>
+      <c r="J7" s="883" t="n"/>
+      <c r="K7" s="883" t="n"/>
+      <c r="L7" s="883" t="n"/>
+      <c r="M7" s="883" t="n"/>
+      <c r="N7" s="883" t="n"/>
+      <c r="O7" s="883" t="n"/>
+      <c r="P7" s="883" t="n"/>
+      <c r="Q7" s="883" t="n"/>
+      <c r="R7" s="883" t="n"/>
+      <c r="S7" s="883" t="n"/>
+      <c r="T7" s="883" t="n"/>
+      <c r="U7" s="883" t="n"/>
+      <c r="V7" s="883" t="n"/>
+      <c r="W7" s="883" t="n"/>
+      <c r="X7" s="883" t="n"/>
+      <c r="Y7" s="883" t="n"/>
+      <c r="Z7" s="883" t="n"/>
+      <c r="AA7" s="883" t="n"/>
+      <c r="AB7" s="883" t="n"/>
+      <c r="AC7" s="883" t="n"/>
+      <c r="AD7" s="883" t="n"/>
+      <c r="AE7" s="883" t="n"/>
+      <c r="AF7" s="883" t="n"/>
+      <c r="AG7" s="883" t="n"/>
+      <c r="AH7" s="883" t="n"/>
+      <c r="AI7" s="883" t="n"/>
+      <c r="AJ7" s="883" t="n"/>
+      <c r="AK7" s="883" t="n"/>
+      <c r="AL7" s="883" t="n"/>
+      <c r="AM7" s="883" t="n"/>
+      <c r="AN7" s="883" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="600" t="inlineStr">
+      <c r="A8" s="884" t="inlineStr">
         <is>
           <t>M365://dossier/JOB-240001</t>
         </is>
       </c>
-      <c r="B8" s="410" t="inlineStr">
+      <c r="B8" s="885" t="inlineStr">
         <is>
           <t>GAGE-001</t>
         </is>
       </c>
-      <c r="C8" s="410" t="inlineStr">
+      <c r="C8" s="885" t="inlineStr">
         <is>
           <t>JOB-240001</t>
         </is>
       </c>
-      <c r="D8" s="410" t="inlineStr">
+      <c r="D8" s="885" t="inlineStr">
         <is>
           <t>WC-3AX-01</t>
         </is>
       </c>
-      <c r="E8" s="410" t="inlineStr">
+      <c r="E8" s="885" t="inlineStr">
         <is>
           <t>Planning Lead</t>
         </is>
       </c>
-      <c r="F8" s="410" t="inlineStr">
+      <c r="F8" s="885" t="inlineStr">
         <is>
           <t>PN-1001 / Rev.A</t>
         </is>
@@ -13846,32 +14225,32 @@
       <c r="AN8" s="846" t="n"/>
     </row>
     <row r="9" hidden="1">
-      <c r="A9" s="600" t="inlineStr">
+      <c r="A9" s="884" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-202/001</t>
         </is>
       </c>
-      <c r="B9" s="410" t="inlineStr">
+      <c r="B9" s="885" t="inlineStr">
         <is>
           <t>GAGE-002</t>
         </is>
       </c>
-      <c r="C9" s="410" t="inlineStr">
+      <c r="C9" s="885" t="inlineStr">
         <is>
           <t>JOB-240002</t>
         </is>
       </c>
-      <c r="D9" s="410" t="inlineStr">
+      <c r="D9" s="885" t="inlineStr">
         <is>
           <t>WC-5AX-02</t>
         </is>
       </c>
-      <c r="E9" s="410" t="inlineStr">
+      <c r="E9" s="885" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="F9" s="410" t="inlineStr">
+      <c r="F9" s="885" t="inlineStr">
         <is>
           <t>PN-1002 / Rev.B</t>
         </is>
@@ -13912,32 +14291,32 @@
       <c r="AN9" s="846" t="n"/>
     </row>
     <row r="10" hidden="1">
-      <c r="A10" s="600" t="inlineStr">
+      <c r="A10" s="884" t="inlineStr">
         <is>
           <t>SP://evidence/FRM-306/002</t>
         </is>
       </c>
-      <c r="B10" s="410" t="inlineStr">
+      <c r="B10" s="885" t="inlineStr">
         <is>
           <t>CMM-001</t>
         </is>
       </c>
-      <c r="C10" s="410" t="inlineStr">
+      <c r="C10" s="885" t="inlineStr">
         <is>
           <t>JOB-240003</t>
         </is>
       </c>
-      <c r="D10" s="410" t="inlineStr">
+      <c r="D10" s="885" t="inlineStr">
         <is>
           <t>CELL-TURN-01</t>
         </is>
       </c>
-      <c r="E10" s="410" t="inlineStr">
+      <c r="E10" s="885" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="F10" s="410" t="inlineStr">
+      <c r="F10" s="885" t="inlineStr">
         <is>
           <t>PN-1003 / Rev.C</t>
         </is>
@@ -13978,32 +14357,32 @@
       <c r="AN10" s="846" t="n"/>
     </row>
     <row r="11" hidden="1">
-      <c r="A11" s="600" t="inlineStr">
+      <c r="A11" s="884" t="inlineStr">
         <is>
           <t>Epicor://Job/JOB-240001</t>
         </is>
       </c>
-      <c r="B11" s="410" t="inlineStr">
+      <c r="B11" s="885" t="inlineStr">
         <is>
           <t>MIC-025</t>
         </is>
       </c>
-      <c r="C11" s="410" t="inlineStr">
+      <c r="C11" s="885" t="inlineStr">
         <is>
           <t>JOB-240004</t>
         </is>
       </c>
-      <c r="D11" s="410" t="inlineStr">
+      <c r="D11" s="885" t="inlineStr">
         <is>
           <t>FIN-01</t>
         </is>
       </c>
-      <c r="E11" s="410" t="inlineStr">
+      <c r="E11" s="885" t="inlineStr">
         <is>
           <t>Engineering Lead</t>
         </is>
       </c>
-      <c r="F11" s="410" t="inlineStr">
+      <c r="F11" s="885" t="inlineStr">
         <is>
           <t>PN-1004 / Rev.D</t>
         </is>
@@ -14047,12 +14426,12 @@
       <c r="A12" s="846" t="n"/>
       <c r="B12" s="846" t="n"/>
       <c r="C12" s="846" t="n"/>
-      <c r="D12" s="410" t="inlineStr">
+      <c r="D12" s="885" t="inlineStr">
         <is>
           <t>GRIND-01</t>
         </is>
       </c>
-      <c r="E12" s="410" t="inlineStr">
+      <c r="E12" s="885" t="inlineStr">
         <is>
           <t>Setup Technician</t>
         </is>
@@ -14098,7 +14477,7 @@
       <c r="B13" s="846" t="n"/>
       <c r="C13" s="846" t="n"/>
       <c r="D13" s="846" t="n"/>
-      <c r="E13" s="410" t="inlineStr">
+      <c r="E13" s="885" t="inlineStr">
         <is>
           <t>Maintenance Lead</t>
         </is>
@@ -14144,7 +14523,7 @@
       <c r="B14" s="846" t="n"/>
       <c r="C14" s="846" t="n"/>
       <c r="D14" s="846" t="n"/>
-      <c r="E14" s="606" t="inlineStr">
+      <c r="E14" s="886" t="inlineStr">
         <is>
           <t>Commercial Owner</t>
         </is>
@@ -14513,6 +14892,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14567,10 +14947,10 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="399" t="n"/>
       <c r="B1" s="325" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="911" t="inlineStr">
         <is>
           <t>CHARACTERISTIC RESULTS</t>
         </is>
@@ -14579,7 +14959,7 @@
       <c r="E1" s="268" t="n"/>
       <c r="F1" s="268" t="n"/>
       <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
+      <c r="H1" s="325" t="n"/>
       <c r="I1" s="716" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -14622,277 +15002,288 @@
       <c r="AN1" s="719" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="326" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="I2" s="720" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="847" t="n"/>
+      <c r="C2" s="847" t="n"/>
+      <c r="D2" s="847" t="n"/>
+      <c r="E2" s="847" t="n"/>
+      <c r="F2" s="847" t="n"/>
+      <c r="G2" s="847" t="n"/>
+      <c r="H2" s="848" t="n"/>
+      <c r="I2" s="347" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="J2" s="721" t="inlineStr">
+      <c r="J2" s="347" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="K2" s="721" t="n"/>
-      <c r="L2" s="721" t="n"/>
-      <c r="M2" s="721" t="n"/>
-      <c r="N2" s="721" t="n"/>
-      <c r="O2" s="721" t="n"/>
-      <c r="P2" s="721" t="n"/>
-      <c r="Q2" s="721" t="n"/>
-      <c r="R2" s="721" t="n"/>
-      <c r="S2" s="721" t="n"/>
-      <c r="T2" s="721" t="n"/>
-      <c r="U2" s="721" t="n"/>
-      <c r="V2" s="721" t="n"/>
-      <c r="W2" s="721" t="n"/>
-      <c r="X2" s="721" t="n"/>
-      <c r="Y2" s="721" t="n"/>
-      <c r="Z2" s="721" t="n"/>
-      <c r="AA2" s="721" t="n"/>
-      <c r="AB2" s="721" t="n"/>
-      <c r="AC2" s="721" t="n"/>
-      <c r="AD2" s="721" t="n"/>
-      <c r="AE2" s="722" t="n"/>
-      <c r="AF2" s="722" t="n"/>
-      <c r="AG2" s="722" t="n"/>
-      <c r="AH2" s="722" t="n"/>
-      <c r="AI2" s="670" t="n"/>
-      <c r="AJ2" s="670" t="n"/>
-      <c r="AK2" s="670" t="n"/>
-      <c r="AL2" s="670" t="n"/>
-      <c r="AM2" s="670" t="n"/>
-      <c r="AN2" s="723" t="n"/>
+      <c r="K2" s="717" t="n"/>
+      <c r="L2" s="717" t="n"/>
+      <c r="M2" s="717" t="n"/>
+      <c r="N2" s="717" t="n"/>
+      <c r="O2" s="717" t="n"/>
+      <c r="P2" s="717" t="n"/>
+      <c r="Q2" s="717" t="n"/>
+      <c r="R2" s="717" t="n"/>
+      <c r="S2" s="717" t="n"/>
+      <c r="T2" s="717" t="n"/>
+      <c r="U2" s="717" t="n"/>
+      <c r="V2" s="717" t="n"/>
+      <c r="W2" s="717" t="n"/>
+      <c r="X2" s="717" t="n"/>
+      <c r="Y2" s="717" t="n"/>
+      <c r="Z2" s="717" t="n"/>
+      <c r="AA2" s="717" t="n"/>
+      <c r="AB2" s="717" t="n"/>
+      <c r="AC2" s="717" t="n"/>
+      <c r="AD2" s="887" t="n"/>
+      <c r="AE2" s="888" t="n"/>
+      <c r="AF2" s="888" t="n"/>
+      <c r="AG2" s="888" t="n"/>
+      <c r="AH2" s="889" t="n"/>
+      <c r="AI2" s="890" t="n"/>
+      <c r="AJ2" s="890" t="n"/>
+      <c r="AK2" s="890" t="n"/>
+      <c r="AL2" s="890" t="n"/>
+      <c r="AM2" s="890" t="n"/>
+      <c r="AN2" s="891" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="326" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="I3" s="720" t="inlineStr">
+      <c r="A3" s="855" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="856" t="n"/>
+      <c r="I3" s="354" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="J3" s="721" t="inlineStr">
+      <c r="J3" s="354" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="K3" s="721" t="n"/>
-      <c r="L3" s="721" t="n"/>
-      <c r="M3" s="721" t="n"/>
-      <c r="N3" s="721" t="n"/>
-      <c r="O3" s="721" t="n"/>
-      <c r="P3" s="721" t="n"/>
-      <c r="Q3" s="721" t="n"/>
-      <c r="R3" s="721" t="n"/>
-      <c r="S3" s="721" t="n"/>
-      <c r="T3" s="721" t="n"/>
-      <c r="U3" s="721" t="n"/>
-      <c r="V3" s="721" t="n"/>
-      <c r="W3" s="721" t="n"/>
-      <c r="X3" s="721" t="n"/>
-      <c r="Y3" s="721" t="n"/>
-      <c r="Z3" s="721" t="n"/>
-      <c r="AA3" s="721" t="n"/>
-      <c r="AB3" s="721" t="n"/>
-      <c r="AC3" s="721" t="n"/>
-      <c r="AD3" s="721" t="n"/>
-      <c r="AE3" s="722" t="n"/>
-      <c r="AF3" s="722" t="n"/>
-      <c r="AG3" s="722" t="n"/>
-      <c r="AH3" s="722" t="n"/>
-      <c r="AI3" s="670" t="n"/>
-      <c r="AJ3" s="670" t="n"/>
-      <c r="AK3" s="670" t="n"/>
-      <c r="AL3" s="670" t="n"/>
-      <c r="AM3" s="670" t="n"/>
-      <c r="AN3" s="723" t="n"/>
+      <c r="K3" s="892" t="n"/>
+      <c r="L3" s="892" t="n"/>
+      <c r="M3" s="892" t="n"/>
+      <c r="N3" s="892" t="n"/>
+      <c r="O3" s="892" t="n"/>
+      <c r="P3" s="892" t="n"/>
+      <c r="Q3" s="892" t="n"/>
+      <c r="R3" s="892" t="n"/>
+      <c r="S3" s="892" t="n"/>
+      <c r="T3" s="892" t="n"/>
+      <c r="U3" s="892" t="n"/>
+      <c r="V3" s="892" t="n"/>
+      <c r="W3" s="892" t="n"/>
+      <c r="X3" s="892" t="n"/>
+      <c r="Y3" s="892" t="n"/>
+      <c r="Z3" s="892" t="n"/>
+      <c r="AA3" s="892" t="n"/>
+      <c r="AB3" s="892" t="n"/>
+      <c r="AC3" s="892" t="n"/>
+      <c r="AD3" s="893" t="n"/>
+      <c r="AE3" s="894" t="n"/>
+      <c r="AF3" s="894" t="n"/>
+      <c r="AG3" s="894" t="n"/>
+      <c r="AH3" s="895" t="n"/>
+      <c r="AI3" s="896" t="n"/>
+      <c r="AJ3" s="896" t="n"/>
+      <c r="AK3" s="896" t="n"/>
+      <c r="AL3" s="896" t="n"/>
+      <c r="AM3" s="896" t="n"/>
+      <c r="AN3" s="897" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="326" t="n"/>
-      <c r="C4" s="724" t="inlineStr">
+      <c r="A4" s="855" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="610" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="I4" s="725" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="856" t="n"/>
+      <c r="I4" s="354" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="726" t="inlineStr"/>
-      <c r="K4" s="726" t="n"/>
-      <c r="L4" s="726" t="n"/>
-      <c r="M4" s="726" t="n"/>
-      <c r="N4" s="726" t="n"/>
-      <c r="O4" s="726" t="n"/>
-      <c r="P4" s="726" t="n"/>
-      <c r="Q4" s="726" t="n"/>
-      <c r="R4" s="726" t="n"/>
-      <c r="S4" s="726" t="n"/>
-      <c r="T4" s="726" t="n"/>
-      <c r="U4" s="726" t="n"/>
-      <c r="V4" s="726" t="n"/>
-      <c r="W4" s="726" t="n"/>
-      <c r="X4" s="726" t="n"/>
-      <c r="Y4" s="726" t="n"/>
-      <c r="Z4" s="726" t="n"/>
-      <c r="AA4" s="726" t="n"/>
-      <c r="AB4" s="726" t="n"/>
-      <c r="AC4" s="726" t="n"/>
-      <c r="AD4" s="726" t="n"/>
-      <c r="AE4" s="722" t="n"/>
-      <c r="AF4" s="722" t="n"/>
-      <c r="AG4" s="722" t="n"/>
-      <c r="AH4" s="722" t="n"/>
-      <c r="AI4" s="670" t="n"/>
-      <c r="AJ4" s="670" t="n"/>
-      <c r="AK4" s="670" t="n"/>
-      <c r="AL4" s="670" t="n"/>
-      <c r="AM4" s="670" t="n"/>
-      <c r="AN4" s="723" t="n"/>
+      <c r="J4" s="535" t="inlineStr"/>
+      <c r="K4" s="535" t="n"/>
+      <c r="L4" s="535" t="n"/>
+      <c r="M4" s="535" t="n"/>
+      <c r="N4" s="535" t="n"/>
+      <c r="O4" s="535" t="n"/>
+      <c r="P4" s="535" t="n"/>
+      <c r="Q4" s="535" t="n"/>
+      <c r="R4" s="535" t="n"/>
+      <c r="S4" s="535" t="n"/>
+      <c r="T4" s="535" t="n"/>
+      <c r="U4" s="535" t="n"/>
+      <c r="V4" s="535" t="n"/>
+      <c r="W4" s="535" t="n"/>
+      <c r="X4" s="535" t="n"/>
+      <c r="Y4" s="535" t="n"/>
+      <c r="Z4" s="535" t="n"/>
+      <c r="AA4" s="535" t="n"/>
+      <c r="AB4" s="535" t="n"/>
+      <c r="AC4" s="535" t="n"/>
+      <c r="AD4" s="898" t="n"/>
+      <c r="AE4" s="894" t="n"/>
+      <c r="AF4" s="894" t="n"/>
+      <c r="AG4" s="894" t="n"/>
+      <c r="AH4" s="895" t="n"/>
+      <c r="AI4" s="896" t="n"/>
+      <c r="AJ4" s="896" t="n"/>
+      <c r="AK4" s="896" t="n"/>
+      <c r="AL4" s="896" t="n"/>
+      <c r="AM4" s="896" t="n"/>
+      <c r="AN4" s="897" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="727" t="inlineStr">
+      <c r="A5" s="855" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="899" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="283" t="n"/>
-      <c r="I5" s="728" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="856" t="n"/>
+      <c r="I5" s="610" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="729" t="inlineStr"/>
-      <c r="K5" s="729" t="n"/>
-      <c r="L5" s="729" t="n"/>
-      <c r="M5" s="729" t="n"/>
-      <c r="N5" s="729" t="n"/>
-      <c r="O5" s="729" t="n"/>
-      <c r="P5" s="729" t="n"/>
-      <c r="Q5" s="729" t="n"/>
-      <c r="R5" s="729" t="n"/>
-      <c r="S5" s="729" t="n"/>
-      <c r="T5" s="729" t="n"/>
-      <c r="U5" s="729" t="n"/>
-      <c r="V5" s="729" t="n"/>
-      <c r="W5" s="729" t="n"/>
-      <c r="X5" s="729" t="n"/>
-      <c r="Y5" s="729" t="n"/>
-      <c r="Z5" s="729" t="n"/>
-      <c r="AA5" s="729" t="n"/>
-      <c r="AB5" s="729" t="n"/>
-      <c r="AC5" s="729" t="n"/>
-      <c r="AD5" s="729" t="n"/>
-      <c r="AE5" s="730" t="n"/>
-      <c r="AF5" s="730" t="n"/>
-      <c r="AG5" s="730" t="n"/>
-      <c r="AH5" s="730" t="n"/>
-      <c r="AI5" s="676" t="n"/>
-      <c r="AJ5" s="676" t="n"/>
-      <c r="AK5" s="676" t="n"/>
-      <c r="AL5" s="676" t="n"/>
-      <c r="AM5" s="676" t="n"/>
-      <c r="AN5" s="731" t="n"/>
+      <c r="J5" s="900" t="inlineStr"/>
+      <c r="K5" s="900" t="n"/>
+      <c r="L5" s="900" t="n"/>
+      <c r="M5" s="900" t="n"/>
+      <c r="N5" s="900" t="n"/>
+      <c r="O5" s="900" t="n"/>
+      <c r="P5" s="900" t="n"/>
+      <c r="Q5" s="900" t="n"/>
+      <c r="R5" s="900" t="n"/>
+      <c r="S5" s="900" t="n"/>
+      <c r="T5" s="900" t="n"/>
+      <c r="U5" s="900" t="n"/>
+      <c r="V5" s="900" t="n"/>
+      <c r="W5" s="900" t="n"/>
+      <c r="X5" s="900" t="n"/>
+      <c r="Y5" s="900" t="n"/>
+      <c r="Z5" s="900" t="n"/>
+      <c r="AA5" s="900" t="n"/>
+      <c r="AB5" s="900" t="n"/>
+      <c r="AC5" s="900" t="n"/>
+      <c r="AD5" s="901" t="n"/>
+      <c r="AE5" s="894" t="n"/>
+      <c r="AF5" s="894" t="n"/>
+      <c r="AG5" s="894" t="n"/>
+      <c r="AH5" s="895" t="n"/>
+      <c r="AI5" s="896" t="n"/>
+      <c r="AJ5" s="896" t="n"/>
+      <c r="AK5" s="896" t="n"/>
+      <c r="AL5" s="896" t="n"/>
+      <c r="AM5" s="896" t="n"/>
+      <c r="AN5" s="897" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="732" t="n"/>
-      <c r="B6" s="678" t="n"/>
-      <c r="C6" s="678" t="n"/>
-      <c r="D6" s="678" t="n"/>
-      <c r="E6" s="678" t="n"/>
-      <c r="F6" s="678" t="n"/>
-      <c r="G6" s="678" t="n"/>
-      <c r="H6" s="678" t="n"/>
-      <c r="I6" s="678" t="n"/>
-      <c r="J6" s="678" t="n"/>
-      <c r="K6" s="678" t="n"/>
-      <c r="L6" s="678" t="n"/>
-      <c r="M6" s="678" t="n"/>
-      <c r="N6" s="678" t="n"/>
-      <c r="O6" s="678" t="n"/>
-      <c r="P6" s="678" t="n"/>
-      <c r="Q6" s="678" t="n"/>
-      <c r="R6" s="678" t="n"/>
-      <c r="S6" s="678" t="n"/>
-      <c r="T6" s="678" t="n"/>
-      <c r="U6" s="678" t="n"/>
-      <c r="V6" s="678" t="n"/>
-      <c r="W6" s="678" t="n"/>
-      <c r="X6" s="678" t="n"/>
-      <c r="Y6" s="678" t="n"/>
-      <c r="Z6" s="678" t="n"/>
-      <c r="AA6" s="678" t="n"/>
-      <c r="AB6" s="678" t="n"/>
-      <c r="AC6" s="678" t="n"/>
-      <c r="AD6" s="678" t="n"/>
-      <c r="AE6" s="678" t="n"/>
-      <c r="AF6" s="678" t="n"/>
-      <c r="AG6" s="678" t="n"/>
-      <c r="AH6" s="678" t="n"/>
-      <c r="AI6" s="678" t="n"/>
-      <c r="AJ6" s="678" t="n"/>
-      <c r="AK6" s="678" t="n"/>
-      <c r="AL6" s="678" t="n"/>
-      <c r="AM6" s="678" t="n"/>
-      <c r="AN6" s="678" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="364" t="n"/>
+      <c r="B6" s="863" t="n"/>
+      <c r="C6" s="863" t="n"/>
+      <c r="D6" s="863" t="n"/>
+      <c r="E6" s="863" t="n"/>
+      <c r="F6" s="863" t="n"/>
+      <c r="G6" s="863" t="n"/>
+      <c r="H6" s="864" t="n"/>
+      <c r="I6" s="863" t="n"/>
+      <c r="J6" s="863" t="n"/>
+      <c r="K6" s="863" t="n"/>
+      <c r="L6" s="863" t="n"/>
+      <c r="M6" s="863" t="n"/>
+      <c r="N6" s="863" t="n"/>
+      <c r="O6" s="863" t="n"/>
+      <c r="P6" s="863" t="n"/>
+      <c r="Q6" s="863" t="n"/>
+      <c r="R6" s="863" t="n"/>
+      <c r="S6" s="863" t="n"/>
+      <c r="T6" s="863" t="n"/>
+      <c r="U6" s="863" t="n"/>
+      <c r="V6" s="863" t="n"/>
+      <c r="W6" s="863" t="n"/>
+      <c r="X6" s="863" t="n"/>
+      <c r="Y6" s="863" t="n"/>
+      <c r="Z6" s="863" t="n"/>
+      <c r="AA6" s="863" t="n"/>
+      <c r="AB6" s="863" t="n"/>
+      <c r="AC6" s="863" t="n"/>
+      <c r="AD6" s="864" t="n"/>
+      <c r="AE6" s="865" t="n"/>
+      <c r="AF6" s="865" t="n"/>
+      <c r="AG6" s="865" t="n"/>
+      <c r="AH6" s="866" t="n"/>
+      <c r="AI6" s="867" t="n"/>
+      <c r="AJ6" s="867" t="n"/>
+      <c r="AK6" s="867" t="n"/>
+      <c r="AL6" s="867" t="n"/>
+      <c r="AM6" s="867" t="n"/>
+      <c r="AN6" s="868" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="679" t="inlineStr">
-        <is>
-          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="289" t="n"/>
-      <c r="K7" s="733" t="n"/>
-      <c r="L7" s="733" t="n"/>
-      <c r="M7" s="733" t="n"/>
-      <c r="N7" s="733" t="n"/>
-      <c r="O7" s="733" t="n"/>
-      <c r="P7" s="733" t="n"/>
-      <c r="Q7" s="733" t="n"/>
-      <c r="R7" s="733" t="n"/>
-      <c r="S7" s="733" t="n"/>
-      <c r="T7" s="733" t="n"/>
-      <c r="U7" s="733" t="n"/>
-      <c r="V7" s="733" t="n"/>
-      <c r="W7" s="733" t="n"/>
-      <c r="X7" s="733" t="n"/>
-      <c r="Y7" s="733" t="n"/>
-      <c r="Z7" s="733" t="n"/>
-      <c r="AA7" s="733" t="n"/>
-      <c r="AB7" s="733" t="n"/>
-      <c r="AC7" s="733" t="n"/>
-      <c r="AD7" s="733" t="n"/>
-      <c r="AE7" s="733" t="n"/>
-      <c r="AF7" s="733" t="n"/>
-      <c r="AG7" s="733" t="n"/>
-      <c r="AH7" s="733" t="n"/>
-      <c r="AI7" s="733" t="n"/>
-      <c r="AJ7" s="733" t="n"/>
-      <c r="AK7" s="733" t="n"/>
-      <c r="AL7" s="733" t="n"/>
-      <c r="AM7" s="733" t="n"/>
-      <c r="AN7" s="734" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="869" t="n"/>
+      <c r="B7" s="870" t="n"/>
+      <c r="C7" s="870" t="n"/>
+      <c r="D7" s="870" t="n"/>
+      <c r="E7" s="870" t="n"/>
+      <c r="F7" s="870" t="n"/>
+      <c r="G7" s="870" t="n"/>
+      <c r="H7" s="870" t="n"/>
+      <c r="I7" s="870" t="n"/>
+      <c r="J7" s="870" t="n"/>
+      <c r="K7" s="869" t="n"/>
+      <c r="L7" s="869" t="n"/>
+      <c r="M7" s="869" t="n"/>
+      <c r="N7" s="869" t="n"/>
+      <c r="O7" s="869" t="n"/>
+      <c r="P7" s="869" t="n"/>
+      <c r="Q7" s="869" t="n"/>
+      <c r="R7" s="869" t="n"/>
+      <c r="S7" s="869" t="n"/>
+      <c r="T7" s="869" t="n"/>
+      <c r="U7" s="869" t="n"/>
+      <c r="V7" s="869" t="n"/>
+      <c r="W7" s="869" t="n"/>
+      <c r="X7" s="869" t="n"/>
+      <c r="Y7" s="869" t="n"/>
+      <c r="Z7" s="869" t="n"/>
+      <c r="AA7" s="869" t="n"/>
+      <c r="AB7" s="869" t="n"/>
+      <c r="AC7" s="869" t="n"/>
+      <c r="AD7" s="869" t="n"/>
+      <c r="AE7" s="869" t="n"/>
+      <c r="AF7" s="869" t="n"/>
+      <c r="AG7" s="869" t="n"/>
+      <c r="AH7" s="869" t="n"/>
+      <c r="AI7" s="869" t="n"/>
+      <c r="AJ7" s="869" t="n"/>
+      <c r="AK7" s="869" t="n"/>
+      <c r="AL7" s="869" t="n"/>
+      <c r="AM7" s="869" t="n"/>
+      <c r="AN7" s="869" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="769" t="inlineStr">
@@ -15178,15 +15569,15 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="752" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
+      <c r="B13" s="686" t="n"/>
+      <c r="C13" s="686" t="n"/>
+      <c r="D13" s="686" t="n"/>
+      <c r="E13" s="686" t="n"/>
+      <c r="F13" s="686" t="n"/>
+      <c r="G13" s="686" t="n"/>
+      <c r="H13" s="686" t="n"/>
+      <c r="I13" s="686" t="n"/>
+      <c r="J13" s="686" t="n"/>
       <c r="K13" s="686" t="n"/>
       <c r="L13" s="686" t="n"/>
       <c r="M13" s="686" t="n"/>
@@ -16245,50 +16636,50 @@
       <c r="AN35" s="751" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="819" t="inlineStr">
+      <c r="A36" s="382" t="inlineStr">
         <is>
           <t>NOTICE  —  Characteristic-by-characteristic FAI results. No uncontrolled copy/paste from other sources.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B36" s="820" t="n"/>
-      <c r="C36" s="820" t="n"/>
-      <c r="D36" s="820" t="n"/>
-      <c r="E36" s="820" t="n"/>
-      <c r="F36" s="820" t="n"/>
-      <c r="G36" s="820" t="n"/>
-      <c r="H36" s="820" t="n"/>
-      <c r="I36" s="820" t="n"/>
-      <c r="J36" s="820" t="n"/>
-      <c r="K36" s="820" t="n"/>
-      <c r="L36" s="820" t="n"/>
-      <c r="M36" s="820" t="n"/>
-      <c r="N36" s="820" t="n"/>
-      <c r="O36" s="820" t="n"/>
-      <c r="P36" s="820" t="n"/>
-      <c r="Q36" s="820" t="n"/>
-      <c r="R36" s="820" t="n"/>
-      <c r="S36" s="820" t="n"/>
-      <c r="T36" s="820" t="n"/>
-      <c r="U36" s="820" t="n"/>
-      <c r="V36" s="820" t="n"/>
-      <c r="W36" s="820" t="n"/>
-      <c r="X36" s="820" t="n"/>
-      <c r="Y36" s="820" t="n"/>
-      <c r="Z36" s="820" t="n"/>
-      <c r="AA36" s="820" t="n"/>
-      <c r="AB36" s="820" t="n"/>
-      <c r="AC36" s="820" t="n"/>
-      <c r="AD36" s="820" t="n"/>
-      <c r="AE36" s="820" t="n"/>
-      <c r="AF36" s="820" t="n"/>
-      <c r="AG36" s="820" t="n"/>
-      <c r="AH36" s="820" t="n"/>
-      <c r="AI36" s="820" t="n"/>
-      <c r="AJ36" s="820" t="n"/>
-      <c r="AK36" s="820" t="n"/>
-      <c r="AL36" s="820" t="n"/>
-      <c r="AM36" s="820" t="n"/>
-      <c r="AN36" s="821" t="n"/>
+      <c r="B36" s="383" t="n"/>
+      <c r="C36" s="383" t="n"/>
+      <c r="D36" s="383" t="n"/>
+      <c r="E36" s="383" t="n"/>
+      <c r="F36" s="383" t="n"/>
+      <c r="G36" s="383" t="n"/>
+      <c r="H36" s="383" t="n"/>
+      <c r="I36" s="383" t="n"/>
+      <c r="J36" s="383" t="n"/>
+      <c r="K36" s="383" t="n"/>
+      <c r="L36" s="383" t="n"/>
+      <c r="M36" s="383" t="n"/>
+      <c r="N36" s="383" t="n"/>
+      <c r="O36" s="383" t="n"/>
+      <c r="P36" s="383" t="n"/>
+      <c r="Q36" s="383" t="n"/>
+      <c r="R36" s="383" t="n"/>
+      <c r="S36" s="383" t="n"/>
+      <c r="T36" s="383" t="n"/>
+      <c r="U36" s="383" t="n"/>
+      <c r="V36" s="383" t="n"/>
+      <c r="W36" s="383" t="n"/>
+      <c r="X36" s="383" t="n"/>
+      <c r="Y36" s="383" t="n"/>
+      <c r="Z36" s="383" t="n"/>
+      <c r="AA36" s="383" t="n"/>
+      <c r="AB36" s="383" t="n"/>
+      <c r="AC36" s="383" t="n"/>
+      <c r="AD36" s="383" t="n"/>
+      <c r="AE36" s="383" t="n"/>
+      <c r="AF36" s="383" t="n"/>
+      <c r="AG36" s="383" t="n"/>
+      <c r="AH36" s="383" t="n"/>
+      <c r="AI36" s="383" t="n"/>
+      <c r="AJ36" s="383" t="n"/>
+      <c r="AK36" s="383" t="n"/>
+      <c r="AL36" s="383" t="n"/>
+      <c r="AM36" s="383" t="n"/>
+      <c r="AN36" s="384" t="n"/>
     </row>
     <row r="37" hidden="1" outlineLevel="1"/>
     <row r="38" hidden="1" outlineLevel="1"/>
@@ -16571,7 +16962,7 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="399" t="n"/>
       <c r="B1" s="325" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -16626,283 +17017,288 @@
       <c r="AN1" s="719" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="326" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="G2" s="759" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="847" t="n"/>
+      <c r="C2" s="847" t="n"/>
+      <c r="D2" s="847" t="n"/>
+      <c r="E2" s="847" t="n"/>
+      <c r="F2" s="847" t="n"/>
+      <c r="G2" s="902" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="H2" s="760" t="inlineStr">
+      <c r="H2" s="903" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="I2" s="721" t="n"/>
-      <c r="J2" s="721" t="n"/>
-      <c r="K2" s="721" t="n"/>
-      <c r="L2" s="721" t="n"/>
-      <c r="M2" s="721" t="n"/>
-      <c r="N2" s="721" t="n"/>
-      <c r="O2" s="721" t="n"/>
-      <c r="P2" s="721" t="n"/>
-      <c r="Q2" s="721" t="n"/>
-      <c r="R2" s="721" t="n"/>
-      <c r="S2" s="721" t="n"/>
-      <c r="T2" s="721" t="n"/>
-      <c r="U2" s="721" t="n"/>
-      <c r="V2" s="721" t="n"/>
-      <c r="W2" s="721" t="n"/>
-      <c r="X2" s="721" t="n"/>
-      <c r="Y2" s="721" t="n"/>
-      <c r="Z2" s="721" t="n"/>
-      <c r="AA2" s="721" t="n"/>
-      <c r="AB2" s="721" t="n"/>
-      <c r="AC2" s="721" t="n"/>
-      <c r="AD2" s="721" t="n"/>
-      <c r="AE2" s="722" t="n"/>
-      <c r="AF2" s="722" t="n"/>
-      <c r="AG2" s="722" t="n"/>
-      <c r="AH2" s="722" t="n"/>
-      <c r="AI2" s="670" t="n"/>
-      <c r="AJ2" s="670" t="n"/>
-      <c r="AK2" s="670" t="n"/>
-      <c r="AL2" s="670" t="n"/>
-      <c r="AM2" s="670" t="n"/>
-      <c r="AN2" s="723" t="n"/>
+      <c r="I2" s="717" t="n"/>
+      <c r="J2" s="717" t="n"/>
+      <c r="K2" s="717" t="n"/>
+      <c r="L2" s="717" t="n"/>
+      <c r="M2" s="717" t="n"/>
+      <c r="N2" s="717" t="n"/>
+      <c r="O2" s="717" t="n"/>
+      <c r="P2" s="717" t="n"/>
+      <c r="Q2" s="717" t="n"/>
+      <c r="R2" s="717" t="n"/>
+      <c r="S2" s="717" t="n"/>
+      <c r="T2" s="717" t="n"/>
+      <c r="U2" s="717" t="n"/>
+      <c r="V2" s="717" t="n"/>
+      <c r="W2" s="717" t="n"/>
+      <c r="X2" s="717" t="n"/>
+      <c r="Y2" s="717" t="n"/>
+      <c r="Z2" s="717" t="n"/>
+      <c r="AA2" s="717" t="n"/>
+      <c r="AB2" s="717" t="n"/>
+      <c r="AC2" s="717" t="n"/>
+      <c r="AD2" s="887" t="n"/>
+      <c r="AE2" s="888" t="n"/>
+      <c r="AF2" s="888" t="n"/>
+      <c r="AG2" s="888" t="n"/>
+      <c r="AH2" s="889" t="n"/>
+      <c r="AI2" s="890" t="n"/>
+      <c r="AJ2" s="890" t="n"/>
+      <c r="AK2" s="890" t="n"/>
+      <c r="AL2" s="890" t="n"/>
+      <c r="AM2" s="890" t="n"/>
+      <c r="AN2" s="891" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="326" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="G3" s="759" t="inlineStr">
+      <c r="A3" s="855" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="635" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="H3" s="760" t="inlineStr">
+      <c r="H3" s="904" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I3" s="721" t="n"/>
-      <c r="J3" s="721" t="n"/>
-      <c r="K3" s="721" t="n"/>
-      <c r="L3" s="721" t="n"/>
-      <c r="M3" s="721" t="n"/>
-      <c r="N3" s="721" t="n"/>
-      <c r="O3" s="721" t="n"/>
-      <c r="P3" s="721" t="n"/>
-      <c r="Q3" s="721" t="n"/>
-      <c r="R3" s="721" t="n"/>
-      <c r="S3" s="721" t="n"/>
-      <c r="T3" s="721" t="n"/>
-      <c r="U3" s="721" t="n"/>
-      <c r="V3" s="721" t="n"/>
-      <c r="W3" s="721" t="n"/>
-      <c r="X3" s="721" t="n"/>
-      <c r="Y3" s="721" t="n"/>
-      <c r="Z3" s="721" t="n"/>
-      <c r="AA3" s="721" t="n"/>
-      <c r="AB3" s="721" t="n"/>
-      <c r="AC3" s="721" t="n"/>
-      <c r="AD3" s="721" t="n"/>
-      <c r="AE3" s="722" t="n"/>
-      <c r="AF3" s="722" t="n"/>
-      <c r="AG3" s="722" t="n"/>
-      <c r="AH3" s="722" t="n"/>
-      <c r="AI3" s="670" t="n"/>
-      <c r="AJ3" s="670" t="n"/>
-      <c r="AK3" s="670" t="n"/>
-      <c r="AL3" s="670" t="n"/>
-      <c r="AM3" s="670" t="n"/>
-      <c r="AN3" s="723" t="n"/>
+      <c r="I3" s="892" t="n"/>
+      <c r="J3" s="892" t="n"/>
+      <c r="K3" s="892" t="n"/>
+      <c r="L3" s="892" t="n"/>
+      <c r="M3" s="892" t="n"/>
+      <c r="N3" s="892" t="n"/>
+      <c r="O3" s="892" t="n"/>
+      <c r="P3" s="892" t="n"/>
+      <c r="Q3" s="892" t="n"/>
+      <c r="R3" s="892" t="n"/>
+      <c r="S3" s="892" t="n"/>
+      <c r="T3" s="892" t="n"/>
+      <c r="U3" s="892" t="n"/>
+      <c r="V3" s="892" t="n"/>
+      <c r="W3" s="892" t="n"/>
+      <c r="X3" s="892" t="n"/>
+      <c r="Y3" s="892" t="n"/>
+      <c r="Z3" s="892" t="n"/>
+      <c r="AA3" s="892" t="n"/>
+      <c r="AB3" s="892" t="n"/>
+      <c r="AC3" s="892" t="n"/>
+      <c r="AD3" s="893" t="n"/>
+      <c r="AE3" s="894" t="n"/>
+      <c r="AF3" s="894" t="n"/>
+      <c r="AG3" s="894" t="n"/>
+      <c r="AH3" s="895" t="n"/>
+      <c r="AI3" s="896" t="n"/>
+      <c r="AJ3" s="896" t="n"/>
+      <c r="AK3" s="896" t="n"/>
+      <c r="AL3" s="896" t="n"/>
+      <c r="AM3" s="896" t="n"/>
+      <c r="AN3" s="897" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="326" t="n"/>
-      <c r="C4" s="724" t="inlineStr">
+      <c r="A4" s="855" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="610" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="G4" s="759" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="635" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="760" t="inlineStr"/>
-      <c r="I4" s="726" t="n"/>
-      <c r="J4" s="726" t="n"/>
-      <c r="K4" s="726" t="n"/>
-      <c r="L4" s="726" t="n"/>
-      <c r="M4" s="726" t="n"/>
-      <c r="N4" s="726" t="n"/>
-      <c r="O4" s="726" t="n"/>
-      <c r="P4" s="726" t="n"/>
-      <c r="Q4" s="726" t="n"/>
-      <c r="R4" s="726" t="n"/>
-      <c r="S4" s="726" t="n"/>
-      <c r="T4" s="726" t="n"/>
-      <c r="U4" s="726" t="n"/>
-      <c r="V4" s="726" t="n"/>
-      <c r="W4" s="726" t="n"/>
-      <c r="X4" s="726" t="n"/>
-      <c r="Y4" s="726" t="n"/>
-      <c r="Z4" s="726" t="n"/>
-      <c r="AA4" s="726" t="n"/>
-      <c r="AB4" s="726" t="n"/>
-      <c r="AC4" s="726" t="n"/>
-      <c r="AD4" s="726" t="n"/>
-      <c r="AE4" s="722" t="n"/>
-      <c r="AF4" s="722" t="n"/>
-      <c r="AG4" s="722" t="n"/>
-      <c r="AH4" s="722" t="n"/>
-      <c r="AI4" s="670" t="n"/>
-      <c r="AJ4" s="670" t="n"/>
-      <c r="AK4" s="670" t="n"/>
-      <c r="AL4" s="670" t="n"/>
-      <c r="AM4" s="670" t="n"/>
-      <c r="AN4" s="723" t="n"/>
+      <c r="H4" s="904" t="inlineStr"/>
+      <c r="I4" s="535" t="n"/>
+      <c r="J4" s="535" t="n"/>
+      <c r="K4" s="535" t="n"/>
+      <c r="L4" s="535" t="n"/>
+      <c r="M4" s="535" t="n"/>
+      <c r="N4" s="535" t="n"/>
+      <c r="O4" s="535" t="n"/>
+      <c r="P4" s="535" t="n"/>
+      <c r="Q4" s="535" t="n"/>
+      <c r="R4" s="535" t="n"/>
+      <c r="S4" s="535" t="n"/>
+      <c r="T4" s="535" t="n"/>
+      <c r="U4" s="535" t="n"/>
+      <c r="V4" s="535" t="n"/>
+      <c r="W4" s="535" t="n"/>
+      <c r="X4" s="535" t="n"/>
+      <c r="Y4" s="535" t="n"/>
+      <c r="Z4" s="535" t="n"/>
+      <c r="AA4" s="535" t="n"/>
+      <c r="AB4" s="535" t="n"/>
+      <c r="AC4" s="535" t="n"/>
+      <c r="AD4" s="898" t="n"/>
+      <c r="AE4" s="894" t="n"/>
+      <c r="AF4" s="894" t="n"/>
+      <c r="AG4" s="894" t="n"/>
+      <c r="AH4" s="895" t="n"/>
+      <c r="AI4" s="896" t="n"/>
+      <c r="AJ4" s="896" t="n"/>
+      <c r="AK4" s="896" t="n"/>
+      <c r="AL4" s="896" t="n"/>
+      <c r="AM4" s="896" t="n"/>
+      <c r="AN4" s="897" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="727" t="inlineStr">
+      <c r="A5" s="855" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="899" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="761" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="635" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" s="762" t="inlineStr"/>
-      <c r="I5" s="729" t="n"/>
-      <c r="J5" s="729" t="n"/>
-      <c r="K5" s="729" t="n"/>
-      <c r="L5" s="729" t="n"/>
-      <c r="M5" s="729" t="n"/>
-      <c r="N5" s="729" t="n"/>
-      <c r="O5" s="729" t="n"/>
-      <c r="P5" s="729" t="n"/>
-      <c r="Q5" s="729" t="n"/>
-      <c r="R5" s="729" t="n"/>
-      <c r="S5" s="729" t="n"/>
-      <c r="T5" s="729" t="n"/>
-      <c r="U5" s="729" t="n"/>
-      <c r="V5" s="729" t="n"/>
-      <c r="W5" s="729" t="n"/>
-      <c r="X5" s="729" t="n"/>
-      <c r="Y5" s="729" t="n"/>
-      <c r="Z5" s="729" t="n"/>
-      <c r="AA5" s="729" t="n"/>
-      <c r="AB5" s="729" t="n"/>
-      <c r="AC5" s="729" t="n"/>
-      <c r="AD5" s="729" t="n"/>
-      <c r="AE5" s="730" t="n"/>
-      <c r="AF5" s="730" t="n"/>
-      <c r="AG5" s="730" t="n"/>
-      <c r="AH5" s="730" t="n"/>
-      <c r="AI5" s="676" t="n"/>
-      <c r="AJ5" s="676" t="n"/>
-      <c r="AK5" s="676" t="n"/>
-      <c r="AL5" s="676" t="n"/>
-      <c r="AM5" s="676" t="n"/>
-      <c r="AN5" s="731" t="n"/>
+      <c r="H5" s="904" t="inlineStr"/>
+      <c r="I5" s="900" t="n"/>
+      <c r="J5" s="900" t="n"/>
+      <c r="K5" s="900" t="n"/>
+      <c r="L5" s="900" t="n"/>
+      <c r="M5" s="900" t="n"/>
+      <c r="N5" s="900" t="n"/>
+      <c r="O5" s="900" t="n"/>
+      <c r="P5" s="900" t="n"/>
+      <c r="Q5" s="900" t="n"/>
+      <c r="R5" s="900" t="n"/>
+      <c r="S5" s="900" t="n"/>
+      <c r="T5" s="900" t="n"/>
+      <c r="U5" s="900" t="n"/>
+      <c r="V5" s="900" t="n"/>
+      <c r="W5" s="900" t="n"/>
+      <c r="X5" s="900" t="n"/>
+      <c r="Y5" s="900" t="n"/>
+      <c r="Z5" s="900" t="n"/>
+      <c r="AA5" s="900" t="n"/>
+      <c r="AB5" s="900" t="n"/>
+      <c r="AC5" s="900" t="n"/>
+      <c r="AD5" s="901" t="n"/>
+      <c r="AE5" s="894" t="n"/>
+      <c r="AF5" s="894" t="n"/>
+      <c r="AG5" s="894" t="n"/>
+      <c r="AH5" s="895" t="n"/>
+      <c r="AI5" s="896" t="n"/>
+      <c r="AJ5" s="896" t="n"/>
+      <c r="AK5" s="896" t="n"/>
+      <c r="AL5" s="896" t="n"/>
+      <c r="AM5" s="896" t="n"/>
+      <c r="AN5" s="897" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="732" t="n"/>
-      <c r="B6" s="678" t="n"/>
-      <c r="C6" s="678" t="n"/>
-      <c r="D6" s="678" t="n"/>
-      <c r="E6" s="678" t="n"/>
-      <c r="F6" s="678" t="n"/>
-      <c r="G6" s="678" t="n"/>
-      <c r="H6" s="678" t="n"/>
-      <c r="I6" s="678" t="n"/>
-      <c r="J6" s="678" t="n"/>
-      <c r="K6" s="678" t="n"/>
-      <c r="L6" s="678" t="n"/>
-      <c r="M6" s="678" t="n"/>
-      <c r="N6" s="678" t="n"/>
-      <c r="O6" s="678" t="n"/>
-      <c r="P6" s="678" t="n"/>
-      <c r="Q6" s="678" t="n"/>
-      <c r="R6" s="678" t="n"/>
-      <c r="S6" s="678" t="n"/>
-      <c r="T6" s="678" t="n"/>
-      <c r="U6" s="678" t="n"/>
-      <c r="V6" s="678" t="n"/>
-      <c r="W6" s="678" t="n"/>
-      <c r="X6" s="678" t="n"/>
-      <c r="Y6" s="678" t="n"/>
-      <c r="Z6" s="678" t="n"/>
-      <c r="AA6" s="678" t="n"/>
-      <c r="AB6" s="678" t="n"/>
-      <c r="AC6" s="678" t="n"/>
-      <c r="AD6" s="678" t="n"/>
-      <c r="AE6" s="678" t="n"/>
-      <c r="AF6" s="678" t="n"/>
-      <c r="AG6" s="678" t="n"/>
-      <c r="AH6" s="678" t="n"/>
-      <c r="AI6" s="678" t="n"/>
-      <c r="AJ6" s="678" t="n"/>
-      <c r="AK6" s="678" t="n"/>
-      <c r="AL6" s="678" t="n"/>
-      <c r="AM6" s="678" t="n"/>
-      <c r="AN6" s="678" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="364" t="n"/>
+      <c r="B6" s="863" t="n"/>
+      <c r="C6" s="863" t="n"/>
+      <c r="D6" s="863" t="n"/>
+      <c r="E6" s="863" t="n"/>
+      <c r="F6" s="863" t="n"/>
+      <c r="G6" s="863" t="n"/>
+      <c r="H6" s="864" t="n"/>
+      <c r="I6" s="863" t="n"/>
+      <c r="J6" s="863" t="n"/>
+      <c r="K6" s="863" t="n"/>
+      <c r="L6" s="863" t="n"/>
+      <c r="M6" s="863" t="n"/>
+      <c r="N6" s="863" t="n"/>
+      <c r="O6" s="863" t="n"/>
+      <c r="P6" s="863" t="n"/>
+      <c r="Q6" s="863" t="n"/>
+      <c r="R6" s="863" t="n"/>
+      <c r="S6" s="863" t="n"/>
+      <c r="T6" s="863" t="n"/>
+      <c r="U6" s="863" t="n"/>
+      <c r="V6" s="863" t="n"/>
+      <c r="W6" s="863" t="n"/>
+      <c r="X6" s="863" t="n"/>
+      <c r="Y6" s="863" t="n"/>
+      <c r="Z6" s="863" t="n"/>
+      <c r="AA6" s="863" t="n"/>
+      <c r="AB6" s="863" t="n"/>
+      <c r="AC6" s="863" t="n"/>
+      <c r="AD6" s="864" t="n"/>
+      <c r="AE6" s="865" t="n"/>
+      <c r="AF6" s="865" t="n"/>
+      <c r="AG6" s="865" t="n"/>
+      <c r="AH6" s="866" t="n"/>
+      <c r="AI6" s="867" t="n"/>
+      <c r="AJ6" s="867" t="n"/>
+      <c r="AK6" s="867" t="n"/>
+      <c r="AL6" s="867" t="n"/>
+      <c r="AM6" s="867" t="n"/>
+      <c r="AN6" s="868" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="679" t="inlineStr">
-        <is>
-          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="733" t="n"/>
-      <c r="J7" s="733" t="n"/>
-      <c r="K7" s="733" t="n"/>
-      <c r="L7" s="733" t="n"/>
-      <c r="M7" s="733" t="n"/>
-      <c r="N7" s="733" t="n"/>
-      <c r="O7" s="733" t="n"/>
-      <c r="P7" s="733" t="n"/>
-      <c r="Q7" s="733" t="n"/>
-      <c r="R7" s="733" t="n"/>
-      <c r="S7" s="733" t="n"/>
-      <c r="T7" s="733" t="n"/>
-      <c r="U7" s="733" t="n"/>
-      <c r="V7" s="733" t="n"/>
-      <c r="W7" s="733" t="n"/>
-      <c r="X7" s="733" t="n"/>
-      <c r="Y7" s="733" t="n"/>
-      <c r="Z7" s="733" t="n"/>
-      <c r="AA7" s="733" t="n"/>
-      <c r="AB7" s="733" t="n"/>
-      <c r="AC7" s="733" t="n"/>
-      <c r="AD7" s="733" t="n"/>
-      <c r="AE7" s="733" t="n"/>
-      <c r="AF7" s="733" t="n"/>
-      <c r="AG7" s="733" t="n"/>
-      <c r="AH7" s="733" t="n"/>
-      <c r="AI7" s="733" t="n"/>
-      <c r="AJ7" s="733" t="n"/>
-      <c r="AK7" s="733" t="n"/>
-      <c r="AL7" s="733" t="n"/>
-      <c r="AM7" s="733" t="n"/>
-      <c r="AN7" s="734" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="869" t="n"/>
+      <c r="B7" s="870" t="n"/>
+      <c r="C7" s="870" t="n"/>
+      <c r="D7" s="870" t="n"/>
+      <c r="E7" s="870" t="n"/>
+      <c r="F7" s="870" t="n"/>
+      <c r="G7" s="870" t="n"/>
+      <c r="H7" s="870" t="n"/>
+      <c r="I7" s="869" t="n"/>
+      <c r="J7" s="869" t="n"/>
+      <c r="K7" s="869" t="n"/>
+      <c r="L7" s="869" t="n"/>
+      <c r="M7" s="869" t="n"/>
+      <c r="N7" s="869" t="n"/>
+      <c r="O7" s="869" t="n"/>
+      <c r="P7" s="869" t="n"/>
+      <c r="Q7" s="869" t="n"/>
+      <c r="R7" s="869" t="n"/>
+      <c r="S7" s="869" t="n"/>
+      <c r="T7" s="869" t="n"/>
+      <c r="U7" s="869" t="n"/>
+      <c r="V7" s="869" t="n"/>
+      <c r="W7" s="869" t="n"/>
+      <c r="X7" s="869" t="n"/>
+      <c r="Y7" s="869" t="n"/>
+      <c r="Z7" s="869" t="n"/>
+      <c r="AA7" s="869" t="n"/>
+      <c r="AB7" s="869" t="n"/>
+      <c r="AC7" s="869" t="n"/>
+      <c r="AD7" s="869" t="n"/>
+      <c r="AE7" s="869" t="n"/>
+      <c r="AF7" s="869" t="n"/>
+      <c r="AG7" s="869" t="n"/>
+      <c r="AH7" s="869" t="n"/>
+      <c r="AI7" s="869" t="n"/>
+      <c r="AJ7" s="869" t="n"/>
+      <c r="AK7" s="869" t="n"/>
+      <c r="AL7" s="869" t="n"/>
+      <c r="AM7" s="869" t="n"/>
+      <c r="AN7" s="869" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="769" t="inlineStr">
@@ -17188,13 +17584,13 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="752" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="B13" s="686" t="n"/>
+      <c r="C13" s="686" t="n"/>
+      <c r="D13" s="686" t="n"/>
+      <c r="E13" s="686" t="n"/>
+      <c r="F13" s="686" t="n"/>
+      <c r="G13" s="686" t="n"/>
+      <c r="H13" s="686" t="n"/>
       <c r="I13" s="686" t="n"/>
       <c r="J13" s="686" t="n"/>
       <c r="K13" s="686" t="n"/>
@@ -17887,50 +18283,50 @@
       <c r="AN27" s="751" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="819" t="inlineStr">
+      <c r="A28" s="382" t="inlineStr">
         <is>
           <t>NOTICE  —  Material, special-process and supporting certification linkage for the FAI package.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="820" t="n"/>
-      <c r="C28" s="820" t="n"/>
-      <c r="D28" s="820" t="n"/>
-      <c r="E28" s="820" t="n"/>
-      <c r="F28" s="820" t="n"/>
-      <c r="G28" s="820" t="n"/>
-      <c r="H28" s="820" t="n"/>
-      <c r="I28" s="820" t="n"/>
-      <c r="J28" s="820" t="n"/>
-      <c r="K28" s="820" t="n"/>
-      <c r="L28" s="820" t="n"/>
-      <c r="M28" s="820" t="n"/>
-      <c r="N28" s="820" t="n"/>
-      <c r="O28" s="820" t="n"/>
-      <c r="P28" s="820" t="n"/>
-      <c r="Q28" s="820" t="n"/>
-      <c r="R28" s="820" t="n"/>
-      <c r="S28" s="820" t="n"/>
-      <c r="T28" s="820" t="n"/>
-      <c r="U28" s="820" t="n"/>
-      <c r="V28" s="820" t="n"/>
-      <c r="W28" s="820" t="n"/>
-      <c r="X28" s="820" t="n"/>
-      <c r="Y28" s="820" t="n"/>
-      <c r="Z28" s="820" t="n"/>
-      <c r="AA28" s="820" t="n"/>
-      <c r="AB28" s="820" t="n"/>
-      <c r="AC28" s="820" t="n"/>
-      <c r="AD28" s="820" t="n"/>
-      <c r="AE28" s="820" t="n"/>
-      <c r="AF28" s="820" t="n"/>
-      <c r="AG28" s="820" t="n"/>
-      <c r="AH28" s="820" t="n"/>
-      <c r="AI28" s="820" t="n"/>
-      <c r="AJ28" s="820" t="n"/>
-      <c r="AK28" s="820" t="n"/>
-      <c r="AL28" s="820" t="n"/>
-      <c r="AM28" s="820" t="n"/>
-      <c r="AN28" s="821" t="n"/>
+      <c r="B28" s="383" t="n"/>
+      <c r="C28" s="383" t="n"/>
+      <c r="D28" s="383" t="n"/>
+      <c r="E28" s="383" t="n"/>
+      <c r="F28" s="383" t="n"/>
+      <c r="G28" s="383" t="n"/>
+      <c r="H28" s="383" t="n"/>
+      <c r="I28" s="383" t="n"/>
+      <c r="J28" s="383" t="n"/>
+      <c r="K28" s="383" t="n"/>
+      <c r="L28" s="383" t="n"/>
+      <c r="M28" s="383" t="n"/>
+      <c r="N28" s="383" t="n"/>
+      <c r="O28" s="383" t="n"/>
+      <c r="P28" s="383" t="n"/>
+      <c r="Q28" s="383" t="n"/>
+      <c r="R28" s="383" t="n"/>
+      <c r="S28" s="383" t="n"/>
+      <c r="T28" s="383" t="n"/>
+      <c r="U28" s="383" t="n"/>
+      <c r="V28" s="383" t="n"/>
+      <c r="W28" s="383" t="n"/>
+      <c r="X28" s="383" t="n"/>
+      <c r="Y28" s="383" t="n"/>
+      <c r="Z28" s="383" t="n"/>
+      <c r="AA28" s="383" t="n"/>
+      <c r="AB28" s="383" t="n"/>
+      <c r="AC28" s="383" t="n"/>
+      <c r="AD28" s="383" t="n"/>
+      <c r="AE28" s="383" t="n"/>
+      <c r="AF28" s="383" t="n"/>
+      <c r="AG28" s="383" t="n"/>
+      <c r="AH28" s="383" t="n"/>
+      <c r="AI28" s="383" t="n"/>
+      <c r="AJ28" s="383" t="n"/>
+      <c r="AK28" s="383" t="n"/>
+      <c r="AL28" s="383" t="n"/>
+      <c r="AM28" s="383" t="n"/>
+      <c r="AN28" s="384" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -18215,7 +18611,7 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="399" t="n"/>
       <c r="B1" s="325" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -18270,286 +18666,288 @@
       <c r="AN1" s="719" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="326" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="F2" s="759" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="847" t="n"/>
+      <c r="C2" s="847" t="n"/>
+      <c r="D2" s="847" t="n"/>
+      <c r="E2" s="847" t="n"/>
+      <c r="F2" s="902" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="G2" s="760" t="inlineStr">
+      <c r="G2" s="758" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="H2" s="767" t="n"/>
-      <c r="I2" s="721" t="n"/>
-      <c r="J2" s="721" t="n"/>
-      <c r="K2" s="721" t="n"/>
-      <c r="L2" s="721" t="n"/>
-      <c r="M2" s="721" t="n"/>
-      <c r="N2" s="721" t="n"/>
-      <c r="O2" s="721" t="n"/>
-      <c r="P2" s="721" t="n"/>
-      <c r="Q2" s="721" t="n"/>
-      <c r="R2" s="721" t="n"/>
-      <c r="S2" s="721" t="n"/>
-      <c r="T2" s="721" t="n"/>
-      <c r="U2" s="721" t="n"/>
-      <c r="V2" s="721" t="n"/>
-      <c r="W2" s="721" t="n"/>
-      <c r="X2" s="721" t="n"/>
-      <c r="Y2" s="721" t="n"/>
-      <c r="Z2" s="721" t="n"/>
-      <c r="AA2" s="721" t="n"/>
-      <c r="AB2" s="721" t="n"/>
-      <c r="AC2" s="721" t="n"/>
-      <c r="AD2" s="721" t="n"/>
-      <c r="AE2" s="722" t="n"/>
-      <c r="AF2" s="722" t="n"/>
-      <c r="AG2" s="722" t="n"/>
-      <c r="AH2" s="722" t="n"/>
-      <c r="AI2" s="670" t="n"/>
-      <c r="AJ2" s="670" t="n"/>
-      <c r="AK2" s="670" t="n"/>
-      <c r="AL2" s="670" t="n"/>
-      <c r="AM2" s="670" t="n"/>
-      <c r="AN2" s="723" t="n"/>
+      <c r="H2" s="905" t="n"/>
+      <c r="I2" s="717" t="n"/>
+      <c r="J2" s="717" t="n"/>
+      <c r="K2" s="717" t="n"/>
+      <c r="L2" s="717" t="n"/>
+      <c r="M2" s="717" t="n"/>
+      <c r="N2" s="717" t="n"/>
+      <c r="O2" s="717" t="n"/>
+      <c r="P2" s="717" t="n"/>
+      <c r="Q2" s="717" t="n"/>
+      <c r="R2" s="717" t="n"/>
+      <c r="S2" s="717" t="n"/>
+      <c r="T2" s="717" t="n"/>
+      <c r="U2" s="717" t="n"/>
+      <c r="V2" s="717" t="n"/>
+      <c r="W2" s="717" t="n"/>
+      <c r="X2" s="717" t="n"/>
+      <c r="Y2" s="717" t="n"/>
+      <c r="Z2" s="717" t="n"/>
+      <c r="AA2" s="717" t="n"/>
+      <c r="AB2" s="717" t="n"/>
+      <c r="AC2" s="717" t="n"/>
+      <c r="AD2" s="887" t="n"/>
+      <c r="AE2" s="888" t="n"/>
+      <c r="AF2" s="888" t="n"/>
+      <c r="AG2" s="888" t="n"/>
+      <c r="AH2" s="889" t="n"/>
+      <c r="AI2" s="890" t="n"/>
+      <c r="AJ2" s="890" t="n"/>
+      <c r="AK2" s="890" t="n"/>
+      <c r="AL2" s="890" t="n"/>
+      <c r="AM2" s="890" t="n"/>
+      <c r="AN2" s="891" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="326" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="F3" s="759" t="inlineStr">
+      <c r="A3" s="855" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="635" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="G3" s="760" t="inlineStr">
+      <c r="G3" s="644" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="H3" s="767" t="n"/>
-      <c r="I3" s="721" t="n"/>
-      <c r="J3" s="721" t="n"/>
-      <c r="K3" s="721" t="n"/>
-      <c r="L3" s="721" t="n"/>
-      <c r="M3" s="721" t="n"/>
-      <c r="N3" s="721" t="n"/>
-      <c r="O3" s="721" t="n"/>
-      <c r="P3" s="721" t="n"/>
-      <c r="Q3" s="721" t="n"/>
-      <c r="R3" s="721" t="n"/>
-      <c r="S3" s="721" t="n"/>
-      <c r="T3" s="721" t="n"/>
-      <c r="U3" s="721" t="n"/>
-      <c r="V3" s="721" t="n"/>
-      <c r="W3" s="721" t="n"/>
-      <c r="X3" s="721" t="n"/>
-      <c r="Y3" s="721" t="n"/>
-      <c r="Z3" s="721" t="n"/>
-      <c r="AA3" s="721" t="n"/>
-      <c r="AB3" s="721" t="n"/>
-      <c r="AC3" s="721" t="n"/>
-      <c r="AD3" s="721" t="n"/>
-      <c r="AE3" s="722" t="n"/>
-      <c r="AF3" s="722" t="n"/>
-      <c r="AG3" s="722" t="n"/>
-      <c r="AH3" s="722" t="n"/>
-      <c r="AI3" s="670" t="n"/>
-      <c r="AJ3" s="670" t="n"/>
-      <c r="AK3" s="670" t="n"/>
-      <c r="AL3" s="670" t="n"/>
-      <c r="AM3" s="670" t="n"/>
-      <c r="AN3" s="723" t="n"/>
+      <c r="H3" s="906" t="n"/>
+      <c r="I3" s="892" t="n"/>
+      <c r="J3" s="892" t="n"/>
+      <c r="K3" s="892" t="n"/>
+      <c r="L3" s="892" t="n"/>
+      <c r="M3" s="892" t="n"/>
+      <c r="N3" s="892" t="n"/>
+      <c r="O3" s="892" t="n"/>
+      <c r="P3" s="892" t="n"/>
+      <c r="Q3" s="892" t="n"/>
+      <c r="R3" s="892" t="n"/>
+      <c r="S3" s="892" t="n"/>
+      <c r="T3" s="892" t="n"/>
+      <c r="U3" s="892" t="n"/>
+      <c r="V3" s="892" t="n"/>
+      <c r="W3" s="892" t="n"/>
+      <c r="X3" s="892" t="n"/>
+      <c r="Y3" s="892" t="n"/>
+      <c r="Z3" s="892" t="n"/>
+      <c r="AA3" s="892" t="n"/>
+      <c r="AB3" s="892" t="n"/>
+      <c r="AC3" s="892" t="n"/>
+      <c r="AD3" s="893" t="n"/>
+      <c r="AE3" s="894" t="n"/>
+      <c r="AF3" s="894" t="n"/>
+      <c r="AG3" s="894" t="n"/>
+      <c r="AH3" s="895" t="n"/>
+      <c r="AI3" s="896" t="n"/>
+      <c r="AJ3" s="896" t="n"/>
+      <c r="AK3" s="896" t="n"/>
+      <c r="AL3" s="896" t="n"/>
+      <c r="AM3" s="896" t="n"/>
+      <c r="AN3" s="897" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="326" t="n"/>
-      <c r="C4" s="724" t="inlineStr">
+      <c r="A4" s="855" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="610" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="F4" s="759" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="635" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G4" s="760" t="inlineStr"/>
-      <c r="H4" s="767" t="n"/>
-      <c r="I4" s="726" t="n"/>
-      <c r="J4" s="726" t="n"/>
-      <c r="K4" s="726" t="n"/>
-      <c r="L4" s="726" t="n"/>
-      <c r="M4" s="726" t="n"/>
-      <c r="N4" s="726" t="n"/>
-      <c r="O4" s="726" t="n"/>
-      <c r="P4" s="726" t="n"/>
-      <c r="Q4" s="726" t="n"/>
-      <c r="R4" s="726" t="n"/>
-      <c r="S4" s="726" t="n"/>
-      <c r="T4" s="726" t="n"/>
-      <c r="U4" s="726" t="n"/>
-      <c r="V4" s="726" t="n"/>
-      <c r="W4" s="726" t="n"/>
-      <c r="X4" s="726" t="n"/>
-      <c r="Y4" s="726" t="n"/>
-      <c r="Z4" s="726" t="n"/>
-      <c r="AA4" s="726" t="n"/>
-      <c r="AB4" s="726" t="n"/>
-      <c r="AC4" s="726" t="n"/>
-      <c r="AD4" s="726" t="n"/>
-      <c r="AE4" s="722" t="n"/>
-      <c r="AF4" s="722" t="n"/>
-      <c r="AG4" s="722" t="n"/>
-      <c r="AH4" s="722" t="n"/>
-      <c r="AI4" s="670" t="n"/>
-      <c r="AJ4" s="670" t="n"/>
-      <c r="AK4" s="670" t="n"/>
-      <c r="AL4" s="670" t="n"/>
-      <c r="AM4" s="670" t="n"/>
-      <c r="AN4" s="723" t="n"/>
+      <c r="G4" s="644" t="inlineStr"/>
+      <c r="H4" s="906" t="n"/>
+      <c r="I4" s="535" t="n"/>
+      <c r="J4" s="535" t="n"/>
+      <c r="K4" s="535" t="n"/>
+      <c r="L4" s="535" t="n"/>
+      <c r="M4" s="535" t="n"/>
+      <c r="N4" s="535" t="n"/>
+      <c r="O4" s="535" t="n"/>
+      <c r="P4" s="535" t="n"/>
+      <c r="Q4" s="535" t="n"/>
+      <c r="R4" s="535" t="n"/>
+      <c r="S4" s="535" t="n"/>
+      <c r="T4" s="535" t="n"/>
+      <c r="U4" s="535" t="n"/>
+      <c r="V4" s="535" t="n"/>
+      <c r="W4" s="535" t="n"/>
+      <c r="X4" s="535" t="n"/>
+      <c r="Y4" s="535" t="n"/>
+      <c r="Z4" s="535" t="n"/>
+      <c r="AA4" s="535" t="n"/>
+      <c r="AB4" s="535" t="n"/>
+      <c r="AC4" s="535" t="n"/>
+      <c r="AD4" s="898" t="n"/>
+      <c r="AE4" s="894" t="n"/>
+      <c r="AF4" s="894" t="n"/>
+      <c r="AG4" s="894" t="n"/>
+      <c r="AH4" s="895" t="n"/>
+      <c r="AI4" s="896" t="n"/>
+      <c r="AJ4" s="896" t="n"/>
+      <c r="AK4" s="896" t="n"/>
+      <c r="AL4" s="896" t="n"/>
+      <c r="AM4" s="896" t="n"/>
+      <c r="AN4" s="897" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="727" t="inlineStr">
+      <c r="A5" s="855" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="899" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="761" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="635" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="G5" s="762" t="inlineStr"/>
-      <c r="H5" s="768" t="n"/>
-      <c r="I5" s="729" t="n"/>
-      <c r="J5" s="729" t="n"/>
-      <c r="K5" s="729" t="n"/>
-      <c r="L5" s="729" t="n"/>
-      <c r="M5" s="729" t="n"/>
-      <c r="N5" s="729" t="n"/>
-      <c r="O5" s="729" t="n"/>
-      <c r="P5" s="729" t="n"/>
-      <c r="Q5" s="729" t="n"/>
-      <c r="R5" s="729" t="n"/>
-      <c r="S5" s="729" t="n"/>
-      <c r="T5" s="729" t="n"/>
-      <c r="U5" s="729" t="n"/>
-      <c r="V5" s="729" t="n"/>
-      <c r="W5" s="729" t="n"/>
-      <c r="X5" s="729" t="n"/>
-      <c r="Y5" s="729" t="n"/>
-      <c r="Z5" s="729" t="n"/>
-      <c r="AA5" s="729" t="n"/>
-      <c r="AB5" s="729" t="n"/>
-      <c r="AC5" s="729" t="n"/>
-      <c r="AD5" s="729" t="n"/>
-      <c r="AE5" s="730" t="n"/>
-      <c r="AF5" s="730" t="n"/>
-      <c r="AG5" s="730" t="n"/>
-      <c r="AH5" s="730" t="n"/>
-      <c r="AI5" s="676" t="n"/>
-      <c r="AJ5" s="676" t="n"/>
-      <c r="AK5" s="676" t="n"/>
-      <c r="AL5" s="676" t="n"/>
-      <c r="AM5" s="676" t="n"/>
-      <c r="AN5" s="731" t="n"/>
+      <c r="G5" s="644" t="inlineStr"/>
+      <c r="H5" s="906" t="n"/>
+      <c r="I5" s="900" t="n"/>
+      <c r="J5" s="900" t="n"/>
+      <c r="K5" s="900" t="n"/>
+      <c r="L5" s="900" t="n"/>
+      <c r="M5" s="900" t="n"/>
+      <c r="N5" s="900" t="n"/>
+      <c r="O5" s="900" t="n"/>
+      <c r="P5" s="900" t="n"/>
+      <c r="Q5" s="900" t="n"/>
+      <c r="R5" s="900" t="n"/>
+      <c r="S5" s="900" t="n"/>
+      <c r="T5" s="900" t="n"/>
+      <c r="U5" s="900" t="n"/>
+      <c r="V5" s="900" t="n"/>
+      <c r="W5" s="900" t="n"/>
+      <c r="X5" s="900" t="n"/>
+      <c r="Y5" s="900" t="n"/>
+      <c r="Z5" s="900" t="n"/>
+      <c r="AA5" s="900" t="n"/>
+      <c r="AB5" s="900" t="n"/>
+      <c r="AC5" s="900" t="n"/>
+      <c r="AD5" s="901" t="n"/>
+      <c r="AE5" s="894" t="n"/>
+      <c r="AF5" s="894" t="n"/>
+      <c r="AG5" s="894" t="n"/>
+      <c r="AH5" s="895" t="n"/>
+      <c r="AI5" s="896" t="n"/>
+      <c r="AJ5" s="896" t="n"/>
+      <c r="AK5" s="896" t="n"/>
+      <c r="AL5" s="896" t="n"/>
+      <c r="AM5" s="896" t="n"/>
+      <c r="AN5" s="897" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="732" t="n"/>
-      <c r="B6" s="678" t="n"/>
-      <c r="C6" s="678" t="n"/>
-      <c r="D6" s="678" t="n"/>
-      <c r="E6" s="678" t="n"/>
-      <c r="F6" s="678" t="n"/>
-      <c r="G6" s="678" t="n"/>
-      <c r="H6" s="678" t="n"/>
-      <c r="I6" s="678" t="n"/>
-      <c r="J6" s="678" t="n"/>
-      <c r="K6" s="678" t="n"/>
-      <c r="L6" s="678" t="n"/>
-      <c r="M6" s="678" t="n"/>
-      <c r="N6" s="678" t="n"/>
-      <c r="O6" s="678" t="n"/>
-      <c r="P6" s="678" t="n"/>
-      <c r="Q6" s="678" t="n"/>
-      <c r="R6" s="678" t="n"/>
-      <c r="S6" s="678" t="n"/>
-      <c r="T6" s="678" t="n"/>
-      <c r="U6" s="678" t="n"/>
-      <c r="V6" s="678" t="n"/>
-      <c r="W6" s="678" t="n"/>
-      <c r="X6" s="678" t="n"/>
-      <c r="Y6" s="678" t="n"/>
-      <c r="Z6" s="678" t="n"/>
-      <c r="AA6" s="678" t="n"/>
-      <c r="AB6" s="678" t="n"/>
-      <c r="AC6" s="678" t="n"/>
-      <c r="AD6" s="678" t="n"/>
-      <c r="AE6" s="678" t="n"/>
-      <c r="AF6" s="678" t="n"/>
-      <c r="AG6" s="678" t="n"/>
-      <c r="AH6" s="678" t="n"/>
-      <c r="AI6" s="678" t="n"/>
-      <c r="AJ6" s="678" t="n"/>
-      <c r="AK6" s="678" t="n"/>
-      <c r="AL6" s="678" t="n"/>
-      <c r="AM6" s="678" t="n"/>
-      <c r="AN6" s="678" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="364" t="n"/>
+      <c r="B6" s="863" t="n"/>
+      <c r="C6" s="863" t="n"/>
+      <c r="D6" s="863" t="n"/>
+      <c r="E6" s="863" t="n"/>
+      <c r="F6" s="863" t="n"/>
+      <c r="G6" s="863" t="n"/>
+      <c r="H6" s="864" t="n"/>
+      <c r="I6" s="863" t="n"/>
+      <c r="J6" s="863" t="n"/>
+      <c r="K6" s="863" t="n"/>
+      <c r="L6" s="863" t="n"/>
+      <c r="M6" s="863" t="n"/>
+      <c r="N6" s="863" t="n"/>
+      <c r="O6" s="863" t="n"/>
+      <c r="P6" s="863" t="n"/>
+      <c r="Q6" s="863" t="n"/>
+      <c r="R6" s="863" t="n"/>
+      <c r="S6" s="863" t="n"/>
+      <c r="T6" s="863" t="n"/>
+      <c r="U6" s="863" t="n"/>
+      <c r="V6" s="863" t="n"/>
+      <c r="W6" s="863" t="n"/>
+      <c r="X6" s="863" t="n"/>
+      <c r="Y6" s="863" t="n"/>
+      <c r="Z6" s="863" t="n"/>
+      <c r="AA6" s="863" t="n"/>
+      <c r="AB6" s="863" t="n"/>
+      <c r="AC6" s="863" t="n"/>
+      <c r="AD6" s="864" t="n"/>
+      <c r="AE6" s="865" t="n"/>
+      <c r="AF6" s="865" t="n"/>
+      <c r="AG6" s="865" t="n"/>
+      <c r="AH6" s="866" t="n"/>
+      <c r="AI6" s="867" t="n"/>
+      <c r="AJ6" s="867" t="n"/>
+      <c r="AK6" s="867" t="n"/>
+      <c r="AL6" s="867" t="n"/>
+      <c r="AM6" s="867" t="n"/>
+      <c r="AN6" s="868" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="679" t="inlineStr">
-        <is>
-          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="733" t="n"/>
-      <c r="I7" s="733" t="n"/>
-      <c r="J7" s="733" t="n"/>
-      <c r="K7" s="733" t="n"/>
-      <c r="L7" s="733" t="n"/>
-      <c r="M7" s="733" t="n"/>
-      <c r="N7" s="733" t="n"/>
-      <c r="O7" s="733" t="n"/>
-      <c r="P7" s="733" t="n"/>
-      <c r="Q7" s="733" t="n"/>
-      <c r="R7" s="733" t="n"/>
-      <c r="S7" s="733" t="n"/>
-      <c r="T7" s="733" t="n"/>
-      <c r="U7" s="733" t="n"/>
-      <c r="V7" s="733" t="n"/>
-      <c r="W7" s="733" t="n"/>
-      <c r="X7" s="733" t="n"/>
-      <c r="Y7" s="733" t="n"/>
-      <c r="Z7" s="733" t="n"/>
-      <c r="AA7" s="733" t="n"/>
-      <c r="AB7" s="733" t="n"/>
-      <c r="AC7" s="733" t="n"/>
-      <c r="AD7" s="733" t="n"/>
-      <c r="AE7" s="733" t="n"/>
-      <c r="AF7" s="733" t="n"/>
-      <c r="AG7" s="733" t="n"/>
-      <c r="AH7" s="733" t="n"/>
-      <c r="AI7" s="733" t="n"/>
-      <c r="AJ7" s="733" t="n"/>
-      <c r="AK7" s="733" t="n"/>
-      <c r="AL7" s="733" t="n"/>
-      <c r="AM7" s="733" t="n"/>
-      <c r="AN7" s="734" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="869" t="n"/>
+      <c r="B7" s="870" t="n"/>
+      <c r="C7" s="870" t="n"/>
+      <c r="D7" s="870" t="n"/>
+      <c r="E7" s="870" t="n"/>
+      <c r="F7" s="870" t="n"/>
+      <c r="G7" s="870" t="n"/>
+      <c r="H7" s="869" t="n"/>
+      <c r="I7" s="869" t="n"/>
+      <c r="J7" s="869" t="n"/>
+      <c r="K7" s="869" t="n"/>
+      <c r="L7" s="869" t="n"/>
+      <c r="M7" s="869" t="n"/>
+      <c r="N7" s="869" t="n"/>
+      <c r="O7" s="869" t="n"/>
+      <c r="P7" s="869" t="n"/>
+      <c r="Q7" s="869" t="n"/>
+      <c r="R7" s="869" t="n"/>
+      <c r="S7" s="869" t="n"/>
+      <c r="T7" s="869" t="n"/>
+      <c r="U7" s="869" t="n"/>
+      <c r="V7" s="869" t="n"/>
+      <c r="W7" s="869" t="n"/>
+      <c r="X7" s="869" t="n"/>
+      <c r="Y7" s="869" t="n"/>
+      <c r="Z7" s="869" t="n"/>
+      <c r="AA7" s="869" t="n"/>
+      <c r="AB7" s="869" t="n"/>
+      <c r="AC7" s="869" t="n"/>
+      <c r="AD7" s="869" t="n"/>
+      <c r="AE7" s="869" t="n"/>
+      <c r="AF7" s="869" t="n"/>
+      <c r="AG7" s="869" t="n"/>
+      <c r="AH7" s="869" t="n"/>
+      <c r="AI7" s="869" t="n"/>
+      <c r="AJ7" s="869" t="n"/>
+      <c r="AK7" s="869" t="n"/>
+      <c r="AL7" s="869" t="n"/>
+      <c r="AM7" s="869" t="n"/>
+      <c r="AN7" s="869" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="769" t="inlineStr">
@@ -18835,12 +19233,12 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="752" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+      <c r="B13" s="686" t="n"/>
+      <c r="C13" s="686" t="n"/>
+      <c r="D13" s="686" t="n"/>
+      <c r="E13" s="686" t="n"/>
+      <c r="F13" s="686" t="n"/>
+      <c r="G13" s="686" t="n"/>
       <c r="H13" s="686" t="n"/>
       <c r="I13" s="686" t="n"/>
       <c r="J13" s="686" t="n"/>
@@ -19530,50 +19928,50 @@
       <c r="AN27" s="751" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="819" t="inlineStr">
+      <c r="A28" s="382" t="inlineStr">
         <is>
           <t>NOTICE  —  Use for revalidation triggers, scope and follow-up approval actions.  Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B28" s="820" t="n"/>
-      <c r="C28" s="820" t="n"/>
-      <c r="D28" s="820" t="n"/>
-      <c r="E28" s="820" t="n"/>
-      <c r="F28" s="820" t="n"/>
-      <c r="G28" s="820" t="n"/>
-      <c r="H28" s="820" t="n"/>
-      <c r="I28" s="820" t="n"/>
-      <c r="J28" s="820" t="n"/>
-      <c r="K28" s="820" t="n"/>
-      <c r="L28" s="820" t="n"/>
-      <c r="M28" s="820" t="n"/>
-      <c r="N28" s="820" t="n"/>
-      <c r="O28" s="820" t="n"/>
-      <c r="P28" s="820" t="n"/>
-      <c r="Q28" s="820" t="n"/>
-      <c r="R28" s="820" t="n"/>
-      <c r="S28" s="820" t="n"/>
-      <c r="T28" s="820" t="n"/>
-      <c r="U28" s="820" t="n"/>
-      <c r="V28" s="820" t="n"/>
-      <c r="W28" s="820" t="n"/>
-      <c r="X28" s="820" t="n"/>
-      <c r="Y28" s="820" t="n"/>
-      <c r="Z28" s="820" t="n"/>
-      <c r="AA28" s="820" t="n"/>
-      <c r="AB28" s="820" t="n"/>
-      <c r="AC28" s="820" t="n"/>
-      <c r="AD28" s="820" t="n"/>
-      <c r="AE28" s="820" t="n"/>
-      <c r="AF28" s="820" t="n"/>
-      <c r="AG28" s="820" t="n"/>
-      <c r="AH28" s="820" t="n"/>
-      <c r="AI28" s="820" t="n"/>
-      <c r="AJ28" s="820" t="n"/>
-      <c r="AK28" s="820" t="n"/>
-      <c r="AL28" s="820" t="n"/>
-      <c r="AM28" s="820" t="n"/>
-      <c r="AN28" s="821" t="n"/>
+      <c r="B28" s="383" t="n"/>
+      <c r="C28" s="383" t="n"/>
+      <c r="D28" s="383" t="n"/>
+      <c r="E28" s="383" t="n"/>
+      <c r="F28" s="383" t="n"/>
+      <c r="G28" s="383" t="n"/>
+      <c r="H28" s="383" t="n"/>
+      <c r="I28" s="383" t="n"/>
+      <c r="J28" s="383" t="n"/>
+      <c r="K28" s="383" t="n"/>
+      <c r="L28" s="383" t="n"/>
+      <c r="M28" s="383" t="n"/>
+      <c r="N28" s="383" t="n"/>
+      <c r="O28" s="383" t="n"/>
+      <c r="P28" s="383" t="n"/>
+      <c r="Q28" s="383" t="n"/>
+      <c r="R28" s="383" t="n"/>
+      <c r="S28" s="383" t="n"/>
+      <c r="T28" s="383" t="n"/>
+      <c r="U28" s="383" t="n"/>
+      <c r="V28" s="383" t="n"/>
+      <c r="W28" s="383" t="n"/>
+      <c r="X28" s="383" t="n"/>
+      <c r="Y28" s="383" t="n"/>
+      <c r="Z28" s="383" t="n"/>
+      <c r="AA28" s="383" t="n"/>
+      <c r="AB28" s="383" t="n"/>
+      <c r="AC28" s="383" t="n"/>
+      <c r="AD28" s="383" t="n"/>
+      <c r="AE28" s="383" t="n"/>
+      <c r="AF28" s="383" t="n"/>
+      <c r="AG28" s="383" t="n"/>
+      <c r="AH28" s="383" t="n"/>
+      <c r="AI28" s="383" t="n"/>
+      <c r="AJ28" s="383" t="n"/>
+      <c r="AK28" s="383" t="n"/>
+      <c r="AL28" s="383" t="n"/>
+      <c r="AM28" s="383" t="n"/>
+      <c r="AN28" s="384" t="n"/>
     </row>
     <row r="29" hidden="1" outlineLevel="1"/>
     <row r="30" hidden="1" outlineLevel="1"/>
@@ -19858,358 +20256,354 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="827" t="n"/>
-      <c r="B1" s="828" t="n"/>
-      <c r="C1" s="828" t="n"/>
-      <c r="D1" s="828" t="n"/>
-      <c r="E1" s="828" t="n"/>
-      <c r="F1" s="828" t="n"/>
-      <c r="G1" s="828" t="n"/>
-      <c r="H1" s="829" t="n"/>
-      <c r="I1" s="830" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="871" t="n"/>
+      <c r="B1" s="775" t="n"/>
+      <c r="C1" s="775" t="n"/>
+      <c r="D1" s="775" t="n"/>
+      <c r="E1" s="775" t="n"/>
+      <c r="F1" s="775" t="n"/>
+      <c r="G1" s="775" t="n"/>
+      <c r="H1" s="872" t="n"/>
+      <c r="I1" s="873" t="inlineStr">
         <is>
           <t>FAI REPORT</t>
         </is>
       </c>
-      <c r="J1" s="828" t="n"/>
-      <c r="K1" s="828" t="n"/>
-      <c r="L1" s="828" t="n"/>
-      <c r="M1" s="828" t="n"/>
-      <c r="N1" s="828" t="n"/>
-      <c r="O1" s="828" t="n"/>
-      <c r="P1" s="828" t="n"/>
-      <c r="Q1" s="828" t="n"/>
-      <c r="R1" s="828" t="n"/>
-      <c r="S1" s="828" t="n"/>
-      <c r="T1" s="828" t="n"/>
-      <c r="U1" s="828" t="n"/>
-      <c r="V1" s="828" t="n"/>
-      <c r="W1" s="828" t="n"/>
-      <c r="X1" s="828" t="n"/>
-      <c r="Y1" s="828" t="n"/>
-      <c r="Z1" s="828" t="n"/>
-      <c r="AA1" s="828" t="n"/>
-      <c r="AB1" s="828" t="n"/>
-      <c r="AC1" s="828" t="n"/>
-      <c r="AD1" s="829" t="n"/>
-      <c r="AE1" s="518" t="inlineStr">
+      <c r="J1" s="775" t="n"/>
+      <c r="K1" s="775" t="n"/>
+      <c r="L1" s="775" t="n"/>
+      <c r="M1" s="775" t="n"/>
+      <c r="N1" s="775" t="n"/>
+      <c r="O1" s="775" t="n"/>
+      <c r="P1" s="775" t="n"/>
+      <c r="Q1" s="775" t="n"/>
+      <c r="R1" s="775" t="n"/>
+      <c r="S1" s="775" t="n"/>
+      <c r="T1" s="775" t="n"/>
+      <c r="U1" s="775" t="n"/>
+      <c r="V1" s="775" t="n"/>
+      <c r="W1" s="775" t="n"/>
+      <c r="X1" s="775" t="n"/>
+      <c r="Y1" s="775" t="n"/>
+      <c r="Z1" s="775" t="n"/>
+      <c r="AA1" s="775" t="n"/>
+      <c r="AB1" s="775" t="n"/>
+      <c r="AC1" s="775" t="n"/>
+      <c r="AD1" s="872" t="n"/>
+      <c r="AE1" s="519" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="828" t="n"/>
-      <c r="AG1" s="828" t="n"/>
-      <c r="AH1" s="831" t="n"/>
-      <c r="AI1" s="521" t="inlineStr">
+      <c r="AF1" s="775" t="n"/>
+      <c r="AG1" s="775" t="n"/>
+      <c r="AH1" s="874" t="n"/>
+      <c r="AI1" s="522" t="inlineStr">
         <is>
           <t>FRM-311</t>
         </is>
       </c>
-      <c r="AJ1" s="828" t="n"/>
-      <c r="AK1" s="828" t="n"/>
-      <c r="AL1" s="828" t="n"/>
-      <c r="AM1" s="828" t="n"/>
-      <c r="AN1" s="829" t="n"/>
+      <c r="AJ1" s="775" t="n"/>
+      <c r="AK1" s="775" t="n"/>
+      <c r="AL1" s="775" t="n"/>
+      <c r="AM1" s="775" t="n"/>
+      <c r="AN1" s="872" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="832" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="833" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="833" t="n"/>
-      <c r="AE2" s="834" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="847" t="n"/>
+      <c r="C2" s="847" t="n"/>
+      <c r="D2" s="847" t="n"/>
+      <c r="E2" s="847" t="n"/>
+      <c r="F2" s="847" t="n"/>
+      <c r="G2" s="847" t="n"/>
+      <c r="H2" s="848" t="n"/>
+      <c r="I2" s="847" t="n"/>
+      <c r="J2" s="847" t="n"/>
+      <c r="K2" s="847" t="n"/>
+      <c r="L2" s="847" t="n"/>
+      <c r="M2" s="847" t="n"/>
+      <c r="N2" s="847" t="n"/>
+      <c r="O2" s="847" t="n"/>
+      <c r="P2" s="847" t="n"/>
+      <c r="Q2" s="847" t="n"/>
+      <c r="R2" s="847" t="n"/>
+      <c r="S2" s="847" t="n"/>
+      <c r="T2" s="847" t="n"/>
+      <c r="U2" s="847" t="n"/>
+      <c r="V2" s="847" t="n"/>
+      <c r="W2" s="847" t="n"/>
+      <c r="X2" s="847" t="n"/>
+      <c r="Y2" s="847" t="n"/>
+      <c r="Z2" s="847" t="n"/>
+      <c r="AA2" s="847" t="n"/>
+      <c r="AB2" s="847" t="n"/>
+      <c r="AC2" s="847" t="n"/>
+      <c r="AD2" s="848" t="n"/>
+      <c r="AE2" s="849" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="835" t="n"/>
-      <c r="AI2" s="836" t="inlineStr">
+      <c r="AF2" s="850" t="n"/>
+      <c r="AG2" s="850" t="n"/>
+      <c r="AH2" s="851" t="n"/>
+      <c r="AI2" s="852" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="833" t="n"/>
+      <c r="AJ2" s="853" t="n"/>
+      <c r="AK2" s="853" t="n"/>
+      <c r="AL2" s="853" t="n"/>
+      <c r="AM2" s="853" t="n"/>
+      <c r="AN2" s="854" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="832" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="833" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="833" t="n"/>
-      <c r="AE3" s="834" t="inlineStr">
+      <c r="A3" s="855" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="856" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="856" t="n"/>
+      <c r="AE3" s="857" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="835" t="n"/>
-      <c r="AI3" s="836" t="inlineStr">
+      <c r="AF3" s="858" t="n"/>
+      <c r="AG3" s="858" t="n"/>
+      <c r="AH3" s="859" t="n"/>
+      <c r="AI3" s="741" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="833" t="n"/>
+      <c r="AJ3" s="860" t="n"/>
+      <c r="AK3" s="860" t="n"/>
+      <c r="AL3" s="860" t="n"/>
+      <c r="AM3" s="860" t="n"/>
+      <c r="AN3" s="861" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="832" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="833" t="n"/>
-      <c r="I4" s="837" t="inlineStr">
+      <c r="A4" s="855" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="856" t="n"/>
+      <c r="I4" s="354" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="833" t="n"/>
-      <c r="AE4" s="834" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="856" t="n"/>
+      <c r="AE4" s="857" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="835" t="n"/>
-      <c r="AI4" s="836" t="inlineStr">
+      <c r="AF4" s="858" t="n"/>
+      <c r="AG4" s="858" t="n"/>
+      <c r="AH4" s="859" t="n"/>
+      <c r="AI4" s="741" t="inlineStr">
         <is>
           <t>QA / Engineering</t>
         </is>
       </c>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="833" t="n"/>
+      <c r="AJ4" s="860" t="n"/>
+      <c r="AK4" s="860" t="n"/>
+      <c r="AL4" s="860" t="n"/>
+      <c r="AM4" s="860" t="n"/>
+      <c r="AN4" s="861" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="838" t="n"/>
-      <c r="B5" s="839" t="n"/>
-      <c r="C5" s="839" t="n"/>
-      <c r="D5" s="839" t="n"/>
-      <c r="E5" s="839" t="n"/>
-      <c r="F5" s="839" t="n"/>
-      <c r="G5" s="839" t="n"/>
-      <c r="H5" s="840" t="n"/>
-      <c r="I5" s="841" t="inlineStr">
+      <c r="A5" s="855" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="856" t="n"/>
+      <c r="I5" s="610" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="839" t="n"/>
-      <c r="K5" s="839" t="n"/>
-      <c r="L5" s="839" t="n"/>
-      <c r="M5" s="839" t="n"/>
-      <c r="N5" s="839" t="n"/>
-      <c r="O5" s="839" t="n"/>
-      <c r="P5" s="839" t="n"/>
-      <c r="Q5" s="839" t="n"/>
-      <c r="R5" s="839" t="n"/>
-      <c r="S5" s="839" t="n"/>
-      <c r="T5" s="839" t="n"/>
-      <c r="U5" s="839" t="n"/>
-      <c r="V5" s="839" t="n"/>
-      <c r="W5" s="839" t="n"/>
-      <c r="X5" s="839" t="n"/>
-      <c r="Y5" s="839" t="n"/>
-      <c r="Z5" s="839" t="n"/>
-      <c r="AA5" s="839" t="n"/>
-      <c r="AB5" s="839" t="n"/>
-      <c r="AC5" s="839" t="n"/>
-      <c r="AD5" s="840" t="n"/>
-      <c r="AE5" s="842" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="856" t="n"/>
+      <c r="AE5" s="857" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="839" t="n"/>
-      <c r="AG5" s="839" t="n"/>
-      <c r="AH5" s="843" t="n"/>
-      <c r="AI5" s="844" t="inlineStr">
+      <c r="AF5" s="858" t="n"/>
+      <c r="AG5" s="858" t="n"/>
+      <c r="AH5" s="859" t="n"/>
+      <c r="AI5" s="741" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="839" t="n"/>
-      <c r="AK5" s="839" t="n"/>
-      <c r="AL5" s="839" t="n"/>
-      <c r="AM5" s="839" t="n"/>
-      <c r="AN5" s="840" t="n"/>
+      <c r="AJ5" s="860" t="n"/>
+      <c r="AK5" s="860" t="n"/>
+      <c r="AL5" s="860" t="n"/>
+      <c r="AM5" s="860" t="n"/>
+      <c r="AN5" s="861" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="845" t="n"/>
-      <c r="B6" s="845" t="n"/>
-      <c r="C6" s="845" t="n"/>
-      <c r="D6" s="845" t="n"/>
-      <c r="E6" s="845" t="n"/>
-      <c r="F6" s="845" t="n"/>
-      <c r="G6" s="845" t="n"/>
-      <c r="H6" s="845" t="n"/>
-      <c r="I6" s="845" t="n"/>
-      <c r="J6" s="845" t="n"/>
-      <c r="K6" s="845" t="n"/>
-      <c r="L6" s="845" t="n"/>
-      <c r="M6" s="845" t="n"/>
-      <c r="N6" s="845" t="n"/>
-      <c r="O6" s="845" t="n"/>
-      <c r="P6" s="845" t="n"/>
-      <c r="Q6" s="845" t="n"/>
-      <c r="R6" s="845" t="n"/>
-      <c r="S6" s="845" t="n"/>
-      <c r="T6" s="845" t="n"/>
-      <c r="U6" s="845" t="n"/>
-      <c r="V6" s="845" t="n"/>
-      <c r="W6" s="845" t="n"/>
-      <c r="X6" s="845" t="n"/>
-      <c r="Y6" s="845" t="n"/>
-      <c r="Z6" s="845" t="n"/>
-      <c r="AA6" s="845" t="n"/>
-      <c r="AB6" s="845" t="n"/>
-      <c r="AC6" s="845" t="n"/>
-      <c r="AD6" s="845" t="n"/>
-      <c r="AE6" s="845" t="n"/>
-      <c r="AF6" s="845" t="n"/>
-      <c r="AG6" s="845" t="n"/>
-      <c r="AH6" s="845" t="n"/>
-      <c r="AI6" s="845" t="n"/>
-      <c r="AJ6" s="845" t="n"/>
-      <c r="AK6" s="845" t="n"/>
-      <c r="AL6" s="845" t="n"/>
-      <c r="AM6" s="845" t="n"/>
-      <c r="AN6" s="845" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="875" t="n"/>
+      <c r="B6" s="876" t="n"/>
+      <c r="C6" s="876" t="n"/>
+      <c r="D6" s="876" t="n"/>
+      <c r="E6" s="876" t="n"/>
+      <c r="F6" s="876" t="n"/>
+      <c r="G6" s="876" t="n"/>
+      <c r="H6" s="877" t="n"/>
+      <c r="I6" s="876" t="n"/>
+      <c r="J6" s="876" t="n"/>
+      <c r="K6" s="876" t="n"/>
+      <c r="L6" s="876" t="n"/>
+      <c r="M6" s="876" t="n"/>
+      <c r="N6" s="876" t="n"/>
+      <c r="O6" s="876" t="n"/>
+      <c r="P6" s="876" t="n"/>
+      <c r="Q6" s="876" t="n"/>
+      <c r="R6" s="876" t="n"/>
+      <c r="S6" s="876" t="n"/>
+      <c r="T6" s="876" t="n"/>
+      <c r="U6" s="876" t="n"/>
+      <c r="V6" s="876" t="n"/>
+      <c r="W6" s="876" t="n"/>
+      <c r="X6" s="876" t="n"/>
+      <c r="Y6" s="876" t="n"/>
+      <c r="Z6" s="876" t="n"/>
+      <c r="AA6" s="876" t="n"/>
+      <c r="AB6" s="876" t="n"/>
+      <c r="AC6" s="876" t="n"/>
+      <c r="AD6" s="877" t="n"/>
+      <c r="AE6" s="878" t="n"/>
+      <c r="AF6" s="878" t="n"/>
+      <c r="AG6" s="878" t="n"/>
+      <c r="AH6" s="879" t="n"/>
+      <c r="AI6" s="880" t="n"/>
+      <c r="AJ6" s="880" t="n"/>
+      <c r="AK6" s="880" t="n"/>
+      <c r="AL6" s="880" t="n"/>
+      <c r="AM6" s="880" t="n"/>
+      <c r="AN6" s="881" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="648" t="inlineStr">
-        <is>
-          <t>REF_LINKS</t>
-        </is>
-      </c>
-      <c r="B7" s="775" t="n"/>
-      <c r="C7" s="775" t="n"/>
-      <c r="D7" s="775" t="n"/>
-      <c r="E7" s="775" t="n"/>
-      <c r="F7" s="775" t="n"/>
-      <c r="G7" s="775" t="n"/>
-      <c r="H7" s="846" t="n"/>
-      <c r="I7" s="846" t="n"/>
-      <c r="J7" s="846" t="n"/>
-      <c r="K7" s="846" t="n"/>
-      <c r="L7" s="846" t="n"/>
-      <c r="M7" s="846" t="n"/>
-      <c r="N7" s="846" t="n"/>
-      <c r="O7" s="846" t="n"/>
-      <c r="P7" s="846" t="n"/>
-      <c r="Q7" s="846" t="n"/>
-      <c r="R7" s="846" t="n"/>
-      <c r="S7" s="846" t="n"/>
-      <c r="T7" s="846" t="n"/>
-      <c r="U7" s="846" t="n"/>
-      <c r="V7" s="846" t="n"/>
-      <c r="W7" s="846" t="n"/>
-      <c r="X7" s="846" t="n"/>
-      <c r="Y7" s="846" t="n"/>
-      <c r="Z7" s="846" t="n"/>
-      <c r="AA7" s="846" t="n"/>
-      <c r="AB7" s="846" t="n"/>
-      <c r="AC7" s="846" t="n"/>
-      <c r="AD7" s="846" t="n"/>
-      <c r="AE7" s="846" t="n"/>
-      <c r="AF7" s="846" t="n"/>
-      <c r="AG7" s="846" t="n"/>
-      <c r="AH7" s="846" t="n"/>
-      <c r="AI7" s="846" t="n"/>
-      <c r="AJ7" s="846" t="n"/>
-      <c r="AK7" s="846" t="n"/>
-      <c r="AL7" s="846" t="n"/>
-      <c r="AM7" s="846" t="n"/>
-      <c r="AN7" s="846" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="907" t="n"/>
+      <c r="B7" s="870" t="n"/>
+      <c r="C7" s="870" t="n"/>
+      <c r="D7" s="870" t="n"/>
+      <c r="E7" s="870" t="n"/>
+      <c r="F7" s="870" t="n"/>
+      <c r="G7" s="870" t="n"/>
+      <c r="H7" s="883" t="n"/>
+      <c r="I7" s="883" t="n"/>
+      <c r="J7" s="883" t="n"/>
+      <c r="K7" s="883" t="n"/>
+      <c r="L7" s="883" t="n"/>
+      <c r="M7" s="883" t="n"/>
+      <c r="N7" s="883" t="n"/>
+      <c r="O7" s="883" t="n"/>
+      <c r="P7" s="883" t="n"/>
+      <c r="Q7" s="883" t="n"/>
+      <c r="R7" s="883" t="n"/>
+      <c r="S7" s="883" t="n"/>
+      <c r="T7" s="883" t="n"/>
+      <c r="U7" s="883" t="n"/>
+      <c r="V7" s="883" t="n"/>
+      <c r="W7" s="883" t="n"/>
+      <c r="X7" s="883" t="n"/>
+      <c r="Y7" s="883" t="n"/>
+      <c r="Z7" s="883" t="n"/>
+      <c r="AA7" s="883" t="n"/>
+      <c r="AB7" s="883" t="n"/>
+      <c r="AC7" s="883" t="n"/>
+      <c r="AD7" s="883" t="n"/>
+      <c r="AE7" s="883" t="n"/>
+      <c r="AF7" s="883" t="n"/>
+      <c r="AG7" s="883" t="n"/>
+      <c r="AH7" s="883" t="n"/>
+      <c r="AI7" s="883" t="n"/>
+      <c r="AJ7" s="883" t="n"/>
+      <c r="AK7" s="883" t="n"/>
+      <c r="AL7" s="883" t="n"/>
+      <c r="AM7" s="883" t="n"/>
+      <c r="AN7" s="883" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="649" t="inlineStr">
+      <c r="A8" s="908" t="inlineStr">
         <is>
           <t>Reference Epicor / M365 / controlled documents only.</t>
         </is>
@@ -20249,7 +20643,7 @@
       <c r="AN8" s="846" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="650" t="inlineStr">
+      <c r="A9" s="909" t="inlineStr">
         <is>
           <t>Ref Type</t>
         </is>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -5085,6 +5085,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5115,6 +5118,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5145,6 +5151,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5175,6 +5184,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -10940,6 +10952,7 @@
       <c r="I34" s="393" t="n"/>
       <c r="J34" s="394" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="405" t="inlineStr">
         <is>
@@ -11656,6 +11669,7 @@
       <c r="G26" s="397" t="n"/>
       <c r="H26" s="394" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="405" t="inlineStr">
         <is>
@@ -12342,6 +12356,7 @@
       <c r="F26" s="393" t="n"/>
       <c r="G26" s="394" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="405" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -4,12 +4,12 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-311_FAI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAR_RESULTS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATL_PROC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVALIDATION" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAR_RESULTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATL_PROC" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVALIDATION" sheetId="6" state="veryHidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="7" state="veryHidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_STATUS_CORE">'_LISTS'!$A$2:$A$7</definedName>
@@ -10952,7 +10952,6 @@
       <c r="I34" s="393" t="n"/>
       <c r="J34" s="394" t="n"/>
     </row>
-    <row r="35"/>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="405" t="inlineStr">
         <is>
@@ -11669,7 +11668,6 @@
       <c r="G26" s="397" t="n"/>
       <c r="H26" s="394" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="405" t="inlineStr">
         <is>
@@ -12356,7 +12354,6 @@
       <c r="F26" s="393" t="n"/>
       <c r="G26" s="394" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="405" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -5850,7 +5850,7 @@
       <c r="BR5" s="285" t="n"/>
       <c r="BS5" s="286" t="inlineStr">
         <is>
-          <t>QA Manager</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="BT5" s="283" t="n"/>

--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -4,12 +4,13 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM-311_FAI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAR_RESULTS" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATL_PROC" sheetId="5" state="veryHidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVALIDATION" sheetId="6" state="veryHidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="7" state="veryHidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_IMPORT" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAR_RESULTS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATL_PROC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVALIDATION" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_STATUS_CORE">'_LISTS'!$A$2:$A$7</definedName>
@@ -4936,6 +4937,41 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -5067,11 +5103,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>161925</colOff>
+      <colOff>314325</colOff>
       <row>0</row>
-      <rowOff>314325</rowOff>
+      <rowOff>152400</rowOff>
     </from>
-    <ext cx="1123950" cy="323850"/>
+    <ext cx="2257425" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5100,11 +5136,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>161925</colOff>
+      <colOff>314325</colOff>
       <row>0</row>
-      <rowOff>314325</rowOff>
+      <rowOff>152400</rowOff>
     </from>
-    <ext cx="1123950" cy="323850"/>
+    <ext cx="2257425" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5133,44 +5169,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>161925</colOff>
+      <colOff>314325</colOff>
       <row>0</row>
-      <rowOff>314325</rowOff>
+      <rowOff>152400</rowOff>
     </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
+    <ext cx="2257425" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5850,7 +5853,7 @@
       <c r="BR5" s="285" t="n"/>
       <c r="BS5" s="286" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>QA Manager</t>
         </is>
       </c>
       <c r="BT5" s="283" t="n"/>
@@ -6327,7 +6330,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="298" t="inlineStr">
         <is>
-          <t>Sample / First Article ID</t>
+          <t>Linked FRM-302 / FRM-641</t>
         </is>
       </c>
       <c r="B12" s="283" t="n"/>
@@ -6372,7 +6375,7 @@
       <c r="AO12" s="285" t="n"/>
       <c r="AP12" s="300" t="inlineStr">
         <is>
-          <t>Record Status</t>
+          <t>Ref: SOP-301</t>
         </is>
       </c>
       <c r="AQ12" s="283" t="n"/>
@@ -6388,7 +6391,11 @@
       <c r="BA12" s="283" t="n"/>
       <c r="BB12" s="283" t="n"/>
       <c r="BC12" s="285" t="n"/>
-      <c r="BD12" s="286" t="n"/>
+      <c r="BD12" s="286" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="BE12" s="283" t="n"/>
       <c r="BF12" s="283" t="n"/>
       <c r="BG12" s="283" t="n"/>
@@ -9500,6 +9507,28 @@
     <mergeCell ref="O18:AO18"/>
     <mergeCell ref="BS5:CD5"/>
   </mergeCells>
+  <conditionalFormatting sqref="BM22:BM31">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BH35:BH39">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="16">
     <dataValidation sqref="O8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled drop-down values only." prompt="Select REF_JOB_WO_MASTER" type="list">
       <formula1>=_IMPORT!$C$2:$C$5</formula1>
@@ -12960,9 +12989,88 @@
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-302, FRM-641; Parent ref: SOP-301; CF: checklist Result; CF: action Status</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-311_FAI_Report.xlsx
@@ -4824,7 +4824,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="80" fillId="47" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4954,6 +4954,121 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>Thông tin FAI
+AS9102 Rev C yêu cầu FAI cho first article.
+FAI phải cover tất cả characteristics trên bản vẽ.</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số FAI
+Mã duy nhất cho First Article Inspection.
+Ví dụ: FAI-HES1234-001</t>
+      </text>
+    </comment>
+    <comment ref="AC9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã chi tiết / Phiên bản
+Part number và revision.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Phiên bản bản vẽ
+Drawing revision áp dụng cho FAI này.</t>
+      </text>
+    </comment>
+    <comment ref="AC10" authorId="0" shapeId="0">
+      <text>
+        <t>Loại FAI
+Full = lần đầu sản xuất part mới.
+Partial = thay đổi ảnh hưởng một số features.
+Delta = chỉ kiểm tra features bị thay đổi.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Thông tin part (Form 1 AS9102)
+Ghi thông tin nhận dạng part, vật liệu, quy trình sản xuất.</t>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>Tên part
+Tên đầy đủ của part.
+Ví dụ: Chamber Lid, Gas Distribution Plate.</t>
+      </text>
+    </comment>
+    <comment ref="AC13" authorId="0" shapeId="0">
+      <text>
+        <t>Vật liệu / Spec
+Grade vật liệu và specification.
+Ví dụ: AL6061-T6 per AMS-QQ-A-250/11.</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0">
+      <text>
+        <t>Khách hàng / PO
+Tên khách hàng và số PO.</t>
+      </text>
+    </comment>
+    <comment ref="AC14" authorId="0" shapeId="0">
+      <text>
+        <t>Tóm tắt quy trình sản xuất
+Liệt kê các bước chính: CNC turning → CNC milling → deburr → anodize → inspect → clean pack.</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả đo từng đặc tính (Form 3 AS9102)
+Ghi TẤT CẢ dimensions và yêu cầu từ bản vẽ.
+Mỗi dòng = 1 characteristic. Phải đo và ghi kết quả actual.
+AS9102 yêu cầu 100% characteristics phải được verify.</t>
+      </text>
+    </comment>
+    <comment ref="H17" authorId="0" shapeId="0">
+      <text>
+        <t>Đặc tính / Kích thước
+Ghi mô tả characteristic từ bản vẽ.
+Bao gồm balloon number nếu có.
+Ví dụ: Ø25.00 ±0.02 (Balloon #5)</t>
+      </text>
+    </comment>
+    <comment ref="AD17" authorId="0" shapeId="0">
+      <text>
+        <t>Danh nghĩa / Dung sai
+Ghi giá trị nominal và tolerance từ bản vẽ.
+Ví dụ: 25.00 ±0.02, Ra 0.8 max, Position Ø0.05.</t>
+      </text>
+    </comment>
+    <comment ref="AR17" authorId="0" shapeId="0">
+      <text>
+        <t>Giá trị thực tế
+Ghi giá trị đo thực tế.
+Ví dụ: 25.01, Ra 0.6, Position Ø0.03.
+Phải ghi số cụ thể, không ghi "OK" hay "PASS".</t>
+      </text>
+    </comment>
+    <comment ref="AX17" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS = trong dung sai.
+FAIL = ngoài dung sai → ghi NCR.
+NA = không đo được (ghi lý do trong ghi chú).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5275,7 +5390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:BD48"/>
+  <dimension ref="A2:BD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.375" customWidth="1" style="264" min="1" max="1"/>
@@ -6296,8 +6411,9 @@
       <c r="BD17" s="479" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>1</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="n"/>
@@ -6337,7 +6453,7 @@
       <c r="AC18" s="492" t="n"/>
       <c r="AD18" s="495" t="inlineStr">
         <is>
-          <t>(Enter nominal +/- tolerance).</t>
+          <t>(Nominal ± tolerance).</t>
         </is>
       </c>
       <c r="AE18" s="491" t="n"/>
@@ -6368,8 +6484,9 @@
       <c r="BD18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>2</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="n"/>
@@ -6432,8 +6549,9 @@
       <c r="BD19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>3</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="492" t="n"/>
@@ -6496,8 +6614,9 @@
       <c r="BD20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="490" t="n">
-        <v>4</v>
+      <c r="A21" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B21" s="491" t="n"/>
       <c r="C21" s="492" t="n"/>
@@ -6556,8 +6675,9 @@
       <c r="BD21" s="498" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="490" t="n">
-        <v>5</v>
+      <c r="A22" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B22" s="491" t="n"/>
       <c r="C22" s="492" t="n"/>
@@ -6616,8 +6736,9 @@
       <c r="BD22" s="498" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="490" t="n">
-        <v>6</v>
+      <c r="A23" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B23" s="491" t="n"/>
       <c r="C23" s="492" t="n"/>
@@ -6676,8 +6797,9 @@
       <c r="BD23" s="498" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="264">
-      <c r="A24" s="490" t="n">
-        <v>7</v>
+      <c r="A24" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B24" s="491" t="n"/>
       <c r="C24" s="492" t="n"/>
@@ -6736,8 +6858,9 @@
       <c r="BD24" s="498" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="264">
-      <c r="A25" s="490" t="n">
-        <v>8</v>
+      <c r="A25" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B25" s="491" t="n"/>
       <c r="C25" s="492" t="n"/>
@@ -6796,8 +6919,9 @@
       <c r="BD25" s="498" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="264">
-      <c r="A26" s="490" t="n">
-        <v>9</v>
+      <c r="A26" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B26" s="491" t="n"/>
       <c r="C26" s="492" t="n"/>
@@ -6856,8 +6980,9 @@
       <c r="BD26" s="498" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="264">
-      <c r="A27" s="490" t="n">
-        <v>10</v>
+      <c r="A27" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B27" s="491" t="n"/>
       <c r="C27" s="492" t="n"/>
@@ -6916,8 +7041,9 @@
       <c r="BD27" s="498" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="264">
-      <c r="A28" s="490" t="n">
-        <v>11</v>
+      <c r="A28" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B28" s="491" t="n"/>
       <c r="C28" s="492" t="n"/>
@@ -6976,8 +7102,9 @@
       <c r="BD28" s="498" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="264">
-      <c r="A29" s="490" t="n">
-        <v>12</v>
+      <c r="A29" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B29" s="491" t="n"/>
       <c r="C29" s="492" t="n"/>
@@ -7036,8 +7163,9 @@
       <c r="BD29" s="498" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="264">
-      <c r="A30" s="490" t="n">
-        <v>13</v>
+      <c r="A30" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B30" s="491" t="n"/>
       <c r="C30" s="492" t="n"/>
@@ -7096,8 +7224,9 @@
       <c r="BD30" s="498" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="264">
-      <c r="A31" s="490" t="n">
-        <v>14</v>
+      <c r="A31" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B31" s="491" t="n"/>
       <c r="C31" s="492" t="n"/>
@@ -7156,8 +7285,9 @@
       <c r="BD31" s="498" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="264">
-      <c r="A32" s="490" t="n">
-        <v>15</v>
+      <c r="A32" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B32" s="491" t="n"/>
       <c r="C32" s="492" t="n"/>
@@ -7216,8 +7346,9 @@
       <c r="BD32" s="498" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1" s="264">
-      <c r="A33" s="490" t="n">
-        <v>16</v>
+      <c r="A33" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B33" s="491" t="n"/>
       <c r="C33" s="492" t="n"/>
@@ -7276,8 +7407,9 @@
       <c r="BD33" s="498" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1" s="264">
-      <c r="A34" s="490" t="n">
-        <v>17</v>
+      <c r="A34" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B34" s="491" t="n"/>
       <c r="C34" s="492" t="n"/>
@@ -7336,8 +7468,9 @@
       <c r="BD34" s="498" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="264">
-      <c r="A35" s="490" t="n">
-        <v>18</v>
+      <c r="A35" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B35" s="491" t="n"/>
       <c r="C35" s="492" t="n"/>
@@ -7396,8 +7529,9 @@
       <c r="BD35" s="498" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="264">
-      <c r="A36" s="490" t="n">
-        <v>19</v>
+      <c r="A36" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B36" s="491" t="n"/>
       <c r="C36" s="492" t="n"/>
@@ -7456,8 +7590,9 @@
       <c r="BD36" s="498" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1" s="264">
-      <c r="A37" s="490" t="n">
-        <v>20</v>
+      <c r="A37" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B37" s="491" t="n"/>
       <c r="C37" s="492" t="n"/>
@@ -7516,8 +7651,9 @@
       <c r="BD37" s="498" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1" s="264">
-      <c r="A38" s="490" t="n">
-        <v>21</v>
+      <c r="A38" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B38" s="491" t="n"/>
       <c r="C38" s="492" t="n"/>
@@ -7576,8 +7712,9 @@
       <c r="BD38" s="498" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1" s="264">
-      <c r="A39" s="490" t="n">
-        <v>22</v>
+      <c r="A39" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
       </c>
       <c r="B39" s="491" t="n"/>
       <c r="C39" s="492" t="n"/>
@@ -7636,453 +7773,495 @@
       <c r="BD39" s="498" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1" s="264">
-      <c r="A40" s="503" t="n">
-        <v>23</v>
-      </c>
-      <c r="B40" s="481" t="n"/>
-      <c r="C40" s="482" t="n"/>
-      <c r="D40" s="504" t="n"/>
-      <c r="E40" s="481" t="n"/>
-      <c r="F40" s="481" t="n"/>
-      <c r="G40" s="482" t="n"/>
-      <c r="H40" s="505" t="n"/>
-      <c r="I40" s="481" t="n"/>
-      <c r="J40" s="481" t="n"/>
-      <c r="K40" s="481" t="n"/>
-      <c r="L40" s="481" t="n"/>
-      <c r="M40" s="481" t="n"/>
-      <c r="N40" s="481" t="n"/>
-      <c r="O40" s="481" t="n"/>
-      <c r="P40" s="481" t="n"/>
-      <c r="Q40" s="481" t="n"/>
-      <c r="R40" s="481" t="n"/>
-      <c r="S40" s="481" t="n"/>
-      <c r="T40" s="481" t="n"/>
-      <c r="U40" s="481" t="n"/>
-      <c r="V40" s="481" t="n"/>
-      <c r="W40" s="481" t="n"/>
-      <c r="X40" s="481" t="n"/>
-      <c r="Y40" s="481" t="n"/>
-      <c r="Z40" s="481" t="n"/>
-      <c r="AA40" s="481" t="n"/>
-      <c r="AB40" s="481" t="n"/>
-      <c r="AC40" s="482" t="n"/>
-      <c r="AD40" s="504" t="n"/>
-      <c r="AE40" s="481" t="n"/>
-      <c r="AF40" s="481" t="n"/>
-      <c r="AG40" s="481" t="n"/>
-      <c r="AH40" s="481" t="n"/>
-      <c r="AI40" s="481" t="n"/>
-      <c r="AJ40" s="481" t="n"/>
-      <c r="AK40" s="481" t="n"/>
-      <c r="AL40" s="481" t="n"/>
-      <c r="AM40" s="481" t="n"/>
-      <c r="AN40" s="481" t="n"/>
-      <c r="AO40" s="481" t="n"/>
-      <c r="AP40" s="481" t="n"/>
-      <c r="AQ40" s="482" t="n"/>
-      <c r="AR40" s="506" t="n"/>
-      <c r="AS40" s="481" t="n"/>
-      <c r="AT40" s="481" t="n"/>
-      <c r="AU40" s="481" t="n"/>
-      <c r="AV40" s="481" t="n"/>
-      <c r="AW40" s="482" t="n"/>
-      <c r="AX40" s="507" t="n"/>
-      <c r="AY40" s="481" t="n"/>
-      <c r="AZ40" s="481" t="n"/>
-      <c r="BA40" s="481" t="n"/>
-      <c r="BB40" s="481" t="n"/>
-      <c r="BC40" s="481" t="n"/>
-      <c r="BD40" s="486" t="n"/>
+      <c r="A40" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
+      </c>
+      <c r="B40" s="491" t="n"/>
+      <c r="C40" s="492" t="n"/>
+      <c r="D40" s="500" t="n"/>
+      <c r="E40" s="491" t="n"/>
+      <c r="F40" s="491" t="n"/>
+      <c r="G40" s="492" t="n"/>
+      <c r="H40" s="502" t="n"/>
+      <c r="I40" s="491" t="n"/>
+      <c r="J40" s="491" t="n"/>
+      <c r="K40" s="491" t="n"/>
+      <c r="L40" s="491" t="n"/>
+      <c r="M40" s="491" t="n"/>
+      <c r="N40" s="491" t="n"/>
+      <c r="O40" s="491" t="n"/>
+      <c r="P40" s="491" t="n"/>
+      <c r="Q40" s="491" t="n"/>
+      <c r="R40" s="491" t="n"/>
+      <c r="S40" s="491" t="n"/>
+      <c r="T40" s="491" t="n"/>
+      <c r="U40" s="491" t="n"/>
+      <c r="V40" s="491" t="n"/>
+      <c r="W40" s="491" t="n"/>
+      <c r="X40" s="491" t="n"/>
+      <c r="Y40" s="491" t="n"/>
+      <c r="Z40" s="491" t="n"/>
+      <c r="AA40" s="491" t="n"/>
+      <c r="AB40" s="491" t="n"/>
+      <c r="AC40" s="492" t="n"/>
+      <c r="AD40" s="500" t="n"/>
+      <c r="AE40" s="491" t="n"/>
+      <c r="AF40" s="491" t="n"/>
+      <c r="AG40" s="491" t="n"/>
+      <c r="AH40" s="491" t="n"/>
+      <c r="AI40" s="491" t="n"/>
+      <c r="AJ40" s="491" t="n"/>
+      <c r="AK40" s="491" t="n"/>
+      <c r="AL40" s="491" t="n"/>
+      <c r="AM40" s="491" t="n"/>
+      <c r="AN40" s="491" t="n"/>
+      <c r="AO40" s="491" t="n"/>
+      <c r="AP40" s="491" t="n"/>
+      <c r="AQ40" s="492" t="n"/>
+      <c r="AR40" s="496" t="n"/>
+      <c r="AS40" s="491" t="n"/>
+      <c r="AT40" s="491" t="n"/>
+      <c r="AU40" s="491" t="n"/>
+      <c r="AV40" s="491" t="n"/>
+      <c r="AW40" s="492" t="n"/>
+      <c r="AX40" s="497" t="n"/>
+      <c r="AY40" s="491" t="n"/>
+      <c r="AZ40" s="491" t="n"/>
+      <c r="BA40" s="491" t="n"/>
+      <c r="BB40" s="491" t="n"/>
+      <c r="BC40" s="491" t="n"/>
+      <c r="BD40" s="498" t="n"/>
     </row>
-    <row r="41" ht="4" customHeight="1" s="264">
-      <c r="A41" s="469" t="n"/>
-      <c r="B41" s="26" t="n"/>
-      <c r="C41" s="26" t="n"/>
-      <c r="D41" s="26" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="26" t="n"/>
-      <c r="G41" s="26" t="n"/>
-      <c r="H41" s="26" t="n"/>
-      <c r="I41" s="26" t="n"/>
-      <c r="J41" s="26" t="n"/>
-      <c r="K41" s="26" t="n"/>
-      <c r="L41" s="26" t="n"/>
-      <c r="M41" s="26" t="n"/>
-      <c r="N41" s="26" t="n"/>
-      <c r="O41" s="26" t="n"/>
-      <c r="P41" s="26" t="n"/>
-      <c r="Q41" s="26" t="n"/>
-      <c r="R41" s="26" t="n"/>
-      <c r="S41" s="26" t="n"/>
-      <c r="T41" s="26" t="n"/>
-      <c r="U41" s="26" t="n"/>
-      <c r="V41" s="26" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="26" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="26" t="n"/>
-      <c r="AB41" s="26" t="n"/>
-      <c r="AC41" s="26" t="n"/>
-      <c r="AD41" s="26" t="n"/>
-      <c r="AE41" s="26" t="n"/>
-      <c r="AF41" s="26" t="n"/>
-      <c r="AG41" s="26" t="n"/>
-      <c r="AH41" s="26" t="n"/>
-      <c r="AI41" s="26" t="n"/>
-      <c r="AJ41" s="26" t="n"/>
-      <c r="AK41" s="26" t="n"/>
-      <c r="AL41" s="26" t="n"/>
-      <c r="AM41" s="26" t="n"/>
-      <c r="AN41" s="26" t="n"/>
-      <c r="AO41" s="26" t="n"/>
-      <c r="AP41" s="26" t="n"/>
-      <c r="AQ41" s="26" t="n"/>
-      <c r="AR41" s="26" t="n"/>
-      <c r="AS41" s="26" t="n"/>
-      <c r="AT41" s="26" t="n"/>
-      <c r="AU41" s="26" t="n"/>
-      <c r="AV41" s="26" t="n"/>
-      <c r="AW41" s="26" t="n"/>
-      <c r="AX41" s="26" t="n"/>
-      <c r="AY41" s="26" t="n"/>
-      <c r="AZ41" s="26" t="n"/>
-      <c r="BA41" s="26" t="n"/>
-      <c r="BB41" s="26" t="n"/>
-      <c r="BC41" s="26" t="n"/>
-      <c r="BD41" s="26" t="n"/>
+    <row r="41" ht="20" customHeight="1" s="264">
+      <c r="A41" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
+      </c>
+      <c r="B41" s="491" t="n"/>
+      <c r="C41" s="492" t="n"/>
+      <c r="D41" s="500" t="n"/>
+      <c r="E41" s="491" t="n"/>
+      <c r="F41" s="491" t="n"/>
+      <c r="G41" s="492" t="n"/>
+      <c r="H41" s="501" t="n"/>
+      <c r="I41" s="491" t="n"/>
+      <c r="J41" s="491" t="n"/>
+      <c r="K41" s="491" t="n"/>
+      <c r="L41" s="491" t="n"/>
+      <c r="M41" s="491" t="n"/>
+      <c r="N41" s="491" t="n"/>
+      <c r="O41" s="491" t="n"/>
+      <c r="P41" s="491" t="n"/>
+      <c r="Q41" s="491" t="n"/>
+      <c r="R41" s="491" t="n"/>
+      <c r="S41" s="491" t="n"/>
+      <c r="T41" s="491" t="n"/>
+      <c r="U41" s="491" t="n"/>
+      <c r="V41" s="491" t="n"/>
+      <c r="W41" s="491" t="n"/>
+      <c r="X41" s="491" t="n"/>
+      <c r="Y41" s="491" t="n"/>
+      <c r="Z41" s="491" t="n"/>
+      <c r="AA41" s="491" t="n"/>
+      <c r="AB41" s="491" t="n"/>
+      <c r="AC41" s="492" t="n"/>
+      <c r="AD41" s="500" t="n"/>
+      <c r="AE41" s="491" t="n"/>
+      <c r="AF41" s="491" t="n"/>
+      <c r="AG41" s="491" t="n"/>
+      <c r="AH41" s="491" t="n"/>
+      <c r="AI41" s="491" t="n"/>
+      <c r="AJ41" s="491" t="n"/>
+      <c r="AK41" s="491" t="n"/>
+      <c r="AL41" s="491" t="n"/>
+      <c r="AM41" s="491" t="n"/>
+      <c r="AN41" s="491" t="n"/>
+      <c r="AO41" s="491" t="n"/>
+      <c r="AP41" s="491" t="n"/>
+      <c r="AQ41" s="492" t="n"/>
+      <c r="AR41" s="496" t="n"/>
+      <c r="AS41" s="491" t="n"/>
+      <c r="AT41" s="491" t="n"/>
+      <c r="AU41" s="491" t="n"/>
+      <c r="AV41" s="491" t="n"/>
+      <c r="AW41" s="492" t="n"/>
+      <c r="AX41" s="497" t="n"/>
+      <c r="AY41" s="491" t="n"/>
+      <c r="AZ41" s="491" t="n"/>
+      <c r="BA41" s="491" t="n"/>
+      <c r="BB41" s="491" t="n"/>
+      <c r="BC41" s="491" t="n"/>
+      <c r="BD41" s="498" t="n"/>
     </row>
-    <row r="42" ht="17" customHeight="1" s="264">
-      <c r="A42" s="470" t="inlineStr">
+    <row r="42" ht="20" customHeight="1" s="264">
+      <c r="A42" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
+      </c>
+      <c r="B42" s="491" t="n"/>
+      <c r="C42" s="492" t="n"/>
+      <c r="D42" s="500" t="n"/>
+      <c r="E42" s="491" t="n"/>
+      <c r="F42" s="491" t="n"/>
+      <c r="G42" s="492" t="n"/>
+      <c r="H42" s="502" t="n"/>
+      <c r="I42" s="491" t="n"/>
+      <c r="J42" s="491" t="n"/>
+      <c r="K42" s="491" t="n"/>
+      <c r="L42" s="491" t="n"/>
+      <c r="M42" s="491" t="n"/>
+      <c r="N42" s="491" t="n"/>
+      <c r="O42" s="491" t="n"/>
+      <c r="P42" s="491" t="n"/>
+      <c r="Q42" s="491" t="n"/>
+      <c r="R42" s="491" t="n"/>
+      <c r="S42" s="491" t="n"/>
+      <c r="T42" s="491" t="n"/>
+      <c r="U42" s="491" t="n"/>
+      <c r="V42" s="491" t="n"/>
+      <c r="W42" s="491" t="n"/>
+      <c r="X42" s="491" t="n"/>
+      <c r="Y42" s="491" t="n"/>
+      <c r="Z42" s="491" t="n"/>
+      <c r="AA42" s="491" t="n"/>
+      <c r="AB42" s="491" t="n"/>
+      <c r="AC42" s="492" t="n"/>
+      <c r="AD42" s="500" t="n"/>
+      <c r="AE42" s="491" t="n"/>
+      <c r="AF42" s="491" t="n"/>
+      <c r="AG42" s="491" t="n"/>
+      <c r="AH42" s="491" t="n"/>
+      <c r="AI42" s="491" t="n"/>
+      <c r="AJ42" s="491" t="n"/>
+      <c r="AK42" s="491" t="n"/>
+      <c r="AL42" s="491" t="n"/>
+      <c r="AM42" s="491" t="n"/>
+      <c r="AN42" s="491" t="n"/>
+      <c r="AO42" s="491" t="n"/>
+      <c r="AP42" s="491" t="n"/>
+      <c r="AQ42" s="492" t="n"/>
+      <c r="AR42" s="496" t="n"/>
+      <c r="AS42" s="491" t="n"/>
+      <c r="AT42" s="491" t="n"/>
+      <c r="AU42" s="491" t="n"/>
+      <c r="AV42" s="491" t="n"/>
+      <c r="AW42" s="492" t="n"/>
+      <c r="AX42" s="497" t="n"/>
+      <c r="AY42" s="491" t="n"/>
+      <c r="AZ42" s="491" t="n"/>
+      <c r="BA42" s="491" t="n"/>
+      <c r="BB42" s="491" t="n"/>
+      <c r="BC42" s="491" t="n"/>
+      <c r="BD42" s="498" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="264">
+      <c r="A43" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
+      </c>
+      <c r="B43" s="491" t="n"/>
+      <c r="C43" s="492" t="n"/>
+      <c r="D43" s="500" t="n"/>
+      <c r="E43" s="491" t="n"/>
+      <c r="F43" s="491" t="n"/>
+      <c r="G43" s="492" t="n"/>
+      <c r="H43" s="501" t="n"/>
+      <c r="I43" s="491" t="n"/>
+      <c r="J43" s="491" t="n"/>
+      <c r="K43" s="491" t="n"/>
+      <c r="L43" s="491" t="n"/>
+      <c r="M43" s="491" t="n"/>
+      <c r="N43" s="491" t="n"/>
+      <c r="O43" s="491" t="n"/>
+      <c r="P43" s="491" t="n"/>
+      <c r="Q43" s="491" t="n"/>
+      <c r="R43" s="491" t="n"/>
+      <c r="S43" s="491" t="n"/>
+      <c r="T43" s="491" t="n"/>
+      <c r="U43" s="491" t="n"/>
+      <c r="V43" s="491" t="n"/>
+      <c r="W43" s="491" t="n"/>
+      <c r="X43" s="491" t="n"/>
+      <c r="Y43" s="491" t="n"/>
+      <c r="Z43" s="491" t="n"/>
+      <c r="AA43" s="491" t="n"/>
+      <c r="AB43" s="491" t="n"/>
+      <c r="AC43" s="492" t="n"/>
+      <c r="AD43" s="500" t="n"/>
+      <c r="AE43" s="491" t="n"/>
+      <c r="AF43" s="491" t="n"/>
+      <c r="AG43" s="491" t="n"/>
+      <c r="AH43" s="491" t="n"/>
+      <c r="AI43" s="491" t="n"/>
+      <c r="AJ43" s="491" t="n"/>
+      <c r="AK43" s="491" t="n"/>
+      <c r="AL43" s="491" t="n"/>
+      <c r="AM43" s="491" t="n"/>
+      <c r="AN43" s="491" t="n"/>
+      <c r="AO43" s="491" t="n"/>
+      <c r="AP43" s="491" t="n"/>
+      <c r="AQ43" s="492" t="n"/>
+      <c r="AR43" s="496" t="n"/>
+      <c r="AS43" s="491" t="n"/>
+      <c r="AT43" s="491" t="n"/>
+      <c r="AU43" s="491" t="n"/>
+      <c r="AV43" s="491" t="n"/>
+      <c r="AW43" s="492" t="n"/>
+      <c r="AX43" s="497" t="n"/>
+      <c r="AY43" s="491" t="n"/>
+      <c r="AZ43" s="491" t="n"/>
+      <c r="BA43" s="491" t="n"/>
+      <c r="BB43" s="491" t="n"/>
+      <c r="BC43" s="491" t="n"/>
+      <c r="BD43" s="498" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="264">
+      <c r="A44" s="490">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
+      </c>
+      <c r="B44" s="491" t="n"/>
+      <c r="C44" s="492" t="n"/>
+      <c r="D44" s="500" t="n"/>
+      <c r="E44" s="491" t="n"/>
+      <c r="F44" s="491" t="n"/>
+      <c r="G44" s="492" t="n"/>
+      <c r="H44" s="502" t="n"/>
+      <c r="I44" s="491" t="n"/>
+      <c r="J44" s="491" t="n"/>
+      <c r="K44" s="491" t="n"/>
+      <c r="L44" s="491" t="n"/>
+      <c r="M44" s="491" t="n"/>
+      <c r="N44" s="491" t="n"/>
+      <c r="O44" s="491" t="n"/>
+      <c r="P44" s="491" t="n"/>
+      <c r="Q44" s="491" t="n"/>
+      <c r="R44" s="491" t="n"/>
+      <c r="S44" s="491" t="n"/>
+      <c r="T44" s="491" t="n"/>
+      <c r="U44" s="491" t="n"/>
+      <c r="V44" s="491" t="n"/>
+      <c r="W44" s="491" t="n"/>
+      <c r="X44" s="491" t="n"/>
+      <c r="Y44" s="491" t="n"/>
+      <c r="Z44" s="491" t="n"/>
+      <c r="AA44" s="491" t="n"/>
+      <c r="AB44" s="491" t="n"/>
+      <c r="AC44" s="492" t="n"/>
+      <c r="AD44" s="500" t="n"/>
+      <c r="AE44" s="491" t="n"/>
+      <c r="AF44" s="491" t="n"/>
+      <c r="AG44" s="491" t="n"/>
+      <c r="AH44" s="491" t="n"/>
+      <c r="AI44" s="491" t="n"/>
+      <c r="AJ44" s="491" t="n"/>
+      <c r="AK44" s="491" t="n"/>
+      <c r="AL44" s="491" t="n"/>
+      <c r="AM44" s="491" t="n"/>
+      <c r="AN44" s="491" t="n"/>
+      <c r="AO44" s="491" t="n"/>
+      <c r="AP44" s="491" t="n"/>
+      <c r="AQ44" s="492" t="n"/>
+      <c r="AR44" s="496" t="n"/>
+      <c r="AS44" s="491" t="n"/>
+      <c r="AT44" s="491" t="n"/>
+      <c r="AU44" s="491" t="n"/>
+      <c r="AV44" s="491" t="n"/>
+      <c r="AW44" s="492" t="n"/>
+      <c r="AX44" s="497" t="n"/>
+      <c r="AY44" s="491" t="n"/>
+      <c r="AZ44" s="491" t="n"/>
+      <c r="BA44" s="491" t="n"/>
+      <c r="BB44" s="491" t="n"/>
+      <c r="BC44" s="491" t="n"/>
+      <c r="BD44" s="498" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1" s="264">
+      <c r="A45" s="503">
+        <f>ROW()-ROW($A$18)+1</f>
+        <v/>
+      </c>
+      <c r="B45" s="481" t="n"/>
+      <c r="C45" s="482" t="n"/>
+      <c r="D45" s="504" t="n"/>
+      <c r="E45" s="481" t="n"/>
+      <c r="F45" s="481" t="n"/>
+      <c r="G45" s="482" t="n"/>
+      <c r="H45" s="505" t="n"/>
+      <c r="I45" s="481" t="n"/>
+      <c r="J45" s="481" t="n"/>
+      <c r="K45" s="481" t="n"/>
+      <c r="L45" s="481" t="n"/>
+      <c r="M45" s="481" t="n"/>
+      <c r="N45" s="481" t="n"/>
+      <c r="O45" s="481" t="n"/>
+      <c r="P45" s="481" t="n"/>
+      <c r="Q45" s="481" t="n"/>
+      <c r="R45" s="481" t="n"/>
+      <c r="S45" s="481" t="n"/>
+      <c r="T45" s="481" t="n"/>
+      <c r="U45" s="481" t="n"/>
+      <c r="V45" s="481" t="n"/>
+      <c r="W45" s="481" t="n"/>
+      <c r="X45" s="481" t="n"/>
+      <c r="Y45" s="481" t="n"/>
+      <c r="Z45" s="481" t="n"/>
+      <c r="AA45" s="481" t="n"/>
+      <c r="AB45" s="481" t="n"/>
+      <c r="AC45" s="482" t="n"/>
+      <c r="AD45" s="504" t="n"/>
+      <c r="AE45" s="481" t="n"/>
+      <c r="AF45" s="481" t="n"/>
+      <c r="AG45" s="481" t="n"/>
+      <c r="AH45" s="481" t="n"/>
+      <c r="AI45" s="481" t="n"/>
+      <c r="AJ45" s="481" t="n"/>
+      <c r="AK45" s="481" t="n"/>
+      <c r="AL45" s="481" t="n"/>
+      <c r="AM45" s="481" t="n"/>
+      <c r="AN45" s="481" t="n"/>
+      <c r="AO45" s="481" t="n"/>
+      <c r="AP45" s="481" t="n"/>
+      <c r="AQ45" s="482" t="n"/>
+      <c r="AR45" s="506" t="n"/>
+      <c r="AS45" s="481" t="n"/>
+      <c r="AT45" s="481" t="n"/>
+      <c r="AU45" s="481" t="n"/>
+      <c r="AV45" s="481" t="n"/>
+      <c r="AW45" s="482" t="n"/>
+      <c r="AX45" s="507" t="n"/>
+      <c r="AY45" s="481" t="n"/>
+      <c r="AZ45" s="481" t="n"/>
+      <c r="BA45" s="481" t="n"/>
+      <c r="BB45" s="481" t="n"/>
+      <c r="BC45" s="481" t="n"/>
+      <c r="BD45" s="486" t="n"/>
+    </row>
+    <row r="46" ht="4" customHeight="1" s="264">
+      <c r="A46" s="469" t="n"/>
+      <c r="B46" s="26" t="n"/>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="26" t="n"/>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="26" t="n"/>
+      <c r="G46" s="26" t="n"/>
+      <c r="H46" s="26" t="n"/>
+      <c r="I46" s="26" t="n"/>
+      <c r="J46" s="26" t="n"/>
+      <c r="K46" s="26" t="n"/>
+      <c r="L46" s="26" t="n"/>
+      <c r="M46" s="26" t="n"/>
+      <c r="N46" s="26" t="n"/>
+      <c r="O46" s="26" t="n"/>
+      <c r="P46" s="26" t="n"/>
+      <c r="Q46" s="26" t="n"/>
+      <c r="R46" s="26" t="n"/>
+      <c r="S46" s="26" t="n"/>
+      <c r="T46" s="26" t="n"/>
+      <c r="U46" s="26" t="n"/>
+      <c r="V46" s="26" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="26" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="26" t="n"/>
+      <c r="AB46" s="26" t="n"/>
+      <c r="AC46" s="26" t="n"/>
+      <c r="AD46" s="26" t="n"/>
+      <c r="AE46" s="26" t="n"/>
+      <c r="AF46" s="26" t="n"/>
+      <c r="AG46" s="26" t="n"/>
+      <c r="AH46" s="26" t="n"/>
+      <c r="AI46" s="26" t="n"/>
+      <c r="AJ46" s="26" t="n"/>
+      <c r="AK46" s="26" t="n"/>
+      <c r="AL46" s="26" t="n"/>
+      <c r="AM46" s="26" t="n"/>
+      <c r="AN46" s="26" t="n"/>
+      <c r="AO46" s="26" t="n"/>
+      <c r="AP46" s="26" t="n"/>
+      <c r="AQ46" s="26" t="n"/>
+      <c r="AR46" s="26" t="n"/>
+      <c r="AS46" s="26" t="n"/>
+      <c r="AT46" s="26" t="n"/>
+      <c r="AU46" s="26" t="n"/>
+      <c r="AV46" s="26" t="n"/>
+      <c r="AW46" s="26" t="n"/>
+      <c r="AX46" s="26" t="n"/>
+      <c r="AY46" s="26" t="n"/>
+      <c r="AZ46" s="26" t="n"/>
+      <c r="BA46" s="26" t="n"/>
+      <c r="BB46" s="26" t="n"/>
+      <c r="BC46" s="26" t="n"/>
+      <c r="BD46" s="26" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1" s="264">
+      <c r="A47" s="470" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  APPROVAL</t>
         </is>
       </c>
-      <c r="B42" s="471" t="n"/>
-      <c r="C42" s="471" t="n"/>
-      <c r="D42" s="471" t="n"/>
-      <c r="E42" s="471" t="n"/>
-      <c r="F42" s="471" t="n"/>
-      <c r="G42" s="471" t="n"/>
-      <c r="H42" s="471" t="n"/>
-      <c r="I42" s="471" t="n"/>
-      <c r="J42" s="471" t="n"/>
-      <c r="K42" s="471" t="n"/>
-      <c r="L42" s="471" t="n"/>
-      <c r="M42" s="471" t="n"/>
-      <c r="N42" s="471" t="n"/>
-      <c r="O42" s="471" t="n"/>
-      <c r="P42" s="471" t="n"/>
-      <c r="Q42" s="471" t="n"/>
-      <c r="R42" s="471" t="n"/>
-      <c r="S42" s="471" t="n"/>
-      <c r="T42" s="471" t="n"/>
-      <c r="U42" s="471" t="n"/>
-      <c r="V42" s="471" t="n"/>
-      <c r="W42" s="471" t="n"/>
-      <c r="X42" s="471" t="n"/>
-      <c r="Y42" s="471" t="n"/>
-      <c r="Z42" s="471" t="n"/>
-      <c r="AA42" s="471" t="n"/>
-      <c r="AB42" s="471" t="n"/>
-      <c r="AC42" s="471" t="n"/>
-      <c r="AD42" s="471" t="n"/>
-      <c r="AE42" s="471" t="n"/>
-      <c r="AF42" s="471" t="n"/>
-      <c r="AG42" s="471" t="n"/>
-      <c r="AH42" s="471" t="n"/>
-      <c r="AI42" s="471" t="n"/>
-      <c r="AJ42" s="471" t="n"/>
-      <c r="AK42" s="471" t="n"/>
-      <c r="AL42" s="471" t="n"/>
-      <c r="AM42" s="471" t="n"/>
-      <c r="AN42" s="471" t="n"/>
-      <c r="AO42" s="471" t="n"/>
-      <c r="AP42" s="471" t="n"/>
-      <c r="AQ42" s="471" t="n"/>
-      <c r="AR42" s="471" t="n"/>
-      <c r="AS42" s="471" t="n"/>
-      <c r="AT42" s="471" t="n"/>
-      <c r="AU42" s="471" t="n"/>
-      <c r="AV42" s="471" t="n"/>
-      <c r="AW42" s="471" t="n"/>
-      <c r="AX42" s="471" t="n"/>
-      <c r="AY42" s="471" t="n"/>
-      <c r="AZ42" s="471" t="n"/>
-      <c r="BA42" s="471" t="n"/>
-      <c r="BB42" s="471" t="n"/>
-      <c r="BC42" s="471" t="n"/>
-      <c r="BD42" s="472" t="n"/>
+      <c r="B47" s="471" t="n"/>
+      <c r="C47" s="471" t="n"/>
+      <c r="D47" s="471" t="n"/>
+      <c r="E47" s="471" t="n"/>
+      <c r="F47" s="471" t="n"/>
+      <c r="G47" s="471" t="n"/>
+      <c r="H47" s="471" t="n"/>
+      <c r="I47" s="471" t="n"/>
+      <c r="J47" s="471" t="n"/>
+      <c r="K47" s="471" t="n"/>
+      <c r="L47" s="471" t="n"/>
+      <c r="M47" s="471" t="n"/>
+      <c r="N47" s="471" t="n"/>
+      <c r="O47" s="471" t="n"/>
+      <c r="P47" s="471" t="n"/>
+      <c r="Q47" s="471" t="n"/>
+      <c r="R47" s="471" t="n"/>
+      <c r="S47" s="471" t="n"/>
+      <c r="T47" s="471" t="n"/>
+      <c r="U47" s="471" t="n"/>
+      <c r="V47" s="471" t="n"/>
+      <c r="W47" s="471" t="n"/>
+      <c r="X47" s="471" t="n"/>
+      <c r="Y47" s="471" t="n"/>
+      <c r="Z47" s="471" t="n"/>
+      <c r="AA47" s="471" t="n"/>
+      <c r="AB47" s="471" t="n"/>
+      <c r="AC47" s="471" t="n"/>
+      <c r="AD47" s="471" t="n"/>
+      <c r="AE47" s="471" t="n"/>
+      <c r="AF47" s="471" t="n"/>
+      <c r="AG47" s="471" t="n"/>
+      <c r="AH47" s="471" t="n"/>
+      <c r="AI47" s="471" t="n"/>
+      <c r="AJ47" s="471" t="n"/>
+      <c r="AK47" s="471" t="n"/>
+      <c r="AL47" s="471" t="n"/>
+      <c r="AM47" s="471" t="n"/>
+      <c r="AN47" s="471" t="n"/>
+      <c r="AO47" s="471" t="n"/>
+      <c r="AP47" s="471" t="n"/>
+      <c r="AQ47" s="471" t="n"/>
+      <c r="AR47" s="471" t="n"/>
+      <c r="AS47" s="471" t="n"/>
+      <c r="AT47" s="471" t="n"/>
+      <c r="AU47" s="471" t="n"/>
+      <c r="AV47" s="471" t="n"/>
+      <c r="AW47" s="471" t="n"/>
+      <c r="AX47" s="471" t="n"/>
+      <c r="AY47" s="471" t="n"/>
+      <c r="AZ47" s="471" t="n"/>
+      <c r="BA47" s="471" t="n"/>
+      <c r="BB47" s="471" t="n"/>
+      <c r="BC47" s="471" t="n"/>
+      <c r="BD47" s="472" t="n"/>
     </row>
-    <row r="43" ht="17" customHeight="1" s="264">
-      <c r="A43" s="508" t="inlineStr">
+    <row r="48" ht="17" customHeight="1" s="264">
+      <c r="A48" s="508" t="inlineStr">
         <is>
           <t>Inspector</t>
-        </is>
-      </c>
-      <c r="B43" s="471" t="n"/>
-      <c r="C43" s="471" t="n"/>
-      <c r="D43" s="471" t="n"/>
-      <c r="E43" s="471" t="n"/>
-      <c r="F43" s="471" t="n"/>
-      <c r="G43" s="471" t="n"/>
-      <c r="H43" s="471" t="n"/>
-      <c r="I43" s="471" t="n"/>
-      <c r="J43" s="471" t="n"/>
-      <c r="K43" s="471" t="n"/>
-      <c r="L43" s="471" t="n"/>
-      <c r="M43" s="471" t="n"/>
-      <c r="N43" s="471" t="n"/>
-      <c r="O43" s="471" t="n"/>
-      <c r="P43" s="471" t="n"/>
-      <c r="Q43" s="471" t="n"/>
-      <c r="R43" s="472" t="n"/>
-      <c r="S43" s="508" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="T43" s="471" t="n"/>
-      <c r="U43" s="471" t="n"/>
-      <c r="V43" s="471" t="n"/>
-      <c r="W43" s="471" t="n"/>
-      <c r="X43" s="471" t="n"/>
-      <c r="Y43" s="471" t="n"/>
-      <c r="Z43" s="471" t="n"/>
-      <c r="AA43" s="471" t="n"/>
-      <c r="AB43" s="471" t="n"/>
-      <c r="AC43" s="471" t="n"/>
-      <c r="AD43" s="471" t="n"/>
-      <c r="AE43" s="471" t="n"/>
-      <c r="AF43" s="471" t="n"/>
-      <c r="AG43" s="471" t="n"/>
-      <c r="AH43" s="471" t="n"/>
-      <c r="AI43" s="471" t="n"/>
-      <c r="AJ43" s="471" t="n"/>
-      <c r="AK43" s="472" t="n"/>
-      <c r="AL43" s="508" t="inlineStr">
-        <is>
-          <t>QA Manager</t>
-        </is>
-      </c>
-      <c r="AM43" s="471" t="n"/>
-      <c r="AN43" s="471" t="n"/>
-      <c r="AO43" s="471" t="n"/>
-      <c r="AP43" s="471" t="n"/>
-      <c r="AQ43" s="471" t="n"/>
-      <c r="AR43" s="471" t="n"/>
-      <c r="AS43" s="471" t="n"/>
-      <c r="AT43" s="471" t="n"/>
-      <c r="AU43" s="471" t="n"/>
-      <c r="AV43" s="471" t="n"/>
-      <c r="AW43" s="471" t="n"/>
-      <c r="AX43" s="471" t="n"/>
-      <c r="AY43" s="471" t="n"/>
-      <c r="AZ43" s="471" t="n"/>
-      <c r="BA43" s="471" t="n"/>
-      <c r="BB43" s="471" t="n"/>
-      <c r="BC43" s="471" t="n"/>
-      <c r="BD43" s="472" t="n"/>
-    </row>
-    <row r="44" ht="26" customHeight="1" s="264">
-      <c r="A44" s="509" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="B44" s="510" t="n"/>
-      <c r="C44" s="510" t="n"/>
-      <c r="D44" s="510" t="n"/>
-      <c r="E44" s="510" t="n"/>
-      <c r="F44" s="510" t="n"/>
-      <c r="G44" s="510" t="n"/>
-      <c r="H44" s="510" t="n"/>
-      <c r="I44" s="510" t="n"/>
-      <c r="J44" s="510" t="n"/>
-      <c r="K44" s="510" t="n"/>
-      <c r="L44" s="510" t="n"/>
-      <c r="M44" s="510" t="n"/>
-      <c r="N44" s="510" t="n"/>
-      <c r="O44" s="510" t="n"/>
-      <c r="P44" s="510" t="n"/>
-      <c r="Q44" s="510" t="n"/>
-      <c r="R44" s="511" t="n"/>
-      <c r="S44" s="509" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="T44" s="510" t="n"/>
-      <c r="U44" s="510" t="n"/>
-      <c r="V44" s="510" t="n"/>
-      <c r="W44" s="510" t="n"/>
-      <c r="X44" s="510" t="n"/>
-      <c r="Y44" s="510" t="n"/>
-      <c r="Z44" s="510" t="n"/>
-      <c r="AA44" s="510" t="n"/>
-      <c r="AB44" s="510" t="n"/>
-      <c r="AC44" s="510" t="n"/>
-      <c r="AD44" s="510" t="n"/>
-      <c r="AE44" s="510" t="n"/>
-      <c r="AF44" s="510" t="n"/>
-      <c r="AG44" s="510" t="n"/>
-      <c r="AH44" s="510" t="n"/>
-      <c r="AI44" s="510" t="n"/>
-      <c r="AJ44" s="510" t="n"/>
-      <c r="AK44" s="511" t="n"/>
-      <c r="AL44" s="509" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="AM44" s="510" t="n"/>
-      <c r="AN44" s="510" t="n"/>
-      <c r="AO44" s="510" t="n"/>
-      <c r="AP44" s="510" t="n"/>
-      <c r="AQ44" s="510" t="n"/>
-      <c r="AR44" s="510" t="n"/>
-      <c r="AS44" s="510" t="n"/>
-      <c r="AT44" s="510" t="n"/>
-      <c r="AU44" s="510" t="n"/>
-      <c r="AV44" s="510" t="n"/>
-      <c r="AW44" s="510" t="n"/>
-      <c r="AX44" s="510" t="n"/>
-      <c r="AY44" s="510" t="n"/>
-      <c r="AZ44" s="510" t="n"/>
-      <c r="BA44" s="510" t="n"/>
-      <c r="BB44" s="510" t="n"/>
-      <c r="BC44" s="510" t="n"/>
-      <c r="BD44" s="511" t="n"/>
-    </row>
-    <row r="45" ht="26" customHeight="1" s="264">
-      <c r="A45" s="512" t="n"/>
-      <c r="R45" s="513" t="n"/>
-      <c r="S45" s="512" t="n"/>
-      <c r="AK45" s="513" t="n"/>
-      <c r="AL45" s="512" t="n"/>
-      <c r="BD45" s="513" t="n"/>
-    </row>
-    <row r="46" ht="26" customHeight="1" s="264">
-      <c r="A46" s="514" t="n"/>
-      <c r="B46" s="481" t="n"/>
-      <c r="C46" s="481" t="n"/>
-      <c r="D46" s="481" t="n"/>
-      <c r="E46" s="481" t="n"/>
-      <c r="F46" s="481" t="n"/>
-      <c r="G46" s="481" t="n"/>
-      <c r="H46" s="481" t="n"/>
-      <c r="I46" s="481" t="n"/>
-      <c r="J46" s="481" t="n"/>
-      <c r="K46" s="481" t="n"/>
-      <c r="L46" s="481" t="n"/>
-      <c r="M46" s="481" t="n"/>
-      <c r="N46" s="481" t="n"/>
-      <c r="O46" s="481" t="n"/>
-      <c r="P46" s="481" t="n"/>
-      <c r="Q46" s="481" t="n"/>
-      <c r="R46" s="486" t="n"/>
-      <c r="S46" s="514" t="n"/>
-      <c r="T46" s="481" t="n"/>
-      <c r="U46" s="481" t="n"/>
-      <c r="V46" s="481" t="n"/>
-      <c r="W46" s="481" t="n"/>
-      <c r="X46" s="481" t="n"/>
-      <c r="Y46" s="481" t="n"/>
-      <c r="Z46" s="481" t="n"/>
-      <c r="AA46" s="481" t="n"/>
-      <c r="AB46" s="481" t="n"/>
-      <c r="AC46" s="481" t="n"/>
-      <c r="AD46" s="481" t="n"/>
-      <c r="AE46" s="481" t="n"/>
-      <c r="AF46" s="481" t="n"/>
-      <c r="AG46" s="481" t="n"/>
-      <c r="AH46" s="481" t="n"/>
-      <c r="AI46" s="481" t="n"/>
-      <c r="AJ46" s="481" t="n"/>
-      <c r="AK46" s="486" t="n"/>
-      <c r="AL46" s="514" t="n"/>
-      <c r="AM46" s="481" t="n"/>
-      <c r="AN46" s="481" t="n"/>
-      <c r="AO46" s="481" t="n"/>
-      <c r="AP46" s="481" t="n"/>
-      <c r="AQ46" s="481" t="n"/>
-      <c r="AR46" s="481" t="n"/>
-      <c r="AS46" s="481" t="n"/>
-      <c r="AT46" s="481" t="n"/>
-      <c r="AU46" s="481" t="n"/>
-      <c r="AV46" s="481" t="n"/>
-      <c r="AW46" s="481" t="n"/>
-      <c r="AX46" s="481" t="n"/>
-      <c r="AY46" s="481" t="n"/>
-      <c r="AZ46" s="481" t="n"/>
-      <c r="BA46" s="481" t="n"/>
-      <c r="BB46" s="481" t="n"/>
-      <c r="BC46" s="481" t="n"/>
-      <c r="BD46" s="486" t="n"/>
-    </row>
-    <row r="47" ht="4" customHeight="1" s="264">
-      <c r="A47" s="469" t="n"/>
-      <c r="B47" s="26" t="n"/>
-      <c r="C47" s="26" t="n"/>
-      <c r="D47" s="26" t="n"/>
-      <c r="E47" s="26" t="n"/>
-      <c r="F47" s="26" t="n"/>
-      <c r="G47" s="26" t="n"/>
-      <c r="H47" s="26" t="n"/>
-      <c r="I47" s="26" t="n"/>
-      <c r="J47" s="26" t="n"/>
-      <c r="K47" s="26" t="n"/>
-      <c r="L47" s="26" t="n"/>
-      <c r="M47" s="26" t="n"/>
-      <c r="N47" s="26" t="n"/>
-      <c r="O47" s="26" t="n"/>
-      <c r="P47" s="26" t="n"/>
-      <c r="Q47" s="26" t="n"/>
-      <c r="R47" s="26" t="n"/>
-      <c r="S47" s="26" t="n"/>
-      <c r="T47" s="26" t="n"/>
-      <c r="U47" s="26" t="n"/>
-      <c r="V47" s="26" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
-      <c r="Y47" s="26" t="n"/>
-      <c r="Z47" s="26" t="n"/>
-      <c r="AA47" s="26" t="n"/>
-      <c r="AB47" s="26" t="n"/>
-      <c r="AC47" s="26" t="n"/>
-      <c r="AD47" s="26" t="n"/>
-      <c r="AE47" s="26" t="n"/>
-      <c r="AF47" s="26" t="n"/>
-      <c r="AG47" s="26" t="n"/>
-      <c r="AH47" s="26" t="n"/>
-      <c r="AI47" s="26" t="n"/>
-      <c r="AJ47" s="26" t="n"/>
-      <c r="AK47" s="26" t="n"/>
-      <c r="AL47" s="26" t="n"/>
-      <c r="AM47" s="26" t="n"/>
-      <c r="AN47" s="26" t="n"/>
-      <c r="AO47" s="26" t="n"/>
-      <c r="AP47" s="26" t="n"/>
-      <c r="AQ47" s="26" t="n"/>
-      <c r="AR47" s="26" t="n"/>
-      <c r="AS47" s="26" t="n"/>
-      <c r="AT47" s="26" t="n"/>
-      <c r="AU47" s="26" t="n"/>
-      <c r="AV47" s="26" t="n"/>
-      <c r="AW47" s="26" t="n"/>
-      <c r="AX47" s="26" t="n"/>
-      <c r="AY47" s="26" t="n"/>
-      <c r="AZ47" s="26" t="n"/>
-      <c r="BA47" s="26" t="n"/>
-      <c r="BB47" s="26" t="n"/>
-      <c r="BC47" s="26" t="n"/>
-      <c r="BD47" s="26" t="n"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" s="264">
-      <c r="A48" s="515" t="inlineStr">
-        <is>
-          <t>NOTICE — Per AS9102 Rev C. One form per FAI event. Ref: SOP-301. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B48" s="471" t="n"/>
@@ -8101,8 +8280,12 @@
       <c r="O48" s="471" t="n"/>
       <c r="P48" s="471" t="n"/>
       <c r="Q48" s="471" t="n"/>
-      <c r="R48" s="471" t="n"/>
-      <c r="S48" s="471" t="n"/>
+      <c r="R48" s="472" t="n"/>
+      <c r="S48" s="508" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
       <c r="T48" s="471" t="n"/>
       <c r="U48" s="471" t="n"/>
       <c r="V48" s="471" t="n"/>
@@ -8120,8 +8303,12 @@
       <c r="AH48" s="471" t="n"/>
       <c r="AI48" s="471" t="n"/>
       <c r="AJ48" s="471" t="n"/>
-      <c r="AK48" s="471" t="n"/>
-      <c r="AL48" s="471" t="n"/>
+      <c r="AK48" s="472" t="n"/>
+      <c r="AL48" s="508" t="inlineStr">
+        <is>
+          <t>QA Manager</t>
+        </is>
+      </c>
       <c r="AM48" s="471" t="n"/>
       <c r="AN48" s="471" t="n"/>
       <c r="AO48" s="471" t="n"/>
@@ -8141,15 +8328,271 @@
       <c r="BC48" s="471" t="n"/>
       <c r="BD48" s="472" t="n"/>
     </row>
+    <row r="49" ht="26" customHeight="1" s="264">
+      <c r="A49" s="509" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="B49" s="510" t="n"/>
+      <c r="C49" s="510" t="n"/>
+      <c r="D49" s="510" t="n"/>
+      <c r="E49" s="510" t="n"/>
+      <c r="F49" s="510" t="n"/>
+      <c r="G49" s="510" t="n"/>
+      <c r="H49" s="510" t="n"/>
+      <c r="I49" s="510" t="n"/>
+      <c r="J49" s="510" t="n"/>
+      <c r="K49" s="510" t="n"/>
+      <c r="L49" s="510" t="n"/>
+      <c r="M49" s="510" t="n"/>
+      <c r="N49" s="510" t="n"/>
+      <c r="O49" s="510" t="n"/>
+      <c r="P49" s="510" t="n"/>
+      <c r="Q49" s="510" t="n"/>
+      <c r="R49" s="511" t="n"/>
+      <c r="S49" s="509" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="T49" s="510" t="n"/>
+      <c r="U49" s="510" t="n"/>
+      <c r="V49" s="510" t="n"/>
+      <c r="W49" s="510" t="n"/>
+      <c r="X49" s="510" t="n"/>
+      <c r="Y49" s="510" t="n"/>
+      <c r="Z49" s="510" t="n"/>
+      <c r="AA49" s="510" t="n"/>
+      <c r="AB49" s="510" t="n"/>
+      <c r="AC49" s="510" t="n"/>
+      <c r="AD49" s="510" t="n"/>
+      <c r="AE49" s="510" t="n"/>
+      <c r="AF49" s="510" t="n"/>
+      <c r="AG49" s="510" t="n"/>
+      <c r="AH49" s="510" t="n"/>
+      <c r="AI49" s="510" t="n"/>
+      <c r="AJ49" s="510" t="n"/>
+      <c r="AK49" s="511" t="n"/>
+      <c r="AL49" s="509" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="AM49" s="510" t="n"/>
+      <c r="AN49" s="510" t="n"/>
+      <c r="AO49" s="510" t="n"/>
+      <c r="AP49" s="510" t="n"/>
+      <c r="AQ49" s="510" t="n"/>
+      <c r="AR49" s="510" t="n"/>
+      <c r="AS49" s="510" t="n"/>
+      <c r="AT49" s="510" t="n"/>
+      <c r="AU49" s="510" t="n"/>
+      <c r="AV49" s="510" t="n"/>
+      <c r="AW49" s="510" t="n"/>
+      <c r="AX49" s="510" t="n"/>
+      <c r="AY49" s="510" t="n"/>
+      <c r="AZ49" s="510" t="n"/>
+      <c r="BA49" s="510" t="n"/>
+      <c r="BB49" s="510" t="n"/>
+      <c r="BC49" s="510" t="n"/>
+      <c r="BD49" s="511" t="n"/>
+    </row>
+    <row r="50" ht="26" customHeight="1" s="264">
+      <c r="A50" s="512" t="n"/>
+      <c r="R50" s="513" t="n"/>
+      <c r="S50" s="512" t="n"/>
+      <c r="AK50" s="513" t="n"/>
+      <c r="AL50" s="512" t="n"/>
+      <c r="BD50" s="513" t="n"/>
+    </row>
+    <row r="51" ht="26" customHeight="1" s="264">
+      <c r="A51" s="514" t="n"/>
+      <c r="B51" s="481" t="n"/>
+      <c r="C51" s="481" t="n"/>
+      <c r="D51" s="481" t="n"/>
+      <c r="E51" s="481" t="n"/>
+      <c r="F51" s="481" t="n"/>
+      <c r="G51" s="481" t="n"/>
+      <c r="H51" s="481" t="n"/>
+      <c r="I51" s="481" t="n"/>
+      <c r="J51" s="481" t="n"/>
+      <c r="K51" s="481" t="n"/>
+      <c r="L51" s="481" t="n"/>
+      <c r="M51" s="481" t="n"/>
+      <c r="N51" s="481" t="n"/>
+      <c r="O51" s="481" t="n"/>
+      <c r="P51" s="481" t="n"/>
+      <c r="Q51" s="481" t="n"/>
+      <c r="R51" s="486" t="n"/>
+      <c r="S51" s="514" t="n"/>
+      <c r="T51" s="481" t="n"/>
+      <c r="U51" s="481" t="n"/>
+      <c r="V51" s="481" t="n"/>
+      <c r="W51" s="481" t="n"/>
+      <c r="X51" s="481" t="n"/>
+      <c r="Y51" s="481" t="n"/>
+      <c r="Z51" s="481" t="n"/>
+      <c r="AA51" s="481" t="n"/>
+      <c r="AB51" s="481" t="n"/>
+      <c r="AC51" s="481" t="n"/>
+      <c r="AD51" s="481" t="n"/>
+      <c r="AE51" s="481" t="n"/>
+      <c r="AF51" s="481" t="n"/>
+      <c r="AG51" s="481" t="n"/>
+      <c r="AH51" s="481" t="n"/>
+      <c r="AI51" s="481" t="n"/>
+      <c r="AJ51" s="481" t="n"/>
+      <c r="AK51" s="486" t="n"/>
+      <c r="AL51" s="514" t="n"/>
+      <c r="AM51" s="481" t="n"/>
+      <c r="AN51" s="481" t="n"/>
+      <c r="AO51" s="481" t="n"/>
+      <c r="AP51" s="481" t="n"/>
+      <c r="AQ51" s="481" t="n"/>
+      <c r="AR51" s="481" t="n"/>
+      <c r="AS51" s="481" t="n"/>
+      <c r="AT51" s="481" t="n"/>
+      <c r="AU51" s="481" t="n"/>
+      <c r="AV51" s="481" t="n"/>
+      <c r="AW51" s="481" t="n"/>
+      <c r="AX51" s="481" t="n"/>
+      <c r="AY51" s="481" t="n"/>
+      <c r="AZ51" s="481" t="n"/>
+      <c r="BA51" s="481" t="n"/>
+      <c r="BB51" s="481" t="n"/>
+      <c r="BC51" s="481" t="n"/>
+      <c r="BD51" s="486" t="n"/>
+    </row>
+    <row r="52" ht="4" customHeight="1" s="264">
+      <c r="A52" s="469" t="n"/>
+      <c r="B52" s="26" t="n"/>
+      <c r="C52" s="26" t="n"/>
+      <c r="D52" s="26" t="n"/>
+      <c r="E52" s="26" t="n"/>
+      <c r="F52" s="26" t="n"/>
+      <c r="G52" s="26" t="n"/>
+      <c r="H52" s="26" t="n"/>
+      <c r="I52" s="26" t="n"/>
+      <c r="J52" s="26" t="n"/>
+      <c r="K52" s="26" t="n"/>
+      <c r="L52" s="26" t="n"/>
+      <c r="M52" s="26" t="n"/>
+      <c r="N52" s="26" t="n"/>
+      <c r="O52" s="26" t="n"/>
+      <c r="P52" s="26" t="n"/>
+      <c r="Q52" s="26" t="n"/>
+      <c r="R52" s="26" t="n"/>
+      <c r="S52" s="26" t="n"/>
+      <c r="T52" s="26" t="n"/>
+      <c r="U52" s="26" t="n"/>
+      <c r="V52" s="26" t="n"/>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="26" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="26" t="n"/>
+      <c r="AB52" s="26" t="n"/>
+      <c r="AC52" s="26" t="n"/>
+      <c r="AD52" s="26" t="n"/>
+      <c r="AE52" s="26" t="n"/>
+      <c r="AF52" s="26" t="n"/>
+      <c r="AG52" s="26" t="n"/>
+      <c r="AH52" s="26" t="n"/>
+      <c r="AI52" s="26" t="n"/>
+      <c r="AJ52" s="26" t="n"/>
+      <c r="AK52" s="26" t="n"/>
+      <c r="AL52" s="26" t="n"/>
+      <c r="AM52" s="26" t="n"/>
+      <c r="AN52" s="26" t="n"/>
+      <c r="AO52" s="26" t="n"/>
+      <c r="AP52" s="26" t="n"/>
+      <c r="AQ52" s="26" t="n"/>
+      <c r="AR52" s="26" t="n"/>
+      <c r="AS52" s="26" t="n"/>
+      <c r="AT52" s="26" t="n"/>
+      <c r="AU52" s="26" t="n"/>
+      <c r="AV52" s="26" t="n"/>
+      <c r="AW52" s="26" t="n"/>
+      <c r="AX52" s="26" t="n"/>
+      <c r="AY52" s="26" t="n"/>
+      <c r="AZ52" s="26" t="n"/>
+      <c r="BA52" s="26" t="n"/>
+      <c r="BB52" s="26" t="n"/>
+      <c r="BC52" s="26" t="n"/>
+      <c r="BD52" s="26" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1" s="264">
+      <c r="A53" s="515" t="inlineStr">
+        <is>
+          <t>NOTICE — Per AS9102 Rev C. 100% of characteristics must be measured. FAIL on any characteristic requires NCR and disposition before approval. Ref: SOP-301. Retain: 10 years.</t>
+        </is>
+      </c>
+      <c r="B53" s="471" t="n"/>
+      <c r="C53" s="471" t="n"/>
+      <c r="D53" s="471" t="n"/>
+      <c r="E53" s="471" t="n"/>
+      <c r="F53" s="471" t="n"/>
+      <c r="G53" s="471" t="n"/>
+      <c r="H53" s="471" t="n"/>
+      <c r="I53" s="471" t="n"/>
+      <c r="J53" s="471" t="n"/>
+      <c r="K53" s="471" t="n"/>
+      <c r="L53" s="471" t="n"/>
+      <c r="M53" s="471" t="n"/>
+      <c r="N53" s="471" t="n"/>
+      <c r="O53" s="471" t="n"/>
+      <c r="P53" s="471" t="n"/>
+      <c r="Q53" s="471" t="n"/>
+      <c r="R53" s="471" t="n"/>
+      <c r="S53" s="471" t="n"/>
+      <c r="T53" s="471" t="n"/>
+      <c r="U53" s="471" t="n"/>
+      <c r="V53" s="471" t="n"/>
+      <c r="W53" s="471" t="n"/>
+      <c r="X53" s="471" t="n"/>
+      <c r="Y53" s="471" t="n"/>
+      <c r="Z53" s="471" t="n"/>
+      <c r="AA53" s="471" t="n"/>
+      <c r="AB53" s="471" t="n"/>
+      <c r="AC53" s="471" t="n"/>
+      <c r="AD53" s="471" t="n"/>
+      <c r="AE53" s="471" t="n"/>
+      <c r="AF53" s="471" t="n"/>
+      <c r="AG53" s="471" t="n"/>
+      <c r="AH53" s="471" t="n"/>
+      <c r="AI53" s="471" t="n"/>
+      <c r="AJ53" s="471" t="n"/>
+      <c r="AK53" s="471" t="n"/>
+      <c r="AL53" s="471" t="n"/>
+      <c r="AM53" s="471" t="n"/>
+      <c r="AN53" s="471" t="n"/>
+      <c r="AO53" s="471" t="n"/>
+      <c r="AP53" s="471" t="n"/>
+      <c r="AQ53" s="471" t="n"/>
+      <c r="AR53" s="471" t="n"/>
+      <c r="AS53" s="471" t="n"/>
+      <c r="AT53" s="471" t="n"/>
+      <c r="AU53" s="471" t="n"/>
+      <c r="AV53" s="471" t="n"/>
+      <c r="AW53" s="471" t="n"/>
+      <c r="AX53" s="471" t="n"/>
+      <c r="AY53" s="471" t="n"/>
+      <c r="AZ53" s="471" t="n"/>
+      <c r="BA53" s="471" t="n"/>
+      <c r="BB53" s="471" t="n"/>
+      <c r="BC53" s="471" t="n"/>
+      <c r="BD53" s="472" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="190">
+  <mergeCells count="220">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AD18:AQ18"/>
     <mergeCell ref="A37:C37"/>
-    <mergeCell ref="AL43:BD43"/>
     <mergeCell ref="AW2:BD2"/>
     <mergeCell ref="H27:AC27"/>
     <mergeCell ref="AD33:AQ33"/>
+    <mergeCell ref="A52:BD52"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="AX24:BD24"/>
@@ -8159,46 +8602,54 @@
     <mergeCell ref="AR33:AW33"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="AQ5:AV5"/>
+    <mergeCell ref="H42:AC42"/>
     <mergeCell ref="D20:G20"/>
+    <mergeCell ref="AD44:AQ44"/>
     <mergeCell ref="AW3:BD3"/>
     <mergeCell ref="AX26:BD26"/>
     <mergeCell ref="AD34:AQ34"/>
     <mergeCell ref="AD28:AQ28"/>
     <mergeCell ref="H35:AC35"/>
     <mergeCell ref="AQ4:AV4"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="AR35:AW35"/>
-    <mergeCell ref="S43:AK43"/>
     <mergeCell ref="D22:G22"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AD27:AQ27"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="L2:AP4"/>
+    <mergeCell ref="D45:G45"/>
     <mergeCell ref="AD36:AQ36"/>
     <mergeCell ref="AQ6:AV6"/>
     <mergeCell ref="AD30:AQ30"/>
+    <mergeCell ref="AD45:AQ45"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="K13:AB13"/>
-    <mergeCell ref="A44:R46"/>
+    <mergeCell ref="A48:R48"/>
     <mergeCell ref="AD22:AQ22"/>
     <mergeCell ref="AX17:BD17"/>
     <mergeCell ref="A47:BD47"/>
     <mergeCell ref="AM14:BD14"/>
     <mergeCell ref="AR39:AW39"/>
+    <mergeCell ref="H45:AC45"/>
     <mergeCell ref="AX28:BD28"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="H32:AC32"/>
     <mergeCell ref="AX37:BD37"/>
+    <mergeCell ref="AX43:BD43"/>
     <mergeCell ref="D24:G24"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="AD24:AQ24"/>
     <mergeCell ref="AX30:BD30"/>
     <mergeCell ref="AX39:BD39"/>
     <mergeCell ref="AD38:AQ38"/>
+    <mergeCell ref="D42:G42"/>
     <mergeCell ref="AQ2:AV2"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="AX20:BD20"/>
     <mergeCell ref="AR40:AW40"/>
+    <mergeCell ref="AX42:BD42"/>
     <mergeCell ref="AX29:BD29"/>
     <mergeCell ref="D26:G26"/>
     <mergeCell ref="AX23:BD23"/>
@@ -8208,6 +8659,7 @@
     <mergeCell ref="A15:BD15"/>
     <mergeCell ref="AR24:AW24"/>
     <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D44:G44"/>
     <mergeCell ref="AM10:BD10"/>
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="D34:G34"/>
@@ -8216,28 +8668,29 @@
     <mergeCell ref="AD19:AQ19"/>
     <mergeCell ref="H26:AC26"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="AL44:BD46"/>
     <mergeCell ref="AR26:AW26"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="D36:G36"/>
     <mergeCell ref="A7:BD7"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="AR38:AW38"/>
-    <mergeCell ref="A41:BD41"/>
     <mergeCell ref="A16:BD16"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="H34:AC34"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H39:AC39"/>
+    <mergeCell ref="AR43:AW43"/>
     <mergeCell ref="AR18:AW18"/>
     <mergeCell ref="AX32:BD32"/>
+    <mergeCell ref="AX41:BD41"/>
     <mergeCell ref="H36:AC36"/>
     <mergeCell ref="K9:AB9"/>
-    <mergeCell ref="A42:BD42"/>
     <mergeCell ref="L5:AP5"/>
     <mergeCell ref="AX25:BD25"/>
     <mergeCell ref="D37:G37"/>
     <mergeCell ref="AD37:AQ37"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A53:BD53"/>
     <mergeCell ref="AX18:BD18"/>
     <mergeCell ref="AX33:BD33"/>
     <mergeCell ref="AC9:AL9"/>
@@ -8253,32 +8706,43 @@
     <mergeCell ref="D38:G38"/>
     <mergeCell ref="AD29:AQ29"/>
     <mergeCell ref="AD23:AQ23"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="AR30:AW30"/>
-    <mergeCell ref="A48:BD48"/>
     <mergeCell ref="AW4:BD4"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H23:AC23"/>
     <mergeCell ref="A11:BD11"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H43:AC43"/>
+    <mergeCell ref="AX44:BD44"/>
     <mergeCell ref="AX22:BD22"/>
     <mergeCell ref="AC13:AL13"/>
-    <mergeCell ref="A43:R43"/>
     <mergeCell ref="AX31:BD31"/>
     <mergeCell ref="AR32:AW32"/>
+    <mergeCell ref="H41:AC41"/>
+    <mergeCell ref="AR41:AW41"/>
     <mergeCell ref="K10:AB10"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A46:BD46"/>
     <mergeCell ref="AX21:BD21"/>
     <mergeCell ref="D27:G27"/>
     <mergeCell ref="H25:AC25"/>
+    <mergeCell ref="AD41:AQ41"/>
+    <mergeCell ref="AL49:BD51"/>
     <mergeCell ref="D17:G17"/>
+    <mergeCell ref="AX45:BD45"/>
+    <mergeCell ref="A49:R51"/>
     <mergeCell ref="AR27:AW27"/>
+    <mergeCell ref="AD43:AQ43"/>
     <mergeCell ref="AR37:AW37"/>
     <mergeCell ref="H17:AC17"/>
     <mergeCell ref="D28:G28"/>
     <mergeCell ref="A8:BD8"/>
     <mergeCell ref="AC10:AL10"/>
     <mergeCell ref="AQ3:AV3"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="AD42:AQ42"/>
     <mergeCell ref="D25:G25"/>
     <mergeCell ref="H22:AC22"/>
     <mergeCell ref="AD17:AQ17"/>
@@ -8286,6 +8750,7 @@
     <mergeCell ref="D30:G30"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="AR19:AW19"/>
+    <mergeCell ref="S49:AK51"/>
     <mergeCell ref="AM9:BD9"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="AR34:AW34"/>
@@ -8294,12 +8759,13 @@
     <mergeCell ref="AR25:AW25"/>
     <mergeCell ref="L6:AP6"/>
     <mergeCell ref="A9:J9"/>
+    <mergeCell ref="AL48:BD48"/>
     <mergeCell ref="AX35:BD35"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H30:AC30"/>
     <mergeCell ref="AD25:AQ25"/>
     <mergeCell ref="AR36:AW36"/>
-    <mergeCell ref="S44:AK46"/>
+    <mergeCell ref="AR45:AW45"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="K14:AB14"/>
     <mergeCell ref="AW6:BD6"/>
@@ -8317,24 +8783,31 @@
     <mergeCell ref="AD40:AQ40"/>
     <mergeCell ref="AX40:BD40"/>
     <mergeCell ref="AX27:BD27"/>
+    <mergeCell ref="H44:AC44"/>
     <mergeCell ref="AX36:BD36"/>
+    <mergeCell ref="AR44:AW44"/>
     <mergeCell ref="AR22:AW22"/>
     <mergeCell ref="H31:AC31"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="AR31:AW31"/>
     <mergeCell ref="H40:AC40"/>
+    <mergeCell ref="S48:AK48"/>
+    <mergeCell ref="AR42:AW42"/>
     <mergeCell ref="D32:G32"/>
     <mergeCell ref="H21:AC21"/>
+    <mergeCell ref="D41:G41"/>
     <mergeCell ref="AD32:AQ32"/>
     <mergeCell ref="A12:BD12"/>
     <mergeCell ref="AC14:AL14"/>
     <mergeCell ref="AD26:AQ26"/>
     <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A2:K6"/>
+    <mergeCell ref="D43:G43"/>
     <mergeCell ref="AR23:AW23"/>
     <mergeCell ref="AM13:BD13"/>
   </mergeCells>
-  <conditionalFormatting sqref="AR18:AR40">
+  <conditionalFormatting sqref="AR18:AR45">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -8346,13 +8819,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AR18 AR19 AR20 AR21 AR22 AR23 AR24 AR25 AR26 AR27 AR28 AR29 AR30 AR31 AR32 AR33 AR34 AR35 AR36 AR37 AR38 AR39 AR40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AR18 AR19 AR20 AR21 AR22 AR23 AR24 AR25 AR26 AR27 AR28 AR29 AR30 AR31 AR32 AR33 AR34 AR35 AR36 AR37 AR38 AR39 AR40 AR41 AR42 AR43 AR44 AR45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=LISTS!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
